--- a/templates/questions-template.xlsx
+++ b/templates/questions-template.xlsx
@@ -4,7 +4,9 @@
   <sheets>
     <sheet name="Questions" sheetId="1" r:id="rId1"/>
     <sheet name="Column Guide" sheetId="2" r:id="rId2"/>
+    <sheet name="Dropdown Lists" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -65,6 +67,36 @@
     <col min="12" max="12" width="70" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="42" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
+    <col min="19" max="19" width="42" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="22" max="22" width="42" customWidth="1"/>
+    <col min="23" max="23" width="22" customWidth="1"/>
+    <col min="24" max="24" width="42" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
+    <col min="27" max="27" width="42" customWidth="1"/>
+    <col min="28" max="28" width="22" customWidth="1"/>
+    <col min="29" max="29" width="42" customWidth="1"/>
+    <col min="30" max="30" width="18" customWidth="1"/>
+    <col min="31" max="31" width="14" customWidth="1"/>
+    <col min="32" max="32" width="42" customWidth="1"/>
+    <col min="33" max="33" width="22" customWidth="1"/>
+    <col min="34" max="34" width="42" customWidth="1"/>
+    <col min="35" max="35" width="18" customWidth="1"/>
+    <col min="36" max="36" width="14" customWidth="1"/>
+    <col min="37" max="37" width="42" customWidth="1"/>
+    <col min="38" max="38" width="22" customWidth="1"/>
+    <col min="39" max="39" width="42" customWidth="1"/>
+    <col min="40" max="40" width="18" customWidth="1"/>
+    <col min="41" max="41" width="14" customWidth="1"/>
+    <col min="42" max="42" width="42" customWidth="1"/>
+    <col min="43" max="43" width="22" customWidth="1"/>
+    <col min="44" max="44" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -138,12 +170,160 @@
           <t>active</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr" s="1">
+        <is>
+          <t>part1_label</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr" s="1">
+        <is>
+          <t>part1_type</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr" s="1">
+        <is>
+          <t>part1_choices</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr" s="1">
+        <is>
+          <t>part1_answer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr" s="1">
+        <is>
+          <t>part1_accepted_answers</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr" s="1">
+        <is>
+          <t>part2_label</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr" s="1">
+        <is>
+          <t>part2_type</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr" s="1">
+        <is>
+          <t>part2_choices</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr" s="1">
+        <is>
+          <t>part2_answer</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr" s="1">
+        <is>
+          <t>part2_accepted_answers</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr" s="1">
+        <is>
+          <t>part3_label</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr" s="1">
+        <is>
+          <t>part3_type</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr" s="1">
+        <is>
+          <t>part3_choices</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr" s="1">
+        <is>
+          <t>part3_answer</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr" s="1">
+        <is>
+          <t>part3_accepted_answers</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr" s="1">
+        <is>
+          <t>part4_label</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr" s="1">
+        <is>
+          <t>part4_type</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr" s="1">
+        <is>
+          <t>part4_choices</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr" s="1">
+        <is>
+          <t>part4_answer</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr" s="1">
+        <is>
+          <t>part4_accepted_answers</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr" s="1">
+        <is>
+          <t>part5_label</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr" s="1">
+        <is>
+          <t>part5_type</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr" s="1">
+        <is>
+          <t>part5_choices</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr" s="1">
+        <is>
+          <t>part5_answer</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr" s="1">
+        <is>
+          <t>part5_accepted_answers</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr" s="1">
+        <is>
+          <t>part6_label</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr" s="1">
+        <is>
+          <t>part6_type</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr" s="1">
+        <is>
+          <t>part6_choices</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr" s="1">
+        <is>
+          <t>part6_answer</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr" s="1">
+        <is>
+          <t>part6_accepted_answers</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ifrs15-five-steps-contract</t>
-        </is>
+      <c r="A2">
+        <f>IF(G2&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -185,11 +365,6 @@
           <t>contract</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>strict</t>
@@ -212,10 +387,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ias37-provision-recognition</t>
-        </is>
+      <c r="A3">
+        <f>IF(G3&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -247,11 +420,6 @@
           <t>Name the probability threshold phrase needed before recognising a provision.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>probable outflow of economic benefits</t>
@@ -284,10 +452,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ifrs16-rou-initial-direct-costs</t>
-        </is>
+      <c r="A4">
+        <f>IF(G4&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -329,11 +495,6 @@
           <t>Initial direct costs</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>strict</t>
@@ -356,10 +517,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ifrs15-service-warranty</t>
-        </is>
+      <c r="A5">
+        <f>IF(G5&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -391,21 +550,11 @@
           <t>Explain to yourself whether a separately priced extended warranty is assurance-type or service-type, then reveal the answer.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>A separately priced extended warranty is normally a service-type warranty and a separate performance obligation.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>self_mark</t>
@@ -428,10 +577,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ias37-expected-value</t>
-        </is>
+      <c r="A6">
+        <f>IF(G6&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -463,11 +610,6 @@
           <t>For a large population of similar warranty claims, which measurement model should be used?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>expected value</t>
@@ -500,10 +642,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ifrs15-standard-name</t>
-        </is>
+      <c r="A7">
+        <f>IF(G7&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -535,11 +675,6 @@
           <t>IFRS 15</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>Revenue from Contracts with Customers</t>
@@ -572,10 +707,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ias37-standard-number</t>
-        </is>
+      <c r="A8">
+        <f>IF(G8&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -607,11 +740,6 @@
           <t>Provisions, Contingent Liabilities and Contingent Assets</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>IAS 37</t>
@@ -643,17 +771,5230 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9">
+        <f>IF(G9&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IAS 37</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Recognition criteria</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recognition</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>multi_part</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A provision requires a present ____, a probable ____, and a reliable estimate.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>strict</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>IAS 37 recognition needs a **present obligation**, a **probable outflow**, and a reliable estimate.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>First gap</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>asset|obligation|liability|expense</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>obligation</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Second gap</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>inflow|outflow|expense|asset</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <f>IF(G10&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IAS 37</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Recognition criteria</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recognition</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>multi_part</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A provision is recognised for a ____ obligation where an ____ is probable.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>variants</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>The key phrases are **present obligation** and **outflow**.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>First gap</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>dropdown</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>present|future|possible</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Second gap</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>outflow</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>outflow of economic benefits|probable outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <f>IF(G11&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IAS 37</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Recognition criteria</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recognition</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>multi_select</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Which are IAS 37 provision recognition criteria?</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Present obligation|Probable outflow|Reliable estimate|Future business plan</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Present obligation|Probable outflow|Reliable estimate</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>strict</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>The recognition criteria are **present obligation**, **probable outflow**, and **reliable estimate**.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <f>IF(G12&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>IF(G13&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <f>IF(G14&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <f>IF(G15&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <f>IF(G16&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <f>IF(G17&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <f>IF(G18&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <f>IF(G19&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <f>IF(G20&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <f>IF(G21&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <f>IF(G22&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <f>IF(G23&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <f>IF(G24&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <f>IF(G25&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <f>IF(G26&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>IF(G27&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <f>IF(G28&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <f>IF(G29&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <f>IF(G30&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <f>IF(G31&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <f>IF(G32&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <f>IF(G33&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <f>IF(G34&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <f>IF(G35&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <f>IF(G36&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <f>IF(G37&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <f>IF(G38&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <f>IF(G39&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <f>IF(G40&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>IF(G41&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <f>IF(G42&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <f>IF(G43&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <f>IF(G44&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <f>IF(G45&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <f>IF(G46&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <f>IF(G47&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <f>IF(G48&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <f>IF(G49&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <f>IF(G50&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <f>IF(G51&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <f>IF(G52&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <f>IF(G53&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <f>IF(G54&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>IF(G55&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <f>IF(G56&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <f>IF(G57&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <f>IF(G58&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <f>IF(G59&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <f>IF(G60&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <f>IF(G61&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <f>IF(G62&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <f>IF(G63&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <f>IF(G64&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <f>IF(G65&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <f>IF(G66&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <f>IF(G67&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <f>IF(G68&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <f>IF(G69&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <f>IF(G70&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <f>IF(G71&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <f>IF(G72&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <f>IF(G73&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <f>IF(G74&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <f>IF(G75&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <f>IF(G76&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <f>IF(G77&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <f>IF(G78&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <f>IF(G79&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <f>IF(G80&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <f>IF(G81&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <f>IF(G82&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <f>IF(G83&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <f>IF(G84&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <f>IF(G85&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <f>IF(G86&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <f>IF(G87&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <f>IF(G88&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <f>IF(G89&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <f>IF(G90&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <f>IF(G91&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <f>IF(G92&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <f>IF(G93&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <f>IF(G94&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <f>IF(G95&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <f>IF(G96&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <f>IF(G97&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <f>IF(G98&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <f>IF(G99&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <f>IF(G100&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <f>IF(G101&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <f>IF(G102&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <f>IF(G103&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <f>IF(G104&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <f>IF(G105&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <f>IF(G106&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <f>IF(G107&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <f>IF(G108&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <f>IF(G109&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <f>IF(G110&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <f>IF(G111&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <f>IF(G112&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <f>IF(G113&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <f>IF(G114&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <f>IF(G115&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <f>IF(G116&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <f>IF(G117&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <f>IF(G118&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <f>IF(G119&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <f>IF(G120&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <f>IF(G121&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <f>IF(G122&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <f>IF(G123&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <f>IF(G124&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <f>IF(G125&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <f>IF(G126&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <f>IF(G127&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <f>IF(G128&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <f>IF(G129&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <f>IF(G130&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <f>IF(G131&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <f>IF(G132&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <f>IF(G133&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <f>IF(G134&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <f>IF(G135&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <f>IF(G136&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <f>IF(G137&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <f>IF(G138&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <f>IF(G139&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <f>IF(G140&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <f>IF(G141&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <f>IF(G142&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <f>IF(G143&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <f>IF(G144&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <f>IF(G145&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <f>IF(G146&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <f>IF(G147&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <f>IF(G148&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <f>IF(G149&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <f>IF(G150&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <f>IF(G151&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <f>IF(G152&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <f>IF(G153&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <f>IF(G154&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <f>IF(G155&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <f>IF(G156&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <f>IF(G157&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <f>IF(G158&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <f>IF(G159&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <f>IF(G160&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <f>IF(G161&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <f>IF(G162&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <f>IF(G163&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <f>IF(G164&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <f>IF(G165&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <f>IF(G166&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <f>IF(G167&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <f>IF(G168&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <f>IF(G169&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <f>IF(G170&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <f>IF(G171&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <f>IF(G172&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <f>IF(G173&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <f>IF(G174&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <f>IF(G175&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <f>IF(G176&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <f>IF(G177&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <f>IF(G178&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <f>IF(G179&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <f>IF(G180&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <f>IF(G181&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <f>IF(G182&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <f>IF(G183&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <f>IF(G184&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <f>IF(G185&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <f>IF(G186&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <f>IF(G187&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <f>IF(G188&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <f>IF(G189&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <f>IF(G190&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <f>IF(G191&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <f>IF(G192&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <f>IF(G193&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <f>IF(G194&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <f>IF(G195&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <f>IF(G196&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <f>IF(G197&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <f>IF(G198&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <f>IF(G199&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <f>IF(G200&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <f>IF(G201&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <f>IF(G202&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <f>IF(G203&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <f>IF(G204&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <f>IF(G205&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <f>IF(G206&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <f>IF(G207&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <f>IF(G208&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <f>IF(G209&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <f>IF(G210&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <f>IF(G211&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <f>IF(G212&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <f>IF(G213&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <f>IF(G214&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <f>IF(G215&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <f>IF(G216&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <f>IF(G217&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <f>IF(G218&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <f>IF(G219&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <f>IF(G220&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <f>IF(G221&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <f>IF(G222&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <f>IF(G223&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <f>IF(G224&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <f>IF(G225&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <f>IF(G226&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <f>IF(G227&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <f>IF(G228&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <f>IF(G229&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <f>IF(G230&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <f>IF(G231&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <f>IF(G232&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <f>IF(G233&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <f>IF(G234&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <f>IF(G235&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <f>IF(G236&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <f>IF(G237&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <f>IF(G238&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <f>IF(G239&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <f>IF(G240&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <f>IF(G241&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <f>IF(G242&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <f>IF(G243&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <f>IF(G244&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <f>IF(G245&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <f>IF(G246&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <f>IF(G247&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <f>IF(G248&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <f>IF(G249&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <f>IF(G250&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <f>IF(G251&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <f>IF(G252&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <f>IF(G253&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <f>IF(G254&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <f>IF(G255&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <f>IF(G256&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <f>IF(G257&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <f>IF(G258&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <f>IF(G259&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <f>IF(G260&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <f>IF(G261&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <f>IF(G262&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <f>IF(G263&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <f>IF(G264&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <f>IF(G265&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <f>IF(G266&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <f>IF(G267&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <f>IF(G268&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <f>IF(G269&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <f>IF(G270&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <f>IF(G271&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <f>IF(G272&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <f>IF(G273&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <f>IF(G274&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <f>IF(G275&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <f>IF(G276&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <f>IF(G277&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <f>IF(G278&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <f>IF(G279&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <f>IF(G280&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <f>IF(G281&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <f>IF(G282&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <f>IF(G283&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <f>IF(G284&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <f>IF(G285&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <f>IF(G286&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <f>IF(G287&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <f>IF(G288&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <f>IF(G289&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <f>IF(G290&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <f>IF(G291&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <f>IF(G292&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <f>IF(G293&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <f>IF(G294&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <f>IF(G295&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <f>IF(G296&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <f>IF(G297&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <f>IF(G298&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <f>IF(G299&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <f>IF(G300&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <f>IF(G301&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <f>IF(G302&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <f>IF(G303&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <f>IF(G304&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <f>IF(G305&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <f>IF(G306&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <f>IF(G307&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <f>IF(G308&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <f>IF(G309&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <f>IF(G310&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <f>IF(G311&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <f>IF(G312&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <f>IF(G313&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <f>IF(G314&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <f>IF(G315&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <f>IF(G316&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <f>IF(G317&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <f>IF(G318&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <f>IF(G319&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <f>IF(G320&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <f>IF(G321&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <f>IF(G322&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <f>IF(G323&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <f>IF(G324&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <f>IF(G325&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <f>IF(G326&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <f>IF(G327&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <f>IF(G328&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <f>IF(G329&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <f>IF(G330&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <f>IF(G331&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <f>IF(G332&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <f>IF(G333&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <f>IF(G334&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <f>IF(G335&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <f>IF(G336&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <f>IF(G337&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <f>IF(G338&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <f>IF(G339&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <f>IF(G340&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <f>IF(G341&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <f>IF(G342&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <f>IF(G343&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <f>IF(G344&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <f>IF(G345&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <f>IF(G346&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <f>IF(G347&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <f>IF(G348&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <f>IF(G349&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <f>IF(G350&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <f>IF(G351&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <f>IF(G352&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <f>IF(G353&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <f>IF(G354&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <f>IF(G355&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <f>IF(G356&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <f>IF(G357&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <f>IF(G358&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <f>IF(G359&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <f>IF(G360&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <f>IF(G361&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <f>IF(G362&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <f>IF(G363&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <f>IF(G364&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <f>IF(G365&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <f>IF(G366&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <f>IF(G367&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <f>IF(G368&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <f>IF(G369&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <f>IF(G370&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <f>IF(G371&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <f>IF(G372&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <f>IF(G373&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <f>IF(G374&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375">
+        <f>IF(G375&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376">
+        <f>IF(G376&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377">
+        <f>IF(G377&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <f>IF(G378&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <f>IF(G379&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <f>IF(G380&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <f>IF(G381&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382">
+        <f>IF(G382&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383">
+        <f>IF(G383&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384">
+        <f>IF(G384&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385">
+        <f>IF(G385&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386">
+        <f>IF(G386&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387">
+        <f>IF(G387&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388">
+        <f>IF(G388&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389">
+        <f>IF(G389&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390">
+        <f>IF(G390&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391">
+        <f>IF(G391&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392">
+        <f>IF(G392&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393">
+        <f>IF(G393&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394">
+        <f>IF(G394&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395">
+        <f>IF(G395&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396">
+        <f>IF(G396&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397">
+        <f>IF(G397&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398">
+        <f>IF(G398&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399">
+        <f>IF(G399&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400">
+        <f>IF(G400&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401">
+        <f>IF(G401&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402">
+        <f>IF(G402&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403">
+        <f>IF(G403&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404">
+        <f>IF(G404&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405">
+        <f>IF(G405&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406">
+        <f>IF(G406&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407">
+        <f>IF(G407&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408">
+        <f>IF(G408&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409">
+        <f>IF(G409&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410">
+        <f>IF(G410&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411">
+        <f>IF(G411&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412">
+        <f>IF(G412&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413">
+        <f>IF(G413&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414">
+        <f>IF(G414&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415">
+        <f>IF(G415&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416">
+        <f>IF(G416&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417">
+        <f>IF(G417&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418">
+        <f>IF(G418&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419">
+        <f>IF(G419&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420">
+        <f>IF(G420&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421">
+        <f>IF(G421&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422">
+        <f>IF(G422&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423">
+        <f>IF(G423&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424">
+        <f>IF(G424&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425">
+        <f>IF(G425&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426">
+        <f>IF(G426&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427">
+        <f>IF(G427&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428">
+        <f>IF(G428&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429">
+        <f>IF(G429&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430">
+        <f>IF(G430&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431">
+        <f>IF(G431&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432">
+        <f>IF(G432&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433">
+        <f>IF(G433&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434">
+        <f>IF(G434&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435">
+        <f>IF(G435&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436">
+        <f>IF(G436&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437">
+        <f>IF(G437&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438">
+        <f>IF(G438&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439">
+        <f>IF(G439&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440">
+        <f>IF(G440&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441">
+        <f>IF(G441&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442">
+        <f>IF(G442&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443">
+        <f>IF(G443&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444">
+        <f>IF(G444&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445">
+        <f>IF(G445&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446">
+        <f>IF(G446&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447">
+        <f>IF(G447&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448">
+        <f>IF(G448&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449">
+        <f>IF(G449&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450">
+        <f>IF(G450&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451">
+        <f>IF(G451&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452">
+        <f>IF(G452&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453">
+        <f>IF(G453&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454">
+        <f>IF(G454&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455">
+        <f>IF(G455&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456">
+        <f>IF(G456&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457">
+        <f>IF(G457&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458">
+        <f>IF(G458&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459">
+        <f>IF(G459&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460">
+        <f>IF(G460&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461">
+        <f>IF(G461&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462">
+        <f>IF(G462&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463">
+        <f>IF(G463&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464">
+        <f>IF(G464&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465">
+        <f>IF(G465&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466">
+        <f>IF(G466&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467">
+        <f>IF(G467&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468">
+        <f>IF(G468&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469">
+        <f>IF(G469&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470">
+        <f>IF(G470&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471">
+        <f>IF(G471&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472">
+        <f>IF(G472&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473">
+        <f>IF(G473&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474">
+        <f>IF(G474&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475">
+        <f>IF(G475&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476">
+        <f>IF(G476&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477">
+        <f>IF(G477&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478">
+        <f>IF(G478&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479">
+        <f>IF(G479&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480">
+        <f>IF(G480&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481">
+        <f>IF(G481&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482">
+        <f>IF(G482&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483">
+        <f>IF(G483&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484">
+        <f>IF(G484&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485">
+        <f>IF(G485&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486">
+        <f>IF(G486&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487">
+        <f>IF(G487&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488">
+        <f>IF(G488&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489">
+        <f>IF(G489&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490">
+        <f>IF(G490&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491">
+        <f>IF(G491&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492">
+        <f>IF(G492&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493">
+        <f>IF(G493&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494">
+        <f>IF(G494&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495">
+        <f>IF(G495&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496">
+        <f>IF(G496&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497">
+        <f>IF(G497&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498">
+        <f>IF(G498&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499">
+        <f>IF(G499&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500">
+        <f>IF(G500&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501">
+        <f>IF(G501&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502">
+        <f>IF(G502&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503">
+        <f>IF(G503&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504">
+        <f>IF(G504&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505">
+        <f>IF(G505&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506">
+        <f>IF(G506&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507">
+        <f>IF(G507&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508">
+        <f>IF(G508&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509">
+        <f>IF(G509&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510">
+        <f>IF(G510&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511">
+        <f>IF(G511&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512">
+        <f>IF(G512&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513">
+        <f>IF(G513&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514">
+        <f>IF(G514&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515">
+        <f>IF(G515&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516">
+        <f>IF(G516&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517">
+        <f>IF(G517&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518">
+        <f>IF(G518&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519">
+        <f>IF(G519&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520">
+        <f>IF(G520&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521">
+        <f>IF(G521&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522">
+        <f>IF(G522&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523">
+        <f>IF(G523&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524">
+        <f>IF(G524&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525">
+        <f>IF(G525&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526">
+        <f>IF(G526&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527">
+        <f>IF(G527&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528">
+        <f>IF(G528&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529">
+        <f>IF(G529&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530">
+        <f>IF(G530&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531">
+        <f>IF(G531&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532">
+        <f>IF(G532&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533">
+        <f>IF(G533&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534">
+        <f>IF(G534&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535">
+        <f>IF(G535&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536">
+        <f>IF(G536&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537">
+        <f>IF(G537&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538">
+        <f>IF(G538&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539">
+        <f>IF(G539&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540">
+        <f>IF(G540&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541">
+        <f>IF(G541&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542">
+        <f>IF(G542&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543">
+        <f>IF(G543&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544">
+        <f>IF(G544&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545">
+        <f>IF(G545&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546">
+        <f>IF(G546&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547">
+        <f>IF(G547&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548">
+        <f>IF(G548&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549">
+        <f>IF(G549&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550">
+        <f>IF(G550&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551">
+        <f>IF(G551&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552">
+        <f>IF(G552&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553">
+        <f>IF(G553&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554">
+        <f>IF(G554&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555">
+        <f>IF(G555&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556">
+        <f>IF(G556&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557">
+        <f>IF(G557&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558">
+        <f>IF(G558&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559">
+        <f>IF(G559&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560">
+        <f>IF(G560&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561">
+        <f>IF(G561&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562">
+        <f>IF(G562&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563">
+        <f>IF(G563&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564">
+        <f>IF(G564&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565">
+        <f>IF(G565&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566">
+        <f>IF(G566&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567">
+        <f>IF(G567&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568">
+        <f>IF(G568&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569">
+        <f>IF(G569&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570">
+        <f>IF(G570&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571">
+        <f>IF(G571&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572">
+        <f>IF(G572&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573">
+        <f>IF(G573&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574">
+        <f>IF(G574&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575">
+        <f>IF(G575&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576">
+        <f>IF(G576&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577">
+        <f>IF(G577&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578">
+        <f>IF(G578&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579">
+        <f>IF(G579&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580">
+        <f>IF(G580&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581">
+        <f>IF(G581&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582">
+        <f>IF(G582&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583">
+        <f>IF(G583&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584">
+        <f>IF(G584&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585">
+        <f>IF(G585&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586">
+        <f>IF(G586&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587">
+        <f>IF(G587&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588">
+        <f>IF(G588&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589">
+        <f>IF(G589&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590">
+        <f>IF(G590&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591">
+        <f>IF(G591&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592">
+        <f>IF(G592&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593">
+        <f>IF(G593&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594">
+        <f>IF(G594&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595">
+        <f>IF(G595&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596">
+        <f>IF(G596&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597">
+        <f>IF(G597&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598">
+        <f>IF(G598&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599">
+        <f>IF(G599&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600">
+        <f>IF(G600&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601">
+        <f>IF(G601&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602">
+        <f>IF(G602&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603">
+        <f>IF(G603&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604">
+        <f>IF(G604&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605">
+        <f>IF(G605&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606">
+        <f>IF(G606&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607">
+        <f>IF(G607&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608">
+        <f>IF(G608&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609">
+        <f>IF(G609&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610">
+        <f>IF(G610&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611">
+        <f>IF(G611&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612">
+        <f>IF(G612&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613">
+        <f>IF(G613&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614">
+        <f>IF(G614&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615">
+        <f>IF(G615&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616">
+        <f>IF(G616&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617">
+        <f>IF(G617&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618">
+        <f>IF(G618&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619">
+        <f>IF(G619&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620">
+        <f>IF(G620&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621">
+        <f>IF(G621&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622">
+        <f>IF(G622&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623">
+        <f>IF(G623&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624">
+        <f>IF(G624&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625">
+        <f>IF(G625&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626">
+        <f>IF(G626&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627">
+        <f>IF(G627&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628">
+        <f>IF(G628&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629">
+        <f>IF(G629&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630">
+        <f>IF(G630&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631">
+        <f>IF(G631&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632">
+        <f>IF(G632&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633">
+        <f>IF(G633&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634">
+        <f>IF(G634&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635">
+        <f>IF(G635&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636">
+        <f>IF(G636&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637">
+        <f>IF(G637&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638">
+        <f>IF(G638&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639">
+        <f>IF(G639&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640">
+        <f>IF(G640&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641">
+        <f>IF(G641&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642">
+        <f>IF(G642&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643">
+        <f>IF(G643&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644">
+        <f>IF(G644&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645">
+        <f>IF(G645&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646">
+        <f>IF(G646&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647">
+        <f>IF(G647&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648">
+        <f>IF(G648&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649">
+        <f>IF(G649&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650">
+        <f>IF(G650&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651">
+        <f>IF(G651&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652">
+        <f>IF(G652&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653">
+        <f>IF(G653&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654">
+        <f>IF(G654&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655">
+        <f>IF(G655&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656">
+        <f>IF(G656&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657">
+        <f>IF(G657&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658">
+        <f>IF(G658&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659">
+        <f>IF(G659&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660">
+        <f>IF(G660&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661">
+        <f>IF(G661&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662">
+        <f>IF(G662&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663">
+        <f>IF(G663&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664">
+        <f>IF(G664&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665">
+        <f>IF(G665&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666">
+        <f>IF(G666&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667">
+        <f>IF(G667&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668">
+        <f>IF(G668&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669">
+        <f>IF(G669&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670">
+        <f>IF(G670&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671">
+        <f>IF(G671&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672">
+        <f>IF(G672&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673">
+        <f>IF(G673&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674">
+        <f>IF(G674&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675">
+        <f>IF(G675&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676">
+        <f>IF(G676&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677">
+        <f>IF(G677&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678">
+        <f>IF(G678&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679">
+        <f>IF(G679&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680">
+        <f>IF(G680&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681">
+        <f>IF(G681&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682">
+        <f>IF(G682&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683">
+        <f>IF(G683&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684">
+        <f>IF(G684&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685">
+        <f>IF(G685&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686">
+        <f>IF(G686&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687">
+        <f>IF(G687&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688">
+        <f>IF(G688&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689">
+        <f>IF(G689&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690">
+        <f>IF(G690&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691">
+        <f>IF(G691&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692">
+        <f>IF(G692&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693">
+        <f>IF(G693&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694">
+        <f>IF(G694&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695">
+        <f>IF(G695&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696">
+        <f>IF(G696&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697">
+        <f>IF(G697&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698">
+        <f>IF(G698&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699">
+        <f>IF(G699&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700">
+        <f>IF(G700&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701">
+        <f>IF(G701&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702">
+        <f>IF(G702&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703">
+        <f>IF(G703&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704">
+        <f>IF(G704&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705">
+        <f>IF(G705&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706">
+        <f>IF(G706&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707">
+        <f>IF(G707&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708">
+        <f>IF(G708&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709">
+        <f>IF(G709&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710">
+        <f>IF(G710&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711">
+        <f>IF(G711&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712">
+        <f>IF(G712&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713">
+        <f>IF(G713&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714">
+        <f>IF(G714&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715">
+        <f>IF(G715&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716">
+        <f>IF(G716&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717">
+        <f>IF(G717&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718">
+        <f>IF(G718&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719">
+        <f>IF(G719&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720">
+        <f>IF(G720&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721">
+        <f>IF(G721&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722">
+        <f>IF(G722&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723">
+        <f>IF(G723&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724">
+        <f>IF(G724&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725">
+        <f>IF(G725&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726">
+        <f>IF(G726&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727">
+        <f>IF(G727&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728">
+        <f>IF(G728&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729">
+        <f>IF(G729&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730">
+        <f>IF(G730&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731">
+        <f>IF(G731&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732">
+        <f>IF(G732&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733">
+        <f>IF(G733&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734">
+        <f>IF(G734&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735">
+        <f>IF(G735&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736">
+        <f>IF(G736&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737">
+        <f>IF(G737&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738">
+        <f>IF(G738&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739">
+        <f>IF(G739&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740">
+        <f>IF(G740&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741">
+        <f>IF(G741&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742">
+        <f>IF(G742&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743">
+        <f>IF(G743&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744">
+        <f>IF(G744&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745">
+        <f>IF(G745&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746">
+        <f>IF(G746&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747">
+        <f>IF(G747&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748">
+        <f>IF(G748&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749">
+        <f>IF(G749&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750">
+        <f>IF(G750&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751">
+        <f>IF(G751&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752">
+        <f>IF(G752&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753">
+        <f>IF(G753&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754">
+        <f>IF(G754&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755">
+        <f>IF(G755&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756">
+        <f>IF(G756&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757">
+        <f>IF(G757&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758">
+        <f>IF(G758&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759">
+        <f>IF(G759&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760">
+        <f>IF(G760&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761">
+        <f>IF(G761&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762">
+        <f>IF(G762&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763">
+        <f>IF(G763&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764">
+        <f>IF(G764&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765">
+        <f>IF(G765&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766">
+        <f>IF(G766&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767">
+        <f>IF(G767&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768">
+        <f>IF(G768&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769">
+        <f>IF(G769&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770">
+        <f>IF(G770&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771">
+        <f>IF(G771&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772">
+        <f>IF(G772&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773">
+        <f>IF(G773&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774">
+        <f>IF(G774&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775">
+        <f>IF(G775&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776">
+        <f>IF(G776&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777">
+        <f>IF(G777&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778">
+        <f>IF(G778&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779">
+        <f>IF(G779&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780">
+        <f>IF(G780&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781">
+        <f>IF(G781&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782">
+        <f>IF(G782&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783">
+        <f>IF(G783&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784">
+        <f>IF(G784&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785">
+        <f>IF(G785&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786">
+        <f>IF(G786&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787">
+        <f>IF(G787&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788">
+        <f>IF(G788&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789">
+        <f>IF(G789&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790">
+        <f>IF(G790&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791">
+        <f>IF(G791&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792">
+        <f>IF(G792&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793">
+        <f>IF(G793&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794">
+        <f>IF(G794&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795">
+        <f>IF(G795&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796">
+        <f>IF(G796&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797">
+        <f>IF(G797&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798">
+        <f>IF(G798&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799">
+        <f>IF(G799&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800">
+        <f>IF(G800&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801">
+        <f>IF(G801&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802">
+        <f>IF(G802&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803">
+        <f>IF(G803&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804">
+        <f>IF(G804&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805">
+        <f>IF(G805&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806">
+        <f>IF(G806&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807">
+        <f>IF(G807&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808">
+        <f>IF(G808&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809">
+        <f>IF(G809&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810">
+        <f>IF(G810&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811">
+        <f>IF(G811&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812">
+        <f>IF(G812&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813">
+        <f>IF(G813&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814">
+        <f>IF(G814&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815">
+        <f>IF(G815&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816">
+        <f>IF(G816&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817">
+        <f>IF(G817&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818">
+        <f>IF(G818&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819">
+        <f>IF(G819&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820">
+        <f>IF(G820&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821">
+        <f>IF(G821&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822">
+        <f>IF(G822&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823">
+        <f>IF(G823&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824">
+        <f>IF(G824&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825">
+        <f>IF(G825&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826">
+        <f>IF(G826&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827">
+        <f>IF(G827&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828">
+        <f>IF(G828&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829">
+        <f>IF(G829&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830">
+        <f>IF(G830&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831">
+        <f>IF(G831&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832">
+        <f>IF(G832&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833">
+        <f>IF(G833&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834">
+        <f>IF(G834&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835">
+        <f>IF(G835&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836">
+        <f>IF(G836&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837">
+        <f>IF(G837&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838">
+        <f>IF(G838&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839">
+        <f>IF(G839&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840">
+        <f>IF(G840&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841">
+        <f>IF(G841&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842">
+        <f>IF(G842&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843">
+        <f>IF(G843&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844">
+        <f>IF(G844&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845">
+        <f>IF(G845&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846">
+        <f>IF(G846&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847">
+        <f>IF(G847&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848">
+        <f>IF(G848&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849">
+        <f>IF(G849&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850">
+        <f>IF(G850&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851">
+        <f>IF(G851&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852">
+        <f>IF(G852&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853">
+        <f>IF(G853&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854">
+        <f>IF(G854&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855">
+        <f>IF(G855&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856">
+        <f>IF(G856&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857">
+        <f>IF(G857&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858">
+        <f>IF(G858&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859">
+        <f>IF(G859&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860">
+        <f>IF(G860&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861">
+        <f>IF(G861&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862">
+        <f>IF(G862&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863">
+        <f>IF(G863&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864">
+        <f>IF(G864&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865">
+        <f>IF(G865&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866">
+        <f>IF(G866&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867">
+        <f>IF(G867&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868">
+        <f>IF(G868&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869">
+        <f>IF(G869&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870">
+        <f>IF(G870&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871">
+        <f>IF(G871&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872">
+        <f>IF(G872&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873">
+        <f>IF(G873&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874">
+        <f>IF(G874&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875">
+        <f>IF(G875&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876">
+        <f>IF(G876&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877">
+        <f>IF(G877&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878">
+        <f>IF(G878&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879">
+        <f>IF(G879&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880">
+        <f>IF(G880&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881">
+        <f>IF(G881&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882">
+        <f>IF(G882&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883">
+        <f>IF(G883&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884">
+        <f>IF(G884&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885">
+        <f>IF(G885&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886">
+        <f>IF(G886&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887">
+        <f>IF(G887&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888">
+        <f>IF(G888&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889">
+        <f>IF(G889&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890">
+        <f>IF(G890&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891">
+        <f>IF(G891&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892">
+        <f>IF(G892&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893">
+        <f>IF(G893&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894">
+        <f>IF(G894&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895">
+        <f>IF(G895&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896">
+        <f>IF(G896&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897">
+        <f>IF(G897&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898">
+        <f>IF(G898&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899">
+        <f>IF(G899&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900">
+        <f>IF(G900&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901">
+        <f>IF(G901&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902">
+        <f>IF(G902&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903">
+        <f>IF(G903&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904">
+        <f>IF(G904&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905">
+        <f>IF(G905&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906">
+        <f>IF(G906&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907">
+        <f>IF(G907&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908">
+        <f>IF(G908&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909">
+        <f>IF(G909&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910">
+        <f>IF(G910&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911">
+        <f>IF(G911&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912">
+        <f>IF(G912&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913">
+        <f>IF(G913&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914">
+        <f>IF(G914&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915">
+        <f>IF(G915&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916">
+        <f>IF(G916&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917">
+        <f>IF(G917&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918">
+        <f>IF(G918&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919">
+        <f>IF(G919&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920">
+        <f>IF(G920&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921">
+        <f>IF(G921&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922">
+        <f>IF(G922&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923">
+        <f>IF(G923&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924">
+        <f>IF(G924&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925">
+        <f>IF(G925&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926">
+        <f>IF(G926&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927">
+        <f>IF(G927&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928">
+        <f>IF(G928&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929">
+        <f>IF(G929&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930">
+        <f>IF(G930&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931">
+        <f>IF(G931&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932">
+        <f>IF(G932&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933">
+        <f>IF(G933&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934">
+        <f>IF(G934&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935">
+        <f>IF(G935&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936">
+        <f>IF(G936&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937">
+        <f>IF(G937&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938">
+        <f>IF(G938&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939">
+        <f>IF(G939&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940">
+        <f>IF(G940&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941">
+        <f>IF(G941&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942">
+        <f>IF(G942&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943">
+        <f>IF(G943&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944">
+        <f>IF(G944&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945">
+        <f>IF(G945&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946">
+        <f>IF(G946&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947">
+        <f>IF(G947&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948">
+        <f>IF(G948&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949">
+        <f>IF(G949&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950">
+        <f>IF(G950&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951">
+        <f>IF(G951&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952">
+        <f>IF(G952&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953">
+        <f>IF(G953&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954">
+        <f>IF(G954&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955">
+        <f>IF(G955&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956">
+        <f>IF(G956&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957">
+        <f>IF(G957&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958">
+        <f>IF(G958&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959">
+        <f>IF(G959&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960">
+        <f>IF(G960&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961">
+        <f>IF(G961&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962">
+        <f>IF(G962&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963">
+        <f>IF(G963&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964">
+        <f>IF(G964&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965">
+        <f>IF(G965&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966">
+        <f>IF(G966&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967">
+        <f>IF(G967&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968">
+        <f>IF(G968&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969">
+        <f>IF(G969&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970">
+        <f>IF(G970&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971">
+        <f>IF(G971&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972">
+        <f>IF(G972&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973">
+        <f>IF(G973&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974">
+        <f>IF(G974&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975">
+        <f>IF(G975&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976">
+        <f>IF(G976&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977">
+        <f>IF(G977&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978">
+        <f>IF(G978&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979">
+        <f>IF(G979&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980">
+        <f>IF(G980&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981">
+        <f>IF(G981&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982">
+        <f>IF(G982&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983">
+        <f>IF(G983&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984">
+        <f>IF(G984&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985">
+        <f>IF(G985&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986">
+        <f>IF(G986&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987">
+        <f>IF(G987&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988">
+        <f>IF(G988&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989">
+        <f>IF(G989&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990">
+        <f>IF(G990&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991">
+        <f>IF(G991&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992">
+        <f>IF(G992&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993">
+        <f>IF(G993&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994">
+        <f>IF(G994&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995">
+        <f>IF(G995&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996">
+        <f>IF(G996&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997">
+        <f>IF(G997&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998">
+        <f>IF(G998&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999">
+        <f>IF(G999&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000">
+        <f>IF(G1000&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001">
+        <f>IF(G1001&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N8"/>
+  <autoFilter ref="A1:AR11"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E1001">
+      <formula1>'Dropdown Lists'!$A$2:$A$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1001">
+      <formula1>'Dropdown Lists'!$B$2:$B$9</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="96" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="110" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -686,7 +6027,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stable unique key. Use lowercase words with hyphens. If blank, the app generates one.</t>
+          <t>Stable unique key. In Excel, A2:A1001 contains a formula that generates an ID when the question cell is populated. Paste generated IDs as values if you need them to stop recalculating.</t>
         </is>
       </c>
     </row>
@@ -754,7 +6095,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Recognition, Measurement, Presentation, Disclosure, Classification, etc.</t>
+          <t>Choose from the Questions tab dropdown. Values come from Dropdown Lists column A.</t>
         </is>
       </c>
     </row>
@@ -771,7 +6112,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mcq, dropdown, text, self_mark, calculation, or standard_match.</t>
+          <t>Choose from the Questions tab dropdown. Values come from Dropdown Lists column B.</t>
         </is>
       </c>
     </row>
@@ -788,7 +6129,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>The question prompt. For standard_match, this can be either IFRS 15 or Revenue from Contracts with Customers.</t>
+          <t>The question prompt. For multi_part, use ____ to indicate gaps where useful.</t>
         </is>
       </c>
     </row>
@@ -800,12 +6141,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Required for mcq/dropdown</t>
+          <t>Required for mcq/dropdown/multi_select</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pipe-separated choices, e.g. contract|transaction price|performance obligation. Leave blank for standard_match.</t>
+          <t>Pipe-separated choices. For multi_select, these are checkbox options.</t>
         </is>
       </c>
     </row>
@@ -817,12 +6158,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Required except multi_part</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The exact answer to show after checking. For standard_match, this is the corresponding standard number or name.</t>
+          <t>Exact answer. For multi_select, pipe-separated correct options.</t>
         </is>
       </c>
     </row>
@@ -839,7 +6180,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pipe-separated alternatives for variants mode, e.g. Revenue from contracts|International Financial Reporting Standard 15.</t>
+          <t>Pipe-separated alternatives for variants mode.</t>
         </is>
       </c>
     </row>
@@ -856,7 +6197,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>strict, variants, or self_mark. variants is useful for standard_match names.</t>
+          <t>strict, variants, or self_mark. variants also applies to multi_part text accepted answers.</t>
         </is>
       </c>
     </row>
@@ -911,7 +6252,201 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>partN_label</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Label shown beside a multi_part input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>partN_type</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Required for populated parts</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>text or dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>partN_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Required for dropdown parts</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pipe-separated dropdown options.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>partN_answer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Required for populated parts</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Correct answer for that part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>partN_accepted_answers</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Pipe-separated alternatives for text parts in variants mode.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C15"/>
+  <autoFilter ref="A1:C20"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>Categories</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t>Question Types</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Recognition</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dropdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Presentation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Disclosure</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>self_mark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Derecognition</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>standard_match</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>multi_part</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>multi_select</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
 </worksheet>
 </file>
--- a/templates/questions-template.xlsx
+++ b/templates/questions-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frcltd-my.sharepoint.com/personal/r_marks_frc_org_uk/Documents/Desktop/sbr/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="11_E9F32361FE4863DD78B1E2FB72030FF8208E8B85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A0201B1-F45E-4119-A136-592B9A8B8B0E}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_E9F32361FE4863DD78B1E2FB72030FF8208E8B85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F227E38-6A2E-40B3-B026-8FBDF27A4A0B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3935" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3848" uniqueCount="1010">
   <si>
     <t>id</t>
   </si>
@@ -2449,9 +2449,6 @@
     <t>Application</t>
   </si>
   <si>
-    <t>ias-2-standard-match</t>
-  </si>
-  <si>
     <t>IFRS Accounting Standards</t>
   </si>
   <si>
@@ -2467,9 +2464,6 @@
     <t>IAS 2 is **Inventories**.</t>
   </si>
   <si>
-    <t>ias-7-standard-match</t>
-  </si>
-  <si>
     <t>IAS 7</t>
   </si>
   <si>
@@ -2479,9 +2473,6 @@
     <t>IAS 7 is **Statement of Cash Flows**.</t>
   </si>
   <si>
-    <t>ias-8-standard-match</t>
-  </si>
-  <si>
     <t>IAS 8</t>
   </si>
   <si>
@@ -2491,9 +2482,6 @@
     <t>IAS 8 is **Basis of Preparation of Financial Statements**.</t>
   </si>
   <si>
-    <t>ias-10-standard-match</t>
-  </si>
-  <si>
     <t>IAS 10</t>
   </si>
   <si>
@@ -2503,9 +2491,6 @@
     <t>IAS 10 is **Events After the Reporting Period**.</t>
   </si>
   <si>
-    <t>ias-16-standard-match</t>
-  </si>
-  <si>
     <t>IAS 16</t>
   </si>
   <si>
@@ -2515,9 +2500,6 @@
     <t>IAS 16 is **Property, Plant and Equipment**.</t>
   </si>
   <si>
-    <t>ias-19-standard-match</t>
-  </si>
-  <si>
     <t>IAS 19</t>
   </si>
   <si>
@@ -2527,9 +2509,6 @@
     <t>IAS 19 is **Employee Benefits**.</t>
   </si>
   <si>
-    <t>ias-20-standard-match</t>
-  </si>
-  <si>
     <t>IAS 20</t>
   </si>
   <si>
@@ -2539,9 +2518,6 @@
     <t>IAS 20 is **Accounting for Government Grants and Disclosure of Government Assistance**.</t>
   </si>
   <si>
-    <t>ias-21-standard-match</t>
-  </si>
-  <si>
     <t>IAS 21</t>
   </si>
   <si>
@@ -2551,9 +2527,6 @@
     <t>IAS 21 is **The Effects of Changes in Foreign Exchange Rates**.</t>
   </si>
   <si>
-    <t>ias-23-standard-match</t>
-  </si>
-  <si>
     <t>IAS 23</t>
   </si>
   <si>
@@ -2563,9 +2536,6 @@
     <t>IAS 23 is **Borrowing Costs**.</t>
   </si>
   <si>
-    <t>ias-24-standard-match</t>
-  </si>
-  <si>
     <t>IAS 24</t>
   </si>
   <si>
@@ -2575,9 +2545,6 @@
     <t>IAS 24 is **Related Party Disclosures**.</t>
   </si>
   <si>
-    <t>ias-27-standard-match</t>
-  </si>
-  <si>
     <t>IAS 27</t>
   </si>
   <si>
@@ -2587,9 +2554,6 @@
     <t>IAS 27 is **Separate Financial Statements**.</t>
   </si>
   <si>
-    <t>ias-28-standard-match</t>
-  </si>
-  <si>
     <t>IAS 28</t>
   </si>
   <si>
@@ -2599,9 +2563,6 @@
     <t>IAS 28 is **Investments in Associates and Joint Ventures**.</t>
   </si>
   <si>
-    <t>ias-32-standard-match</t>
-  </si>
-  <si>
     <t>IAS 32</t>
   </si>
   <si>
@@ -2611,9 +2572,6 @@
     <t>IAS 32 is **Financial Instruments: Presentation**.</t>
   </si>
   <si>
-    <t>ias-33-standard-match</t>
-  </si>
-  <si>
     <t>IAS 33</t>
   </si>
   <si>
@@ -2623,9 +2581,6 @@
     <t>IAS 33 is **Earnings per Share**.</t>
   </si>
   <si>
-    <t>ias-34-standard-match</t>
-  </si>
-  <si>
     <t>IAS 34</t>
   </si>
   <si>
@@ -2635,9 +2590,6 @@
     <t>IAS 34 is **Interim Financial Reporting**.</t>
   </si>
   <si>
-    <t>ias-36-standard-match</t>
-  </si>
-  <si>
     <t>IAS 36</t>
   </si>
   <si>
@@ -2647,9 +2599,6 @@
     <t>IAS 36 is **Impairment of Assets**.</t>
   </si>
   <si>
-    <t>ias-37-standard-match</t>
-  </si>
-  <si>
     <t>IAS 37</t>
   </si>
   <si>
@@ -2659,9 +2608,6 @@
     <t>IAS 37 is **Provisions, Contingent Liabilities and Contingent Assets**.</t>
   </si>
   <si>
-    <t>ias-38-standard-match</t>
-  </si>
-  <si>
     <t>IAS 38</t>
   </si>
   <si>
@@ -2671,9 +2617,6 @@
     <t>IAS 38 is **Intangible Assets**.</t>
   </si>
   <si>
-    <t>ias-40-standard-match</t>
-  </si>
-  <si>
     <t>IAS 40</t>
   </si>
   <si>
@@ -2683,9 +2626,6 @@
     <t>IAS 40 is **Investment Property**.</t>
   </si>
   <si>
-    <t>ias-41-standard-match</t>
-  </si>
-  <si>
     <t>IAS 41</t>
   </si>
   <si>
@@ -2695,9 +2635,6 @@
     <t>IAS 41 is **Agriculture**.</t>
   </si>
   <si>
-    <t>ifrs-1-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 1</t>
   </si>
   <si>
@@ -2707,9 +2644,6 @@
     <t>IFRS 1 is **First-time Adoption of International Financial Reporting Standards**.</t>
   </si>
   <si>
-    <t>ifrs-2-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 2</t>
   </si>
   <si>
@@ -2719,9 +2653,6 @@
     <t>IFRS 2 is **Share-based Payment**.</t>
   </si>
   <si>
-    <t>ifrs-3-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 3</t>
   </si>
   <si>
@@ -2731,9 +2662,6 @@
     <t>IFRS 3 is **Business Combinations**.</t>
   </si>
   <si>
-    <t>ifrs-5-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 5</t>
   </si>
   <si>
@@ -2743,9 +2671,6 @@
     <t>IFRS 5 is **Non-current Assets Held for Sale and Discontinued Operations**.</t>
   </si>
   <si>
-    <t>ifrs-7-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 7</t>
   </si>
   <si>
@@ -2755,9 +2680,6 @@
     <t>IFRS 7 is **Financial Instruments: Disclosures**.</t>
   </si>
   <si>
-    <t>ifrs-8-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 8</t>
   </si>
   <si>
@@ -2767,9 +2689,6 @@
     <t>IFRS 8 is **Operating Segments**.</t>
   </si>
   <si>
-    <t>ifrs-9-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 9</t>
   </si>
   <si>
@@ -2779,9 +2698,6 @@
     <t>IFRS 9 is **Financial Instruments**.</t>
   </si>
   <si>
-    <t>ifrs-10-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 10</t>
   </si>
   <si>
@@ -2791,9 +2707,6 @@
     <t>IFRS 10 is **Consolidated Financial Statements**.</t>
   </si>
   <si>
-    <t>ifrs-11-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 11</t>
   </si>
   <si>
@@ -2803,9 +2716,6 @@
     <t>IFRS 11 is **Joint Arrangements**.</t>
   </si>
   <si>
-    <t>ifrs-12-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 12</t>
   </si>
   <si>
@@ -2815,9 +2725,6 @@
     <t>IFRS 12 is **Disclosure of Interests in other Entities**.</t>
   </si>
   <si>
-    <t>ifrs-13-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 13</t>
   </si>
   <si>
@@ -2827,27 +2734,18 @@
     <t>IFRS 13 is **Fair Value Measurement**.</t>
   </si>
   <si>
-    <t>ifrs-15-standard-match</t>
-  </si>
-  <si>
     <t>Revenue from Contracts with Customers</t>
   </si>
   <si>
     <t>IFRS 15 is **Revenue from Contracts with Customers**.</t>
   </si>
   <si>
-    <t>ifrs-16-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 16</t>
   </si>
   <si>
     <t>IFRS 16 is **Leases**.</t>
   </si>
   <si>
-    <t>ifrs-18-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 18</t>
   </si>
   <si>
@@ -2857,9 +2755,6 @@
     <t>IFRS 18 is **Presentation and Disclosure in Financial Statements**.</t>
   </si>
   <si>
-    <t>ifrs-19-standard-match</t>
-  </si>
-  <si>
     <t>IFRS 19</t>
   </si>
   <si>
@@ -2869,9 +2764,6 @@
     <t>IFRS 19 is **Subsidiaries without Public Accountability**.</t>
   </si>
   <si>
-    <t>ifrs-for-smes-standard-match</t>
-  </si>
-  <si>
     <t>IFRS for SMEs</t>
   </si>
   <si>
@@ -2881,9 +2773,6 @@
     <t>IFRS for SMEs is **IFRS for Small and Medium-sized Entities**.</t>
   </si>
   <si>
-    <t>ifrs-s1-standard-match</t>
-  </si>
-  <si>
     <t>IFRS S1</t>
   </si>
   <si>
@@ -2896,9 +2785,6 @@
     <t>IFRS S1 is **General Requirements for Disclosure of Sustainability-related Financial Information**.</t>
   </si>
   <si>
-    <t>ifrs-s2-standard-match</t>
-  </si>
-  <si>
     <t>IFRS S2</t>
   </si>
   <si>
@@ -2908,9 +2794,6 @@
     <t>IFRS S2 is **Climate-related Disclosures**.</t>
   </si>
   <si>
-    <t>conceptual-framework-standard-match</t>
-  </si>
-  <si>
     <t>Conceptual Framework</t>
   </si>
   <si>
@@ -2923,9 +2806,6 @@
     <t>The Conceptual Framework is **Conceptual Framework for Financial Reporting**.</t>
   </si>
   <si>
-    <t>ifrs-practice-statements-1-and-2-standard-match</t>
-  </si>
-  <si>
     <t>IFRS Practice Statements 1&amp;2</t>
   </si>
   <si>
@@ -2936,6 +2816,255 @@
   </si>
   <si>
     <t>Standard matcher</t>
+  </si>
+  <si>
+    <t>ifrs15-advance-payment-contract-liability</t>
+  </si>
+  <si>
+    <t>A customer pays in advance but control transfers two years later. The cash received should initially be recognised as a ____.</t>
+  </si>
+  <si>
+    <t>revenue|contract liability|trade receivable|refund liability</t>
+  </si>
+  <si>
+    <t>contract liability</t>
+  </si>
+  <si>
+    <t>This tops up the existing five-step question by testing the **timing consequence**: advance cash is not revenue until control transfers; it is initially a contract liability.</t>
+  </si>
+  <si>
+    <t>ifrs15-significant-financing-component-rate</t>
+  </si>
+  <si>
+    <t>For a significant financing component, what rate should be used to adjust the promised consideration?</t>
+  </si>
+  <si>
+    <t>the rate reflecting credit characteristics of the party receiving financing</t>
+  </si>
+  <si>
+    <t>discount rate reflecting credit characteristics|rate reflecting credit characteristics|customer cash price discount rate</t>
+  </si>
+  <si>
+    <t>This captures the Calibra nuance: the discounting rate should reflect the **credit characteristics of the party receiving financing**, not simply a convenient market rate.</t>
+  </si>
+  <si>
+    <t>ifrs15-control-transfer-completion</t>
+  </si>
+  <si>
+    <t>Transfer of control</t>
+  </si>
+  <si>
+    <t>A property developer retains title and possession during construction. When is revenue recognised if control only passes on completion?</t>
+  </si>
+  <si>
+    <t>When the contract is signed|When cash is received|When construction is completed and control passes|Over time during construction</t>
+  </si>
+  <si>
+    <t>When construction is completed and control passes</t>
+  </si>
+  <si>
+    <t>This avoids premature revenue recognition: if title, possession and control transfer only on completion, revenue is recognised **at that point**, even if cash was received earlier.</t>
+  </si>
+  <si>
+    <t>ifrs15-gift-card-initial-treatment</t>
+  </si>
+  <si>
+    <t>Gift cards</t>
+  </si>
+  <si>
+    <t>Cash received from selling a gift card is initially recognised as a ____ because the performance obligation has not yet been satisfied.</t>
+  </si>
+  <si>
+    <t>contract liability|revenue|refund liability|financial liability</t>
+  </si>
+  <si>
+    <t>This adds a high-frequency retail scenario: gift cards are **prepayments**, so revenue waits until goods/services are transferred or breakage is recognised.</t>
+  </si>
+  <si>
+    <t>ifrs15-breakage-pattern</t>
+  </si>
+  <si>
+    <t>Breakage</t>
+  </si>
+  <si>
+    <t>If expected gift card breakage can be estimated reliably and revenue reversal is highly improbable, how is breakage revenue recognised?</t>
+  </si>
+  <si>
+    <t>Immediately in full|In proportion to the pattern of rights exercised|Only when the card expires|Never recognised</t>
+  </si>
+  <si>
+    <t>In proportion to the pattern of rights exercised</t>
+  </si>
+  <si>
+    <t>This tests the nuance beyond gift-card liability: reliable expected breakage is recognised **in proportion to rights exercised**, not automatically upfront.</t>
+  </si>
+  <si>
+    <t>ifrs15-usage-royalty-trigger</t>
+  </si>
+  <si>
+    <t>Royalties</t>
+  </si>
+  <si>
+    <t>For a usage-based royalty, when should revenue generally be recognised?</t>
+  </si>
+  <si>
+    <t>as the usage occurs</t>
+  </si>
+  <si>
+    <t>when usage occurs|as usage occurs|when the customer uses the licence|based on usage</t>
+  </si>
+  <si>
+    <t>This targets Kiki’s royalty point: usage-based royalties are recognised **as usage occurs**, assuming contract criteria remain met.</t>
+  </si>
+  <si>
+    <t>ifrs15-collectability-reassessment</t>
+  </si>
+  <si>
+    <t>Contract criteria</t>
+  </si>
+  <si>
+    <t>Complete the collectability rule: IFRS 15 contract criteria are reassessed only if there is a significant change in ____ and ____.</t>
+  </si>
+  <si>
+    <t>facts</t>
+  </si>
+  <si>
+    <t>circumstances</t>
+  </si>
+  <si>
+    <t>This adds the important exam nuance that collectability is not continuously re-tested without reason; reassess contract criteria only after a **significant change in facts and circumstances**.</t>
+  </si>
+  <si>
+    <t>ifrs15-consignment-indicators</t>
+  </si>
+  <si>
+    <t>Which indicators suggest a consignment arrangement where the manufacturer retains control?</t>
+  </si>
+  <si>
+    <t>Dealer can set any price permanently|Manufacturer controls product until sale to end customer|Manufacturer can require return or transfer of product|Dealer has no unconditional obligation to pay|Dealer has legal title immediately</t>
+  </si>
+  <si>
+    <t>Manufacturer controls product until sale to end customer|Manufacturer can require return or transfer of product|Dealer has no unconditional obligation to pay</t>
+  </si>
+  <si>
+    <t>This tests the consignment indicators efficiently: control has not passed if the supplier still controls the product, can require return/transfer, and the dealer lacks an **unconditional payment obligation**.</t>
+  </si>
+  <si>
+    <t>ifrs15-right-of-return-liability</t>
+  </si>
+  <si>
+    <t>Right of return</t>
+  </si>
+  <si>
+    <t>For goods expected to be returned, the seller recognises a refund ____ rather than revenue.</t>
+  </si>
+  <si>
+    <t>asset|liability|expense|provision</t>
+  </si>
+  <si>
+    <t>liability</t>
+  </si>
+  <si>
+    <t>This adds the right-of-return structure: expected returns are excluded from revenue and create a **refund liability**.</t>
+  </si>
+  <si>
+    <t>ifrs15-right-of-return-asset</t>
+  </si>
+  <si>
+    <t>What asset is recognised for the seller’s right to recover inventory expected to be returned?</t>
+  </si>
+  <si>
+    <t>right of return asset</t>
+  </si>
+  <si>
+    <t>right-of-return asset|asset for right to recover products|right to recover returned inventory</t>
+  </si>
+  <si>
+    <t>This tests the often-missed second side of return accounting: recognise a **right-of-return asset** for inventory expected back, subject to recoverability.</t>
+  </si>
+  <si>
+    <t>ifrs15-upfront-fee-admin-task</t>
+  </si>
+  <si>
+    <t>A joining fee only covers setting up an account and issuing a card. What is the key IFRS 15 conclusion?</t>
+  </si>
+  <si>
+    <t>It is always immediate revenue|It is a separate performance obligation|It is an administrative task and not a performance obligation|It is a financial liability</t>
+  </si>
+  <si>
+    <t>It is an administrative task and not a performance obligation</t>
+  </si>
+  <si>
+    <t>This is a high-yield nuance: administrative setup does **not transfer a good or service**, so the fee is usually deferred and recognised as access is provided.</t>
+  </si>
+  <si>
+    <t>ifrs15-allocate-relative-ssp</t>
+  </si>
+  <si>
+    <t>Transaction price allocation</t>
+  </si>
+  <si>
+    <t>Calculation</t>
+  </si>
+  <si>
+    <t>A bundle sells for $2,000. Relative standalone selling prices total $2,100. The computer SSP is $1,720. What revenue is allocated to the computer?</t>
+  </si>
+  <si>
+    <t>$1,638.1|1638|1,638|1638.10|$1,638.10</t>
+  </si>
+  <si>
+    <t>This turns Cial into a quick calculation: allocate transaction price using **relative standalone selling prices**: $1,720 / $2,100 × $2,000 = $1,638.1.</t>
+  </si>
+  <si>
+    <t>ifrs15-estimating-ssp-methods</t>
+  </si>
+  <si>
+    <t>Standalone selling price</t>
+  </si>
+  <si>
+    <t>Which methods can help estimate standalone selling price when it is not directly observable?</t>
+  </si>
+  <si>
+    <t>Adjusted market assessment approach|Expected cost plus margin approach|Residual approach where appropriate|Historical cost model|Expected credit loss model</t>
+  </si>
+  <si>
+    <t>Adjusted market assessment approach|Expected cost plus margin approach|Residual approach where appropriate</t>
+  </si>
+  <si>
+    <t>This captures Cial’s estimation nuance: where SSP is not observable, IFRS 15 allows estimation methods such as **adjusted market assessment**, **expected cost plus margin**, and sometimes **residual**.</t>
+  </si>
+  <si>
+    <t>ifrs15-software-updates-single-po</t>
+  </si>
+  <si>
+    <t>Software licences and updates</t>
+  </si>
+  <si>
+    <t>Explain to yourself when a software licence and updates may be a single performance obligation, then reveal the answer.</t>
+  </si>
+  <si>
+    <t>They may be a single performance obligation when the updates are integral or essential to the customer obtaining the intended benefit from the licence, so the promise is a combined service recognised over time.</t>
+  </si>
+  <si>
+    <t>This tops up Sitka’s judgment issue: do not mechanically split licence and updates; assess whether the updates are **separately identifiable** or part of one combined promise.</t>
+  </si>
+  <si>
+    <t>ifrs15-over-time-service-contract</t>
+  </si>
+  <si>
+    <t>Timing of recognition</t>
+  </si>
+  <si>
+    <t>If the customer simultaneously receives and consumes the benefits as the entity performs, the performance obligation is satisfied ____.</t>
+  </si>
+  <si>
+    <t>at contract inception|over time|only on invoice|only when cash is received</t>
+  </si>
+  <si>
+    <t>over time</t>
+  </si>
+  <si>
+    <t>This reinforces the key timing distinction behind the software/update scenario: simultaneous receipt and consumption points to **over-time** recognition.</t>
   </si>
 </sst>
 </file>
@@ -3988,7 +4117,7 @@
     <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f ca="1">IF(G2&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>1237ffda-763f-ec38-14f8-7b0462d3e74d</v>
+        <v>406b0f5a-d4bc-e3f4-c949-15549277a84b</v>
       </c>
       <c r="B2" t="s">
         <v>336</v>
@@ -4123,7 +4252,7 @@
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f t="shared" ref="A3:A66" ca="1" si="0">IF(G3&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>92e6d63e-bbc0-d14f-cfb8-9b85cad130eb</v>
+        <v>68b78703-8ed8-70d4-a4d0-18876a171734</v>
       </c>
       <c r="B3" t="s">
         <v>336</v>
@@ -4258,7 +4387,7 @@
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>e2e64a6f-ccba-659b-0267-99e51bb838d8</v>
+        <v>47400359-5477-aa5e-42ab-6eca48e371f1</v>
       </c>
       <c r="B4" t="s">
         <v>336</v>
@@ -4393,7 +4522,7 @@
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>5dc46709-baed-5634-34ed-d6f1af52f82c</v>
+        <v>0e108d57-3974-58b1-eabd-249f34ab8658</v>
       </c>
       <c r="B5" t="s">
         <v>336</v>
@@ -4528,7 +4657,7 @@
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>614f5f76-7f96-a7ab-8d0b-bc6851801ce2</v>
+        <v>3ea29330-f606-441d-b9e1-2e654f4786c8</v>
       </c>
       <c r="B6" t="s">
         <v>336</v>
@@ -4663,7 +4792,7 @@
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>8c2e7f95-ab85-4a42-832a-f4ca749c1361</v>
+        <v>e0325b7d-a70e-994c-9506-63620c25b0dd</v>
       </c>
       <c r="B7" t="s">
         <v>336</v>
@@ -4798,7 +4927,7 @@
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>be5fe475-ad59-907e-e23e-3ad29626306c</v>
+        <v>b20f70da-eb13-9e26-7529-d88b40a83631</v>
       </c>
       <c r="B8" t="s">
         <v>336</v>
@@ -4933,7 +5062,7 @@
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>728d2107-480b-7f54-f710-fe7ae7b628fd</v>
+        <v>bcdbbf99-c68d-7878-a92f-1d6a30422370</v>
       </c>
       <c r="B9" t="s">
         <v>336</v>
@@ -5068,7 +5197,7 @@
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>c823e0d3-4549-0204-3dfb-7b7f7c36f6ca</v>
+        <v>f50771af-10c8-94fa-e5a9-612e4b92ca21</v>
       </c>
       <c r="B10" t="s">
         <v>336</v>
@@ -5203,7 +5332,7 @@
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>8518f74c-5d44-6b40-c4c3-77f99cde9d16</v>
+        <v>25aa9330-4105-4d28-7bf7-7890151c2df4</v>
       </c>
       <c r="B11" t="s">
         <v>336</v>
@@ -5338,7 +5467,7 @@
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>9d072218-fb23-ff1a-4bca-a36478c99085</v>
+        <v>55c86b7e-f947-986c-39d3-595ab97b0441</v>
       </c>
       <c r="B12" t="s">
         <v>336</v>
@@ -5473,7 +5602,7 @@
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>32356f48-5451-d9ff-4957-b01df9c6ef9e</v>
+        <v>a47f8705-2893-0dd0-7661-8f4f93fd867a</v>
       </c>
       <c r="B13" t="s">
         <v>336</v>
@@ -5608,7 +5737,7 @@
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>7842bba9-d0f7-60f8-501a-80182d277bea</v>
+        <v>47909e90-5f45-037a-6edb-be03b8fe45c8</v>
       </c>
       <c r="B14" t="s">
         <v>336</v>
@@ -5743,7 +5872,7 @@
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>9641b560-8bca-c15d-9ba3-38d84b395d34</v>
+        <v>fca212f3-7038-dda3-8aa7-d70da6d079b5</v>
       </c>
       <c r="B15" t="s">
         <v>336</v>
@@ -5878,7 +6007,7 @@
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>62785193-81f7-b8d2-8160-63596c82442e</v>
+        <v>75e6df73-199e-d949-b53e-d3d84056fcf6</v>
       </c>
       <c r="B16" t="s">
         <v>336</v>
@@ -6013,7 +6142,7 @@
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>94745712-3807-bfe8-4604-e7e662d1b5d0</v>
+        <v>853f731c-e19d-aeff-5c4f-498d9e9c8a51</v>
       </c>
       <c r="B17" t="s">
         <v>336</v>
@@ -6148,7 +6277,7 @@
     <row r="18" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>d8e0d875-6623-8b0c-ae09-ac8ac907230b</v>
+        <v>5620cd2b-5b09-d6db-1ca4-16152d875f7f</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
@@ -6283,7 +6412,7 @@
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>63b07e6b-6b98-a117-a445-3be450aa792f</v>
+        <v>c2512300-a45b-860f-39a5-7a450010263f</v>
       </c>
       <c r="B19" t="s">
         <v>336</v>
@@ -6418,7 +6547,7 @@
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>6a2082b6-b2f8-c165-c211-8905e384036a</v>
+        <v>d8eadc15-a5d5-0289-74c9-cc366db79af7</v>
       </c>
       <c r="B20" t="s">
         <v>336</v>
@@ -6553,7 +6682,7 @@
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>16d6b145-eb9d-f6cf-3dac-be99c1d1828f</v>
+        <v>a3688bfc-849f-fb44-f670-10ba3a7225c6</v>
       </c>
       <c r="B21" t="s">
         <v>336</v>
@@ -6688,7 +6817,7 @@
     <row r="22" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>21a66639-afed-6a41-8445-4a8ac6e9e688</v>
+        <v>d59a7aba-0505-aa0b-8afe-845422f3e760</v>
       </c>
       <c r="B22" t="s">
         <v>336</v>
@@ -6823,7 +6952,7 @@
     <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>d27f73e5-3276-91e9-e264-3df0bbbeeeed</v>
+        <v>9b8ec626-7ec7-cfa4-8566-e33bb0370f07</v>
       </c>
       <c r="B23" t="s">
         <v>336</v>
@@ -6958,7 +7087,7 @@
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>9f203251-d67c-0d72-278a-cc9c75e8e39d</v>
+        <v>78ecad80-eeed-0e15-44bd-241696d6c0ef</v>
       </c>
       <c r="B24" t="s">
         <v>336</v>
@@ -7093,7 +7222,7 @@
     <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>dcbf1637-84b2-a900-4eda-9d49a7046c79</v>
+        <v>3d0c2200-869c-abb9-5557-479ff3a89555</v>
       </c>
       <c r="B25" t="s">
         <v>336</v>
@@ -7228,7 +7357,7 @@
     <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>b0837b53-f47d-dbc0-ef6a-79c6d96c2739</v>
+        <v>4510e5eb-ff31-4032-33a7-729ae90da120</v>
       </c>
       <c r="B26" t="s">
         <v>336</v>
@@ -7363,7 +7492,7 @@
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>8d319c11-65b4-273a-6a58-522ba28b4a00</v>
+        <v>2472fed3-9ce4-2d27-c073-ec9c339ddbdc</v>
       </c>
       <c r="B27" t="s">
         <v>336</v>
@@ -7498,7 +7627,7 @@
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>4e6fecc1-b7d4-637c-affe-81442da84504</v>
+        <v>cbe7eacd-28ec-5014-913f-3bdf22fa6319</v>
       </c>
       <c r="B28" t="s">
         <v>336</v>
@@ -7633,7 +7762,7 @@
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>d73a8a68-53ea-6fdb-37f2-94fd25fe524e</v>
+        <v>18e7050c-3d05-a922-12e4-c0cd362e8c55</v>
       </c>
       <c r="B29" t="s">
         <v>336</v>
@@ -7768,7 +7897,7 @@
     <row r="30" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>f82dc111-9ede-6c00-babe-d7367d2f89f1</v>
+        <v>eb0a863a-ca14-67fa-c22e-8534406e0e88</v>
       </c>
       <c r="B30" t="s">
         <v>336</v>
@@ -7903,7 +8032,7 @@
     <row r="31" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>c76e911f-6573-fc2c-4177-a3569de71f83</v>
+        <v>3b1ae48b-0a42-d1db-7189-d38e176c0a0a</v>
       </c>
       <c r="B31" t="s">
         <v>336</v>
@@ -8038,7 +8167,7 @@
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a723696a-1640-c57f-d014-8b8027d1ab14</v>
+        <v>98eb9749-ab0d-51b4-f669-2a1c94a1b2bb</v>
       </c>
       <c r="B32" t="s">
         <v>336</v>
@@ -8173,7 +8302,7 @@
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29823745-c4bf-4a81-6e94-7e2f174d0aeb</v>
+        <v>52671820-ffef-6146-15f1-fba89c193bf8</v>
       </c>
       <c r="B33" t="s">
         <v>336</v>
@@ -8308,7 +8437,7 @@
     <row r="34" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>fbffcfd0-bc3d-e834-12ae-477ed23abec0</v>
+        <v>b99a2dad-74a8-95a3-571a-2e79b501831d</v>
       </c>
       <c r="B34" t="s">
         <v>336</v>
@@ -8443,7 +8572,7 @@
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>3562445e-6ad7-4c25-fb54-82f3f3676ddf</v>
+        <v>d04b7cad-f5ba-a305-1a4b-6347f840e70d</v>
       </c>
       <c r="B35" t="s">
         <v>336</v>
@@ -8578,7 +8707,7 @@
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>c2baf0d8-e3e6-13e3-41d0-a6e6a28b1a28</v>
+        <v>064d4ed1-1c64-11b8-7696-464be02ec332</v>
       </c>
       <c r="B36" t="s">
         <v>336</v>
@@ -8713,7 +8842,7 @@
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2c4da9ba-7f56-c953-172c-ed9849e9d8ae</v>
+        <v>6656d817-8e66-e805-f14e-a56592d4188d</v>
       </c>
       <c r="B37" t="s">
         <v>336</v>
@@ -8848,7 +8977,7 @@
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>25b42d59-69b6-8a51-c0f7-4f98c3f63cd7</v>
+        <v>7fe147e1-bdcb-07b4-f5c5-1a8bfd2e5657</v>
       </c>
       <c r="B38" t="s">
         <v>336</v>
@@ -8983,7 +9112,7 @@
     <row r="39" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>92eda232-f7fe-fb2e-4d83-b0683747b647</v>
+        <v>bbfee1ff-e8c2-00d8-7cb6-44b9e85b9273</v>
       </c>
       <c r="B39" t="s">
         <v>336</v>
@@ -9118,7 +9247,7 @@
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>de7bb4d1-4ffb-66ca-6d75-d94d28acba10</v>
+        <v>11ea5b4b-dd5c-91f2-d0c4-cfa939b66c6d</v>
       </c>
       <c r="B40" t="s">
         <v>336</v>
@@ -9253,7 +9382,7 @@
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>c69967e0-106f-5b8b-db50-fa1b33ac3adb</v>
+        <v>27e7ee4f-6ea4-d194-3411-f510fd2c93cb</v>
       </c>
       <c r="B41" t="s">
         <v>336</v>
@@ -9388,7 +9517,7 @@
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2f3011aa-3d0f-63ce-fb31-c1bad580b583</v>
+        <v>349034b1-9131-1eb7-a824-5efcc6004e1a</v>
       </c>
       <c r="B42" t="s">
         <v>336</v>
@@ -9523,7 +9652,7 @@
     <row r="43" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>8c44107e-e763-6b04-1f47-a48eb4ed1543</v>
+        <v>a02f325a-3a04-f144-77d6-1ad6b4cc9542</v>
       </c>
       <c r="B43" t="s">
         <v>336</v>
@@ -9658,7 +9787,7 @@
     <row r="44" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>4fec3fc3-3bd4-cb5a-c6e9-dec7ca10f8f4</v>
+        <v>851fec32-5e7c-21bb-4fd8-b102053b17fa</v>
       </c>
       <c r="B44" t="s">
         <v>336</v>
@@ -9793,7 +9922,7 @@
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>b2248264-6bf9-4799-70c3-eb9a31f065f2</v>
+        <v>6f77a22b-160f-7c2e-fea5-31ada5e265f4</v>
       </c>
       <c r="B45" t="s">
         <v>336</v>
@@ -9928,7 +10057,7 @@
     <row r="46" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>46a93fc6-d5de-dbc7-53c8-882f3499d449</v>
+        <v>2d0313f6-b1e0-cc2c-64f9-26290dae2c23</v>
       </c>
       <c r="B46" t="s">
         <v>111</v>
@@ -10024,7 +10153,7 @@
     <row r="47" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>49749e34-2fe8-7b54-b41e-d3cd7d532282</v>
+        <v>4c856f14-e82b-fa4a-7bcb-0c8a4d633674</v>
       </c>
       <c r="B47" t="s">
         <v>111</v>
@@ -10066,7 +10195,7 @@
     <row r="48" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ec774cf0-cce2-7885-8837-b5be7df95401</v>
+        <v>3335c3f6-242c-b03a-6dd0-57a61e64fe13</v>
       </c>
       <c r="B48" t="s">
         <v>111</v>
@@ -10108,7 +10237,7 @@
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>bb522037-f4ef-7cff-cb62-9b08edc2ed96</v>
+        <v>e5b4cf65-0dd4-3a66-6167-550662fd58a3</v>
       </c>
       <c r="B49" t="s">
         <v>111</v>
@@ -10150,7 +10279,7 @@
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>1939ced7-5f68-4540-41b2-d798865b77ef</v>
+        <v>10e95df1-017b-8133-b5ef-a6748d706e3e</v>
       </c>
       <c r="B50" t="s">
         <v>111</v>
@@ -10192,7 +10321,7 @@
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>6ec2de9f-a0e9-b935-17be-836e1f67d7b6</v>
+        <v>97e0102c-8d94-2286-7e22-354e06353514</v>
       </c>
       <c r="B51" t="s">
         <v>111</v>
@@ -10234,7 +10363,7 @@
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>b0c54741-ab4a-050b-efb3-4b08d6bdc1b6</v>
+        <v>27188ba9-e11f-bda1-f733-9842315d0cd9</v>
       </c>
       <c r="B52" t="s">
         <v>111</v>
@@ -10276,7 +10405,7 @@
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>bf5256a0-582b-4a02-c038-11b054bac8c4</v>
+        <v>8c40e910-206b-59c7-a308-e8d403586e11</v>
       </c>
       <c r="B53" t="s">
         <v>111</v>
@@ -10336,7 +10465,7 @@
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>815a22c8-2da1-491a-ea84-b3086e6b5b15</v>
+        <v>a331574b-3eec-161a-ef78-e1754e2fbd3c</v>
       </c>
       <c r="B54" t="s">
         <v>111</v>
@@ -10378,7 +10507,7 @@
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>7fe7c6ef-21c3-1c2c-b368-6f1bf41daaf2</v>
+        <v>321979ea-b4cd-532c-30e4-1d94798783ea</v>
       </c>
       <c r="B55" t="s">
         <v>111</v>
@@ -10420,7 +10549,7 @@
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>d4720ef2-06c1-1e82-4fd9-5f4b21d4a37d</v>
+        <v>b4fd407a-a534-6156-4897-e9aa6735c76b</v>
       </c>
       <c r="B56" t="s">
         <v>111</v>
@@ -10462,7 +10591,7 @@
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>797296d6-e108-0169-6369-d37155d81f77</v>
+        <v>bb23484b-5d6c-6612-7e77-218d3b1e45b8</v>
       </c>
       <c r="B57" t="s">
         <v>111</v>
@@ -10504,7 +10633,7 @@
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>fd7d859e-4b2c-dde1-45f8-01968a7bd187</v>
+        <v>28111167-7464-a33e-8dc9-6df1476d8c01</v>
       </c>
       <c r="B58" t="s">
         <v>111</v>
@@ -10546,7 +10675,7 @@
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>6662ef64-c899-5ef0-6082-5a41c3baf976</v>
+        <v>29bf6f7a-1a0d-757f-fb59-f8d9ccf5c03a</v>
       </c>
       <c r="B59" t="s">
         <v>111</v>
@@ -10588,7 +10717,7 @@
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>5cc957ee-6bfe-2905-ae89-232533ec5921</v>
+        <v>a5f11473-7071-cb82-7a8d-be93ea49ffc2</v>
       </c>
       <c r="B60" t="s">
         <v>111</v>
@@ -10630,7 +10759,7 @@
     <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>c873905d-4274-6f4f-c78d-7b07e392f495</v>
+        <v>48d4df53-94f3-6c6d-7e0d-98c24fb21bff</v>
       </c>
       <c r="B61" t="s">
         <v>111</v>
@@ -10690,7 +10819,7 @@
     <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>f75203a6-b1c6-ba2a-9a61-9b05ccadcf35</v>
+        <v>de3f00ad-f6fd-eb86-d110-e7b4180a93f9</v>
       </c>
       <c r="B62" t="s">
         <v>111</v>
@@ -10732,7 +10861,7 @@
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>15c788c0-20c5-cca6-85fe-6c381e33f6db</v>
+        <v>11f1b688-dead-1fa6-2110-07b50f4bd0d0</v>
       </c>
       <c r="B63" t="s">
         <v>111</v>
@@ -10792,7 +10921,7 @@
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>e299d4e6-3d6d-4ca2-dba3-a7fcf84dcad9</v>
+        <v>8b498459-18fc-2cf5-61db-a252ef3ca6b3</v>
       </c>
       <c r="B64" t="s">
         <v>111</v>
@@ -10834,7 +10963,7 @@
     <row r="65" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a845fb62-1ef9-d6d5-7be0-fc2652a05299</v>
+        <v>395a8053-82b1-46ef-fa1a-c3dcc80dd533</v>
       </c>
       <c r="B65" t="s">
         <v>111</v>
@@ -10894,7 +11023,7 @@
     <row r="66" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>972939fd-2f1b-adf9-a72f-2f7e08c29208</v>
+        <v>a70de057-4dd7-8e08-1e0c-b14c6c6a9a01</v>
       </c>
       <c r="B66" t="s">
         <v>111</v>
@@ -10954,7 +11083,7 @@
     <row r="67" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
         <f t="shared" ref="A67:A130" ca="1" si="1">IF(G67&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>aa084591-f41c-6192-9c33-af85e229febb</v>
+        <v>f8345c1d-7712-49aa-c97e-e999a8314ff3</v>
       </c>
       <c r="B67" t="s">
         <v>111</v>
@@ -10996,7 +11125,7 @@
     <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>bf5eb341-e237-b3d3-0922-ebbc091c3208</v>
+        <v>faf4116c-5040-4c6a-90fd-0a4246f747af</v>
       </c>
       <c r="B68" t="s">
         <v>111</v>
@@ -11056,7 +11185,7 @@
     <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>423a96fd-69f8-188d-98aa-76a95abc5c60</v>
+        <v>a3ad1320-c240-e256-053b-6038986399c5</v>
       </c>
       <c r="B69" t="s">
         <v>111</v>
@@ -11095,7 +11224,7 @@
     <row r="70" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>8da06177-0d41-efc1-99df-9dc86193417e</v>
+        <v>de71b684-a3c9-81f1-da81-cd631a576f6b</v>
       </c>
       <c r="B70" t="s">
         <v>111</v>
@@ -11134,7 +11263,7 @@
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>af7afbfe-15cb-3125-a9fb-43ac5feb3cc7</v>
+        <v>be58435b-768e-cfab-c703-b6d95f3ee44b</v>
       </c>
       <c r="B71" t="s">
         <v>111</v>
@@ -11176,7 +11305,7 @@
     <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>c83ee8f7-d084-1c1e-70a5-ae851b4dfd51</v>
+        <v>614e5a01-fa08-527a-cfcf-09d301bd59a2</v>
       </c>
       <c r="B72" t="s">
         <v>111</v>
@@ -11218,7 +11347,7 @@
     <row r="73" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>42082edf-bee5-29d5-f2a8-bc88da86f05c</v>
+        <v>e360e7a5-2a46-1e28-ce77-c98ac0a1d6b6</v>
       </c>
       <c r="B73" t="s">
         <v>111</v>
@@ -11260,7 +11389,7 @@
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>b5f91325-4035-8859-61c8-34e0cbfd9766</v>
+        <v>38305d8a-1e0f-93bd-9eb2-6504df0fd70e</v>
       </c>
       <c r="B74" t="s">
         <v>111</v>
@@ -11302,7 +11431,7 @@
     <row r="75" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>dc883a18-5ecb-7a05-8e2c-c0526a053f3a</v>
+        <v>eb1f4ecd-d8ef-eeac-1d30-b42379c29081</v>
       </c>
       <c r="B75" t="s">
         <v>111</v>
@@ -11344,7 +11473,7 @@
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>6a628282-16a5-f386-0201-fe8f04ee5598</v>
+        <v>e828e935-8c29-4314-5a79-42ce3b28cf11</v>
       </c>
       <c r="B76" t="s">
         <v>111</v>
@@ -11386,7 +11515,7 @@
     <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>c96ae7c4-9fa1-b89b-020b-da9b119ce37c</v>
+        <v>de0ae8e8-bacc-907f-581b-1059def8b646</v>
       </c>
       <c r="B77" t="s">
         <v>111</v>
@@ -11428,7 +11557,7 @@
     <row r="78" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>09f6abfd-24ce-cfe6-7a16-b1ff4c72ece7</v>
+        <v>1784d9f6-bdb2-dc00-615c-3d515141ccda</v>
       </c>
       <c r="B78" t="s">
         <v>111</v>
@@ -11470,7 +11599,7 @@
     <row r="79" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>12667bb9-251f-ef4d-298c-bb8214bb23ae</v>
+        <v>d2e523d0-58c8-7557-cf71-e3d3277dc4d2</v>
       </c>
       <c r="B79" t="s">
         <v>111</v>
@@ -11542,7 +11671,7 @@
     <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ba864e0c-6c20-4df5-5ffd-28e6059e8c5b</v>
+        <v>e4a00e9f-9473-a26e-6312-63b49cb68bf8</v>
       </c>
       <c r="B80" t="s">
         <v>111</v>
@@ -11614,7 +11743,7 @@
     <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>a0415461-cd5e-d8d8-9ee9-ffc6b3a97c45</v>
+        <v>bd559f45-6856-10a9-f261-1cac25377535</v>
       </c>
       <c r="B81" t="s">
         <v>111</v>
@@ -11656,7 +11785,7 @@
     <row r="82" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>4a3e008e-32b1-c2fc-4748-634689bf43a0</v>
+        <v>2cfbeb54-71c2-812d-41e0-58a85d966a1d</v>
       </c>
       <c r="B82" t="s">
         <v>111</v>
@@ -11698,7 +11827,7 @@
     <row r="83" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>c0ff0cdf-2f81-682d-d783-e5b816d631af</v>
+        <v>194c3674-1185-3c54-8e1e-743a59490f82</v>
       </c>
       <c r="B83" t="s">
         <v>111</v>
@@ -11740,7 +11869,7 @@
     <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>58950925-e738-01b0-3dc4-3648febe1ecd</v>
+        <v>207f4613-1c4d-e628-379b-96b1f9f91d06</v>
       </c>
       <c r="B84" t="s">
         <v>111</v>
@@ -11800,7 +11929,7 @@
     <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>63c02022-fb00-79e4-0daa-d65d072d3bf5</v>
+        <v>f15e517b-3170-2951-31c9-efec49b8484c</v>
       </c>
       <c r="B85" t="s">
         <v>111</v>
@@ -11860,7 +11989,7 @@
     <row r="86" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>aefbd325-d846-89ca-3cde-3623edd592cb</v>
+        <v>63b79d2e-ae68-6ad4-9508-d8ab8c8ca8a8</v>
       </c>
       <c r="B86" t="s">
         <v>111</v>
@@ -11902,7 +12031,7 @@
     <row r="87" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>c3520c20-40bc-bdd8-30d9-e8ed370596ce</v>
+        <v>df5964c7-701f-8417-e7bf-586eda78ed1c</v>
       </c>
       <c r="B87" t="s">
         <v>111</v>
@@ -11944,7 +12073,7 @@
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>6b9b4867-351f-9c93-0bec-7009dd3d5b38</v>
+        <v>91009f64-f13f-c54f-3ab6-0ee6fe942da8</v>
       </c>
       <c r="B88" t="s">
         <v>111</v>
@@ -11986,7 +12115,7 @@
     <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>36e6f9ce-6744-fc17-eadd-140bd86e30ad</v>
+        <v>e04c9a6f-85e5-898e-497e-c48d102624b4</v>
       </c>
       <c r="B89" t="s">
         <v>111</v>
@@ -12028,7 +12157,7 @@
     <row r="90" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>81666cc0-48f2-2dfa-79c0-aff2abf63e38</v>
+        <v>5c54cf09-558b-785a-fd87-20d875eac991</v>
       </c>
       <c r="B90" t="s">
         <v>111</v>
@@ -12070,7 +12199,7 @@
     <row r="91" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>d1129c1e-28cb-7e1d-3330-20ce9bc6d2fd</v>
+        <v>8e34e420-e5a2-7d69-ec19-7d2c6faffecd</v>
       </c>
       <c r="B91" t="s">
         <v>111</v>
@@ -12142,7 +12271,7 @@
     <row r="92" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>664f5e79-07de-8cfe-b92a-ce1546a91c6b</v>
+        <v>4a92a4da-5036-d811-21a0-142fc71eb4e0</v>
       </c>
       <c r="B92" t="s">
         <v>111</v>
@@ -12184,7 +12313,7 @@
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>de1a0ad9-efb5-cf29-25c1-37846ebbb492</v>
+        <v>05b14c99-7617-aaf6-f5bf-be578ad0abbf</v>
       </c>
       <c r="B93" t="s">
         <v>111</v>
@@ -12226,7 +12355,7 @@
     <row r="94" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>7d1b031a-e444-8944-deda-851a2d47929c</v>
+        <v>bf51acea-380a-3705-88cb-fd6562b6600a</v>
       </c>
       <c r="B94" t="s">
         <v>111</v>
@@ -12268,7 +12397,7 @@
     <row r="95" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>8a59d475-8c8f-8dba-174e-a88d0853d4fe</v>
+        <v>878a2f09-d381-a07f-6889-29f5780d5b13</v>
       </c>
       <c r="B95" t="s">
         <v>111</v>
@@ -12310,7 +12439,7 @@
     <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>b176aea4-0c3e-1ee3-29a1-6b22525cc486</v>
+        <v>d02aa243-2c51-9c43-04a8-edaac9b3d0e8</v>
       </c>
       <c r="B96" t="s">
         <v>111</v>
@@ -12352,7 +12481,7 @@
     <row r="97" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>78b88113-1aa2-f286-9190-9f5f41d2a0a1</v>
+        <v>407bfe48-40c7-5c21-1c61-6b4581873aaa</v>
       </c>
       <c r="B97" t="s">
         <v>111</v>
@@ -12394,7 +12523,7 @@
     <row r="98" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>a6fa38ae-0ec8-a5ae-73fd-addc6d81fc86</v>
+        <v>8c42dfc2-6b53-5eec-6b89-cdffabee3db0</v>
       </c>
       <c r="B98" t="s">
         <v>111</v>
@@ -12454,7 +12583,7 @@
     <row r="99" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>b9f44f31-7571-9cc2-8be2-1a3816bff836</v>
+        <v>29aaa963-1d0f-845c-2f2f-f71533f3f306</v>
       </c>
       <c r="B99" t="s">
         <v>111</v>
@@ -12496,7 +12625,7 @@
     <row r="100" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>64bbf478-7e8c-8d6f-8122-0b18f1c047f7</v>
+        <v>3c3a5ce3-7523-e3f2-722d-c7745fea5e56</v>
       </c>
       <c r="B100" t="s">
         <v>111</v>
@@ -12538,7 +12667,7 @@
     <row r="101" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>76c329c7-b863-924e-bf49-b401bc4704f0</v>
+        <v>a550503a-8062-e0cb-2b82-89dbbe0d54d4</v>
       </c>
       <c r="B101" t="s">
         <v>111</v>
@@ -12580,7 +12709,7 @@
     <row r="102" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>30e2a56e-2cbf-526e-255e-d167bcb01365</v>
+        <v>06fbefd3-a44f-7139-895d-d3989632084e</v>
       </c>
       <c r="B102" t="s">
         <v>111</v>
@@ -12640,7 +12769,7 @@
     <row r="103" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>6c93869e-f4f8-0b7c-2c2c-f0d6859c6fa3</v>
+        <v>0fbc1b5f-3257-8fc0-7117-87652e1859e1</v>
       </c>
       <c r="B103" t="s">
         <v>111</v>
@@ -12682,7 +12811,7 @@
     <row r="104" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>0583ec77-4578-75ce-8f80-5bccb5ab1063</v>
+        <v>a0e8b184-b938-5c0e-4637-6905ff6a1e60</v>
       </c>
       <c r="B104" t="s">
         <v>111</v>
@@ -12724,7 +12853,7 @@
     <row r="105" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>cc928eb6-53e5-9f5b-ec99-63a704a02671</v>
+        <v>63a417f1-2095-c5db-accd-da480012029a</v>
       </c>
       <c r="B105" t="s">
         <v>111</v>
@@ -12766,7 +12895,7 @@
     <row r="106" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>50502da8-6a83-a6e5-ec16-f89a2c78d6d4</v>
+        <v>40b2b020-e25b-5da7-ac49-be3df774785f</v>
       </c>
       <c r="B106" t="s">
         <v>111</v>
@@ -12808,7 +12937,7 @@
     <row r="107" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>fb70789e-d0e9-2bd4-cb18-cb8ca2c29f44</v>
+        <v>763b87bb-bdaf-ccd0-cf82-ebc7a36e843f</v>
       </c>
       <c r="B107" t="s">
         <v>111</v>
@@ -12904,7 +13033,7 @@
     <row r="108" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>66b120f2-897a-a38b-26ee-14f7c8f3fb71</v>
+        <v>781f7c15-802a-7fd6-e576-ecbe1af883e4</v>
       </c>
       <c r="B108" t="s">
         <v>111</v>
@@ -12946,7 +13075,7 @@
     <row r="109" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>72f9c805-c2bb-5bf8-5ed9-639d78e4b6d1</v>
+        <v>d44e8093-2fa6-e690-afcb-1b6e1bbb0547</v>
       </c>
       <c r="B109" t="s">
         <v>111</v>
@@ -12988,7 +13117,7 @@
     <row r="110" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>4603cc8e-958f-3660-c7c1-f04ceb5155e5</v>
+        <v>abd692e0-4204-88e6-0f6d-208330c61e5b</v>
       </c>
       <c r="B110" t="s">
         <v>111</v>
@@ -13030,7 +13159,7 @@
     <row r="111" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2a9dea15-6a8a-f9a0-cf05-4e1ab6f855cf</v>
+        <v>dbbca0a0-dec3-ef6a-f85b-5fa6cd62e940</v>
       </c>
       <c r="B111" t="s">
         <v>111</v>
@@ -13072,7 +13201,7 @@
     <row r="112" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>7b85d467-4c99-1573-8ad2-7983f1f25aa9</v>
+        <v>73d25e5e-89b5-f815-05b5-c1d35221931c</v>
       </c>
       <c r="B112" t="s">
         <v>111</v>
@@ -13132,7 +13261,7 @@
     <row r="113" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>41196774-9580-ffc4-c1a3-750e71f98f81</v>
+        <v>c4497e6c-56d0-ad9b-2814-7f6dcf335318</v>
       </c>
       <c r="B113" t="s">
         <v>111</v>
@@ -13174,7 +13303,7 @@
     <row r="114" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>5c91b94e-4b4e-e6dd-1826-27aeb4674deb</v>
+        <v>5a6f2dcf-4d5e-6a93-edca-6e422607e54a</v>
       </c>
       <c r="B114" t="s">
         <v>111</v>
@@ -13216,7 +13345,7 @@
     <row r="115" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>28538fe1-9c62-f885-a3e7-40984e2da762</v>
+        <v>60ee2aff-938b-d52b-114a-8bda7f877785</v>
       </c>
       <c r="B115" t="s">
         <v>111</v>
@@ -13276,7 +13405,7 @@
     <row r="116" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>3385ab6d-741d-1b06-b11e-cb4dd73eb3d9</v>
+        <v>f4f1994a-4485-e24d-eb9c-e3316c56931b</v>
       </c>
       <c r="B116" t="s">
         <v>111</v>
@@ -13318,7 +13447,7 @@
     <row r="117" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>74c176f1-4668-fef8-9973-762efa5bd8fc</v>
+        <v>042f8b6c-fb3e-762e-da8f-2212801473ba</v>
       </c>
       <c r="B117" t="s">
         <v>111</v>
@@ -13360,7 +13489,7 @@
     <row r="118" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>4ca6b01e-0431-b3e3-7194-c937fceeb628</v>
+        <v>f9ca5b70-976a-89a8-b4ea-bc0d32f03b6e</v>
       </c>
       <c r="B118" t="s">
         <v>111</v>
@@ -13402,7 +13531,7 @@
     <row r="119" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>a86957a5-cc51-8bc1-72d9-cc021c471b81</v>
+        <v>1f402cc8-0022-7484-79cd-8f51f4351cd6</v>
       </c>
       <c r="B119" t="s">
         <v>111</v>
@@ -13444,7 +13573,7 @@
     <row r="120" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>a46b5086-5067-0be9-3491-9c3e027954db</v>
+        <v>7193085e-09c4-3bcc-95d5-356b63b84456</v>
       </c>
       <c r="B120" t="s">
         <v>111</v>
@@ -13486,7 +13615,7 @@
     <row r="121" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>424504d0-c9e5-59a7-5df8-1084317cff57</v>
+        <v>9ca7e444-c0de-4b63-ef0b-eb3ddcd75413</v>
       </c>
       <c r="B121" t="s">
         <v>111</v>
@@ -13528,7 +13657,7 @@
     <row r="122" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>a2998114-23d4-9cda-965c-e59b9ae2b84a</v>
+        <v>8fedbe52-f8e3-7de7-cf05-360fe7f09ffb</v>
       </c>
       <c r="B122" t="s">
         <v>111</v>
@@ -13570,7 +13699,7 @@
     <row r="123" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>955e0266-e87e-c0db-dc8e-2560b275664c</v>
+        <v>ce33d53a-58e8-443f-ac38-6629764f8603</v>
       </c>
       <c r="B123" t="s">
         <v>111</v>
@@ -13612,7 +13741,7 @@
     <row r="124" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>7c529603-f2b8-f795-0f98-2e3942a1c43a</v>
+        <v>5de6e699-74d3-c310-ac35-03bc9f635c52</v>
       </c>
       <c r="B124" t="s">
         <v>111</v>
@@ -13654,7 +13783,7 @@
     <row r="125" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>750df42f-b7c0-d9dc-deb9-38977d61eca9</v>
+        <v>35a9ef3f-aed0-0689-429b-be3bc3dc7c76</v>
       </c>
       <c r="B125" t="s">
         <v>111</v>
@@ -13726,7 +13855,7 @@
     <row r="126" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>55bef44b-d148-d396-d659-d8aa3b44d149</v>
+        <v>1e0a5cc2-2899-7487-e355-79f0f2e35f3b</v>
       </c>
       <c r="B126" t="s">
         <v>111</v>
@@ -13768,7 +13897,7 @@
     <row r="127" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>059552b7-5d64-ab65-dfd5-71a29edbd344</v>
+        <v>5d8db8e1-6d6c-8a4e-3d9e-1f5f376589ad</v>
       </c>
       <c r="B127" t="s">
         <v>111</v>
@@ -13810,7 +13939,7 @@
     <row r="128" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>0eae7772-0329-43ff-ae52-75b0dc131881</v>
+        <v>d5657bba-2894-5f65-47ee-d6a7ed52114b</v>
       </c>
       <c r="B128" t="s">
         <v>111</v>
@@ -13852,7 +13981,7 @@
     <row r="129" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>bb9be493-bb43-3d21-027a-f4d637d1fc83</v>
+        <v>53741233-a30c-6b9a-4045-d8ce16c4d648</v>
       </c>
       <c r="B129" t="s">
         <v>111</v>
@@ -13894,7 +14023,7 @@
     <row r="130" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>db8c1f96-462d-ef18-9fd5-0f609665effe</v>
+        <v>2694c1f4-b9d6-4e20-07e1-8dc8c455f453</v>
       </c>
       <c r="B130" t="s">
         <v>111</v>
@@ -13936,7 +14065,7 @@
     <row r="131" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A131" t="str">
         <f t="shared" ref="A131:A133" ca="1" si="2">IF(G131&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>cf8acee4-cb75-c1df-da83-709910a7185e</v>
+        <v>ccfa0a3e-bfeb-312e-8812-bbb4221e4aeb</v>
       </c>
       <c r="B131" t="s">
         <v>111</v>
@@ -14020,7 +14149,7 @@
     <row r="132" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A132" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>c722a915-13d8-cefc-51a0-c98e114f18f8</v>
+        <v>276094a9-5d3d-2b14-09e6-0b18975857c5</v>
       </c>
       <c r="B132" t="s">
         <v>111</v>
@@ -14062,7 +14191,7 @@
     <row r="133" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>ff442dfb-eff0-014e-2401-f47dcde8e3f1</v>
+        <v>b5bf7c5b-526c-aa9b-dd71-78d20e7690f4</v>
       </c>
       <c r="B133" t="s">
         <v>111</v>
@@ -14134,19 +14263,19 @@
     <row r="134" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A134" t="str">
         <f t="shared" ref="A134:A194" ca="1" si="3">IF(G134&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>aa43afbf-e39b-4c09-1f0a-0ea9d1e49ac9</v>
+        <v>3eb395b1-1c4a-b49b-0351-1ac075794e7c</v>
       </c>
       <c r="B134" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C134" t="s">
+        <v>804</v>
+      </c>
+      <c r="D134" t="s">
         <v>805</v>
       </c>
-      <c r="D134" t="s">
+      <c r="E134" t="s">
         <v>806</v>
-      </c>
-      <c r="E134" t="s">
-        <v>807</v>
       </c>
       <c r="F134" t="s">
         <v>342</v>
@@ -14155,13 +14284,13 @@
         <v>510</v>
       </c>
       <c r="I134" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K134" t="s">
         <v>52</v>
       </c>
       <c r="L134" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="M134" t="s">
         <v>54</v>
@@ -14173,34 +14302,34 @@
     <row r="135" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>ea6bfc07-6745-98ac-4201-3888f4898876</v>
+        <v>21d2e564-542d-47d2-8cf4-817a7838bce7</v>
       </c>
       <c r="B135" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C135" t="s">
+        <v>804</v>
+      </c>
+      <c r="D135" t="s">
         <v>805</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
         <v>806</v>
-      </c>
-      <c r="E135" t="s">
-        <v>807</v>
       </c>
       <c r="F135" t="s">
         <v>342</v>
       </c>
       <c r="G135" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="I135" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="K135" t="s">
         <v>52</v>
       </c>
       <c r="L135" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="M135" t="s">
         <v>54</v>
@@ -14212,34 +14341,34 @@
     <row r="136" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>68ca37e9-eeeb-b0d6-d553-0ded1d8a9b64</v>
+        <v>9f337f24-f756-944b-dec6-c9efda416781</v>
       </c>
       <c r="B136" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C136" t="s">
+        <v>804</v>
+      </c>
+      <c r="D136" t="s">
         <v>805</v>
       </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
         <v>806</v>
-      </c>
-      <c r="E136" t="s">
-        <v>807</v>
       </c>
       <c r="F136" t="s">
         <v>342</v>
       </c>
       <c r="G136" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="I136" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="K136" t="s">
         <v>52</v>
       </c>
       <c r="L136" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="M136" t="s">
         <v>54</v>
@@ -14251,34 +14380,34 @@
     <row r="137" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>a8f9b56d-355d-a158-2331-e78df1b7821a</v>
+        <v>718ec756-12c0-4ef6-a1a0-a38f19dd9a97</v>
       </c>
       <c r="B137" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C137" t="s">
+        <v>804</v>
+      </c>
+      <c r="D137" t="s">
         <v>805</v>
       </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
         <v>806</v>
-      </c>
-      <c r="E137" t="s">
-        <v>807</v>
       </c>
       <c r="F137" t="s">
         <v>342</v>
       </c>
       <c r="G137" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="I137" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="K137" t="s">
         <v>52</v>
       </c>
       <c r="L137" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="M137" t="s">
         <v>54</v>
@@ -14290,34 +14419,34 @@
     <row r="138" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>686d55e4-8cc7-571c-87ce-ec1e37314c81</v>
+        <v>c3495598-a724-68e1-d875-d56536c69005</v>
       </c>
       <c r="B138" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C138" t="s">
+        <v>804</v>
+      </c>
+      <c r="D138" t="s">
         <v>805</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
         <v>806</v>
-      </c>
-      <c r="E138" t="s">
-        <v>807</v>
       </c>
       <c r="F138" t="s">
         <v>342</v>
       </c>
       <c r="G138" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="I138" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K138" t="s">
         <v>52</v>
       </c>
       <c r="L138" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="M138" t="s">
         <v>54</v>
@@ -14329,34 +14458,34 @@
     <row r="139" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>bfed248b-37cf-ce56-d250-536a950ecdb5</v>
+        <v>662527df-3cdf-82ad-52f9-c4fb25f20d8a</v>
       </c>
       <c r="B139" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C139" t="s">
+        <v>804</v>
+      </c>
+      <c r="D139" t="s">
         <v>805</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>806</v>
-      </c>
-      <c r="E139" t="s">
-        <v>807</v>
       </c>
       <c r="F139" t="s">
         <v>342</v>
       </c>
       <c r="G139" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="I139" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="K139" t="s">
         <v>52</v>
       </c>
       <c r="L139" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="M139" t="s">
         <v>54</v>
@@ -14368,34 +14497,34 @@
     <row r="140" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>cfa34ead-ee89-e265-2529-b02bb9dcf0c3</v>
+        <v>edbf89fd-b1f2-b1b1-3009-22e7e385aa0a</v>
       </c>
       <c r="B140" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C140" t="s">
+        <v>804</v>
+      </c>
+      <c r="D140" t="s">
         <v>805</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
         <v>806</v>
-      </c>
-      <c r="E140" t="s">
-        <v>807</v>
       </c>
       <c r="F140" t="s">
         <v>342</v>
       </c>
       <c r="G140" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="I140" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="K140" t="s">
         <v>52</v>
       </c>
       <c r="L140" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="M140" t="s">
         <v>54</v>
@@ -14407,34 +14536,34 @@
     <row r="141" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>cf76842b-9900-d48e-6b0f-06516cace6ed</v>
+        <v>ef99b2c3-cc1c-36d1-502e-354baa50183d</v>
       </c>
       <c r="B141" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C141" t="s">
+        <v>804</v>
+      </c>
+      <c r="D141" t="s">
         <v>805</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
         <v>806</v>
-      </c>
-      <c r="E141" t="s">
-        <v>807</v>
       </c>
       <c r="F141" t="s">
         <v>342</v>
       </c>
       <c r="G141" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="I141" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="K141" t="s">
         <v>52</v>
       </c>
       <c r="L141" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="M141" t="s">
         <v>54</v>
@@ -14446,34 +14575,34 @@
     <row r="142" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>bc75531b-bc9f-4553-dc9a-8eb5870edadc</v>
+        <v>3505fd5a-4c9b-4383-83fe-0bd5e4e263a0</v>
       </c>
       <c r="B142" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C142" t="s">
+        <v>804</v>
+      </c>
+      <c r="D142" t="s">
         <v>805</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>806</v>
-      </c>
-      <c r="E142" t="s">
-        <v>807</v>
       </c>
       <c r="F142" t="s">
         <v>342</v>
       </c>
       <c r="G142" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="I142" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="K142" t="s">
         <v>52</v>
       </c>
       <c r="L142" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="M142" t="s">
         <v>54</v>
@@ -14485,34 +14614,34 @@
     <row r="143" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>6e3ebc07-e8f8-448e-c30d-5953af3062ff</v>
+        <v>9d7406e7-e3e8-4b99-9011-cd8de96e1da9</v>
       </c>
       <c r="B143" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C143" t="s">
+        <v>804</v>
+      </c>
+      <c r="D143" t="s">
         <v>805</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
         <v>806</v>
-      </c>
-      <c r="E143" t="s">
-        <v>807</v>
       </c>
       <c r="F143" t="s">
         <v>342</v>
       </c>
       <c r="G143" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
       <c r="I143" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="K143" t="s">
         <v>52</v>
       </c>
       <c r="L143" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
       <c r="M143" t="s">
         <v>54</v>
@@ -14524,34 +14653,34 @@
     <row r="144" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>5bd005a3-8340-ca61-4f4f-3be9610e9d63</v>
+        <v>5b0ff0a0-ab93-8260-7226-3f173f18bf77</v>
       </c>
       <c r="B144" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C144" t="s">
+        <v>804</v>
+      </c>
+      <c r="D144" t="s">
         <v>805</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
         <v>806</v>
-      </c>
-      <c r="E144" t="s">
-        <v>807</v>
       </c>
       <c r="F144" t="s">
         <v>342</v>
       </c>
       <c r="G144" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="I144" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
       <c r="K144" t="s">
         <v>52</v>
       </c>
       <c r="L144" t="s">
-        <v>849</v>
+        <v>838</v>
       </c>
       <c r="M144" t="s">
         <v>54</v>
@@ -14563,34 +14692,34 @@
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>eed7a3b3-5e94-b453-c81d-3a01e64b77ca</v>
+        <v>64a3fa0b-43e5-f849-3f4e-774819b44ed3</v>
       </c>
       <c r="B145" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C145" t="s">
+        <v>804</v>
+      </c>
+      <c r="D145" t="s">
         <v>805</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
         <v>806</v>
-      </c>
-      <c r="E145" t="s">
-        <v>807</v>
       </c>
       <c r="F145" t="s">
         <v>342</v>
       </c>
       <c r="G145" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="I145" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
       <c r="K145" t="s">
         <v>52</v>
       </c>
       <c r="L145" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="M145" t="s">
         <v>54</v>
@@ -14602,34 +14731,34 @@
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>94067d2a-c4de-d48f-ecf1-1c9f5bfcc5c0</v>
+        <v>c7199877-4b85-e627-82e5-8189be2d1f8a</v>
       </c>
       <c r="B146" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C146" t="s">
+        <v>804</v>
+      </c>
+      <c r="D146" t="s">
         <v>805</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>806</v>
-      </c>
-      <c r="E146" t="s">
-        <v>807</v>
       </c>
       <c r="F146" t="s">
         <v>342</v>
       </c>
       <c r="G146" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="I146" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
       <c r="K146" t="s">
         <v>52</v>
       </c>
       <c r="L146" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="M146" t="s">
         <v>54</v>
@@ -14641,34 +14770,34 @@
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>be9c950a-39e4-babc-c5e0-ac6482abdb84</v>
+        <v>58419e0a-68a9-7899-331c-c387b53efa5e</v>
       </c>
       <c r="B147" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C147" t="s">
+        <v>804</v>
+      </c>
+      <c r="D147" t="s">
         <v>805</v>
       </c>
-      <c r="D147" t="s">
+      <c r="E147" t="s">
         <v>806</v>
-      </c>
-      <c r="E147" t="s">
-        <v>807</v>
       </c>
       <c r="F147" t="s">
         <v>342</v>
       </c>
       <c r="G147" t="s">
-        <v>859</v>
+        <v>845</v>
       </c>
       <c r="I147" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="K147" t="s">
         <v>52</v>
       </c>
       <c r="L147" t="s">
-        <v>861</v>
+        <v>847</v>
       </c>
       <c r="M147" t="s">
         <v>54</v>
@@ -14680,35 +14809,35 @@
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>ee0e0b46-716c-d30f-5701-03423ea0097b</v>
+        <v>060293ce-d0fe-5611-c2c1-118c1a60cbf9</v>
       </c>
       <c r="B148" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C148" t="s">
+        <v>804</v>
+      </c>
+      <c r="D148" t="s">
         <v>805</v>
       </c>
-      <c r="D148" t="s">
+      <c r="E148" t="s">
         <v>806</v>
-      </c>
-      <c r="E148" t="s">
-        <v>807</v>
       </c>
       <c r="F148" t="s">
         <v>342</v>
       </c>
       <c r="G148" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="H148" s="2"/>
       <c r="I148" t="s">
-        <v>864</v>
+        <v>849</v>
       </c>
       <c r="K148" t="s">
         <v>52</v>
       </c>
       <c r="L148" t="s">
-        <v>865</v>
+        <v>850</v>
       </c>
       <c r="M148" t="s">
         <v>54</v>
@@ -14720,34 +14849,34 @@
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>3f381233-cc4b-2681-3ac1-4b56028f3e2d</v>
+        <v>c054709f-3658-c883-91ba-edcc4e497cbb</v>
       </c>
       <c r="B149" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C149" t="s">
+        <v>804</v>
+      </c>
+      <c r="D149" t="s">
         <v>805</v>
       </c>
-      <c r="D149" t="s">
+      <c r="E149" t="s">
         <v>806</v>
-      </c>
-      <c r="E149" t="s">
-        <v>807</v>
       </c>
       <c r="F149" t="s">
         <v>342</v>
       </c>
       <c r="G149" t="s">
-        <v>867</v>
+        <v>851</v>
       </c>
       <c r="I149" t="s">
-        <v>868</v>
+        <v>852</v>
       </c>
       <c r="K149" t="s">
         <v>52</v>
       </c>
       <c r="L149" t="s">
-        <v>869</v>
+        <v>853</v>
       </c>
       <c r="M149" t="s">
         <v>54</v>
@@ -14759,34 +14888,34 @@
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>11aa2014-f28f-1536-d458-373de1ecb600</v>
+        <v>2a48d2b2-0784-1ede-42ae-025e7bc42fd1</v>
       </c>
       <c r="B150" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C150" t="s">
+        <v>804</v>
+      </c>
+      <c r="D150" t="s">
         <v>805</v>
       </c>
-      <c r="D150" t="s">
+      <c r="E150" t="s">
         <v>806</v>
-      </c>
-      <c r="E150" t="s">
-        <v>807</v>
       </c>
       <c r="F150" t="s">
         <v>342</v>
       </c>
       <c r="G150" t="s">
-        <v>871</v>
+        <v>854</v>
       </c>
       <c r="I150" t="s">
-        <v>872</v>
+        <v>855</v>
       </c>
       <c r="K150" t="s">
         <v>52</v>
       </c>
       <c r="L150" t="s">
-        <v>873</v>
+        <v>856</v>
       </c>
       <c r="M150" t="s">
         <v>54</v>
@@ -14798,34 +14927,34 @@
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>c09623d4-9efc-410b-2a94-363424bf3c07</v>
+        <v>d3474ec3-2695-5d6f-e906-425fd7f2bd91</v>
       </c>
       <c r="B151" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C151" t="s">
+        <v>804</v>
+      </c>
+      <c r="D151" t="s">
         <v>805</v>
       </c>
-      <c r="D151" t="s">
+      <c r="E151" t="s">
         <v>806</v>
-      </c>
-      <c r="E151" t="s">
-        <v>807</v>
       </c>
       <c r="F151" t="s">
         <v>342</v>
       </c>
       <c r="G151" t="s">
-        <v>875</v>
+        <v>857</v>
       </c>
       <c r="I151" t="s">
-        <v>876</v>
+        <v>858</v>
       </c>
       <c r="K151" t="s">
         <v>52</v>
       </c>
       <c r="L151" t="s">
-        <v>877</v>
+        <v>859</v>
       </c>
       <c r="M151" t="s">
         <v>54</v>
@@ -14837,34 +14966,34 @@
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>91b716d0-6899-aeb0-364d-1bd2409ab775</v>
+        <v>1aeb8334-caad-8269-e133-818d68d1dd67</v>
       </c>
       <c r="B152" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C152" t="s">
+        <v>804</v>
+      </c>
+      <c r="D152" t="s">
         <v>805</v>
       </c>
-      <c r="D152" t="s">
+      <c r="E152" t="s">
         <v>806</v>
-      </c>
-      <c r="E152" t="s">
-        <v>807</v>
       </c>
       <c r="F152" t="s">
         <v>342</v>
       </c>
       <c r="G152" t="s">
-        <v>879</v>
+        <v>860</v>
       </c>
       <c r="I152" t="s">
-        <v>880</v>
+        <v>861</v>
       </c>
       <c r="K152" t="s">
         <v>52</v>
       </c>
       <c r="L152" t="s">
-        <v>881</v>
+        <v>862</v>
       </c>
       <c r="M152" t="s">
         <v>54</v>
@@ -14876,34 +15005,34 @@
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>8ac0d859-2836-bf1d-349c-c3139e287074</v>
+        <v>2a5cd7bf-22cd-8de4-2af2-bafceb725227</v>
       </c>
       <c r="B153" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C153" t="s">
+        <v>804</v>
+      </c>
+      <c r="D153" t="s">
         <v>805</v>
       </c>
-      <c r="D153" t="s">
+      <c r="E153" t="s">
         <v>806</v>
-      </c>
-      <c r="E153" t="s">
-        <v>807</v>
       </c>
       <c r="F153" t="s">
         <v>342</v>
       </c>
       <c r="G153" t="s">
-        <v>883</v>
+        <v>863</v>
       </c>
       <c r="I153" t="s">
-        <v>884</v>
+        <v>864</v>
       </c>
       <c r="K153" t="s">
         <v>52</v>
       </c>
       <c r="L153" t="s">
-        <v>885</v>
+        <v>865</v>
       </c>
       <c r="M153" t="s">
         <v>54</v>
@@ -14915,34 +15044,34 @@
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>4817e5b3-24e7-12b1-964c-47050a15550d</v>
+        <v>04354069-d674-1ad2-5b68-2e0449b15467</v>
       </c>
       <c r="B154" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C154" t="s">
+        <v>804</v>
+      </c>
+      <c r="D154" t="s">
         <v>805</v>
       </c>
-      <c r="D154" t="s">
+      <c r="E154" t="s">
         <v>806</v>
-      </c>
-      <c r="E154" t="s">
-        <v>807</v>
       </c>
       <c r="F154" t="s">
         <v>342</v>
       </c>
       <c r="G154" t="s">
-        <v>887</v>
+        <v>866</v>
       </c>
       <c r="I154" t="s">
-        <v>888</v>
+        <v>867</v>
       </c>
       <c r="K154" t="s">
         <v>52</v>
       </c>
       <c r="L154" t="s">
-        <v>889</v>
+        <v>868</v>
       </c>
       <c r="M154" t="s">
         <v>54</v>
@@ -14954,34 +15083,34 @@
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>f9c26159-f718-14c2-f566-8dfc7e3be40f</v>
+        <v>49613cee-d3c2-b0db-b2ab-647b44088eaa</v>
       </c>
       <c r="B155" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C155" t="s">
+        <v>804</v>
+      </c>
+      <c r="D155" t="s">
         <v>805</v>
       </c>
-      <c r="D155" t="s">
+      <c r="E155" t="s">
         <v>806</v>
-      </c>
-      <c r="E155" t="s">
-        <v>807</v>
       </c>
       <c r="F155" t="s">
         <v>342</v>
       </c>
       <c r="G155" t="s">
-        <v>891</v>
+        <v>869</v>
       </c>
       <c r="I155" t="s">
-        <v>892</v>
+        <v>870</v>
       </c>
       <c r="K155" t="s">
         <v>52</v>
       </c>
       <c r="L155" t="s">
-        <v>893</v>
+        <v>871</v>
       </c>
       <c r="M155" t="s">
         <v>54</v>
@@ -14993,34 +15122,34 @@
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>c457bd75-adc9-4a5f-c31a-235b48533c5c</v>
+        <v>a5647d72-daa0-5f64-5684-008b45e14561</v>
       </c>
       <c r="B156" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C156" t="s">
+        <v>804</v>
+      </c>
+      <c r="D156" t="s">
         <v>805</v>
       </c>
-      <c r="D156" t="s">
+      <c r="E156" t="s">
         <v>806</v>
-      </c>
-      <c r="E156" t="s">
-        <v>807</v>
       </c>
       <c r="F156" t="s">
         <v>342</v>
       </c>
       <c r="G156" t="s">
-        <v>895</v>
+        <v>872</v>
       </c>
       <c r="I156" t="s">
-        <v>896</v>
+        <v>873</v>
       </c>
       <c r="K156" t="s">
         <v>52</v>
       </c>
       <c r="L156" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
       <c r="M156" t="s">
         <v>54</v>
@@ -15032,34 +15161,34 @@
     <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>4dca0fd5-0e55-e4a6-5630-1dce0918ba82</v>
+        <v>b6a6beb2-4c0c-fdab-d5bb-59c07eb440f9</v>
       </c>
       <c r="B157" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C157" t="s">
+        <v>804</v>
+      </c>
+      <c r="D157" t="s">
         <v>805</v>
       </c>
-      <c r="D157" t="s">
+      <c r="E157" t="s">
         <v>806</v>
-      </c>
-      <c r="E157" t="s">
-        <v>807</v>
       </c>
       <c r="F157" t="s">
         <v>342</v>
       </c>
       <c r="G157" t="s">
-        <v>899</v>
+        <v>875</v>
       </c>
       <c r="I157" t="s">
-        <v>900</v>
+        <v>876</v>
       </c>
       <c r="K157" t="s">
         <v>52</v>
       </c>
       <c r="L157" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="M157" t="s">
         <v>54</v>
@@ -15071,34 +15200,34 @@
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d6d65351-89af-4c93-bc6a-f713b8acc18e</v>
+        <v>4c8ee47e-82bb-ee9c-112f-dc9d330754ec</v>
       </c>
       <c r="B158" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C158" t="s">
+        <v>804</v>
+      </c>
+      <c r="D158" t="s">
         <v>805</v>
       </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
         <v>806</v>
-      </c>
-      <c r="E158" t="s">
-        <v>807</v>
       </c>
       <c r="F158" t="s">
         <v>342</v>
       </c>
       <c r="G158" t="s">
-        <v>903</v>
+        <v>878</v>
       </c>
       <c r="I158" t="s">
-        <v>904</v>
+        <v>879</v>
       </c>
       <c r="K158" t="s">
         <v>52</v>
       </c>
       <c r="L158" t="s">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="M158" t="s">
         <v>54</v>
@@ -15110,34 +15239,34 @@
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>2963cc8b-c90d-8435-b13f-7db050c981fb</v>
+        <v>4b8d3a7c-84f4-2715-a051-b2411fbac346</v>
       </c>
       <c r="B159" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C159" t="s">
+        <v>804</v>
+      </c>
+      <c r="D159" t="s">
         <v>805</v>
       </c>
-      <c r="D159" t="s">
+      <c r="E159" t="s">
         <v>806</v>
-      </c>
-      <c r="E159" t="s">
-        <v>807</v>
       </c>
       <c r="F159" t="s">
         <v>342</v>
       </c>
       <c r="G159" t="s">
-        <v>907</v>
+        <v>881</v>
       </c>
       <c r="I159" t="s">
-        <v>908</v>
+        <v>882</v>
       </c>
       <c r="K159" t="s">
         <v>52</v>
       </c>
       <c r="L159" t="s">
-        <v>909</v>
+        <v>883</v>
       </c>
       <c r="M159" t="s">
         <v>54</v>
@@ -15149,34 +15278,34 @@
     <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>33e615f4-993a-5278-3c06-d6f3e23a273e</v>
+        <v>91c7b8af-8633-ee71-a30d-e9509dcf2965</v>
       </c>
       <c r="B160" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C160" t="s">
+        <v>804</v>
+      </c>
+      <c r="D160" t="s">
         <v>805</v>
       </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
         <v>806</v>
-      </c>
-      <c r="E160" t="s">
-        <v>807</v>
       </c>
       <c r="F160" t="s">
         <v>342</v>
       </c>
       <c r="G160" t="s">
-        <v>911</v>
+        <v>884</v>
       </c>
       <c r="I160" t="s">
-        <v>912</v>
+        <v>885</v>
       </c>
       <c r="K160" t="s">
         <v>52</v>
       </c>
       <c r="L160" t="s">
-        <v>913</v>
+        <v>886</v>
       </c>
       <c r="M160" t="s">
         <v>54</v>
@@ -15188,34 +15317,34 @@
     <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>b06b2b8d-7ae7-0a28-8909-fd982175eeb7</v>
+        <v>96e63b86-cb66-904a-5419-869de81e41f9</v>
       </c>
       <c r="B161" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C161" t="s">
+        <v>804</v>
+      </c>
+      <c r="D161" t="s">
         <v>805</v>
       </c>
-      <c r="D161" t="s">
+      <c r="E161" t="s">
         <v>806</v>
-      </c>
-      <c r="E161" t="s">
-        <v>807</v>
       </c>
       <c r="F161" t="s">
         <v>342</v>
       </c>
       <c r="G161" t="s">
-        <v>915</v>
+        <v>887</v>
       </c>
       <c r="I161" t="s">
-        <v>916</v>
+        <v>888</v>
       </c>
       <c r="K161" t="s">
         <v>52</v>
       </c>
       <c r="L161" t="s">
-        <v>917</v>
+        <v>889</v>
       </c>
       <c r="M161" t="s">
         <v>54</v>
@@ -15227,34 +15356,34 @@
     <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>7c9e313c-7607-d6db-e093-85329218c752</v>
+        <v>164b8eef-0a98-4d13-131c-dd0dc1ead051</v>
       </c>
       <c r="B162" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C162" t="s">
+        <v>804</v>
+      </c>
+      <c r="D162" t="s">
         <v>805</v>
       </c>
-      <c r="D162" t="s">
+      <c r="E162" t="s">
         <v>806</v>
-      </c>
-      <c r="E162" t="s">
-        <v>807</v>
       </c>
       <c r="F162" t="s">
         <v>342</v>
       </c>
       <c r="G162" t="s">
-        <v>919</v>
+        <v>890</v>
       </c>
       <c r="I162" t="s">
-        <v>920</v>
+        <v>891</v>
       </c>
       <c r="K162" t="s">
         <v>52</v>
       </c>
       <c r="L162" t="s">
-        <v>921</v>
+        <v>892</v>
       </c>
       <c r="M162" t="s">
         <v>54</v>
@@ -15266,34 +15395,34 @@
     <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>66eb9371-5a7f-9be0-9631-11707ce431e8</v>
+        <v>f38bbf69-f81e-9528-8e5d-69910290a8c7</v>
       </c>
       <c r="B163" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C163" t="s">
+        <v>804</v>
+      </c>
+      <c r="D163" t="s">
         <v>805</v>
       </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
         <v>806</v>
-      </c>
-      <c r="E163" t="s">
-        <v>807</v>
       </c>
       <c r="F163" t="s">
         <v>342</v>
       </c>
       <c r="G163" t="s">
-        <v>923</v>
+        <v>893</v>
       </c>
       <c r="I163" t="s">
-        <v>924</v>
+        <v>894</v>
       </c>
       <c r="K163" t="s">
         <v>52</v>
       </c>
       <c r="L163" t="s">
-        <v>925</v>
+        <v>895</v>
       </c>
       <c r="M163" t="s">
         <v>54</v>
@@ -15305,34 +15434,34 @@
     <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>7c825a3e-a0eb-d36a-37d6-22f3bf313b24</v>
+        <v>95383076-fd81-cfe7-d34c-a0b5d6490e3d</v>
       </c>
       <c r="B164" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C164" t="s">
+        <v>804</v>
+      </c>
+      <c r="D164" t="s">
         <v>805</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
         <v>806</v>
-      </c>
-      <c r="E164" t="s">
-        <v>807</v>
       </c>
       <c r="F164" t="s">
         <v>342</v>
       </c>
       <c r="G164" t="s">
-        <v>927</v>
+        <v>896</v>
       </c>
       <c r="I164" t="s">
-        <v>928</v>
+        <v>897</v>
       </c>
       <c r="K164" t="s">
         <v>52</v>
       </c>
       <c r="L164" t="s">
-        <v>929</v>
+        <v>898</v>
       </c>
       <c r="M164" t="s">
         <v>54</v>
@@ -15344,19 +15473,19 @@
     <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>96531620-8e8d-d081-5795-178b7434dd7d</v>
+        <v>381f84b3-950c-217d-3ed0-770fdfc0d777</v>
       </c>
       <c r="B165" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C165" t="s">
+        <v>804</v>
+      </c>
+      <c r="D165" t="s">
         <v>805</v>
       </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
         <v>806</v>
-      </c>
-      <c r="E165" t="s">
-        <v>807</v>
       </c>
       <c r="F165" t="s">
         <v>342</v>
@@ -15365,13 +15494,13 @@
         <v>111</v>
       </c>
       <c r="I165" t="s">
-        <v>931</v>
+        <v>899</v>
       </c>
       <c r="K165" t="s">
         <v>52</v>
       </c>
       <c r="L165" t="s">
-        <v>932</v>
+        <v>900</v>
       </c>
       <c r="M165" t="s">
         <v>54</v>
@@ -15383,25 +15512,25 @@
     <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>c87d500d-7704-4241-3b54-a5e9fdabbd3a</v>
+        <v>9a1f2b9e-001e-6a3f-c77e-f83984b38d43</v>
       </c>
       <c r="B166" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C166" t="s">
+        <v>804</v>
+      </c>
+      <c r="D166" t="s">
         <v>805</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
         <v>806</v>
-      </c>
-      <c r="E166" t="s">
-        <v>807</v>
       </c>
       <c r="F166" t="s">
         <v>342</v>
       </c>
       <c r="G166" t="s">
-        <v>934</v>
+        <v>901</v>
       </c>
       <c r="I166" t="s">
         <v>227</v>
@@ -15410,7 +15539,7 @@
         <v>52</v>
       </c>
       <c r="L166" t="s">
-        <v>935</v>
+        <v>902</v>
       </c>
       <c r="M166" t="s">
         <v>54</v>
@@ -15422,34 +15551,34 @@
     <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>24fb4637-8645-03fc-2f2f-245bd1dc670f</v>
+        <v>8ed73d90-f548-ab4e-2b25-af0077aec072</v>
       </c>
       <c r="B167" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C167" t="s">
+        <v>804</v>
+      </c>
+      <c r="D167" t="s">
         <v>805</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>806</v>
-      </c>
-      <c r="E167" t="s">
-        <v>807</v>
       </c>
       <c r="F167" t="s">
         <v>342</v>
       </c>
       <c r="G167" t="s">
-        <v>937</v>
+        <v>903</v>
       </c>
       <c r="I167" t="s">
-        <v>938</v>
+        <v>904</v>
       </c>
       <c r="K167" t="s">
         <v>52</v>
       </c>
       <c r="L167" t="s">
-        <v>939</v>
+        <v>905</v>
       </c>
       <c r="M167" t="s">
         <v>54</v>
@@ -15461,34 +15590,34 @@
     <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>b335ba49-346a-10ed-84fe-16a7822d8ba4</v>
+        <v>d00ddce6-b7d6-bed5-2473-98cc9b4a8938</v>
       </c>
       <c r="B168" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C168" t="s">
+        <v>804</v>
+      </c>
+      <c r="D168" t="s">
         <v>805</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
         <v>806</v>
-      </c>
-      <c r="E168" t="s">
-        <v>807</v>
       </c>
       <c r="F168" t="s">
         <v>342</v>
       </c>
       <c r="G168" t="s">
-        <v>941</v>
+        <v>906</v>
       </c>
       <c r="I168" t="s">
-        <v>942</v>
+        <v>907</v>
       </c>
       <c r="K168" t="s">
         <v>52</v>
       </c>
       <c r="L168" t="s">
-        <v>943</v>
+        <v>908</v>
       </c>
       <c r="M168" t="s">
         <v>54</v>
@@ -15500,34 +15629,34 @@
     <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>59e35c7b-46d2-bf28-f0c9-699e0890ecba</v>
+        <v>56d6b505-f484-0c14-c326-f08176e42700</v>
       </c>
       <c r="B169" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C169" t="s">
+        <v>804</v>
+      </c>
+      <c r="D169" t="s">
         <v>805</v>
       </c>
-      <c r="D169" t="s">
+      <c r="E169" t="s">
         <v>806</v>
-      </c>
-      <c r="E169" t="s">
-        <v>807</v>
       </c>
       <c r="F169" t="s">
         <v>342</v>
       </c>
       <c r="G169" t="s">
-        <v>945</v>
+        <v>909</v>
       </c>
       <c r="I169" t="s">
-        <v>946</v>
+        <v>910</v>
       </c>
       <c r="K169" t="s">
         <v>52</v>
       </c>
       <c r="L169" t="s">
-        <v>947</v>
+        <v>911</v>
       </c>
       <c r="M169" t="s">
         <v>54</v>
@@ -15539,34 +15668,34 @@
     <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d18efda4-0adf-a79e-dd3c-b73c9d7463ba</v>
+        <v>b8cbcb6b-4e94-3943-720d-2f7a591c8d43</v>
       </c>
       <c r="B170" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C170" t="s">
-        <v>950</v>
+        <v>913</v>
       </c>
       <c r="D170" t="s">
+        <v>805</v>
+      </c>
+      <c r="E170" t="s">
         <v>806</v>
-      </c>
-      <c r="E170" t="s">
-        <v>807</v>
       </c>
       <c r="F170" t="s">
         <v>342</v>
       </c>
       <c r="G170" t="s">
-        <v>949</v>
+        <v>912</v>
       </c>
       <c r="I170" t="s">
-        <v>951</v>
+        <v>914</v>
       </c>
       <c r="K170" t="s">
         <v>52</v>
       </c>
       <c r="L170" t="s">
-        <v>952</v>
+        <v>915</v>
       </c>
       <c r="M170" t="s">
         <v>54</v>
@@ -15578,34 +15707,34 @@
     <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>110e61d6-c7a4-fefc-6717-c703081712bc</v>
+        <v>ced69534-aeb3-d6d1-39dd-bf4e80f75a96</v>
       </c>
       <c r="B171" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C171" t="s">
-        <v>950</v>
+        <v>913</v>
       </c>
       <c r="D171" t="s">
+        <v>805</v>
+      </c>
+      <c r="E171" t="s">
         <v>806</v>
-      </c>
-      <c r="E171" t="s">
-        <v>807</v>
       </c>
       <c r="F171" t="s">
         <v>342</v>
       </c>
       <c r="G171" t="s">
-        <v>954</v>
+        <v>916</v>
       </c>
       <c r="I171" t="s">
-        <v>955</v>
+        <v>917</v>
       </c>
       <c r="K171" t="s">
         <v>52</v>
       </c>
       <c r="L171" t="s">
-        <v>956</v>
+        <v>918</v>
       </c>
       <c r="M171" t="s">
         <v>54</v>
@@ -15617,34 +15746,34 @@
     <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d633142d-3ca7-9bef-813f-e02b5e0208a9</v>
+        <v>e0c0b6ea-ca4f-aefd-0c47-5727fcce784d</v>
       </c>
       <c r="B172" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C172" t="s">
-        <v>959</v>
+        <v>920</v>
       </c>
       <c r="D172" t="s">
+        <v>805</v>
+      </c>
+      <c r="E172" t="s">
         <v>806</v>
-      </c>
-      <c r="E172" t="s">
-        <v>807</v>
       </c>
       <c r="F172" t="s">
         <v>342</v>
       </c>
       <c r="G172" t="s">
-        <v>958</v>
+        <v>919</v>
       </c>
       <c r="I172" t="s">
-        <v>960</v>
+        <v>921</v>
       </c>
       <c r="K172" t="s">
         <v>52</v>
       </c>
       <c r="L172" t="s">
-        <v>961</v>
+        <v>922</v>
       </c>
       <c r="M172" t="s">
         <v>54</v>
@@ -15656,34 +15785,34 @@
     <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>e48652e9-c0c4-4d5a-e09c-3e4985e9a614</v>
+        <v>aa82ffc0-414a-4def-736e-94ff25d4a776</v>
       </c>
       <c r="B173" t="s">
-        <v>966</v>
+        <v>926</v>
       </c>
       <c r="C173" t="s">
-        <v>959</v>
+        <v>920</v>
       </c>
       <c r="D173" t="s">
+        <v>805</v>
+      </c>
+      <c r="E173" t="s">
         <v>806</v>
-      </c>
-      <c r="E173" t="s">
-        <v>807</v>
       </c>
       <c r="F173" t="s">
         <v>342</v>
       </c>
       <c r="G173" t="s">
-        <v>963</v>
+        <v>923</v>
       </c>
       <c r="I173" t="s">
-        <v>964</v>
+        <v>924</v>
       </c>
       <c r="K173" t="s">
         <v>52</v>
       </c>
       <c r="L173" t="s">
-        <v>965</v>
+        <v>925</v>
       </c>
       <c r="M173" t="s">
         <v>54</v>
@@ -15695,112 +15824,667 @@
     <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
+        <v>5df48305-9026-83f1-67ac-30c2ae61244c</v>
+      </c>
+      <c r="B174" t="s">
+        <v>111</v>
+      </c>
+      <c r="C174" t="s">
+        <v>112</v>
+      </c>
+      <c r="D174" t="s">
+        <v>433</v>
+      </c>
+      <c r="E174" t="s">
+        <v>100</v>
+      </c>
+      <c r="F174" t="s">
+        <v>61</v>
+      </c>
+      <c r="G174" t="s">
+        <v>928</v>
+      </c>
+      <c r="H174" t="s">
+        <v>929</v>
+      </c>
+      <c r="I174" t="s">
+        <v>930</v>
+      </c>
+      <c r="K174" t="s">
+        <v>74</v>
+      </c>
+      <c r="L174" t="s">
+        <v>931</v>
+      </c>
+      <c r="M174" t="s">
+        <v>54</v>
+      </c>
+      <c r="N174" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
+        <v>ac3238dc-03d8-bd1d-b8a3-f3e0a068b1c1</v>
+      </c>
+      <c r="B175" t="s">
+        <v>111</v>
+      </c>
+      <c r="C175" t="s">
+        <v>112</v>
+      </c>
+      <c r="D175" t="s">
+        <v>433</v>
+      </c>
+      <c r="E175" t="s">
+        <v>106</v>
+      </c>
+      <c r="F175" t="s">
+        <v>47</v>
+      </c>
+      <c r="G175" t="s">
+        <v>933</v>
+      </c>
+      <c r="H175" t="s">
+        <v>934</v>
+      </c>
+      <c r="I175" t="s">
+        <v>935</v>
+      </c>
+      <c r="J175" t="s">
+        <v>52</v>
+      </c>
+      <c r="K175" t="s">
+        <v>936</v>
+      </c>
+      <c r="L175" t="s">
+        <v>197</v>
+      </c>
+      <c r="M175" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+        <v>fb30e7a2-a40b-d855-90b1-aa1f3b07ed53</v>
+      </c>
+      <c r="B176" t="s">
+        <v>111</v>
+      </c>
+      <c r="C176" t="s">
+        <v>112</v>
+      </c>
+      <c r="D176" t="s">
+        <v>938</v>
+      </c>
+      <c r="E176" t="s">
+        <v>100</v>
+      </c>
+      <c r="F176" t="s">
+        <v>95</v>
+      </c>
+      <c r="G176" t="s">
+        <v>939</v>
+      </c>
+      <c r="H176" t="s">
+        <v>940</v>
+      </c>
+      <c r="I176" t="s">
+        <v>941</v>
+      </c>
+      <c r="K176" t="s">
+        <v>74</v>
+      </c>
+      <c r="L176" t="s">
+        <v>942</v>
+      </c>
+      <c r="M176" t="s">
+        <v>54</v>
+      </c>
+      <c r="N176" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+        <v>76f3de6a-61cb-fa35-3c45-0cd5eef0423a</v>
+      </c>
+      <c r="B177" t="s">
+        <v>111</v>
+      </c>
+      <c r="C177" t="s">
+        <v>112</v>
+      </c>
+      <c r="D177" t="s">
+        <v>944</v>
+      </c>
+      <c r="E177" t="s">
+        <v>100</v>
+      </c>
+      <c r="F177" t="s">
+        <v>61</v>
+      </c>
+      <c r="G177" t="s">
+        <v>945</v>
+      </c>
+      <c r="H177" t="s">
+        <v>946</v>
+      </c>
+      <c r="I177" t="s">
+        <v>930</v>
+      </c>
+      <c r="K177" t="s">
+        <v>74</v>
+      </c>
+      <c r="L177" t="s">
+        <v>947</v>
+      </c>
+      <c r="M177" t="s">
+        <v>54</v>
+      </c>
+      <c r="N177" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+        <v>0f873c94-a065-d36c-f3e3-c0f4ddf01456</v>
+      </c>
+      <c r="B178" t="s">
+        <v>111</v>
+      </c>
+      <c r="C178" t="s">
+        <v>112</v>
+      </c>
+      <c r="D178" t="s">
+        <v>949</v>
+      </c>
+      <c r="E178" t="s">
+        <v>100</v>
+      </c>
+      <c r="F178" t="s">
+        <v>95</v>
+      </c>
+      <c r="G178" t="s">
+        <v>950</v>
+      </c>
+      <c r="H178" t="s">
+        <v>951</v>
+      </c>
+      <c r="I178" t="s">
+        <v>952</v>
+      </c>
+      <c r="K178" t="s">
+        <v>74</v>
+      </c>
+      <c r="L178" t="s">
+        <v>953</v>
+      </c>
+      <c r="M178" t="s">
+        <v>124</v>
+      </c>
+      <c r="N178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+        <v>d14edce9-d30e-8116-14e3-d5f3c296ab67</v>
+      </c>
+      <c r="B179" t="s">
+        <v>111</v>
+      </c>
+      <c r="C179" t="s">
+        <v>112</v>
+      </c>
+      <c r="D179" t="s">
+        <v>955</v>
+      </c>
+      <c r="E179" t="s">
+        <v>100</v>
+      </c>
+      <c r="F179" t="s">
+        <v>47</v>
+      </c>
+      <c r="G179" t="s">
+        <v>956</v>
+      </c>
+      <c r="H179" t="s">
+        <v>957</v>
+      </c>
+      <c r="I179" t="s">
+        <v>958</v>
+      </c>
+      <c r="J179" t="s">
+        <v>52</v>
+      </c>
+      <c r="K179" t="s">
+        <v>959</v>
+      </c>
+      <c r="L179" t="s">
+        <v>54</v>
+      </c>
+      <c r="M179" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+        <v>5f015f94-af76-d345-b6a6-150a3aa713d2</v>
+      </c>
+      <c r="B180" t="s">
+        <v>111</v>
+      </c>
+      <c r="C180" t="s">
+        <v>112</v>
+      </c>
+      <c r="D180" t="s">
+        <v>961</v>
+      </c>
+      <c r="E180" t="s">
+        <v>100</v>
+      </c>
+      <c r="F180" t="s">
+        <v>57</v>
+      </c>
+      <c r="G180" t="s">
+        <v>962</v>
+      </c>
+      <c r="I180" t="s">
+        <v>963</v>
+      </c>
+      <c r="J180" t="s">
+        <v>964</v>
+      </c>
+      <c r="K180" t="s">
+        <v>52</v>
+      </c>
+      <c r="L180" t="s">
+        <v>965</v>
+      </c>
+      <c r="M180" t="s">
+        <v>197</v>
+      </c>
+      <c r="N180" t="b">
+        <v>1</v>
+      </c>
+      <c r="O180" t="s">
+        <v>60</v>
+      </c>
+      <c r="P180" t="s">
+        <v>47</v>
+      </c>
+      <c r="R180" t="s">
+        <v>963</v>
+      </c>
+      <c r="T180" t="s">
+        <v>64</v>
+      </c>
+      <c r="U180" t="s">
+        <v>47</v>
+      </c>
+      <c r="W180" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+        <v>a0d293c3-d2a6-0e88-3d99-f722ce407f83</v>
+      </c>
+      <c r="B181" t="s">
+        <v>111</v>
+      </c>
+      <c r="C181" t="s">
+        <v>112</v>
+      </c>
+      <c r="D181" t="s">
+        <v>635</v>
+      </c>
+      <c r="E181" t="s">
+        <v>119</v>
+      </c>
+      <c r="F181" t="s">
+        <v>89</v>
+      </c>
+      <c r="G181" t="s">
+        <v>967</v>
+      </c>
+      <c r="H181" t="s">
+        <v>968</v>
+      </c>
+      <c r="I181" t="s">
+        <v>969</v>
+      </c>
+      <c r="K181" t="s">
+        <v>74</v>
+      </c>
+      <c r="L181" t="s">
+        <v>970</v>
+      </c>
+      <c r="M181" t="s">
+        <v>197</v>
+      </c>
+      <c r="N181" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+        <v>b7e708ac-e673-f545-21d6-eed334aa2d4e</v>
+      </c>
+      <c r="B182" t="s">
+        <v>111</v>
+      </c>
+      <c r="C182" t="s">
+        <v>112</v>
+      </c>
+      <c r="D182" t="s">
+        <v>972</v>
+      </c>
+      <c r="E182" t="s">
+        <v>344</v>
+      </c>
+      <c r="F182" t="s">
+        <v>61</v>
+      </c>
+      <c r="G182" t="s">
+        <v>973</v>
+      </c>
+      <c r="H182" t="s">
+        <v>974</v>
+      </c>
+      <c r="I182" t="s">
+        <v>975</v>
+      </c>
+      <c r="K182" t="s">
+        <v>74</v>
+      </c>
+      <c r="L182" t="s">
+        <v>976</v>
+      </c>
+      <c r="M182" t="s">
+        <v>54</v>
+      </c>
+      <c r="N182" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+        <v>4530a150-11f9-160b-bbd4-374b59f3eeba</v>
+      </c>
+      <c r="B183" t="s">
+        <v>111</v>
+      </c>
+      <c r="C183" t="s">
+        <v>112</v>
+      </c>
+      <c r="D183" t="s">
+        <v>972</v>
+      </c>
+      <c r="E183" t="s">
+        <v>344</v>
+      </c>
+      <c r="F183" t="s">
+        <v>47</v>
+      </c>
+      <c r="G183" t="s">
+        <v>978</v>
+      </c>
+      <c r="H183" t="s">
+        <v>979</v>
+      </c>
+      <c r="I183" t="s">
+        <v>980</v>
+      </c>
+      <c r="J183" t="s">
+        <v>52</v>
+      </c>
+      <c r="K183" t="s">
+        <v>981</v>
+      </c>
+      <c r="L183" t="s">
+        <v>197</v>
+      </c>
+      <c r="M183" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+        <v>c9b9dae8-00db-fe01-08f1-eb96565c4a38</v>
+      </c>
+      <c r="B184" t="s">
+        <v>111</v>
+      </c>
+      <c r="C184" t="s">
+        <v>112</v>
+      </c>
+      <c r="D184" t="s">
+        <v>618</v>
+      </c>
+      <c r="E184" t="s">
+        <v>119</v>
+      </c>
+      <c r="F184" t="s">
+        <v>95</v>
+      </c>
+      <c r="G184" t="s">
+        <v>983</v>
+      </c>
+      <c r="H184" t="s">
+        <v>984</v>
+      </c>
+      <c r="I184" t="s">
+        <v>985</v>
+      </c>
+      <c r="K184" t="s">
+        <v>74</v>
+      </c>
+      <c r="L184" t="s">
+        <v>986</v>
+      </c>
+      <c r="M184" t="s">
+        <v>197</v>
+      </c>
+      <c r="N184" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+        <v>19e81e27-adfa-9a7a-6f7d-547a0671ff90</v>
+      </c>
+      <c r="B185" t="s">
+        <v>111</v>
+      </c>
+      <c r="C185" t="s">
+        <v>112</v>
+      </c>
+      <c r="D185" t="s">
+        <v>988</v>
+      </c>
+      <c r="E185" t="s">
+        <v>989</v>
+      </c>
+      <c r="F185" t="s">
+        <v>341</v>
+      </c>
+      <c r="G185" t="s">
+        <v>990</v>
+      </c>
+      <c r="I185">
+        <v>1638.1</v>
+      </c>
+      <c r="J185" t="s">
+        <v>991</v>
+      </c>
+      <c r="K185" t="s">
+        <v>52</v>
+      </c>
+      <c r="L185" t="s">
+        <v>992</v>
+      </c>
+      <c r="M185" t="s">
+        <v>197</v>
+      </c>
+      <c r="N185" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+        <v>94d94320-fad7-2860-60b5-3a55497332ca</v>
+      </c>
+      <c r="B186" t="s">
+        <v>111</v>
+      </c>
+      <c r="C186" t="s">
+        <v>112</v>
+      </c>
+      <c r="D186" t="s">
+        <v>994</v>
+      </c>
+      <c r="E186" t="s">
+        <v>106</v>
+      </c>
+      <c r="F186" t="s">
+        <v>89</v>
+      </c>
+      <c r="G186" t="s">
+        <v>995</v>
+      </c>
+      <c r="H186" t="s">
+        <v>996</v>
+      </c>
+      <c r="I186" t="s">
+        <v>997</v>
+      </c>
+      <c r="K186" t="s">
+        <v>74</v>
+      </c>
+      <c r="L186" t="s">
+        <v>998</v>
+      </c>
+      <c r="M186" t="s">
+        <v>124</v>
+      </c>
+      <c r="N186" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+        <v>e98b078b-fa45-6243-4f9b-b63d307f45ae</v>
+      </c>
+      <c r="B187" t="s">
+        <v>111</v>
+      </c>
+      <c r="C187" t="s">
+        <v>112</v>
+      </c>
+      <c r="D187" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E187" t="s">
+        <v>119</v>
+      </c>
+      <c r="F187" t="s">
+        <v>312</v>
+      </c>
+      <c r="G187" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I187" t="s">
+        <v>1002</v>
+      </c>
+      <c r="K187" t="s">
+        <v>312</v>
+      </c>
+      <c r="L187" t="s">
+        <v>1003</v>
+      </c>
+      <c r="M187" t="s">
+        <v>124</v>
+      </c>
+      <c r="N187" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+        <v>3f527c8b-613c-d475-df1d-81b5858fd049</v>
+      </c>
+      <c r="B188" t="s">
+        <v>111</v>
+      </c>
+      <c r="C188" t="s">
+        <v>112</v>
+      </c>
+      <c r="D188" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E188" t="s">
+        <v>100</v>
+      </c>
+      <c r="F188" t="s">
+        <v>61</v>
+      </c>
+      <c r="G188" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I188" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K188" t="s">
+        <v>74</v>
+      </c>
+      <c r="L188" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M188" t="s">
+        <v>54</v>
+      </c>
+      <c r="N188" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A189" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A190" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A191" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A192" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
@@ -21702,10 +22386,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D278749-E664-410F-B0C8-B3414EA49D59}">
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -21749,36 +22433,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>804</v>
+        <v>927</v>
       </c>
       <c r="B2" t="s">
-        <v>510</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>806</v>
+        <v>433</v>
       </c>
       <c r="E2" t="s">
-        <v>807</v>
+        <v>100</v>
       </c>
       <c r="F2" t="s">
-        <v>342</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
-        <v>510</v>
+        <v>928</v>
+      </c>
+      <c r="H2" t="s">
+        <v>929</v>
       </c>
       <c r="I2" t="s">
-        <v>808</v>
+        <v>930</v>
       </c>
       <c r="K2" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L2" t="s">
-        <v>809</v>
+        <v>931</v>
       </c>
       <c r="M2" t="s">
         <v>54</v>
@@ -21787,74 +22474,80 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>810</v>
+        <v>932</v>
       </c>
       <c r="B3" t="s">
-        <v>811</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>806</v>
+        <v>433</v>
       </c>
       <c r="E3" t="s">
-        <v>807</v>
+        <v>106</v>
       </c>
       <c r="F3" t="s">
-        <v>342</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
-        <v>811</v>
+        <v>933</v>
+      </c>
+      <c r="H3" t="s">
+        <v>934</v>
       </c>
       <c r="I3" t="s">
-        <v>812</v>
+        <v>935</v>
+      </c>
+      <c r="J3" t="s">
+        <v>52</v>
       </c>
       <c r="K3" t="s">
-        <v>52</v>
+        <v>936</v>
       </c>
       <c r="L3" t="s">
-        <v>813</v>
-      </c>
-      <c r="M3" t="s">
-        <v>54</v>
-      </c>
-      <c r="N3" t="b">
+        <v>197</v>
+      </c>
+      <c r="M3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>814</v>
+        <v>937</v>
       </c>
       <c r="B4" t="s">
-        <v>815</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>806</v>
+        <v>938</v>
       </c>
       <c r="E4" t="s">
-        <v>807</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>342</v>
+        <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>815</v>
+        <v>939</v>
+      </c>
+      <c r="H4" t="s">
+        <v>940</v>
       </c>
       <c r="I4" t="s">
-        <v>816</v>
+        <v>941</v>
       </c>
       <c r="K4" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L4" t="s">
-        <v>817</v>
+        <v>942</v>
       </c>
       <c r="M4" t="s">
         <v>54</v>
@@ -21863,36 +22556,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>818</v>
+        <v>943</v>
       </c>
       <c r="B5" t="s">
-        <v>819</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>806</v>
+        <v>944</v>
       </c>
       <c r="E5" t="s">
-        <v>807</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>342</v>
+        <v>61</v>
       </c>
       <c r="G5" t="s">
-        <v>819</v>
+        <v>945</v>
+      </c>
+      <c r="H5" t="s">
+        <v>946</v>
       </c>
       <c r="I5" t="s">
-        <v>820</v>
+        <v>930</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L5" t="s">
-        <v>821</v>
+        <v>947</v>
       </c>
       <c r="M5" t="s">
         <v>54</v>
@@ -21901,188 +22597,221 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>822</v>
+        <v>948</v>
       </c>
       <c r="B6" t="s">
-        <v>823</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>806</v>
+        <v>949</v>
       </c>
       <c r="E6" t="s">
-        <v>807</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>342</v>
+        <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>823</v>
+        <v>950</v>
+      </c>
+      <c r="H6" t="s">
+        <v>951</v>
       </c>
       <c r="I6" t="s">
-        <v>824</v>
+        <v>952</v>
       </c>
       <c r="K6" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L6" t="s">
-        <v>825</v>
+        <v>953</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>826</v>
+        <v>954</v>
       </c>
       <c r="B7" t="s">
-        <v>827</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>806</v>
+        <v>955</v>
       </c>
       <c r="E7" t="s">
-        <v>807</v>
+        <v>100</v>
       </c>
       <c r="F7" t="s">
-        <v>342</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>827</v>
+        <v>956</v>
+      </c>
+      <c r="H7" t="s">
+        <v>957</v>
       </c>
       <c r="I7" t="s">
-        <v>828</v>
+        <v>958</v>
+      </c>
+      <c r="J7" t="s">
+        <v>52</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>959</v>
       </c>
       <c r="L7" t="s">
-        <v>829</v>
-      </c>
-      <c r="M7" t="s">
         <v>54</v>
       </c>
-      <c r="N7" t="b">
+      <c r="M7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>830</v>
+        <v>960</v>
       </c>
       <c r="B8" t="s">
-        <v>831</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>806</v>
+        <v>961</v>
       </c>
       <c r="E8" t="s">
-        <v>807</v>
+        <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>342</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>831</v>
+        <v>962</v>
       </c>
       <c r="I8" t="s">
-        <v>832</v>
+        <v>963</v>
+      </c>
+      <c r="J8" t="s">
+        <v>964</v>
       </c>
       <c r="K8" t="s">
         <v>52</v>
       </c>
       <c r="L8" t="s">
-        <v>833</v>
+        <v>965</v>
       </c>
       <c r="M8" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" t="s">
+        <v>60</v>
+      </c>
+      <c r="P8" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8" t="s">
+        <v>963</v>
+      </c>
+      <c r="T8" t="s">
+        <v>64</v>
+      </c>
+      <c r="U8" t="s">
+        <v>47</v>
+      </c>
+      <c r="W8" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>834</v>
+        <v>966</v>
       </c>
       <c r="B9" t="s">
-        <v>835</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>806</v>
+        <v>635</v>
       </c>
       <c r="E9" t="s">
-        <v>807</v>
+        <v>119</v>
       </c>
       <c r="F9" t="s">
-        <v>342</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s">
-        <v>835</v>
+        <v>967</v>
+      </c>
+      <c r="H9" t="s">
+        <v>968</v>
       </c>
       <c r="I9" t="s">
-        <v>836</v>
+        <v>969</v>
       </c>
       <c r="K9" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
-        <v>837</v>
+        <v>970</v>
       </c>
       <c r="M9" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>838</v>
+        <v>971</v>
       </c>
       <c r="B10" t="s">
-        <v>839</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>806</v>
+        <v>972</v>
       </c>
       <c r="E10" t="s">
-        <v>807</v>
+        <v>344</v>
       </c>
       <c r="F10" t="s">
-        <v>342</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>839</v>
+        <v>973</v>
+      </c>
+      <c r="H10" t="s">
+        <v>974</v>
       </c>
       <c r="I10" t="s">
-        <v>840</v>
+        <v>975</v>
       </c>
       <c r="K10" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L10" t="s">
-        <v>841</v>
+        <v>976</v>
       </c>
       <c r="M10" t="s">
         <v>54</v>
@@ -22091,1182 +22820,246 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>842</v>
+        <v>977</v>
       </c>
       <c r="B11" t="s">
-        <v>843</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>806</v>
+        <v>972</v>
       </c>
       <c r="E11" t="s">
-        <v>807</v>
+        <v>344</v>
       </c>
       <c r="F11" t="s">
-        <v>342</v>
+        <v>47</v>
       </c>
       <c r="G11" t="s">
-        <v>843</v>
+        <v>978</v>
+      </c>
+      <c r="H11" t="s">
+        <v>979</v>
       </c>
       <c r="I11" t="s">
-        <v>844</v>
+        <v>980</v>
+      </c>
+      <c r="J11" t="s">
+        <v>52</v>
       </c>
       <c r="K11" t="s">
-        <v>52</v>
+        <v>981</v>
       </c>
       <c r="L11" t="s">
-        <v>845</v>
-      </c>
-      <c r="M11" t="s">
-        <v>54</v>
-      </c>
-      <c r="N11" t="b">
+        <v>197</v>
+      </c>
+      <c r="M11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>846</v>
+        <v>982</v>
       </c>
       <c r="B12" t="s">
-        <v>847</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>806</v>
+        <v>618</v>
       </c>
       <c r="E12" t="s">
-        <v>807</v>
+        <v>119</v>
       </c>
       <c r="F12" t="s">
-        <v>342</v>
+        <v>95</v>
       </c>
       <c r="G12" t="s">
-        <v>847</v>
+        <v>983</v>
+      </c>
+      <c r="H12" t="s">
+        <v>984</v>
       </c>
       <c r="I12" t="s">
-        <v>848</v>
+        <v>985</v>
       </c>
       <c r="K12" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L12" t="s">
-        <v>849</v>
+        <v>986</v>
       </c>
       <c r="M12" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>850</v>
+        <v>987</v>
       </c>
       <c r="B13" t="s">
-        <v>851</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>806</v>
+        <v>988</v>
       </c>
       <c r="E13" t="s">
-        <v>807</v>
+        <v>989</v>
       </c>
       <c r="F13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G13" t="s">
-        <v>851</v>
-      </c>
-      <c r="I13" t="s">
-        <v>852</v>
+        <v>990</v>
+      </c>
+      <c r="I13">
+        <v>1638.1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>991</v>
       </c>
       <c r="K13" t="s">
         <v>52</v>
       </c>
       <c r="L13" t="s">
-        <v>853</v>
+        <v>992</v>
       </c>
       <c r="M13" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>854</v>
+        <v>993</v>
       </c>
       <c r="B14" t="s">
-        <v>855</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D14" t="s">
-        <v>806</v>
+        <v>994</v>
       </c>
       <c r="E14" t="s">
-        <v>807</v>
+        <v>106</v>
       </c>
       <c r="F14" t="s">
-        <v>342</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>855</v>
+        <v>995</v>
+      </c>
+      <c r="H14" t="s">
+        <v>996</v>
       </c>
       <c r="I14" t="s">
-        <v>856</v>
+        <v>997</v>
       </c>
       <c r="K14" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L14" t="s">
-        <v>857</v>
+        <v>998</v>
       </c>
       <c r="M14" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>858</v>
+        <v>999</v>
       </c>
       <c r="B15" t="s">
-        <v>859</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>806</v>
+        <v>1000</v>
       </c>
       <c r="E15" t="s">
-        <v>807</v>
+        <v>119</v>
       </c>
       <c r="F15" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="G15" t="s">
-        <v>859</v>
+        <v>1001</v>
       </c>
       <c r="I15" t="s">
-        <v>860</v>
+        <v>1002</v>
       </c>
       <c r="K15" t="s">
-        <v>52</v>
+        <v>312</v>
       </c>
       <c r="L15" t="s">
-        <v>861</v>
+        <v>1003</v>
       </c>
       <c r="M15" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>862</v>
+        <v>1004</v>
       </c>
       <c r="B16" t="s">
-        <v>863</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>805</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>806</v>
+        <v>1005</v>
       </c>
       <c r="E16" t="s">
-        <v>807</v>
+        <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>342</v>
+        <v>61</v>
       </c>
       <c r="G16" t="s">
-        <v>863</v>
-      </c>
-      <c r="H16" s="2"/>
+        <v>1006</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>1007</v>
+      </c>
       <c r="I16" t="s">
-        <v>864</v>
+        <v>1008</v>
       </c>
       <c r="K16" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L16" t="s">
-        <v>865</v>
+        <v>1009</v>
       </c>
       <c r="M16" t="s">
         <v>54</v>
       </c>
       <c r="N16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>866</v>
-      </c>
-      <c r="B17" t="s">
-        <v>867</v>
-      </c>
-      <c r="C17" t="s">
-        <v>805</v>
-      </c>
-      <c r="D17" t="s">
-        <v>806</v>
-      </c>
-      <c r="E17" t="s">
-        <v>807</v>
-      </c>
-      <c r="F17" t="s">
-        <v>342</v>
-      </c>
-      <c r="G17" t="s">
-        <v>867</v>
-      </c>
-      <c r="I17" t="s">
-        <v>868</v>
-      </c>
-      <c r="K17" t="s">
-        <v>52</v>
-      </c>
-      <c r="L17" t="s">
-        <v>869</v>
-      </c>
-      <c r="M17" t="s">
-        <v>54</v>
-      </c>
-      <c r="N17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>870</v>
-      </c>
-      <c r="B18" t="s">
-        <v>871</v>
-      </c>
-      <c r="C18" t="s">
-        <v>805</v>
-      </c>
-      <c r="D18" t="s">
-        <v>806</v>
-      </c>
-      <c r="E18" t="s">
-        <v>807</v>
-      </c>
-      <c r="F18" t="s">
-        <v>342</v>
-      </c>
-      <c r="G18" t="s">
-        <v>871</v>
-      </c>
-      <c r="I18" t="s">
-        <v>872</v>
-      </c>
-      <c r="K18" t="s">
-        <v>52</v>
-      </c>
-      <c r="L18" t="s">
-        <v>873</v>
-      </c>
-      <c r="M18" t="s">
-        <v>54</v>
-      </c>
-      <c r="N18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>874</v>
-      </c>
-      <c r="B19" t="s">
-        <v>875</v>
-      </c>
-      <c r="C19" t="s">
-        <v>805</v>
-      </c>
-      <c r="D19" t="s">
-        <v>806</v>
-      </c>
-      <c r="E19" t="s">
-        <v>807</v>
-      </c>
-      <c r="F19" t="s">
-        <v>342</v>
-      </c>
-      <c r="G19" t="s">
-        <v>875</v>
-      </c>
-      <c r="I19" t="s">
-        <v>876</v>
-      </c>
-      <c r="K19" t="s">
-        <v>52</v>
-      </c>
-      <c r="L19" t="s">
-        <v>877</v>
-      </c>
-      <c r="M19" t="s">
-        <v>54</v>
-      </c>
-      <c r="N19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>878</v>
-      </c>
-      <c r="B20" t="s">
-        <v>879</v>
-      </c>
-      <c r="C20" t="s">
-        <v>805</v>
-      </c>
-      <c r="D20" t="s">
-        <v>806</v>
-      </c>
-      <c r="E20" t="s">
-        <v>807</v>
-      </c>
-      <c r="F20" t="s">
-        <v>342</v>
-      </c>
-      <c r="G20" t="s">
-        <v>879</v>
-      </c>
-      <c r="I20" t="s">
-        <v>880</v>
-      </c>
-      <c r="K20" t="s">
-        <v>52</v>
-      </c>
-      <c r="L20" t="s">
-        <v>881</v>
-      </c>
-      <c r="M20" t="s">
-        <v>54</v>
-      </c>
-      <c r="N20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>882</v>
-      </c>
-      <c r="B21" t="s">
-        <v>883</v>
-      </c>
-      <c r="C21" t="s">
-        <v>805</v>
-      </c>
-      <c r="D21" t="s">
-        <v>806</v>
-      </c>
-      <c r="E21" t="s">
-        <v>807</v>
-      </c>
-      <c r="F21" t="s">
-        <v>342</v>
-      </c>
-      <c r="G21" t="s">
-        <v>883</v>
-      </c>
-      <c r="I21" t="s">
-        <v>884</v>
-      </c>
-      <c r="K21" t="s">
-        <v>52</v>
-      </c>
-      <c r="L21" t="s">
-        <v>885</v>
-      </c>
-      <c r="M21" t="s">
-        <v>54</v>
-      </c>
-      <c r="N21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>886</v>
-      </c>
-      <c r="B22" t="s">
-        <v>887</v>
-      </c>
-      <c r="C22" t="s">
-        <v>805</v>
-      </c>
-      <c r="D22" t="s">
-        <v>806</v>
-      </c>
-      <c r="E22" t="s">
-        <v>807</v>
-      </c>
-      <c r="F22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G22" t="s">
-        <v>887</v>
-      </c>
-      <c r="I22" t="s">
-        <v>888</v>
-      </c>
-      <c r="K22" t="s">
-        <v>52</v>
-      </c>
-      <c r="L22" t="s">
-        <v>889</v>
-      </c>
-      <c r="M22" t="s">
-        <v>54</v>
-      </c>
-      <c r="N22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>890</v>
-      </c>
-      <c r="B23" t="s">
-        <v>891</v>
-      </c>
-      <c r="C23" t="s">
-        <v>805</v>
-      </c>
-      <c r="D23" t="s">
-        <v>806</v>
-      </c>
-      <c r="E23" t="s">
-        <v>807</v>
-      </c>
-      <c r="F23" t="s">
-        <v>342</v>
-      </c>
-      <c r="G23" t="s">
-        <v>891</v>
-      </c>
-      <c r="I23" t="s">
-        <v>892</v>
-      </c>
-      <c r="K23" t="s">
-        <v>52</v>
-      </c>
-      <c r="L23" t="s">
-        <v>893</v>
-      </c>
-      <c r="M23" t="s">
-        <v>54</v>
-      </c>
-      <c r="N23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>894</v>
-      </c>
-      <c r="B24" t="s">
-        <v>895</v>
-      </c>
-      <c r="C24" t="s">
-        <v>805</v>
-      </c>
-      <c r="D24" t="s">
-        <v>806</v>
-      </c>
-      <c r="E24" t="s">
-        <v>807</v>
-      </c>
-      <c r="F24" t="s">
-        <v>342</v>
-      </c>
-      <c r="G24" t="s">
-        <v>895</v>
-      </c>
-      <c r="I24" t="s">
-        <v>896</v>
-      </c>
-      <c r="K24" t="s">
-        <v>52</v>
-      </c>
-      <c r="L24" t="s">
-        <v>897</v>
-      </c>
-      <c r="M24" t="s">
-        <v>54</v>
-      </c>
-      <c r="N24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>898</v>
-      </c>
-      <c r="B25" t="s">
-        <v>899</v>
-      </c>
-      <c r="C25" t="s">
-        <v>805</v>
-      </c>
-      <c r="D25" t="s">
-        <v>806</v>
-      </c>
-      <c r="E25" t="s">
-        <v>807</v>
-      </c>
-      <c r="F25" t="s">
-        <v>342</v>
-      </c>
-      <c r="G25" t="s">
-        <v>899</v>
-      </c>
-      <c r="I25" t="s">
-        <v>900</v>
-      </c>
-      <c r="K25" t="s">
-        <v>52</v>
-      </c>
-      <c r="L25" t="s">
-        <v>901</v>
-      </c>
-      <c r="M25" t="s">
-        <v>54</v>
-      </c>
-      <c r="N25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>902</v>
-      </c>
-      <c r="B26" t="s">
-        <v>903</v>
-      </c>
-      <c r="C26" t="s">
-        <v>805</v>
-      </c>
-      <c r="D26" t="s">
-        <v>806</v>
-      </c>
-      <c r="E26" t="s">
-        <v>807</v>
-      </c>
-      <c r="F26" t="s">
-        <v>342</v>
-      </c>
-      <c r="G26" t="s">
-        <v>903</v>
-      </c>
-      <c r="I26" t="s">
-        <v>904</v>
-      </c>
-      <c r="K26" t="s">
-        <v>52</v>
-      </c>
-      <c r="L26" t="s">
-        <v>905</v>
-      </c>
-      <c r="M26" t="s">
-        <v>54</v>
-      </c>
-      <c r="N26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>906</v>
-      </c>
-      <c r="B27" t="s">
-        <v>907</v>
-      </c>
-      <c r="C27" t="s">
-        <v>805</v>
-      </c>
-      <c r="D27" t="s">
-        <v>806</v>
-      </c>
-      <c r="E27" t="s">
-        <v>807</v>
-      </c>
-      <c r="F27" t="s">
-        <v>342</v>
-      </c>
-      <c r="G27" t="s">
-        <v>907</v>
-      </c>
-      <c r="I27" t="s">
-        <v>908</v>
-      </c>
-      <c r="K27" t="s">
-        <v>52</v>
-      </c>
-      <c r="L27" t="s">
-        <v>909</v>
-      </c>
-      <c r="M27" t="s">
-        <v>54</v>
-      </c>
-      <c r="N27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>910</v>
-      </c>
-      <c r="B28" t="s">
-        <v>911</v>
-      </c>
-      <c r="C28" t="s">
-        <v>805</v>
-      </c>
-      <c r="D28" t="s">
-        <v>806</v>
-      </c>
-      <c r="E28" t="s">
-        <v>807</v>
-      </c>
-      <c r="F28" t="s">
-        <v>342</v>
-      </c>
-      <c r="G28" t="s">
-        <v>911</v>
-      </c>
-      <c r="I28" t="s">
-        <v>912</v>
-      </c>
-      <c r="K28" t="s">
-        <v>52</v>
-      </c>
-      <c r="L28" t="s">
-        <v>913</v>
-      </c>
-      <c r="M28" t="s">
-        <v>54</v>
-      </c>
-      <c r="N28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>914</v>
-      </c>
-      <c r="B29" t="s">
-        <v>915</v>
-      </c>
-      <c r="C29" t="s">
-        <v>805</v>
-      </c>
-      <c r="D29" t="s">
-        <v>806</v>
-      </c>
-      <c r="E29" t="s">
-        <v>807</v>
-      </c>
-      <c r="F29" t="s">
-        <v>342</v>
-      </c>
-      <c r="G29" t="s">
-        <v>915</v>
-      </c>
-      <c r="I29" t="s">
-        <v>916</v>
-      </c>
-      <c r="K29" t="s">
-        <v>52</v>
-      </c>
-      <c r="L29" t="s">
-        <v>917</v>
-      </c>
-      <c r="M29" t="s">
-        <v>54</v>
-      </c>
-      <c r="N29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>918</v>
-      </c>
-      <c r="B30" t="s">
-        <v>919</v>
-      </c>
-      <c r="C30" t="s">
-        <v>805</v>
-      </c>
-      <c r="D30" t="s">
-        <v>806</v>
-      </c>
-      <c r="E30" t="s">
-        <v>807</v>
-      </c>
-      <c r="F30" t="s">
-        <v>342</v>
-      </c>
-      <c r="G30" t="s">
-        <v>919</v>
-      </c>
-      <c r="I30" t="s">
-        <v>920</v>
-      </c>
-      <c r="K30" t="s">
-        <v>52</v>
-      </c>
-      <c r="L30" t="s">
-        <v>921</v>
-      </c>
-      <c r="M30" t="s">
-        <v>54</v>
-      </c>
-      <c r="N30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>922</v>
-      </c>
-      <c r="B31" t="s">
-        <v>923</v>
-      </c>
-      <c r="C31" t="s">
-        <v>805</v>
-      </c>
-      <c r="D31" t="s">
-        <v>806</v>
-      </c>
-      <c r="E31" t="s">
-        <v>807</v>
-      </c>
-      <c r="F31" t="s">
-        <v>342</v>
-      </c>
-      <c r="G31" t="s">
-        <v>923</v>
-      </c>
-      <c r="I31" t="s">
-        <v>924</v>
-      </c>
-      <c r="K31" t="s">
-        <v>52</v>
-      </c>
-      <c r="L31" t="s">
-        <v>925</v>
-      </c>
-      <c r="M31" t="s">
-        <v>54</v>
-      </c>
-      <c r="N31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>926</v>
-      </c>
-      <c r="B32" t="s">
-        <v>927</v>
-      </c>
-      <c r="C32" t="s">
-        <v>805</v>
-      </c>
-      <c r="D32" t="s">
-        <v>806</v>
-      </c>
-      <c r="E32" t="s">
-        <v>807</v>
-      </c>
-      <c r="F32" t="s">
-        <v>342</v>
-      </c>
-      <c r="G32" t="s">
-        <v>927</v>
-      </c>
-      <c r="I32" t="s">
-        <v>928</v>
-      </c>
-      <c r="K32" t="s">
-        <v>52</v>
-      </c>
-      <c r="L32" t="s">
-        <v>929</v>
-      </c>
-      <c r="M32" t="s">
-        <v>54</v>
-      </c>
-      <c r="N32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>930</v>
-      </c>
-      <c r="B33" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" t="s">
-        <v>805</v>
-      </c>
-      <c r="D33" t="s">
-        <v>806</v>
-      </c>
-      <c r="E33" t="s">
-        <v>807</v>
-      </c>
-      <c r="F33" t="s">
-        <v>342</v>
-      </c>
-      <c r="G33" t="s">
-        <v>111</v>
-      </c>
-      <c r="I33" t="s">
-        <v>931</v>
-      </c>
-      <c r="K33" t="s">
-        <v>52</v>
-      </c>
-      <c r="L33" t="s">
-        <v>932</v>
-      </c>
-      <c r="M33" t="s">
-        <v>54</v>
-      </c>
-      <c r="N33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>933</v>
-      </c>
-      <c r="B34" t="s">
-        <v>934</v>
-      </c>
-      <c r="C34" t="s">
-        <v>805</v>
-      </c>
-      <c r="D34" t="s">
-        <v>806</v>
-      </c>
-      <c r="E34" t="s">
-        <v>807</v>
-      </c>
-      <c r="F34" t="s">
-        <v>342</v>
-      </c>
-      <c r="G34" t="s">
-        <v>934</v>
-      </c>
-      <c r="I34" t="s">
-        <v>227</v>
-      </c>
-      <c r="K34" t="s">
-        <v>52</v>
-      </c>
-      <c r="L34" t="s">
-        <v>935</v>
-      </c>
-      <c r="M34" t="s">
-        <v>54</v>
-      </c>
-      <c r="N34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>936</v>
-      </c>
-      <c r="B35" t="s">
-        <v>937</v>
-      </c>
-      <c r="C35" t="s">
-        <v>805</v>
-      </c>
-      <c r="D35" t="s">
-        <v>806</v>
-      </c>
-      <c r="E35" t="s">
-        <v>807</v>
-      </c>
-      <c r="F35" t="s">
-        <v>342</v>
-      </c>
-      <c r="G35" t="s">
-        <v>937</v>
-      </c>
-      <c r="I35" t="s">
-        <v>938</v>
-      </c>
-      <c r="K35" t="s">
-        <v>52</v>
-      </c>
-      <c r="L35" t="s">
-        <v>939</v>
-      </c>
-      <c r="M35" t="s">
-        <v>54</v>
-      </c>
-      <c r="N35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>940</v>
-      </c>
-      <c r="B36" t="s">
-        <v>941</v>
-      </c>
-      <c r="C36" t="s">
-        <v>805</v>
-      </c>
-      <c r="D36" t="s">
-        <v>806</v>
-      </c>
-      <c r="E36" t="s">
-        <v>807</v>
-      </c>
-      <c r="F36" t="s">
-        <v>342</v>
-      </c>
-      <c r="G36" t="s">
-        <v>941</v>
-      </c>
-      <c r="I36" t="s">
-        <v>942</v>
-      </c>
-      <c r="K36" t="s">
-        <v>52</v>
-      </c>
-      <c r="L36" t="s">
-        <v>943</v>
-      </c>
-      <c r="M36" t="s">
-        <v>54</v>
-      </c>
-      <c r="N36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>944</v>
-      </c>
-      <c r="B37" t="s">
-        <v>945</v>
-      </c>
-      <c r="C37" t="s">
-        <v>805</v>
-      </c>
-      <c r="D37" t="s">
-        <v>806</v>
-      </c>
-      <c r="E37" t="s">
-        <v>807</v>
-      </c>
-      <c r="F37" t="s">
-        <v>342</v>
-      </c>
-      <c r="G37" t="s">
-        <v>945</v>
-      </c>
-      <c r="I37" t="s">
-        <v>946</v>
-      </c>
-      <c r="K37" t="s">
-        <v>52</v>
-      </c>
-      <c r="L37" t="s">
-        <v>947</v>
-      </c>
-      <c r="M37" t="s">
-        <v>54</v>
-      </c>
-      <c r="N37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>948</v>
-      </c>
-      <c r="B38" t="s">
-        <v>949</v>
-      </c>
-      <c r="C38" t="s">
-        <v>950</v>
-      </c>
-      <c r="D38" t="s">
-        <v>806</v>
-      </c>
-      <c r="E38" t="s">
-        <v>807</v>
-      </c>
-      <c r="F38" t="s">
-        <v>342</v>
-      </c>
-      <c r="G38" t="s">
-        <v>949</v>
-      </c>
-      <c r="I38" t="s">
-        <v>951</v>
-      </c>
-      <c r="K38" t="s">
-        <v>52</v>
-      </c>
-      <c r="L38" t="s">
-        <v>952</v>
-      </c>
-      <c r="M38" t="s">
-        <v>54</v>
-      </c>
-      <c r="N38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>953</v>
-      </c>
-      <c r="B39" t="s">
-        <v>954</v>
-      </c>
-      <c r="C39" t="s">
-        <v>950</v>
-      </c>
-      <c r="D39" t="s">
-        <v>806</v>
-      </c>
-      <c r="E39" t="s">
-        <v>807</v>
-      </c>
-      <c r="F39" t="s">
-        <v>342</v>
-      </c>
-      <c r="G39" t="s">
-        <v>954</v>
-      </c>
-      <c r="I39" t="s">
-        <v>955</v>
-      </c>
-      <c r="K39" t="s">
-        <v>52</v>
-      </c>
-      <c r="L39" t="s">
-        <v>956</v>
-      </c>
-      <c r="M39" t="s">
-        <v>54</v>
-      </c>
-      <c r="N39" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>957</v>
-      </c>
-      <c r="B40" t="s">
-        <v>958</v>
-      </c>
-      <c r="C40" t="s">
-        <v>959</v>
-      </c>
-      <c r="D40" t="s">
-        <v>806</v>
-      </c>
-      <c r="E40" t="s">
-        <v>807</v>
-      </c>
-      <c r="F40" t="s">
-        <v>342</v>
-      </c>
-      <c r="G40" t="s">
-        <v>958</v>
-      </c>
-      <c r="I40" t="s">
-        <v>960</v>
-      </c>
-      <c r="K40" t="s">
-        <v>52</v>
-      </c>
-      <c r="L40" t="s">
-        <v>961</v>
-      </c>
-      <c r="M40" t="s">
-        <v>54</v>
-      </c>
-      <c r="N40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>962</v>
-      </c>
-      <c r="B41" t="s">
-        <v>963</v>
-      </c>
-      <c r="C41" t="s">
-        <v>959</v>
-      </c>
-      <c r="D41" t="s">
-        <v>806</v>
-      </c>
-      <c r="E41" t="s">
-        <v>807</v>
-      </c>
-      <c r="F41" t="s">
-        <v>342</v>
-      </c>
-      <c r="G41" t="s">
-        <v>963</v>
-      </c>
-      <c r="I41" t="s">
-        <v>964</v>
-      </c>
-      <c r="K41" t="s">
-        <v>52</v>
-      </c>
-      <c r="L41" t="s">
-        <v>965</v>
-      </c>
-      <c r="M41" t="s">
-        <v>54</v>
-      </c>
-      <c r="N41" t="b">
         <v>1</v>
       </c>
     </row>

--- a/templates/questions-template.xlsx
+++ b/templates/questions-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frcltd-my.sharepoint.com/personal/r_marks_frc_org_uk/Documents/Desktop/sbr/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="11_E9F32361FE4863DD78B1E2FB72030FF8208E8B85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F227E38-6A2E-40B3-B026-8FBDF27A4A0B}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="11_E9F32361FE4863DD78B1E2FB72030FF8208E8B85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1443B30-0358-475D-AAF6-2F98BE6AB3CA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3848" uniqueCount="1010">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3584" uniqueCount="969">
   <si>
     <t>id</t>
   </si>
@@ -2818,24 +2818,9 @@
     <t>Standard matcher</t>
   </si>
   <si>
-    <t>ifrs15-advance-payment-contract-liability</t>
-  </si>
-  <si>
-    <t>A customer pays in advance but control transfers two years later. The cash received should initially be recognised as a ____.</t>
-  </si>
-  <si>
-    <t>revenue|contract liability|trade receivable|refund liability</t>
-  </si>
-  <si>
     <t>contract liability</t>
   </si>
   <si>
-    <t>This tops up the existing five-step question by testing the **timing consequence**: advance cash is not revenue until control transfers; it is initially a contract liability.</t>
-  </si>
-  <si>
-    <t>ifrs15-significant-financing-component-rate</t>
-  </si>
-  <si>
     <t>For a significant financing component, what rate should be used to adjust the promised consideration?</t>
   </si>
   <si>
@@ -2848,9 +2833,6 @@
     <t>This captures the Calibra nuance: the discounting rate should reflect the **credit characteristics of the party receiving financing**, not simply a convenient market rate.</t>
   </si>
   <si>
-    <t>ifrs15-control-transfer-completion</t>
-  </si>
-  <si>
     <t>Transfer of control</t>
   </si>
   <si>
@@ -2866,9 +2848,6 @@
     <t>This avoids premature revenue recognition: if title, possession and control transfer only on completion, revenue is recognised **at that point**, even if cash was received earlier.</t>
   </si>
   <si>
-    <t>ifrs15-gift-card-initial-treatment</t>
-  </si>
-  <si>
     <t>Gift cards</t>
   </si>
   <si>
@@ -2881,9 +2860,6 @@
     <t>This adds a high-frequency retail scenario: gift cards are **prepayments**, so revenue waits until goods/services are transferred or breakage is recognised.</t>
   </si>
   <si>
-    <t>ifrs15-breakage-pattern</t>
-  </si>
-  <si>
     <t>Breakage</t>
   </si>
   <si>
@@ -2899,9 +2875,6 @@
     <t>This tests the nuance beyond gift-card liability: reliable expected breakage is recognised **in proportion to rights exercised**, not automatically upfront.</t>
   </si>
   <si>
-    <t>ifrs15-usage-royalty-trigger</t>
-  </si>
-  <si>
     <t>Royalties</t>
   </si>
   <si>
@@ -2917,9 +2890,6 @@
     <t>This targets Kiki’s royalty point: usage-based royalties are recognised **as usage occurs**, assuming contract criteria remain met.</t>
   </si>
   <si>
-    <t>ifrs15-collectability-reassessment</t>
-  </si>
-  <si>
     <t>Contract criteria</t>
   </si>
   <si>
@@ -2935,9 +2905,6 @@
     <t>This adds the important exam nuance that collectability is not continuously re-tested without reason; reassess contract criteria only after a **significant change in facts and circumstances**.</t>
   </si>
   <si>
-    <t>ifrs15-consignment-indicators</t>
-  </si>
-  <si>
     <t>Which indicators suggest a consignment arrangement where the manufacturer retains control?</t>
   </si>
   <si>
@@ -2950,9 +2917,6 @@
     <t>This tests the consignment indicators efficiently: control has not passed if the supplier still controls the product, can require return/transfer, and the dealer lacks an **unconditional payment obligation**.</t>
   </si>
   <si>
-    <t>ifrs15-right-of-return-liability</t>
-  </si>
-  <si>
     <t>Right of return</t>
   </si>
   <si>
@@ -2968,9 +2932,6 @@
     <t>This adds the right-of-return structure: expected returns are excluded from revenue and create a **refund liability**.</t>
   </si>
   <si>
-    <t>ifrs15-right-of-return-asset</t>
-  </si>
-  <si>
     <t>What asset is recognised for the seller’s right to recover inventory expected to be returned?</t>
   </si>
   <si>
@@ -2981,97 +2942,13 @@
   </si>
   <si>
     <t>This tests the often-missed second side of return accounting: recognise a **right-of-return asset** for inventory expected back, subject to recoverability.</t>
-  </si>
-  <si>
-    <t>ifrs15-upfront-fee-admin-task</t>
-  </si>
-  <si>
-    <t>A joining fee only covers setting up an account and issuing a card. What is the key IFRS 15 conclusion?</t>
-  </si>
-  <si>
-    <t>It is always immediate revenue|It is a separate performance obligation|It is an administrative task and not a performance obligation|It is a financial liability</t>
-  </si>
-  <si>
-    <t>It is an administrative task and not a performance obligation</t>
-  </si>
-  <si>
-    <t>This is a high-yield nuance: administrative setup does **not transfer a good or service**, so the fee is usually deferred and recognised as access is provided.</t>
-  </si>
-  <si>
-    <t>ifrs15-allocate-relative-ssp</t>
-  </si>
-  <si>
-    <t>Transaction price allocation</t>
-  </si>
-  <si>
-    <t>Calculation</t>
-  </si>
-  <si>
-    <t>A bundle sells for $2,000. Relative standalone selling prices total $2,100. The computer SSP is $1,720. What revenue is allocated to the computer?</t>
-  </si>
-  <si>
-    <t>$1,638.1|1638|1,638|1638.10|$1,638.10</t>
-  </si>
-  <si>
-    <t>This turns Cial into a quick calculation: allocate transaction price using **relative standalone selling prices**: $1,720 / $2,100 × $2,000 = $1,638.1.</t>
-  </si>
-  <si>
-    <t>ifrs15-estimating-ssp-methods</t>
-  </si>
-  <si>
-    <t>Standalone selling price</t>
-  </si>
-  <si>
-    <t>Which methods can help estimate standalone selling price when it is not directly observable?</t>
-  </si>
-  <si>
-    <t>Adjusted market assessment approach|Expected cost plus margin approach|Residual approach where appropriate|Historical cost model|Expected credit loss model</t>
-  </si>
-  <si>
-    <t>Adjusted market assessment approach|Expected cost plus margin approach|Residual approach where appropriate</t>
-  </si>
-  <si>
-    <t>This captures Cial’s estimation nuance: where SSP is not observable, IFRS 15 allows estimation methods such as **adjusted market assessment**, **expected cost plus margin**, and sometimes **residual**.</t>
-  </si>
-  <si>
-    <t>ifrs15-software-updates-single-po</t>
-  </si>
-  <si>
-    <t>Software licences and updates</t>
-  </si>
-  <si>
-    <t>Explain to yourself when a software licence and updates may be a single performance obligation, then reveal the answer.</t>
-  </si>
-  <si>
-    <t>They may be a single performance obligation when the updates are integral or essential to the customer obtaining the intended benefit from the licence, so the promise is a combined service recognised over time.</t>
-  </si>
-  <si>
-    <t>This tops up Sitka’s judgment issue: do not mechanically split licence and updates; assess whether the updates are **separately identifiable** or part of one combined promise.</t>
-  </si>
-  <si>
-    <t>ifrs15-over-time-service-contract</t>
-  </si>
-  <si>
-    <t>Timing of recognition</t>
-  </si>
-  <si>
-    <t>If the customer simultaneously receives and consumes the benefits as the entity performs, the performance obligation is satisfied ____.</t>
-  </si>
-  <si>
-    <t>at contract inception|over time|only on invoice|only when cash is received</t>
-  </si>
-  <si>
-    <t>over time</t>
-  </si>
-  <si>
-    <t>This reinforces the key timing distinction behind the software/update scenario: simultaneous receipt and consumption points to **over-time** recognition.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3202,6 +3079,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3548,10 +3432,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3931,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR1169"/>
+  <dimension ref="A1:AR188"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.5546875" bestFit="1" customWidth="1"/>
@@ -4117,7 +4002,7 @@
     <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f ca="1">IF(G2&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>406b0f5a-d4bc-e3f4-c949-15549277a84b</v>
+        <v>042bbda0-1a8a-3866-bcbb-85172ea65dc4</v>
       </c>
       <c r="B2" t="s">
         <v>336</v>
@@ -4252,7 +4137,7 @@
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
         <f t="shared" ref="A3:A66" ca="1" si="0">IF(G3&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>68b78703-8ed8-70d4-a4d0-18876a171734</v>
+        <v>b16c6690-a07e-4dee-b3cd-9045bcb3946a</v>
       </c>
       <c r="B3" t="s">
         <v>336</v>
@@ -4387,7 +4272,7 @@
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>47400359-5477-aa5e-42ab-6eca48e371f1</v>
+        <v>e2151e68-47cf-6367-2662-122ed87520eb</v>
       </c>
       <c r="B4" t="s">
         <v>336</v>
@@ -4522,7 +4407,7 @@
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>0e108d57-3974-58b1-eabd-249f34ab8658</v>
+        <v>8fc1b16a-5a19-0183-1c95-058733b6a518</v>
       </c>
       <c r="B5" t="s">
         <v>336</v>
@@ -4657,7 +4542,7 @@
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>3ea29330-f606-441d-b9e1-2e654f4786c8</v>
+        <v>b6caae70-8940-7527-a521-dfefb2acfe46</v>
       </c>
       <c r="B6" t="s">
         <v>336</v>
@@ -4792,7 +4677,7 @@
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>e0325b7d-a70e-994c-9506-63620c25b0dd</v>
+        <v>939a39a8-4477-5ede-97ce-398cb991c74f</v>
       </c>
       <c r="B7" t="s">
         <v>336</v>
@@ -4927,7 +4812,7 @@
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>b20f70da-eb13-9e26-7529-d88b40a83631</v>
+        <v>a6bea27c-6c0f-1f57-7858-77048ec06c4e</v>
       </c>
       <c r="B8" t="s">
         <v>336</v>
@@ -5062,7 +4947,7 @@
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>bcdbbf99-c68d-7878-a92f-1d6a30422370</v>
+        <v>44c190d3-18ce-43ef-7f30-6bc9153d2f90</v>
       </c>
       <c r="B9" t="s">
         <v>336</v>
@@ -5197,7 +5082,7 @@
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>f50771af-10c8-94fa-e5a9-612e4b92ca21</v>
+        <v>da813287-2e6b-4682-e383-369511e2b940</v>
       </c>
       <c r="B10" t="s">
         <v>336</v>
@@ -5332,7 +5217,7 @@
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>25aa9330-4105-4d28-7bf7-7890151c2df4</v>
+        <v>3226c3c9-b3bd-992e-8e8a-b52ec7c5e7a9</v>
       </c>
       <c r="B11" t="s">
         <v>336</v>
@@ -5467,7 +5352,7 @@
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>55c86b7e-f947-986c-39d3-595ab97b0441</v>
+        <v>1b322049-30b0-61cd-4b78-45609cf6ac34</v>
       </c>
       <c r="B12" t="s">
         <v>336</v>
@@ -5602,7 +5487,7 @@
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a47f8705-2893-0dd0-7661-8f4f93fd867a</v>
+        <v>4407906e-533d-2a68-2a4e-8f7c7c1b8683</v>
       </c>
       <c r="B13" t="s">
         <v>336</v>
@@ -5737,7 +5622,7 @@
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>47909e90-5f45-037a-6edb-be03b8fe45c8</v>
+        <v>aeb0d49a-a609-7381-dfea-37a1a8c77247</v>
       </c>
       <c r="B14" t="s">
         <v>336</v>
@@ -5872,7 +5757,7 @@
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>fca212f3-7038-dda3-8aa7-d70da6d079b5</v>
+        <v>9e8e52e1-5065-518a-8bae-b79405cc5120</v>
       </c>
       <c r="B15" t="s">
         <v>336</v>
@@ -6007,7 +5892,7 @@
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>75e6df73-199e-d949-b53e-d3d84056fcf6</v>
+        <v>52847ea7-3c94-2c3b-e232-7d457d8827dd</v>
       </c>
       <c r="B16" t="s">
         <v>336</v>
@@ -6142,7 +6027,7 @@
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>853f731c-e19d-aeff-5c4f-498d9e9c8a51</v>
+        <v>6fd17891-811c-9ba3-9005-1e0d3adfbf28</v>
       </c>
       <c r="B17" t="s">
         <v>336</v>
@@ -6277,7 +6162,7 @@
     <row r="18" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>5620cd2b-5b09-d6db-1ca4-16152d875f7f</v>
+        <v>f4c01e85-13ee-2c02-ff5a-82ffae60a1d5</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
@@ -6412,7 +6297,7 @@
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>c2512300-a45b-860f-39a5-7a450010263f</v>
+        <v>a182bc2e-4cd8-b648-44c5-3ff72ff67c24</v>
       </c>
       <c r="B19" t="s">
         <v>336</v>
@@ -6547,7 +6432,7 @@
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>d8eadc15-a5d5-0289-74c9-cc366db79af7</v>
+        <v>f21da402-9bed-d2f6-4704-777424e1e96b</v>
       </c>
       <c r="B20" t="s">
         <v>336</v>
@@ -6682,7 +6567,7 @@
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a3688bfc-849f-fb44-f670-10ba3a7225c6</v>
+        <v>97a12639-c865-eb04-19fa-d63a87eb709a</v>
       </c>
       <c r="B21" t="s">
         <v>336</v>
@@ -6817,7 +6702,7 @@
     <row r="22" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>d59a7aba-0505-aa0b-8afe-845422f3e760</v>
+        <v>6c27b91e-9980-91a4-4e23-baa2bd936b50</v>
       </c>
       <c r="B22" t="s">
         <v>336</v>
@@ -6952,7 +6837,7 @@
     <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>9b8ec626-7ec7-cfa4-8566-e33bb0370f07</v>
+        <v>2b0e8352-6361-df5e-016f-e2bb93a6118d</v>
       </c>
       <c r="B23" t="s">
         <v>336</v>
@@ -7087,7 +6972,7 @@
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>78ecad80-eeed-0e15-44bd-241696d6c0ef</v>
+        <v>cd1833ba-c3d3-d1f5-a631-4afb85cfa8d7</v>
       </c>
       <c r="B24" t="s">
         <v>336</v>
@@ -7222,7 +7107,7 @@
     <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>3d0c2200-869c-abb9-5557-479ff3a89555</v>
+        <v>e6916029-cdb5-cd59-4b20-390aa2a87f93</v>
       </c>
       <c r="B25" t="s">
         <v>336</v>
@@ -7357,7 +7242,7 @@
     <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>4510e5eb-ff31-4032-33a7-729ae90da120</v>
+        <v>83e8b48d-db63-bb69-c234-a227b8a96fa0</v>
       </c>
       <c r="B26" t="s">
         <v>336</v>
@@ -7492,7 +7377,7 @@
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2472fed3-9ce4-2d27-c073-ec9c339ddbdc</v>
+        <v>43c80bde-02f9-9b0e-edbe-ec6b5e1c915b</v>
       </c>
       <c r="B27" t="s">
         <v>336</v>
@@ -7627,7 +7512,7 @@
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>cbe7eacd-28ec-5014-913f-3bdf22fa6319</v>
+        <v>a2e3a295-eec6-720b-b0eb-8cfee6bb4b28</v>
       </c>
       <c r="B28" t="s">
         <v>336</v>
@@ -7762,7 +7647,7 @@
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>18e7050c-3d05-a922-12e4-c0cd362e8c55</v>
+        <v>780e8608-f968-6000-02d3-7d1d87481560</v>
       </c>
       <c r="B29" t="s">
         <v>336</v>
@@ -7897,7 +7782,7 @@
     <row r="30" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>eb0a863a-ca14-67fa-c22e-8534406e0e88</v>
+        <v>f830a610-9454-fe2c-901f-11709b539b8c</v>
       </c>
       <c r="B30" t="s">
         <v>336</v>
@@ -8032,7 +7917,7 @@
     <row r="31" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>3b1ae48b-0a42-d1db-7189-d38e176c0a0a</v>
+        <v>317c814e-b77f-bbe1-0f2d-e455545e2a9f</v>
       </c>
       <c r="B31" t="s">
         <v>336</v>
@@ -8167,7 +8052,7 @@
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>98eb9749-ab0d-51b4-f669-2a1c94a1b2bb</v>
+        <v>2ef5ecb0-30af-1685-9168-edfba36923d8</v>
       </c>
       <c r="B32" t="s">
         <v>336</v>
@@ -8302,7 +8187,7 @@
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>52671820-ffef-6146-15f1-fba89c193bf8</v>
+        <v>c37d4681-8483-0fd3-26b0-4fe3f75ee4bc</v>
       </c>
       <c r="B33" t="s">
         <v>336</v>
@@ -8437,7 +8322,7 @@
     <row r="34" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>b99a2dad-74a8-95a3-571a-2e79b501831d</v>
+        <v>7a7ecc3a-0b82-2256-33e7-a35128a6e1a2</v>
       </c>
       <c r="B34" t="s">
         <v>336</v>
@@ -8572,7 +8457,7 @@
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>d04b7cad-f5ba-a305-1a4b-6347f840e70d</v>
+        <v>f11bcac8-9e48-cb26-c14f-ece2135c459a</v>
       </c>
       <c r="B35" t="s">
         <v>336</v>
@@ -8707,7 +8592,7 @@
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>064d4ed1-1c64-11b8-7696-464be02ec332</v>
+        <v>242ca766-38b6-1643-1e1b-15ae54900817</v>
       </c>
       <c r="B36" t="s">
         <v>336</v>
@@ -8842,7 +8727,7 @@
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>6656d817-8e66-e805-f14e-a56592d4188d</v>
+        <v>5bbc67c3-b2dc-791b-a45d-c72d12911bb7</v>
       </c>
       <c r="B37" t="s">
         <v>336</v>
@@ -8977,7 +8862,7 @@
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>7fe147e1-bdcb-07b4-f5c5-1a8bfd2e5657</v>
+        <v>0ee0a54e-1915-d910-c59d-45948016a5b8</v>
       </c>
       <c r="B38" t="s">
         <v>336</v>
@@ -9112,7 +8997,7 @@
     <row r="39" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>bbfee1ff-e8c2-00d8-7cb6-44b9e85b9273</v>
+        <v>0e219420-ca9c-4923-d984-0950f567046a</v>
       </c>
       <c r="B39" t="s">
         <v>336</v>
@@ -9247,7 +9132,7 @@
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>11ea5b4b-dd5c-91f2-d0c4-cfa939b66c6d</v>
+        <v>57392130-639a-5f63-8e43-c588b51b54b4</v>
       </c>
       <c r="B40" t="s">
         <v>336</v>
@@ -9382,7 +9267,7 @@
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>27e7ee4f-6ea4-d194-3411-f510fd2c93cb</v>
+        <v>6bd0118b-d74d-39b5-dfe1-834c7f004d90</v>
       </c>
       <c r="B41" t="s">
         <v>336</v>
@@ -9517,7 +9402,7 @@
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>349034b1-9131-1eb7-a824-5efcc6004e1a</v>
+        <v>08461f0e-78e7-78c1-f20f-fcf01c12dadf</v>
       </c>
       <c r="B42" t="s">
         <v>336</v>
@@ -9652,7 +9537,7 @@
     <row r="43" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a02f325a-3a04-f144-77d6-1ad6b4cc9542</v>
+        <v>69d49b98-0e8e-4a91-b128-3728532855d3</v>
       </c>
       <c r="B43" t="s">
         <v>336</v>
@@ -9787,7 +9672,7 @@
     <row r="44" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>851fec32-5e7c-21bb-4fd8-b102053b17fa</v>
+        <v>69f99a22-2d98-dd91-f4b9-4bef9dbc2ea8</v>
       </c>
       <c r="B44" t="s">
         <v>336</v>
@@ -9922,7 +9807,7 @@
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>6f77a22b-160f-7c2e-fea5-31ada5e265f4</v>
+        <v>66501066-aa6d-6099-8ac0-2dd00c63174d</v>
       </c>
       <c r="B45" t="s">
         <v>336</v>
@@ -10057,7 +9942,7 @@
     <row r="46" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2d0313f6-b1e0-cc2c-64f9-26290dae2c23</v>
+        <v>02068c69-7e13-158f-fc8c-cb996e771feb</v>
       </c>
       <c r="B46" t="s">
         <v>111</v>
@@ -10153,7 +10038,7 @@
     <row r="47" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>4c856f14-e82b-fa4a-7bcb-0c8a4d633674</v>
+        <v>d8993f6b-6fc5-478a-5469-e66167a83181</v>
       </c>
       <c r="B47" t="s">
         <v>111</v>
@@ -10195,7 +10080,7 @@
     <row r="48" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>3335c3f6-242c-b03a-6dd0-57a61e64fe13</v>
+        <v>5ed721b3-06a2-4eca-6e89-f92e27ed4d7b</v>
       </c>
       <c r="B48" t="s">
         <v>111</v>
@@ -10237,7 +10122,7 @@
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>e5b4cf65-0dd4-3a66-6167-550662fd58a3</v>
+        <v>2ec40969-6cdd-bfae-7918-eb25819c8761</v>
       </c>
       <c r="B49" t="s">
         <v>111</v>
@@ -10279,7 +10164,7 @@
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>10e95df1-017b-8133-b5ef-a6748d706e3e</v>
+        <v>6617e6e0-363d-9eae-52b7-1933098e8487</v>
       </c>
       <c r="B50" t="s">
         <v>111</v>
@@ -10321,7 +10206,7 @@
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>97e0102c-8d94-2286-7e22-354e06353514</v>
+        <v>829133c6-4ada-42d6-7fa1-2e0c62023e0d</v>
       </c>
       <c r="B51" t="s">
         <v>111</v>
@@ -10363,7 +10248,7 @@
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>27188ba9-e11f-bda1-f733-9842315d0cd9</v>
+        <v>f9b268c0-d296-0283-0601-41f3db93dfc5</v>
       </c>
       <c r="B52" t="s">
         <v>111</v>
@@ -10405,7 +10290,7 @@
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>8c40e910-206b-59c7-a308-e8d403586e11</v>
+        <v>07d274ec-0798-c5f2-5672-6e6d9c5d7686</v>
       </c>
       <c r="B53" t="s">
         <v>111</v>
@@ -10465,7 +10350,7 @@
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a331574b-3eec-161a-ef78-e1754e2fbd3c</v>
+        <v>56846715-7f13-327c-4736-913e17eeb8a8</v>
       </c>
       <c r="B54" t="s">
         <v>111</v>
@@ -10507,7 +10392,7 @@
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>321979ea-b4cd-532c-30e4-1d94798783ea</v>
+        <v>cdadbd0f-381e-be71-2ede-119b30fd9872</v>
       </c>
       <c r="B55" t="s">
         <v>111</v>
@@ -10549,7 +10434,7 @@
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>b4fd407a-a534-6156-4897-e9aa6735c76b</v>
+        <v>9623777f-76dc-8da1-10af-0c00faeb3b8f</v>
       </c>
       <c r="B56" t="s">
         <v>111</v>
@@ -10591,7 +10476,7 @@
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>bb23484b-5d6c-6612-7e77-218d3b1e45b8</v>
+        <v>ab5cdf84-7dc5-7016-bae6-780b2716de8a</v>
       </c>
       <c r="B57" t="s">
         <v>111</v>
@@ -10633,7 +10518,7 @@
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>28111167-7464-a33e-8dc9-6df1476d8c01</v>
+        <v>192a8eb4-b21c-008d-ab39-3f10145bb67a</v>
       </c>
       <c r="B58" t="s">
         <v>111</v>
@@ -10675,7 +10560,7 @@
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29bf6f7a-1a0d-757f-fb59-f8d9ccf5c03a</v>
+        <v>1a9fff3c-a017-41bc-f191-8b7d17711d23</v>
       </c>
       <c r="B59" t="s">
         <v>111</v>
@@ -10717,7 +10602,7 @@
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a5f11473-7071-cb82-7a8d-be93ea49ffc2</v>
+        <v>0f39206e-7688-b946-3ae0-67da75110178</v>
       </c>
       <c r="B60" t="s">
         <v>111</v>
@@ -10759,7 +10644,7 @@
     <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>48d4df53-94f3-6c6d-7e0d-98c24fb21bff</v>
+        <v>52e13fbe-7a54-e580-1ffe-a4bf26942340</v>
       </c>
       <c r="B61" t="s">
         <v>111</v>
@@ -10819,7 +10704,7 @@
     <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>de3f00ad-f6fd-eb86-d110-e7b4180a93f9</v>
+        <v>29ce2a55-e336-8138-1162-4a901922364e</v>
       </c>
       <c r="B62" t="s">
         <v>111</v>
@@ -10861,7 +10746,7 @@
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>11f1b688-dead-1fa6-2110-07b50f4bd0d0</v>
+        <v>c30017f1-1799-6125-7d4b-9225d32e1118</v>
       </c>
       <c r="B63" t="s">
         <v>111</v>
@@ -10921,7 +10806,7 @@
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>8b498459-18fc-2cf5-61db-a252ef3ca6b3</v>
+        <v>e2e4aab4-f2fd-eecb-83b1-bf381a276d35</v>
       </c>
       <c r="B64" t="s">
         <v>111</v>
@@ -10963,7 +10848,7 @@
     <row r="65" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>395a8053-82b1-46ef-fa1a-c3dcc80dd533</v>
+        <v>69bd5c39-1d97-95d8-098b-3c772db95f98</v>
       </c>
       <c r="B65" t="s">
         <v>111</v>
@@ -11023,7 +10908,7 @@
     <row r="66" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a70de057-4dd7-8e08-1e0c-b14c6c6a9a01</v>
+        <v>bdd9dd41-dccf-0010-cb2e-dc99ef606170</v>
       </c>
       <c r="B66" t="s">
         <v>111</v>
@@ -11083,7 +10968,7 @@
     <row r="67" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
         <f t="shared" ref="A67:A130" ca="1" si="1">IF(G67&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>f8345c1d-7712-49aa-c97e-e999a8314ff3</v>
+        <v>b90668bd-4e6a-8df9-6229-a46c74f5a789</v>
       </c>
       <c r="B67" t="s">
         <v>111</v>
@@ -11125,7 +11010,7 @@
     <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>faf4116c-5040-4c6a-90fd-0a4246f747af</v>
+        <v>39b8282d-df20-88eb-e87e-bd24080396de</v>
       </c>
       <c r="B68" t="s">
         <v>111</v>
@@ -11185,7 +11070,7 @@
     <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>a3ad1320-c240-e256-053b-6038986399c5</v>
+        <v>3ed06f21-0e72-837d-289a-f271982ccb18</v>
       </c>
       <c r="B69" t="s">
         <v>111</v>
@@ -11224,7 +11109,7 @@
     <row r="70" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>de71b684-a3c9-81f1-da81-cd631a576f6b</v>
+        <v>eb747caa-e933-7158-abc4-d4c1602dcb26</v>
       </c>
       <c r="B70" t="s">
         <v>111</v>
@@ -11263,7 +11148,7 @@
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>be58435b-768e-cfab-c703-b6d95f3ee44b</v>
+        <v>7ed8040f-555e-2796-5e47-f975fb73c5a7</v>
       </c>
       <c r="B71" t="s">
         <v>111</v>
@@ -11305,7 +11190,7 @@
     <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>614e5a01-fa08-527a-cfcf-09d301bd59a2</v>
+        <v>384a4191-b886-9ad9-5959-553a9cb97c19</v>
       </c>
       <c r="B72" t="s">
         <v>111</v>
@@ -11347,7 +11232,7 @@
     <row r="73" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>e360e7a5-2a46-1e28-ce77-c98ac0a1d6b6</v>
+        <v>ff6a97d4-df73-c847-fa23-82f2c88995bd</v>
       </c>
       <c r="B73" t="s">
         <v>111</v>
@@ -11389,7 +11274,7 @@
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>38305d8a-1e0f-93bd-9eb2-6504df0fd70e</v>
+        <v>69e3aa6a-251c-5604-3f58-94255dc95c00</v>
       </c>
       <c r="B74" t="s">
         <v>111</v>
@@ -11431,7 +11316,7 @@
     <row r="75" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>eb1f4ecd-d8ef-eeac-1d30-b42379c29081</v>
+        <v>08411e9c-0a61-b490-8463-fc0938f3a320</v>
       </c>
       <c r="B75" t="s">
         <v>111</v>
@@ -11473,7 +11358,7 @@
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>e828e935-8c29-4314-5a79-42ce3b28cf11</v>
+        <v>45a16661-7d94-43dd-84a5-1cbb142d53fb</v>
       </c>
       <c r="B76" t="s">
         <v>111</v>
@@ -11515,7 +11400,7 @@
     <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>de0ae8e8-bacc-907f-581b-1059def8b646</v>
+        <v>a2fb110d-7ad6-8c41-b7c8-e87a32e40912</v>
       </c>
       <c r="B77" t="s">
         <v>111</v>
@@ -11557,7 +11442,7 @@
     <row r="78" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>1784d9f6-bdb2-dc00-615c-3d515141ccda</v>
+        <v>219a848d-6c26-1ddf-51ec-a0ac46a2e0e0</v>
       </c>
       <c r="B78" t="s">
         <v>111</v>
@@ -11599,7 +11484,7 @@
     <row r="79" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>d2e523d0-58c8-7557-cf71-e3d3277dc4d2</v>
+        <v>542e14e2-b43e-9877-8f40-395093b9ac65</v>
       </c>
       <c r="B79" t="s">
         <v>111</v>
@@ -11671,7 +11556,7 @@
     <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>e4a00e9f-9473-a26e-6312-63b49cb68bf8</v>
+        <v>8cde7031-8dd9-586e-a9b1-6cc080b3a756</v>
       </c>
       <c r="B80" t="s">
         <v>111</v>
@@ -11743,7 +11628,7 @@
     <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>bd559f45-6856-10a9-f261-1cac25377535</v>
+        <v>ff25a3f0-90dc-a1a3-bc6c-85950084faff</v>
       </c>
       <c r="B81" t="s">
         <v>111</v>
@@ -11785,7 +11670,7 @@
     <row r="82" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2cfbeb54-71c2-812d-41e0-58a85d966a1d</v>
+        <v>c4b12133-5121-08c8-ef11-6048cf7d6f76</v>
       </c>
       <c r="B82" t="s">
         <v>111</v>
@@ -11827,7 +11712,7 @@
     <row r="83" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>194c3674-1185-3c54-8e1e-743a59490f82</v>
+        <v>4458ab7a-40b7-765e-8338-76108d41545c</v>
       </c>
       <c r="B83" t="s">
         <v>111</v>
@@ -11869,7 +11754,7 @@
     <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>207f4613-1c4d-e628-379b-96b1f9f91d06</v>
+        <v>ddde5c1b-6316-1061-77cd-3005e73b88a2</v>
       </c>
       <c r="B84" t="s">
         <v>111</v>
@@ -11929,7 +11814,7 @@
     <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>f15e517b-3170-2951-31c9-efec49b8484c</v>
+        <v>42b75a73-134d-e4ae-704b-53211749faa3</v>
       </c>
       <c r="B85" t="s">
         <v>111</v>
@@ -11989,7 +11874,7 @@
     <row r="86" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>63b79d2e-ae68-6ad4-9508-d8ab8c8ca8a8</v>
+        <v>71f99644-369a-1cbd-4719-7cc1835c6782</v>
       </c>
       <c r="B86" t="s">
         <v>111</v>
@@ -12031,7 +11916,7 @@
     <row r="87" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>df5964c7-701f-8417-e7bf-586eda78ed1c</v>
+        <v>c1294a99-34c5-fdd7-1c52-3a56545f8a00</v>
       </c>
       <c r="B87" t="s">
         <v>111</v>
@@ -12073,7 +11958,7 @@
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>91009f64-f13f-c54f-3ab6-0ee6fe942da8</v>
+        <v>58431291-fd2e-5d26-1f2c-5558b7d72e5a</v>
       </c>
       <c r="B88" t="s">
         <v>111</v>
@@ -12115,7 +12000,7 @@
     <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>e04c9a6f-85e5-898e-497e-c48d102624b4</v>
+        <v>933083b2-52bc-b29e-885d-2e4d2c9cf392</v>
       </c>
       <c r="B89" t="s">
         <v>111</v>
@@ -12157,7 +12042,7 @@
     <row r="90" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>5c54cf09-558b-785a-fd87-20d875eac991</v>
+        <v>50ecc509-0f93-45e6-d466-c2bf36f8b479</v>
       </c>
       <c r="B90" t="s">
         <v>111</v>
@@ -12199,7 +12084,7 @@
     <row r="91" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>8e34e420-e5a2-7d69-ec19-7d2c6faffecd</v>
+        <v>f5a9bad7-baaa-645e-5cb7-db84b66bf489</v>
       </c>
       <c r="B91" t="s">
         <v>111</v>
@@ -12271,7 +12156,7 @@
     <row r="92" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>4a92a4da-5036-d811-21a0-142fc71eb4e0</v>
+        <v>aeb2c0b2-bee5-926b-8b59-2a74172a1d56</v>
       </c>
       <c r="B92" t="s">
         <v>111</v>
@@ -12313,7 +12198,7 @@
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>05b14c99-7617-aaf6-f5bf-be578ad0abbf</v>
+        <v>0c4e6b28-f929-3273-6959-6888c1635e71</v>
       </c>
       <c r="B93" t="s">
         <v>111</v>
@@ -12355,7 +12240,7 @@
     <row r="94" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>bf51acea-380a-3705-88cb-fd6562b6600a</v>
+        <v>276a4b25-1992-8855-2192-3b146afdd0b5</v>
       </c>
       <c r="B94" t="s">
         <v>111</v>
@@ -12397,7 +12282,7 @@
     <row r="95" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>878a2f09-d381-a07f-6889-29f5780d5b13</v>
+        <v>da61c75b-0271-8cc8-1ca5-5a46c2fddf48</v>
       </c>
       <c r="B95" t="s">
         <v>111</v>
@@ -12439,7 +12324,7 @@
     <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>d02aa243-2c51-9c43-04a8-edaac9b3d0e8</v>
+        <v>0759baa6-eb80-0db8-97ae-19eadfdaa877</v>
       </c>
       <c r="B96" t="s">
         <v>111</v>
@@ -12481,7 +12366,7 @@
     <row r="97" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>407bfe48-40c7-5c21-1c61-6b4581873aaa</v>
+        <v>a411c358-cfcb-972f-aaa4-9ffa765c9b3c</v>
       </c>
       <c r="B97" t="s">
         <v>111</v>
@@ -12523,7 +12408,7 @@
     <row r="98" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>8c42dfc2-6b53-5eec-6b89-cdffabee3db0</v>
+        <v>4185e0a4-a02d-fb15-1b3e-e07a72f05513</v>
       </c>
       <c r="B98" t="s">
         <v>111</v>
@@ -12583,7 +12468,7 @@
     <row r="99" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>29aaa963-1d0f-845c-2f2f-f71533f3f306</v>
+        <v>5c037389-564d-b386-9aea-9a5d51ca566b</v>
       </c>
       <c r="B99" t="s">
         <v>111</v>
@@ -12625,7 +12510,7 @@
     <row r="100" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>3c3a5ce3-7523-e3f2-722d-c7745fea5e56</v>
+        <v>23df0869-5c1a-e973-08b0-72753fabc52e</v>
       </c>
       <c r="B100" t="s">
         <v>111</v>
@@ -12667,7 +12552,7 @@
     <row r="101" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>a550503a-8062-e0cb-2b82-89dbbe0d54d4</v>
+        <v>aeb47f64-60de-d264-7c21-9dcd0d85674b</v>
       </c>
       <c r="B101" t="s">
         <v>111</v>
@@ -12709,7 +12594,7 @@
     <row r="102" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>06fbefd3-a44f-7139-895d-d3989632084e</v>
+        <v>5d7a215e-d8cf-7e36-29c9-e26ffbf5fcf7</v>
       </c>
       <c r="B102" t="s">
         <v>111</v>
@@ -12769,7 +12654,7 @@
     <row r="103" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>0fbc1b5f-3257-8fc0-7117-87652e1859e1</v>
+        <v>9a3a2482-a54a-09c2-ad07-e4727199bca0</v>
       </c>
       <c r="B103" t="s">
         <v>111</v>
@@ -12811,7 +12696,7 @@
     <row r="104" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>a0e8b184-b938-5c0e-4637-6905ff6a1e60</v>
+        <v>6b77684c-7e6b-c5e0-b12b-e8c6dc83f328</v>
       </c>
       <c r="B104" t="s">
         <v>111</v>
@@ -12853,7 +12738,7 @@
     <row r="105" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>63a417f1-2095-c5db-accd-da480012029a</v>
+        <v>49e226f8-a65a-a470-585f-960337e73489</v>
       </c>
       <c r="B105" t="s">
         <v>111</v>
@@ -12895,7 +12780,7 @@
     <row r="106" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>40b2b020-e25b-5da7-ac49-be3df774785f</v>
+        <v>625b0a73-bc2c-2318-80e9-36df0f959a4a</v>
       </c>
       <c r="B106" t="s">
         <v>111</v>
@@ -12937,7 +12822,7 @@
     <row r="107" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>763b87bb-bdaf-ccd0-cf82-ebc7a36e843f</v>
+        <v>00bc516a-216f-f499-4daf-7129da3bbef0</v>
       </c>
       <c r="B107" t="s">
         <v>111</v>
@@ -13033,7 +12918,7 @@
     <row r="108" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>781f7c15-802a-7fd6-e576-ecbe1af883e4</v>
+        <v>255ed068-5a0c-951a-0fdd-5c064bc731fe</v>
       </c>
       <c r="B108" t="s">
         <v>111</v>
@@ -13075,7 +12960,7 @@
     <row r="109" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>d44e8093-2fa6-e690-afcb-1b6e1bbb0547</v>
+        <v>4eb6adec-7803-317b-1dea-a239091bd69c</v>
       </c>
       <c r="B109" t="s">
         <v>111</v>
@@ -13117,7 +13002,7 @@
     <row r="110" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>abd692e0-4204-88e6-0f6d-208330c61e5b</v>
+        <v>4143bd66-8ec9-8399-6202-5dbd4b8ec671</v>
       </c>
       <c r="B110" t="s">
         <v>111</v>
@@ -13159,7 +13044,7 @@
     <row r="111" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>dbbca0a0-dec3-ef6a-f85b-5fa6cd62e940</v>
+        <v>7620f897-68df-788b-3e8b-b5c548a99752</v>
       </c>
       <c r="B111" t="s">
         <v>111</v>
@@ -13201,7 +13086,7 @@
     <row r="112" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>73d25e5e-89b5-f815-05b5-c1d35221931c</v>
+        <v>d8d50406-3d4d-7ced-f198-af58909092d2</v>
       </c>
       <c r="B112" t="s">
         <v>111</v>
@@ -13261,7 +13146,7 @@
     <row r="113" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>c4497e6c-56d0-ad9b-2814-7f6dcf335318</v>
+        <v>f9b7352d-8cc0-409d-04d3-fc1e90bc2fc9</v>
       </c>
       <c r="B113" t="s">
         <v>111</v>
@@ -13303,7 +13188,7 @@
     <row r="114" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>5a6f2dcf-4d5e-6a93-edca-6e422607e54a</v>
+        <v>7b3b4d06-2a3f-85d7-4d94-b9da5aad9cfd</v>
       </c>
       <c r="B114" t="s">
         <v>111</v>
@@ -13345,7 +13230,7 @@
     <row r="115" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>60ee2aff-938b-d52b-114a-8bda7f877785</v>
+        <v>9a11d46e-edb5-e8c1-327e-df76b777d1e4</v>
       </c>
       <c r="B115" t="s">
         <v>111</v>
@@ -13405,7 +13290,7 @@
     <row r="116" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>f4f1994a-4485-e24d-eb9c-e3316c56931b</v>
+        <v>373bd050-4e6e-b470-509a-59e79f9a76e0</v>
       </c>
       <c r="B116" t="s">
         <v>111</v>
@@ -13447,7 +13332,7 @@
     <row r="117" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>042f8b6c-fb3e-762e-da8f-2212801473ba</v>
+        <v>352f73db-6653-db79-fdd6-e9aa4b5227df</v>
       </c>
       <c r="B117" t="s">
         <v>111</v>
@@ -13489,7 +13374,7 @@
     <row r="118" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>f9ca5b70-976a-89a8-b4ea-bc0d32f03b6e</v>
+        <v>789a3a9e-164a-427a-c560-499938705531</v>
       </c>
       <c r="B118" t="s">
         <v>111</v>
@@ -13531,7 +13416,7 @@
     <row r="119" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>1f402cc8-0022-7484-79cd-8f51f4351cd6</v>
+        <v>8e122ce3-2448-5e98-2123-6e3321b585f2</v>
       </c>
       <c r="B119" t="s">
         <v>111</v>
@@ -13573,7 +13458,7 @@
     <row r="120" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>7193085e-09c4-3bcc-95d5-356b63b84456</v>
+        <v>49970bad-87a0-e4ae-4d27-dc026baaf21e</v>
       </c>
       <c r="B120" t="s">
         <v>111</v>
@@ -13615,7 +13500,7 @@
     <row r="121" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>9ca7e444-c0de-4b63-ef0b-eb3ddcd75413</v>
+        <v>c2480c83-f6f4-ad88-b416-6573e6ef9f8b</v>
       </c>
       <c r="B121" t="s">
         <v>111</v>
@@ -13657,7 +13542,7 @@
     <row r="122" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>8fedbe52-f8e3-7de7-cf05-360fe7f09ffb</v>
+        <v>7b83c1db-ecce-d106-c728-af82128d1372</v>
       </c>
       <c r="B122" t="s">
         <v>111</v>
@@ -13699,7 +13584,7 @@
     <row r="123" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ce33d53a-58e8-443f-ac38-6629764f8603</v>
+        <v>2b1af7fa-6be7-4e34-fb04-c2a436f47df2</v>
       </c>
       <c r="B123" t="s">
         <v>111</v>
@@ -13741,7 +13626,7 @@
     <row r="124" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>5de6e699-74d3-c310-ac35-03bc9f635c52</v>
+        <v>5d054db7-2115-894b-6287-4b87ba8cb6c2</v>
       </c>
       <c r="B124" t="s">
         <v>111</v>
@@ -13783,7 +13668,7 @@
     <row r="125" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>35a9ef3f-aed0-0689-429b-be3bc3dc7c76</v>
+        <v>cbe478e0-2c09-9fce-94f9-98544c2054ab</v>
       </c>
       <c r="B125" t="s">
         <v>111</v>
@@ -13855,7 +13740,7 @@
     <row r="126" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>1e0a5cc2-2899-7487-e355-79f0f2e35f3b</v>
+        <v>0f6e67c9-66e8-dab1-99c2-de75bbc3c590</v>
       </c>
       <c r="B126" t="s">
         <v>111</v>
@@ -13897,7 +13782,7 @@
     <row r="127" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>5d8db8e1-6d6c-8a4e-3d9e-1f5f376589ad</v>
+        <v>61476452-8c3e-2263-8d9c-4b084a24519c</v>
       </c>
       <c r="B127" t="s">
         <v>111</v>
@@ -13939,7 +13824,7 @@
     <row r="128" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>d5657bba-2894-5f65-47ee-d6a7ed52114b</v>
+        <v>2ed74f60-678e-18a5-e545-bbcd43cd4554</v>
       </c>
       <c r="B128" t="s">
         <v>111</v>
@@ -13981,7 +13866,7 @@
     <row r="129" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>53741233-a30c-6b9a-4045-d8ce16c4d648</v>
+        <v>ab868501-7331-ba39-af22-7d3e17891cce</v>
       </c>
       <c r="B129" t="s">
         <v>111</v>
@@ -14023,7 +13908,7 @@
     <row r="130" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A130" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2694c1f4-b9d6-4e20-07e1-8dc8c455f453</v>
+        <v>ae0183de-ce37-7ccc-182d-20e4b3c7c3bd</v>
       </c>
       <c r="B130" t="s">
         <v>111</v>
@@ -14065,7 +13950,7 @@
     <row r="131" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A131" t="str">
         <f t="shared" ref="A131:A133" ca="1" si="2">IF(G131&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>ccfa0a3e-bfeb-312e-8812-bbb4221e4aeb</v>
+        <v>17f6141e-2ff2-be99-900b-fc121e43249b</v>
       </c>
       <c r="B131" t="s">
         <v>111</v>
@@ -14149,7 +14034,7 @@
     <row r="132" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A132" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>276094a9-5d3d-2b14-09e6-0b18975857c5</v>
+        <v>fbbdcad4-0329-5173-9151-cb4756b8dc69</v>
       </c>
       <c r="B132" t="s">
         <v>111</v>
@@ -14191,7 +14076,7 @@
     <row r="133" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A133" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>b5bf7c5b-526c-aa9b-dd71-78d20e7690f4</v>
+        <v>c127a8c2-c924-f40e-400c-ea582af72f31</v>
       </c>
       <c r="B133" t="s">
         <v>111</v>
@@ -14262,8 +14147,8 @@
     </row>
     <row r="134" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A134" t="str">
-        <f t="shared" ref="A134:A194" ca="1" si="3">IF(G134&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>3eb395b1-1c4a-b49b-0351-1ac075794e7c</v>
+        <f t="shared" ref="A134:A188" ca="1" si="3">IF(G134&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+        <v>1e400829-9ece-2aa3-4421-f2143e3bbc9f</v>
       </c>
       <c r="B134" t="s">
         <v>926</v>
@@ -14302,7 +14187,7 @@
     <row r="135" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>21d2e564-542d-47d2-8cf4-817a7838bce7</v>
+        <v>16ab1862-0d14-34e2-b0bb-c4f00173b256</v>
       </c>
       <c r="B135" t="s">
         <v>926</v>
@@ -14341,7 +14226,7 @@
     <row r="136" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>9f337f24-f756-944b-dec6-c9efda416781</v>
+        <v>202a1f39-e437-db02-802d-e0e5eaea2d3c</v>
       </c>
       <c r="B136" t="s">
         <v>926</v>
@@ -14380,7 +14265,7 @@
     <row r="137" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>718ec756-12c0-4ef6-a1a0-a38f19dd9a97</v>
+        <v>f8fcbfff-1688-1d43-9a83-cddf85c19b3f</v>
       </c>
       <c r="B137" t="s">
         <v>926</v>
@@ -14419,7 +14304,7 @@
     <row r="138" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>c3495598-a724-68e1-d875-d56536c69005</v>
+        <v>ba7eaf9c-b7e6-21ba-ea5a-fcb58fc2d7ef</v>
       </c>
       <c r="B138" t="s">
         <v>926</v>
@@ -14458,7 +14343,7 @@
     <row r="139" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>662527df-3cdf-82ad-52f9-c4fb25f20d8a</v>
+        <v>28d65c23-44df-9fd6-df53-cec91267f5ad</v>
       </c>
       <c r="B139" t="s">
         <v>926</v>
@@ -14497,7 +14382,7 @@
     <row r="140" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>edbf89fd-b1f2-b1b1-3009-22e7e385aa0a</v>
+        <v>730526a7-7b76-c91f-ea11-d036c6f11e68</v>
       </c>
       <c r="B140" t="s">
         <v>926</v>
@@ -14536,7 +14421,7 @@
     <row r="141" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>ef99b2c3-cc1c-36d1-502e-354baa50183d</v>
+        <v>65a6020b-9347-e296-d626-13e010ae151b</v>
       </c>
       <c r="B141" t="s">
         <v>926</v>
@@ -14575,7 +14460,7 @@
     <row r="142" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>3505fd5a-4c9b-4383-83fe-0bd5e4e263a0</v>
+        <v>311f22f7-7ac3-9e83-a089-dda187757e30</v>
       </c>
       <c r="B142" t="s">
         <v>926</v>
@@ -14614,7 +14499,7 @@
     <row r="143" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>9d7406e7-e3e8-4b99-9011-cd8de96e1da9</v>
+        <v>5110920e-12ae-384f-f604-fea9e132837b</v>
       </c>
       <c r="B143" t="s">
         <v>926</v>
@@ -14653,7 +14538,7 @@
     <row r="144" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>5b0ff0a0-ab93-8260-7226-3f173f18bf77</v>
+        <v>135b0a03-28b3-78cd-5c90-4277158d4e33</v>
       </c>
       <c r="B144" t="s">
         <v>926</v>
@@ -14692,7 +14577,7 @@
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>64a3fa0b-43e5-f849-3f4e-774819b44ed3</v>
+        <v>069acb01-235e-7be9-1d34-e2172703ac9b</v>
       </c>
       <c r="B145" t="s">
         <v>926</v>
@@ -14731,7 +14616,7 @@
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>c7199877-4b85-e627-82e5-8189be2d1f8a</v>
+        <v>433db9b6-fe7a-1e5d-63d4-794d736a5b32</v>
       </c>
       <c r="B146" t="s">
         <v>926</v>
@@ -14770,7 +14655,7 @@
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>58419e0a-68a9-7899-331c-c387b53efa5e</v>
+        <v>a0b8ef01-f34d-4db3-d348-79aa2cb2790e</v>
       </c>
       <c r="B147" t="s">
         <v>926</v>
@@ -14809,7 +14694,7 @@
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>060293ce-d0fe-5611-c2c1-118c1a60cbf9</v>
+        <v>74a76c21-4299-128d-87f6-d7a9b3881590</v>
       </c>
       <c r="B148" t="s">
         <v>926</v>
@@ -14849,7 +14734,7 @@
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>c054709f-3658-c883-91ba-edcc4e497cbb</v>
+        <v>943dd6a5-d27f-19d5-93b1-2a3a8c90651c</v>
       </c>
       <c r="B149" t="s">
         <v>926</v>
@@ -14888,7 +14773,7 @@
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>2a48d2b2-0784-1ede-42ae-025e7bc42fd1</v>
+        <v>f4f8a294-38c1-254c-bdc5-6d170684832a</v>
       </c>
       <c r="B150" t="s">
         <v>926</v>
@@ -14927,7 +14812,7 @@
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d3474ec3-2695-5d6f-e906-425fd7f2bd91</v>
+        <v>2bb21c19-5402-626c-508b-6bbbb0588a83</v>
       </c>
       <c r="B151" t="s">
         <v>926</v>
@@ -14966,7 +14851,7 @@
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>1aeb8334-caad-8269-e133-818d68d1dd67</v>
+        <v>0afa29bd-035a-6b16-c779-747e8f22dc37</v>
       </c>
       <c r="B152" t="s">
         <v>926</v>
@@ -15005,7 +14890,7 @@
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>2a5cd7bf-22cd-8de4-2af2-bafceb725227</v>
+        <v>06bc1cde-fc04-1ffc-39a8-165ba5b1d046</v>
       </c>
       <c r="B153" t="s">
         <v>926</v>
@@ -15044,7 +14929,7 @@
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>04354069-d674-1ad2-5b68-2e0449b15467</v>
+        <v>8607067c-41b2-7335-afe1-f3e4c8d5d2c3</v>
       </c>
       <c r="B154" t="s">
         <v>926</v>
@@ -15083,7 +14968,7 @@
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>49613cee-d3c2-b0db-b2ab-647b44088eaa</v>
+        <v>c2597366-de77-3855-b7a9-60c4cff26fdf</v>
       </c>
       <c r="B155" t="s">
         <v>926</v>
@@ -15122,7 +15007,7 @@
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>a5647d72-daa0-5f64-5684-008b45e14561</v>
+        <v>1e24047c-4f8b-a228-a4f9-8e1dabba1c68</v>
       </c>
       <c r="B156" t="s">
         <v>926</v>
@@ -15161,7 +15046,7 @@
     <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>b6a6beb2-4c0c-fdab-d5bb-59c07eb440f9</v>
+        <v>62754cf0-213c-200d-36ba-19bf98edce84</v>
       </c>
       <c r="B157" t="s">
         <v>926</v>
@@ -15200,7 +15085,7 @@
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>4c8ee47e-82bb-ee9c-112f-dc9d330754ec</v>
+        <v>8cb00df7-6a32-4487-6983-1b0175cc039e</v>
       </c>
       <c r="B158" t="s">
         <v>926</v>
@@ -15239,7 +15124,7 @@
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>4b8d3a7c-84f4-2715-a051-b2411fbac346</v>
+        <v>2cbc17f3-21a9-c240-368b-dc960eb637fa</v>
       </c>
       <c r="B159" t="s">
         <v>926</v>
@@ -15278,7 +15163,7 @@
     <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>91c7b8af-8633-ee71-a30d-e9509dcf2965</v>
+        <v>80c0fc12-c93a-f00b-7098-dc1fe3c54756</v>
       </c>
       <c r="B160" t="s">
         <v>926</v>
@@ -15314,10 +15199,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>96e63b86-cb66-904a-5419-869de81e41f9</v>
+        <v>0172d2e3-dd25-2f66-afd2-6ff99da2a32f</v>
       </c>
       <c r="B161" t="s">
         <v>926</v>
@@ -15353,10 +15238,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>164b8eef-0a98-4d13-131c-dd0dc1ead051</v>
+        <v>405657c8-8fe9-4959-7c32-41f2448306ba</v>
       </c>
       <c r="B162" t="s">
         <v>926</v>
@@ -15392,10 +15277,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>f38bbf69-f81e-9528-8e5d-69910290a8c7</v>
+        <v>f583fc24-b5c3-e269-eb2c-91360251974d</v>
       </c>
       <c r="B163" t="s">
         <v>926</v>
@@ -15431,10 +15316,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>95383076-fd81-cfe7-d34c-a0b5d6490e3d</v>
+        <v>33dd57a6-e087-8055-834b-8dfe2412a5a0</v>
       </c>
       <c r="B164" t="s">
         <v>926</v>
@@ -15470,10 +15355,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>381f84b3-950c-217d-3ed0-770fdfc0d777</v>
+        <v>1fdde85e-cce5-12f4-5da5-f60c0af1d258</v>
       </c>
       <c r="B165" t="s">
         <v>926</v>
@@ -15509,10 +15394,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>9a1f2b9e-001e-6a3f-c77e-f83984b38d43</v>
+        <v>9ae5b9c4-8ad3-ff12-07c4-24f3a3a74ecd</v>
       </c>
       <c r="B166" t="s">
         <v>926</v>
@@ -15548,10 +15433,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>8ed73d90-f548-ab4e-2b25-af0077aec072</v>
+        <v>0e2261f3-e5ce-c9ef-9f0a-8c041094a84f</v>
       </c>
       <c r="B167" t="s">
         <v>926</v>
@@ -15587,10 +15472,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d00ddce6-b7d6-bed5-2473-98cc9b4a8938</v>
+        <v>9f14911c-ad7d-f78e-f5fe-6fe61fbfdb4e</v>
       </c>
       <c r="B168" t="s">
         <v>926</v>
@@ -15626,10 +15511,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A169" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>56d6b505-f484-0c14-c326-f08176e42700</v>
+        <v>484ef302-1824-0a94-c7ef-7aa2a7dab656</v>
       </c>
       <c r="B169" t="s">
         <v>926</v>
@@ -15665,10 +15550,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A170" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>b8cbcb6b-4e94-3943-720d-2f7a591c8d43</v>
+        <v>0898e398-fdeb-f9e1-8367-a0a4f4d1885e</v>
       </c>
       <c r="B170" t="s">
         <v>926</v>
@@ -15704,10 +15589,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>ced69534-aeb3-d6d1-39dd-bf4e80f75a96</v>
+        <v>e9e6c547-54ef-7cbf-26a9-1b2a7722da44</v>
       </c>
       <c r="B171" t="s">
         <v>926</v>
@@ -15743,10 +15628,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>e0c0b6ea-ca4f-aefd-0c47-5727fcce784d</v>
+        <v>6a7e8cfe-2a0d-9ce5-db65-99f7248b088e</v>
       </c>
       <c r="B172" t="s">
         <v>926</v>
@@ -15782,10 +15667,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>aa82ffc0-414a-4def-736e-94ff25d4a776</v>
+        <v>bf624815-aaa2-1ead-fcb0-ccef0edbdbd7</v>
       </c>
       <c r="B173" t="s">
         <v>926</v>
@@ -15821,6536 +15706,518 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>5df48305-9026-83f1-67ac-30c2ae61244c</v>
-      </c>
-      <c r="B174" t="s">
+        <v>28957050-801f-fd71-2778-551f5745a005</v>
+      </c>
+      <c r="B174" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C174" t="s">
+      <c r="C174" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D174" t="s">
+      <c r="D174" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="E174" t="s">
-        <v>100</v>
-      </c>
-      <c r="F174" t="s">
-        <v>61</v>
-      </c>
-      <c r="G174" t="s">
+      <c r="E174" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G174" s="3" t="s">
         <v>928</v>
       </c>
-      <c r="H174" t="s">
+      <c r="H174" s="3"/>
+      <c r="I174" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="I174" t="s">
+      <c r="J174" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="K174" t="s">
-        <v>74</v>
-      </c>
-      <c r="L174" t="s">
+      <c r="K174" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L174" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="M174" t="s">
-        <v>54</v>
-      </c>
-      <c r="N174" t="b">
+      <c r="M174" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N174" s="3" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O174" s="3"/>
+      <c r="P174" s="3"/>
+      <c r="Q174" s="3"/>
+      <c r="R174" s="3"/>
+      <c r="S174" s="3"/>
+      <c r="T174" s="3"/>
+      <c r="U174" s="3"/>
+      <c r="V174" s="3"/>
+      <c r="W174" s="3"/>
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>ac3238dc-03d8-bd1d-b8a3-f3e0a068b1c1</v>
-      </c>
-      <c r="B175" t="s">
+        <v>814d77ca-e073-3f17-2daf-3a71ef797b44</v>
+      </c>
+      <c r="B175" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C175" t="s">
+      <c r="C175" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D175" t="s">
-        <v>433</v>
-      </c>
-      <c r="E175" t="s">
-        <v>106</v>
-      </c>
-      <c r="F175" t="s">
-        <v>47</v>
-      </c>
-      <c r="G175" t="s">
+      <c r="D175" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G175" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="H175" t="s">
+      <c r="H175" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="I175" t="s">
+      <c r="I175" s="3" t="s">
         <v>935</v>
       </c>
-      <c r="J175" t="s">
-        <v>52</v>
-      </c>
-      <c r="K175" t="s">
+      <c r="J175" s="3"/>
+      <c r="K175" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L175" s="3" t="s">
         <v>936</v>
       </c>
-      <c r="L175" t="s">
-        <v>197</v>
-      </c>
-      <c r="M175" t="b">
+      <c r="M175" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N175" s="3" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O175" s="3"/>
+      <c r="P175" s="3"/>
+      <c r="Q175" s="3"/>
+      <c r="R175" s="3"/>
+      <c r="S175" s="3"/>
+      <c r="T175" s="3"/>
+      <c r="U175" s="3"/>
+      <c r="V175" s="3"/>
+      <c r="W175" s="3"/>
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>fb30e7a2-a40b-d855-90b1-aa1f3b07ed53</v>
-      </c>
-      <c r="B176" t="s">
+        <v>a04dafc4-6f41-2d8d-9f26-f3eeb9b83d8a</v>
+      </c>
+      <c r="B176" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C176" t="s">
+      <c r="C176" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D176" t="s">
+      <c r="D176" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G176" s="3" t="s">
         <v>938</v>
       </c>
-      <c r="E176" t="s">
-        <v>100</v>
-      </c>
-      <c r="F176" t="s">
-        <v>95</v>
-      </c>
-      <c r="G176" t="s">
+      <c r="H176" s="3" t="s">
         <v>939</v>
       </c>
-      <c r="H176" t="s">
+      <c r="I176" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="J176" s="3"/>
+      <c r="K176" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L176" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="I176" t="s">
-        <v>941</v>
-      </c>
-      <c r="K176" t="s">
-        <v>74</v>
-      </c>
-      <c r="L176" t="s">
-        <v>942</v>
-      </c>
-      <c r="M176" t="s">
+      <c r="M176" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="N176" t="b">
+      <c r="N176" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="O176" s="3"/>
+      <c r="P176" s="3"/>
+      <c r="Q176" s="3"/>
+      <c r="R176" s="3"/>
+      <c r="S176" s="3"/>
+      <c r="T176" s="3"/>
+      <c r="U176" s="3"/>
+      <c r="V176" s="3"/>
+      <c r="W176" s="3"/>
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>76f3de6a-61cb-fa35-3c45-0cd5eef0423a</v>
-      </c>
-      <c r="B177" t="s">
+        <v>12e855d6-4e0e-5132-df10-ae656e9013b5</v>
+      </c>
+      <c r="B177" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C177" t="s">
+      <c r="C177" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D177" t="s">
+      <c r="D177" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="I177" s="3" t="s">
         <v>944</v>
       </c>
-      <c r="E177" t="s">
-        <v>100</v>
-      </c>
-      <c r="F177" t="s">
-        <v>61</v>
-      </c>
-      <c r="G177" t="s">
+      <c r="J177" s="3"/>
+      <c r="K177" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L177" s="3" t="s">
         <v>945</v>
       </c>
-      <c r="H177" t="s">
-        <v>946</v>
-      </c>
-      <c r="I177" t="s">
-        <v>930</v>
-      </c>
-      <c r="K177" t="s">
-        <v>74</v>
-      </c>
-      <c r="L177" t="s">
-        <v>947</v>
-      </c>
-      <c r="M177" t="s">
-        <v>54</v>
-      </c>
-      <c r="N177" t="b">
+      <c r="M177" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N177" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="O177" s="3"/>
+      <c r="P177" s="3"/>
+      <c r="Q177" s="3"/>
+      <c r="R177" s="3"/>
+      <c r="S177" s="3"/>
+      <c r="T177" s="3"/>
+      <c r="U177" s="3"/>
+      <c r="V177" s="3"/>
+      <c r="W177" s="3"/>
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>0f873c94-a065-d36c-f3e3-c0f4ddf01456</v>
-      </c>
-      <c r="B178" t="s">
+        <v>49729094-5732-717a-84c3-88e4f336db06</v>
+      </c>
+      <c r="B178" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C178" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D178" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="H178" s="3"/>
+      <c r="I178" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="J178" s="3" t="s">
         <v>949</v>
       </c>
-      <c r="E178" t="s">
-        <v>100</v>
-      </c>
-      <c r="F178" t="s">
-        <v>95</v>
-      </c>
-      <c r="G178" t="s">
+      <c r="K178" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L178" s="3" t="s">
         <v>950</v>
       </c>
-      <c r="H178" t="s">
-        <v>951</v>
-      </c>
-      <c r="I178" t="s">
-        <v>952</v>
-      </c>
-      <c r="K178" t="s">
-        <v>74</v>
-      </c>
-      <c r="L178" t="s">
-        <v>953</v>
-      </c>
-      <c r="M178" t="s">
-        <v>124</v>
-      </c>
-      <c r="N178" t="b">
+      <c r="M178" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N178" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="O178" s="3"/>
+      <c r="P178" s="3"/>
+      <c r="Q178" s="3"/>
+      <c r="R178" s="3"/>
+      <c r="S178" s="3"/>
+      <c r="T178" s="3"/>
+      <c r="U178" s="3"/>
+      <c r="V178" s="3"/>
+      <c r="W178" s="3"/>
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>d14edce9-d30e-8116-14e3-d5f3c296ab67</v>
-      </c>
-      <c r="B179" t="s">
+        <v>64f5ec06-bfcc-bbf6-1373-3ff9a75b660b</v>
+      </c>
+      <c r="B179" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C179" t="s">
+      <c r="C179" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D179" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="H179" s="3"/>
+      <c r="I179" s="3"/>
+      <c r="J179" s="3"/>
+      <c r="K179" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L179" s="3" t="s">
         <v>955</v>
       </c>
-      <c r="E179" t="s">
-        <v>100</v>
-      </c>
-      <c r="F179" t="s">
+      <c r="M179" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N179" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O179" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P179" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G179" t="s">
-        <v>956</v>
-      </c>
-      <c r="H179" t="s">
-        <v>957</v>
-      </c>
-      <c r="I179" t="s">
-        <v>958</v>
-      </c>
-      <c r="J179" t="s">
-        <v>52</v>
-      </c>
-      <c r="K179" t="s">
-        <v>959</v>
-      </c>
-      <c r="L179" t="s">
-        <v>54</v>
-      </c>
-      <c r="M179" t="b">
-        <v>1</v>
+      <c r="Q179" s="3"/>
+      <c r="R179" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="S179" s="3"/>
+      <c r="T179" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U179" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V179" s="3"/>
+      <c r="W179" s="3" t="s">
+        <v>954</v>
       </c>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>5f015f94-af76-d345-b6a6-150a3aa713d2</v>
-      </c>
-      <c r="B180" t="s">
+        <v>8047082d-a1b5-51da-62e7-586d6cc4e15f</v>
+      </c>
+      <c r="B180" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C180" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D180" t="s">
-        <v>961</v>
-      </c>
-      <c r="E180" t="s">
-        <v>100</v>
-      </c>
-      <c r="F180" t="s">
-        <v>57</v>
-      </c>
-      <c r="G180" t="s">
-        <v>962</v>
-      </c>
-      <c r="I180" t="s">
-        <v>963</v>
-      </c>
-      <c r="J180" t="s">
-        <v>964</v>
-      </c>
-      <c r="K180" t="s">
-        <v>52</v>
-      </c>
-      <c r="L180" t="s">
-        <v>965</v>
-      </c>
-      <c r="M180" t="s">
+      <c r="D180" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="H180" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="J180" s="3"/>
+      <c r="K180" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L180" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="M180" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="N180" t="b">
+      <c r="N180" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="O180" t="s">
-        <v>60</v>
-      </c>
-      <c r="P180" t="s">
-        <v>47</v>
-      </c>
-      <c r="R180" t="s">
-        <v>963</v>
-      </c>
-      <c r="T180" t="s">
-        <v>64</v>
-      </c>
-      <c r="U180" t="s">
-        <v>47</v>
-      </c>
-      <c r="W180" t="s">
-        <v>964</v>
-      </c>
+      <c r="O180" s="3"/>
+      <c r="P180" s="3"/>
+      <c r="Q180" s="3"/>
+      <c r="R180" s="3"/>
+      <c r="S180" s="3"/>
+      <c r="T180" s="3"/>
+      <c r="U180" s="3"/>
+      <c r="V180" s="3"/>
+      <c r="W180" s="3"/>
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>a0d293c3-d2a6-0e88-3d99-f722ce407f83</v>
-      </c>
-      <c r="B181" t="s">
+        <v>de881fd7-7160-84bf-c54d-7389ae80201c</v>
+      </c>
+      <c r="B181" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C181" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D181" t="s">
-        <v>635</v>
-      </c>
-      <c r="E181" t="s">
-        <v>119</v>
-      </c>
-      <c r="F181" t="s">
-        <v>89</v>
-      </c>
-      <c r="G181" t="s">
-        <v>967</v>
-      </c>
-      <c r="H181" t="s">
-        <v>968</v>
-      </c>
-      <c r="I181" t="s">
-        <v>969</v>
-      </c>
-      <c r="K181" t="s">
+      <c r="D181" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="J181" s="3"/>
+      <c r="K181" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="L181" t="s">
-        <v>970</v>
-      </c>
-      <c r="M181" t="s">
-        <v>197</v>
-      </c>
-      <c r="N181" t="b">
+      <c r="L181" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="M181" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N181" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="O181" s="3"/>
+      <c r="P181" s="3"/>
+      <c r="Q181" s="3"/>
+      <c r="R181" s="3"/>
+      <c r="S181" s="3"/>
+      <c r="T181" s="3"/>
+      <c r="U181" s="3"/>
+      <c r="V181" s="3"/>
+      <c r="W181" s="3"/>
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>b7e708ac-e673-f545-21d6-eed334aa2d4e</v>
-      </c>
-      <c r="B182" t="s">
+        <v>7a8c1ea9-b37b-9607-8e6e-e3968e12be15</v>
+      </c>
+      <c r="B182" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C182" t="s">
+      <c r="C182" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D182" t="s">
-        <v>972</v>
-      </c>
-      <c r="E182" t="s">
+      <c r="D182" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="E182" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="F182" t="s">
-        <v>61</v>
-      </c>
-      <c r="G182" t="s">
-        <v>973</v>
-      </c>
-      <c r="H182" t="s">
-        <v>974</v>
-      </c>
-      <c r="I182" t="s">
-        <v>975</v>
-      </c>
-      <c r="K182" t="s">
-        <v>74</v>
-      </c>
-      <c r="L182" t="s">
-        <v>976</v>
-      </c>
-      <c r="M182" t="s">
-        <v>54</v>
-      </c>
-      <c r="N182" t="b">
+      <c r="F182" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="H182" s="3"/>
+      <c r="I182" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="J182" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="K182" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L182" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="M182" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N182" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="O182" s="3"/>
+      <c r="P182" s="3"/>
+      <c r="Q182" s="3"/>
+      <c r="R182" s="3"/>
+      <c r="S182" s="3"/>
+      <c r="T182" s="3"/>
+      <c r="U182" s="3"/>
+      <c r="V182" s="3"/>
+      <c r="W182" s="3"/>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A183" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>4530a150-11f9-160b-bbd4-374b59f3eeba</v>
-      </c>
-      <c r="B183" t="s">
-        <v>111</v>
-      </c>
-      <c r="C183" t="s">
-        <v>112</v>
-      </c>
-      <c r="D183" t="s">
-        <v>972</v>
-      </c>
-      <c r="E183" t="s">
-        <v>344</v>
-      </c>
-      <c r="F183" t="s">
-        <v>47</v>
-      </c>
-      <c r="G183" t="s">
-        <v>978</v>
-      </c>
-      <c r="H183" t="s">
-        <v>979</v>
-      </c>
-      <c r="I183" t="s">
-        <v>980</v>
-      </c>
-      <c r="J183" t="s">
-        <v>52</v>
-      </c>
-      <c r="K183" t="s">
-        <v>981</v>
-      </c>
-      <c r="L183" t="s">
-        <v>197</v>
-      </c>
-      <c r="M183" t="b">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A184" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>c9b9dae8-00db-fe01-08f1-eb96565c4a38</v>
-      </c>
-      <c r="B184" t="s">
-        <v>111</v>
-      </c>
-      <c r="C184" t="s">
-        <v>112</v>
-      </c>
-      <c r="D184" t="s">
-        <v>618</v>
-      </c>
-      <c r="E184" t="s">
-        <v>119</v>
-      </c>
-      <c r="F184" t="s">
-        <v>95</v>
-      </c>
-      <c r="G184" t="s">
-        <v>983</v>
-      </c>
-      <c r="H184" t="s">
-        <v>984</v>
-      </c>
-      <c r="I184" t="s">
-        <v>985</v>
-      </c>
-      <c r="K184" t="s">
-        <v>74</v>
-      </c>
-      <c r="L184" t="s">
-        <v>986</v>
-      </c>
-      <c r="M184" t="s">
-        <v>197</v>
-      </c>
-      <c r="N184" t="b">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>19e81e27-adfa-9a7a-6f7d-547a0671ff90</v>
-      </c>
-      <c r="B185" t="s">
-        <v>111</v>
-      </c>
-      <c r="C185" t="s">
-        <v>112</v>
-      </c>
-      <c r="D185" t="s">
-        <v>988</v>
-      </c>
-      <c r="E185" t="s">
-        <v>989</v>
-      </c>
-      <c r="F185" t="s">
-        <v>341</v>
-      </c>
-      <c r="G185" t="s">
-        <v>990</v>
-      </c>
-      <c r="I185">
-        <v>1638.1</v>
-      </c>
-      <c r="J185" t="s">
-        <v>991</v>
-      </c>
-      <c r="K185" t="s">
-        <v>52</v>
-      </c>
-      <c r="L185" t="s">
-        <v>992</v>
-      </c>
-      <c r="M185" t="s">
-        <v>197</v>
-      </c>
-      <c r="N185" t="b">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>94d94320-fad7-2860-60b5-3a55497332ca</v>
-      </c>
-      <c r="B186" t="s">
-        <v>111</v>
-      </c>
-      <c r="C186" t="s">
-        <v>112</v>
-      </c>
-      <c r="D186" t="s">
-        <v>994</v>
-      </c>
-      <c r="E186" t="s">
-        <v>106</v>
-      </c>
-      <c r="F186" t="s">
-        <v>89</v>
-      </c>
-      <c r="G186" t="s">
-        <v>995</v>
-      </c>
-      <c r="H186" t="s">
-        <v>996</v>
-      </c>
-      <c r="I186" t="s">
-        <v>997</v>
-      </c>
-      <c r="K186" t="s">
-        <v>74</v>
-      </c>
-      <c r="L186" t="s">
-        <v>998</v>
-      </c>
-      <c r="M186" t="s">
-        <v>124</v>
-      </c>
-      <c r="N186" t="b">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>e98b078b-fa45-6243-4f9b-b63d307f45ae</v>
-      </c>
-      <c r="B187" t="s">
-        <v>111</v>
-      </c>
-      <c r="C187" t="s">
-        <v>112</v>
-      </c>
-      <c r="D187" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E187" t="s">
-        <v>119</v>
-      </c>
-      <c r="F187" t="s">
-        <v>312</v>
-      </c>
-      <c r="G187" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I187" t="s">
-        <v>1002</v>
-      </c>
-      <c r="K187" t="s">
-        <v>312</v>
-      </c>
-      <c r="L187" t="s">
-        <v>1003</v>
-      </c>
-      <c r="M187" t="s">
-        <v>124</v>
-      </c>
-      <c r="N187" t="b">
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A188" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>3f527c8b-613c-d475-df1d-81b5858fd049</v>
-      </c>
-      <c r="B188" t="s">
-        <v>111</v>
-      </c>
-      <c r="C188" t="s">
-        <v>112</v>
-      </c>
-      <c r="D188" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E188" t="s">
-        <v>100</v>
-      </c>
-      <c r="F188" t="s">
-        <v>61</v>
-      </c>
-      <c r="G188" t="s">
-        <v>1006</v>
-      </c>
-      <c r="H188" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="I188" t="s">
-        <v>1008</v>
-      </c>
-      <c r="K188" t="s">
-        <v>74</v>
-      </c>
-      <c r="L188" t="s">
-        <v>1009</v>
-      </c>
-      <c r="M188" t="s">
-        <v>54</v>
-      </c>
-      <c r="N188" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A189" t="str">
-        <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A190" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A191" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A192" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A193" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A194" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A195" t="str">
-        <f t="shared" ref="A195:A258" ca="1" si="4">IF(G195&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A196" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A197" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A198" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A199" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A200" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A201" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A202" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A203" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A204" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A205" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A206" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A207" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A208" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A209" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A210" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A211" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A212" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A213" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A214" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A215" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A216" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A217" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A218" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A219" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A220" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A221" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A222" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A223" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A224" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A225" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A226" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A227" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A228" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A229" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A230" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A231" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A232" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A233" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A234" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A235" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A236" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A237" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A238" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A239" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A240" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A241" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A242" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A243" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A244" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A245" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A246" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A247" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A248" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A249" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A250" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A251" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A252" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A253" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A254" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A255" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A256" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A257" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A258" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A259" t="str">
-        <f t="shared" ref="A259:A322" ca="1" si="5">IF(G259&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A260" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A261" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A262" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A263" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A264" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A265" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A266" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A267" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A268" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A269" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A270" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A271" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A272" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A273" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A274" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A275" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A276" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A277" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A278" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A279" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A280" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A281" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A282" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A283" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A284" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A285" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A286" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A287" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A288" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A289" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A290" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A291" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A292" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A293" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A294" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A295" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A296" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A297" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A298" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A299" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A300" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A301" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A302" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A303" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A304" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A305" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A306" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A307" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A308" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A309" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A310" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A311" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A312" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A313" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A314" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A315" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A316" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A317" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A318" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A319" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A320" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A321" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A322" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A323" t="str">
-        <f t="shared" ref="A323:A386" ca="1" si="6">IF(G323&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A324" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A325" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A326" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A327" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A328" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A329" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A330" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A331" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A332" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A333" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A334" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A335" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A336" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A337" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A338" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A339" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A340" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A341" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A342" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A343" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A344" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A345" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A346" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A347" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A348" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A349" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A350" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A351" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A352" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A353" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A354" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A355" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A356" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A357" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A358" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A359" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A360" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A361" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A362" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A363" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A364" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A365" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A366" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A367" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A368" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A369" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="370" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A370" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="371" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A371" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A372" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="373" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A373" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="374" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A374" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="375" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A375" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="376" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A376" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="377" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A377" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="378" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A378" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="379" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A379" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="380" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A380" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="381" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A381" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="382" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A382" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A383" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="384" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A384" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A385" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A386" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A387" t="str">
-        <f t="shared" ref="A387:A450" ca="1" si="7">IF(G387&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A388" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A389" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A390" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A391" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A392" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A393" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A394" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A395" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A396" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A397" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A398" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A399" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A400" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A401" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A402" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A403" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A404" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A405" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A406" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A407" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="408" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A408" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="409" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A409" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="410" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A410" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="411" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A411" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="412" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A412" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="413" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A413" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="414" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A414" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="415" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A415" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="416" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A416" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="417" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A417" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A418" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A419" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A420" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A421" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="422" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A422" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="423" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A423" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A424" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="425" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A425" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="426" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A426" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="427" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A427" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="428" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A428" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="429" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A429" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="430" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A430" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A431" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A432" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A433" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A434" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A435" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A436" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="437" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A437" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A438" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A439" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A440" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A441" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A442" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="443" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A443" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A444" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A445" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A446" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A447" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A448" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A449" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A450" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A451" t="str">
-        <f t="shared" ref="A451:A514" ca="1" si="8">IF(G451&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A452" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A453" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A454" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A455" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A456" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A457" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="458" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A458" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="459" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A459" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="460" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A460" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="461" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A461" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="462" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A462" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="463" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A463" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="464" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A464" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A465" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A466" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A467" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="468" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A468" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="469" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A469" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="470" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A470" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="471" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A471" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="472" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A472" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="473" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A473" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="474" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A474" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="475" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A475" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="476" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A476" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="477" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A477" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="478" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A478" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="479" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A479" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="480" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A480" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A481" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A482" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A483" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A484" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A485" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A486" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A487" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A488" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A489" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A490" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A491" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A492" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A493" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A494" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A495" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A496" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="497" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A497" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="498" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A498" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="499" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A499" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="500" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A500" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="501" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A501" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="502" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A502" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="503" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A503" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="504" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A504" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="505" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A505" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="506" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A506" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="507" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A507" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="508" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A508" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="509" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A509" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="510" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A510" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="511" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A511" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="512" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A512" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="513" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A513" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="514" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A514" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="515" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A515" t="str">
-        <f t="shared" ref="A515:A578" ca="1" si="9">IF(G515&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="516" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A516" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="517" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A517" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="518" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A518" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="519" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A519" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="520" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A520" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="521" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A521" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="522" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A522" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="523" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A523" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="524" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A524" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="525" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A525" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="526" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A526" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="527" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A527" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="528" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A528" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="529" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A529" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="530" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A530" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="531" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A531" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="532" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A532" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="533" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A533" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="534" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A534" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="535" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A535" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="536" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A536" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="537" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A537" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="538" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A538" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="539" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A539" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="540" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A540" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="541" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A541" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="542" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A542" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="543" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A543" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="544" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A544" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="545" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A545" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="546" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A546" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="547" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A547" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="548" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A548" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="549" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A549" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="550" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A550" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="551" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A551" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="552" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A552" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="553" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A553" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="554" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A554" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="555" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A555" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="556" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A556" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="557" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A557" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="558" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A558" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="559" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A559" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="560" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A560" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="561" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A561" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="562" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A562" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="563" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A563" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="564" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A564" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="565" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A565" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="566" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A566" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="567" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A567" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="568" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A568" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="569" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A569" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="570" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A570" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="571" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A571" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="572" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A572" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="573" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A573" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="574" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A574" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="575" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A575" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="576" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A576" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="577" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A577" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="578" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A578" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-    </row>
-    <row r="579" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A579" t="str">
-        <f t="shared" ref="A579:A642" ca="1" si="10">IF(G579&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="580" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A580" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="581" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A581" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="582" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A582" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="583" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A583" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="584" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A584" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="585" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A585" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="586" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A586" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="587" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A587" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="588" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A588" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="589" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A589" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="590" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A590" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="591" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A591" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="592" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A592" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="593" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A593" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="594" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A594" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="595" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A595" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="596" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A596" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="597" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A597" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="598" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A598" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="599" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A599" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="600" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A600" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="601" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A601" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="602" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A602" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="603" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A603" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="604" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A604" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="605" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A605" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="606" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A606" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="607" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A607" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="608" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A608" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="609" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A609" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="610" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A610" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="611" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A611" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="612" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A612" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="613" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A613" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="614" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A614" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="615" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A615" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="616" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A616" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="617" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A617" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="618" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A618" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="619" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A619" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="620" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A620" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="621" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A621" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="622" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A622" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="623" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A623" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="624" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A624" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="625" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A625" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="626" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A626" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="627" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A627" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="628" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A628" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="629" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A629" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="630" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A630" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="631" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A631" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="632" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A632" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="633" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A633" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="634" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A634" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="635" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A635" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="636" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A636" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="637" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A637" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="638" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A638" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="639" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A639" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="640" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A640" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="641" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A641" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="642" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A642" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="643" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A643" t="str">
-        <f t="shared" ref="A643:A706" ca="1" si="11">IF(G643&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="644" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A644" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="645" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A645" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="646" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A646" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="647" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A647" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="648" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A648" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="649" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A649" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="650" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A650" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="651" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A651" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="652" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A652" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="653" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A653" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="654" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A654" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="655" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A655" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="656" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A656" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="657" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A657" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="658" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A658" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="659" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A659" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="660" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A660" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="661" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A661" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="662" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A662" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="663" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A663" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="664" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A664" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="665" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A665" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="666" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A666" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="667" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A667" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="668" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A668" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="669" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A669" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="670" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A670" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="671" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A671" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="672" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A672" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="673" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A673" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="674" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A674" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="675" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A675" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="676" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A676" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="677" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A677" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="678" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A678" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="679" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A679" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="680" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A680" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="681" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A681" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="682" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A682" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="683" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A683" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="684" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A684" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="685" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A685" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="686" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A686" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="687" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A687" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="688" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A688" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="689" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A689" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="690" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A690" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="691" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A691" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="692" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A692" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="693" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A693" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="694" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A694" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="695" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A695" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="696" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A696" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="697" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A697" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="698" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A698" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="699" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A699" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="700" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A700" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="701" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A701" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="702" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A702" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="703" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A703" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="704" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A704" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="705" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A705" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="706" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A706" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-    </row>
-    <row r="707" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A707" t="str">
-        <f t="shared" ref="A707:A770" ca="1" si="12">IF(G707&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="708" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A708" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="709" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A709" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="710" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A710" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="711" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A711" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="712" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A712" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="713" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A713" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="714" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A714" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="715" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A715" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="716" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A716" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="717" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A717" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="718" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A718" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="719" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A719" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="720" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A720" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="721" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A721" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="722" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A722" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="723" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A723" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="724" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A724" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="725" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A725" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="726" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A726" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="727" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A727" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="728" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A728" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="729" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A729" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="730" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A730" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="731" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A731" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="732" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A732" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="733" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A733" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="734" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A734" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="735" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A735" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="736" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A736" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="737" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A737" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="738" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A738" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="739" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A739" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="740" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A740" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="741" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A741" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="742" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A742" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="743" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A743" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="744" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A744" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="745" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A745" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="746" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A746" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="747" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A747" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="748" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A748" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="749" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A749" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="750" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A750" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="751" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A751" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="752" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A752" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="753" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A753" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="754" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A754" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="755" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A755" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="756" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A756" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="757" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A757" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="758" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A758" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="759" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A759" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="760" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A760" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="761" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A761" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="762" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A762" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="763" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A763" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="764" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A764" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="765" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A765" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="766" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A766" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="767" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A767" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="768" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A768" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="769" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A769" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="770" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A770" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="771" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A771" t="str">
-        <f t="shared" ref="A771:A834" ca="1" si="13">IF(G771&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="772" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A772" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="773" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A773" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="774" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A774" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="775" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A775" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="776" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A776" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="777" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A777" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="778" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A778" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="779" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A779" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="780" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A780" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="781" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A781" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="782" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A782" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="783" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A783" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="784" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A784" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="785" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A785" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="786" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A786" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="787" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A787" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="788" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A788" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="789" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A789" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="790" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A790" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="791" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A791" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="792" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A792" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="793" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A793" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="794" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A794" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="795" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A795" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="796" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A796" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="797" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A797" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="798" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A798" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="799" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A799" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="800" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A800" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="801" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A801" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="802" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A802" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="803" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A803" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="804" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A804" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="805" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A805" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="806" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A806" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="807" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A807" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="808" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A808" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="809" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A809" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="810" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A810" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="811" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A811" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="812" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A812" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="813" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A813" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="814" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A814" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="815" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A815" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="816" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A816" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="817" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A817" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="818" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A818" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="819" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A819" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="820" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A820" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="821" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A821" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="822" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A822" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="823" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A823" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="824" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A824" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="825" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A825" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="826" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A826" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="827" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A827" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="828" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A828" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="829" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A829" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="830" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A830" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="831" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A831" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="832" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A832" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="833" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A833" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="834" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A834" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="835" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A835" t="str">
-        <f t="shared" ref="A835:A898" ca="1" si="14">IF(G835&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="836" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A836" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="837" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A837" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="838" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A838" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="839" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A839" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="840" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A840" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="841" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A841" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="842" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A842" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="843" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A843" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="844" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A844" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="845" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A845" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="846" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A846" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="847" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A847" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="848" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A848" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="849" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A849" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="850" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A850" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="851" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A851" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="852" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A852" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="853" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A853" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="854" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A854" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="855" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A855" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="856" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A856" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="857" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A857" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="858" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A858" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="859" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A859" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="860" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A860" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="861" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A861" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="862" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A862" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="863" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A863" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="864" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A864" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="865" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A865" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="866" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A866" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="867" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A867" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="868" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A868" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="869" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A869" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="870" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A870" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="871" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A871" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="872" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A872" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="873" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A873" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="874" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A874" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="875" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A875" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="876" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A876" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="877" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A877" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="878" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A878" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="879" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A879" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="880" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A880" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="881" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A881" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="882" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A882" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="883" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A883" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="884" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A884" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="885" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A885" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="886" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A886" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="887" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A887" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="888" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A888" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="889" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A889" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="890" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A890" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="891" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A891" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="892" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A892" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="893" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A893" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="894" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A894" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="895" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A895" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="896" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A896" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="897" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A897" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="898" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A898" t="str">
-        <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-    </row>
-    <row r="899" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A899" t="str">
-        <f t="shared" ref="A899:A962" ca="1" si="15">IF(G899&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="900" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A900" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="901" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A901" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="902" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A902" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="903" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A903" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="904" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A904" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="905" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A905" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="906" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A906" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="907" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A907" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="908" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A908" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="909" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A909" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="910" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A910" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="911" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A911" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="912" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A912" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="913" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A913" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="914" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A914" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="915" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A915" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="916" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A916" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="917" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A917" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="918" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A918" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="919" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A919" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="920" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A920" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="921" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A921" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="922" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A922" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="923" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A923" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="924" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A924" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="925" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A925" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="926" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A926" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="927" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A927" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="928" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A928" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="929" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A929" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="930" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A930" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="931" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A931" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="932" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A932" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="933" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A933" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="934" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A934" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="935" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A935" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="936" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A936" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="937" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A937" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="938" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A938" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="939" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A939" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="940" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A940" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="941" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A941" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="942" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A942" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="943" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A943" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="944" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A944" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="945" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A945" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="946" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A946" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="947" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A947" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="948" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A948" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="949" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A949" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="950" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A950" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="951" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A951" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="952" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A952" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="953" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A953" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="954" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A954" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="955" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A955" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="956" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A956" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="957" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A957" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="958" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A958" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="959" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A959" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="960" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A960" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="961" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A961" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="962" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A962" t="str">
-        <f t="shared" ca="1" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="963" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A963" t="str">
-        <f t="shared" ref="A963:A1026" ca="1" si="16">IF(G963&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="964" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A964" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="965" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A965" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="966" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A966" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="967" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A967" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="968" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A968" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="969" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A969" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="970" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A970" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="971" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A971" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="972" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A972" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="973" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A973" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="974" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A974" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="975" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A975" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="976" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A976" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="977" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A977" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="978" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A978" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="979" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A979" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="980" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A980" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="981" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A981" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="982" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A982" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="983" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A983" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="984" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A984" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="985" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A985" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="986" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A986" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="987" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A987" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="988" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A988" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="989" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A989" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="990" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A990" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="991" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A991" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="992" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A992" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="993" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A993" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="994" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A994" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="995" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A995" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="996" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A996" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="997" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A997" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="998" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A998" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="999" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A999" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1000" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1000" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1001" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1001" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1002" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1002" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1003" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1003" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1004" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1004" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1005" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1005" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1006" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1006" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1007" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1007" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1008" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1008" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1009" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1009" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1010" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1010" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1011" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1011" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1012" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1012" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1013" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1013" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1014" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1014" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1015" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1015" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1016" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1016" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1017" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1017" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1018" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1018" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1019" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1019" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1020" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1020" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1021" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1021" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1022" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1022" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1023" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1023" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1024" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1024" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1025" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1025" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1026" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1026" t="str">
-        <f t="shared" ca="1" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1027" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1027" t="str">
-        <f t="shared" ref="A1027:A1090" ca="1" si="17">IF(G1027&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="1028" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1028" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1029" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1029" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1030" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1030" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1031" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1031" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1032" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1032" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1033" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1033" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1034" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1034" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1035" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1035" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1036" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1036" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1037" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1037" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1038" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1038" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1039" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1039" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1040" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1040" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1041" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1041" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1042" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1042" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1043" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1043" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1044" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1044" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1045" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1045" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1046" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1046" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1047" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1047" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1048" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1048" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1049" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1049" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1050" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1050" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1051" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1051" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1052" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1052" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1053" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1053" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1054" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1054" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1055" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1055" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1056" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1056" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1057" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1057" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1058" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1058" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1059" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1059" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1060" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1060" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1061" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1061" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1062" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1062" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1063" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1063" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1064" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1064" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1065" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1065" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1066" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1066" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1067" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1067" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1068" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1068" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1069" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1069" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1070" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1070" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1071" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1071" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1072" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1072" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1073" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1073" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1074" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1074" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1075" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1075" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1076" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1076" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1077" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1077" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1078" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1078" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1079" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1079" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1080" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1080" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1081" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1081" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1082" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1082" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1083" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1083" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1084" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1084" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1085" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1085" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1086" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1086" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1087" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1087" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1088" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1088" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1089" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1089" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1090" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1090" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1091" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1091" t="str">
-        <f t="shared" ref="A1091:A1154" ca="1" si="18">IF(G1091&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="1092" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1092" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1093" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1093" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1094" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1094" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1095" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1095" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1096" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1096" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1097" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1097" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1098" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1098" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1099" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1099" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1100" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1101" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1102" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1103" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1104" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1105" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1106" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1107" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1108" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1109" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1110" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1111" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1112" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1113" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1114" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1115" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1116" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1117" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1118" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1119" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1120" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1121" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1122" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1123" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1124" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1125" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1126" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1127" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1127" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1128" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1128" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1129" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1129" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1130" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1130" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1131" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1131" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1132" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1132" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1133" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1133" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1134" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1134" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1135" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1135" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1136" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1136" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1137" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1138" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1139" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1140" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1141" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1142" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1143" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1144" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1145" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1146" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1147" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1148" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1149" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1150" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1151" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1152" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1153" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1154" t="str">
-        <f t="shared" ca="1" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1155" t="str">
-        <f t="shared" ref="A1155:A1169" ca="1" si="19">IF(G1155&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="1156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1156" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1157" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1158" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1159" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1160" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1161" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1162" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1163" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1164" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1165" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1166" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1167" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1167" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1168" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1168" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
-    </row>
-    <row r="1169" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1169" t="str">
-        <f t="shared" ca="1" si="19"/>
-        <v/>
-      </c>
+      <c r="H188" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22364,19 +16231,19 @@
           <x14:formula1>
             <xm:f>Sheet1!$C$7:$C$13</xm:f>
           </x14:formula1>
-          <xm:sqref>F73:F133 E134:E1048576 E2:E72</xm:sqref>
+          <xm:sqref>F73:F133 E2:E72 E134:E173 E183:E1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F82C379E-17BC-45F0-BE92-97BE1BFDF793}">
           <x14:formula1>
             <xm:f>Sheet1!$A$7:$A$14</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F72 F134:F1048576 G73:G133</xm:sqref>
+          <xm:sqref>F2:F72 G73:G133 F134:F173 F183:F1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6469E828-7DAC-4E27-A0AC-825DA2AE9210}">
           <x14:formula1>
             <xm:f>Sheet1!$B$7:$B$9</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K72 K134:K1048576 L73:L133</xm:sqref>
+          <xm:sqref>K2:K72 L73:L133 K134:K173 K183:K1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -22386,682 +16253,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D278749-E664-410F-B0C8-B3414EA49D59}">
-  <dimension ref="A1:W16"/>
+  <dimension ref="H16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>927</v>
-      </c>
-      <c r="B2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" t="s">
-        <v>928</v>
-      </c>
-      <c r="H2" t="s">
-        <v>929</v>
-      </c>
-      <c r="I2" t="s">
-        <v>930</v>
-      </c>
-      <c r="K2" t="s">
-        <v>74</v>
-      </c>
-      <c r="L2" t="s">
-        <v>931</v>
-      </c>
-      <c r="M2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>932</v>
-      </c>
-      <c r="B3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" t="s">
-        <v>433</v>
-      </c>
-      <c r="E3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" t="s">
-        <v>933</v>
-      </c>
-      <c r="H3" t="s">
-        <v>934</v>
-      </c>
-      <c r="I3" t="s">
-        <v>935</v>
-      </c>
-      <c r="J3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" t="s">
-        <v>936</v>
-      </c>
-      <c r="L3" t="s">
-        <v>197</v>
-      </c>
-      <c r="M3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>937</v>
-      </c>
-      <c r="B4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" t="s">
-        <v>938</v>
-      </c>
-      <c r="E4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" t="s">
-        <v>939</v>
-      </c>
-      <c r="H4" t="s">
-        <v>940</v>
-      </c>
-      <c r="I4" t="s">
-        <v>941</v>
-      </c>
-      <c r="K4" t="s">
-        <v>74</v>
-      </c>
-      <c r="L4" t="s">
-        <v>942</v>
-      </c>
-      <c r="M4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>943</v>
-      </c>
-      <c r="B5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" t="s">
-        <v>944</v>
-      </c>
-      <c r="E5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" t="s">
-        <v>945</v>
-      </c>
-      <c r="H5" t="s">
-        <v>946</v>
-      </c>
-      <c r="I5" t="s">
-        <v>930</v>
-      </c>
-      <c r="K5" t="s">
-        <v>74</v>
-      </c>
-      <c r="L5" t="s">
-        <v>947</v>
-      </c>
-      <c r="M5" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>948</v>
-      </c>
-      <c r="B6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" t="s">
-        <v>949</v>
-      </c>
-      <c r="E6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G6" t="s">
-        <v>950</v>
-      </c>
-      <c r="H6" t="s">
-        <v>951</v>
-      </c>
-      <c r="I6" t="s">
-        <v>952</v>
-      </c>
-      <c r="K6" t="s">
-        <v>74</v>
-      </c>
-      <c r="L6" t="s">
-        <v>953</v>
-      </c>
-      <c r="M6" t="s">
-        <v>124</v>
-      </c>
-      <c r="N6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>954</v>
-      </c>
-      <c r="B7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" t="s">
-        <v>955</v>
-      </c>
-      <c r="E7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" t="s">
-        <v>956</v>
-      </c>
-      <c r="H7" t="s">
-        <v>957</v>
-      </c>
-      <c r="I7" t="s">
-        <v>958</v>
-      </c>
-      <c r="J7" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" t="s">
-        <v>959</v>
-      </c>
-      <c r="L7" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>960</v>
-      </c>
-      <c r="B8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" t="s">
-        <v>961</v>
-      </c>
-      <c r="E8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" t="s">
-        <v>962</v>
-      </c>
-      <c r="I8" t="s">
-        <v>963</v>
-      </c>
-      <c r="J8" t="s">
-        <v>964</v>
-      </c>
-      <c r="K8" t="s">
-        <v>52</v>
-      </c>
-      <c r="L8" t="s">
-        <v>965</v>
-      </c>
-      <c r="M8" t="s">
-        <v>197</v>
-      </c>
-      <c r="N8" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" t="s">
-        <v>60</v>
-      </c>
-      <c r="P8" t="s">
-        <v>47</v>
-      </c>
-      <c r="R8" t="s">
-        <v>963</v>
-      </c>
-      <c r="T8" t="s">
-        <v>64</v>
-      </c>
-      <c r="U8" t="s">
-        <v>47</v>
-      </c>
-      <c r="W8" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>966</v>
-      </c>
-      <c r="B9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" t="s">
-        <v>635</v>
-      </c>
-      <c r="E9" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" t="s">
-        <v>89</v>
-      </c>
-      <c r="G9" t="s">
-        <v>967</v>
-      </c>
-      <c r="H9" t="s">
-        <v>968</v>
-      </c>
-      <c r="I9" t="s">
-        <v>969</v>
-      </c>
-      <c r="K9" t="s">
-        <v>74</v>
-      </c>
-      <c r="L9" t="s">
-        <v>970</v>
-      </c>
-      <c r="M9" t="s">
-        <v>197</v>
-      </c>
-      <c r="N9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>971</v>
-      </c>
-      <c r="B10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" t="s">
-        <v>972</v>
-      </c>
-      <c r="E10" t="s">
-        <v>344</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" t="s">
-        <v>973</v>
-      </c>
-      <c r="H10" t="s">
-        <v>974</v>
-      </c>
-      <c r="I10" t="s">
-        <v>975</v>
-      </c>
-      <c r="K10" t="s">
-        <v>74</v>
-      </c>
-      <c r="L10" t="s">
-        <v>976</v>
-      </c>
-      <c r="M10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>977</v>
-      </c>
-      <c r="B11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" t="s">
-        <v>972</v>
-      </c>
-      <c r="E11" t="s">
-        <v>344</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" t="s">
-        <v>978</v>
-      </c>
-      <c r="H11" t="s">
-        <v>979</v>
-      </c>
-      <c r="I11" t="s">
-        <v>980</v>
-      </c>
-      <c r="J11" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" t="s">
-        <v>981</v>
-      </c>
-      <c r="L11" t="s">
-        <v>197</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>982</v>
-      </c>
-      <c r="B12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" t="s">
-        <v>618</v>
-      </c>
-      <c r="E12" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G12" t="s">
-        <v>983</v>
-      </c>
-      <c r="H12" t="s">
-        <v>984</v>
-      </c>
-      <c r="I12" t="s">
-        <v>985</v>
-      </c>
-      <c r="K12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L12" t="s">
-        <v>986</v>
-      </c>
-      <c r="M12" t="s">
-        <v>197</v>
-      </c>
-      <c r="N12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>987</v>
-      </c>
-      <c r="B13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D13" t="s">
-        <v>988</v>
-      </c>
-      <c r="E13" t="s">
-        <v>989</v>
-      </c>
-      <c r="F13" t="s">
-        <v>341</v>
-      </c>
-      <c r="G13" t="s">
-        <v>990</v>
-      </c>
-      <c r="I13">
-        <v>1638.1</v>
-      </c>
-      <c r="J13" t="s">
-        <v>991</v>
-      </c>
-      <c r="K13" t="s">
-        <v>52</v>
-      </c>
-      <c r="L13" t="s">
-        <v>992</v>
-      </c>
-      <c r="M13" t="s">
-        <v>197</v>
-      </c>
-      <c r="N13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>993</v>
-      </c>
-      <c r="B14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D14" t="s">
-        <v>994</v>
-      </c>
-      <c r="E14" t="s">
-        <v>106</v>
-      </c>
-      <c r="F14" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" t="s">
-        <v>995</v>
-      </c>
-      <c r="H14" t="s">
-        <v>996</v>
-      </c>
-      <c r="I14" t="s">
-        <v>997</v>
-      </c>
-      <c r="K14" t="s">
-        <v>74</v>
-      </c>
-      <c r="L14" t="s">
-        <v>998</v>
-      </c>
-      <c r="M14" t="s">
-        <v>124</v>
-      </c>
-      <c r="N14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>999</v>
-      </c>
-      <c r="B15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" t="s">
-        <v>312</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1001</v>
-      </c>
-      <c r="I15" t="s">
-        <v>1002</v>
-      </c>
-      <c r="K15" t="s">
-        <v>312</v>
-      </c>
-      <c r="L15" t="s">
-        <v>1003</v>
-      </c>
-      <c r="M15" t="s">
-        <v>124</v>
-      </c>
-      <c r="N15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1006</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="I16" t="s">
-        <v>1008</v>
-      </c>
-      <c r="K16" t="s">
-        <v>74</v>
-      </c>
-      <c r="L16" t="s">
-        <v>1009</v>
-      </c>
-      <c r="M16" t="s">
-        <v>54</v>
-      </c>
-      <c r="N16" t="b">
-        <v>1</v>
-      </c>
+    <row r="16" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H16" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/questions-template.xlsx
+++ b/templates/questions-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frcltd-my.sharepoint.com/personal/r_marks_frc_org_uk/Documents/Desktop/sbr/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="11_E9F32361FE4863DD78B1E2FB72030FF8208E8B85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1443B30-0358-475D-AAF6-2F98BE6AB3CA}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="11_E9F32361FE4863DD78B1E2FB72030FF8208E8B85" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37385D2A-D5F6-4101-9189-485C90BD27F8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,8 +34,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3584" uniqueCount="969">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3573" uniqueCount="964">
   <si>
     <t>id</t>
   </si>
@@ -1177,18 +1199,6 @@
     <t>The entity must **continue to assess the arrangement**. If all criteria are met later, it applies the IFRS 15 revenue recognition model from that point.</t>
   </si>
   <si>
-    <t>Revenue recognition model</t>
-  </si>
-  <si>
-    <t>Which standard is titled Revenue from Contracts with Customers?</t>
-  </si>
-  <si>
-    <t>IAS 18|IFRS 9|IFRS 15|IFRS 18</t>
-  </si>
-  <si>
-    <t>The applicable standard is **IFRS 15 Revenue from Contracts with Customers**.</t>
-  </si>
-  <si>
     <t>Identifying performance obligations</t>
   </si>
   <si>
@@ -2441,9 +2451,6 @@
   </si>
   <si>
     <t>Continuation</t>
-  </si>
-  <si>
-    <t>Standard</t>
   </si>
   <si>
     <t>Application</t>
@@ -3816,7 +3823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR188"/>
+  <dimension ref="A1:AR190"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.5546875" bestFit="1" customWidth="1"/>
@@ -4002,7 +4009,7 @@
     <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" t="str">
         <f ca="1">IF(G2&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>042bbda0-1a8a-3866-bcbb-85172ea65dc4</v>
+        <v>3f271924-94a7-eaa2-dd9b-385da20eb2e9</v>
       </c>
       <c r="B2" t="s">
         <v>336</v>
@@ -4136,8 +4143,8 @@
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
-        <f t="shared" ref="A3:A66" ca="1" si="0">IF(G3&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>b16c6690-a07e-4dee-b3cd-9045bcb3946a</v>
+        <f t="shared" ref="A3:A65" ca="1" si="0">IF(G3&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+        <v>dd63d314-3164-b204-5a5c-d7ef40e8da32</v>
       </c>
       <c r="B3" t="s">
         <v>336</v>
@@ -4272,7 +4279,7 @@
     <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>e2151e68-47cf-6367-2662-122ed87520eb</v>
+        <v>45533a8d-ecf1-b628-7d7a-6ca17c05eb2f</v>
       </c>
       <c r="B4" t="s">
         <v>336</v>
@@ -4407,7 +4414,7 @@
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>8fc1b16a-5a19-0183-1c95-058733b6a518</v>
+        <v>7c290480-8361-d3be-b447-d6e4bec33e37</v>
       </c>
       <c r="B5" t="s">
         <v>336</v>
@@ -4542,7 +4549,7 @@
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>b6caae70-8940-7527-a521-dfefb2acfe46</v>
+        <v>1881aa2a-1946-fd85-36b5-58bccac75392</v>
       </c>
       <c r="B6" t="s">
         <v>336</v>
@@ -4677,7 +4684,7 @@
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>939a39a8-4477-5ede-97ce-398cb991c74f</v>
+        <v>ac29a116-5ac0-eec1-8c7d-a166d9f3b201</v>
       </c>
       <c r="B7" t="s">
         <v>336</v>
@@ -4812,7 +4819,7 @@
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a6bea27c-6c0f-1f57-7858-77048ec06c4e</v>
+        <v>b9d3628d-10a6-40e2-c40e-97fc4db8fc54</v>
       </c>
       <c r="B8" t="s">
         <v>336</v>
@@ -4947,7 +4954,7 @@
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>44c190d3-18ce-43ef-7f30-6bc9153d2f90</v>
+        <v>474acd37-667c-32d5-9f63-bf309e43ce97</v>
       </c>
       <c r="B9" t="s">
         <v>336</v>
@@ -5082,7 +5089,7 @@
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>da813287-2e6b-4682-e383-369511e2b940</v>
+        <v>2e2b3c4a-aea9-e4cd-32ba-957e48087ff8</v>
       </c>
       <c r="B10" t="s">
         <v>336</v>
@@ -5217,7 +5224,7 @@
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>3226c3c9-b3bd-992e-8e8a-b52ec7c5e7a9</v>
+        <v>cc5d8d55-f120-f841-b674-c35c46722a72</v>
       </c>
       <c r="B11" t="s">
         <v>336</v>
@@ -5352,7 +5359,7 @@
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>1b322049-30b0-61cd-4b78-45609cf6ac34</v>
+        <v>c8211e11-003a-0c6f-e743-e19b2a62b968</v>
       </c>
       <c r="B12" t="s">
         <v>336</v>
@@ -5487,7 +5494,7 @@
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>4407906e-533d-2a68-2a4e-8f7c7c1b8683</v>
+        <v>05b7b20b-4e4f-68ef-7e8d-32f7b969c3d3</v>
       </c>
       <c r="B13" t="s">
         <v>336</v>
@@ -5622,7 +5629,7 @@
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>aeb0d49a-a609-7381-dfea-37a1a8c77247</v>
+        <v>7acbeacf-aaa4-1b56-37c9-b303cc9830bd</v>
       </c>
       <c r="B14" t="s">
         <v>336</v>
@@ -5757,7 +5764,7 @@
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>9e8e52e1-5065-518a-8bae-b79405cc5120</v>
+        <v>0b7af9de-a164-f21a-1894-66cc7a1022d0</v>
       </c>
       <c r="B15" t="s">
         <v>336</v>
@@ -5892,7 +5899,7 @@
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>52847ea7-3c94-2c3b-e232-7d457d8827dd</v>
+        <v>bf59c18c-e3b4-0c0b-bd9d-a260239dce03</v>
       </c>
       <c r="B16" t="s">
         <v>336</v>
@@ -6027,7 +6034,7 @@
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>6fd17891-811c-9ba3-9005-1e0d3adfbf28</v>
+        <v>62b7927d-99c3-91cd-ad03-08881940eea9</v>
       </c>
       <c r="B17" t="s">
         <v>336</v>
@@ -6162,7 +6169,7 @@
     <row r="18" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>f4c01e85-13ee-2c02-ff5a-82ffae60a1d5</v>
+        <v>e4674913-43cf-5a0c-04c2-5d5dfd4f5f69</v>
       </c>
       <c r="B18" t="s">
         <v>336</v>
@@ -6297,7 +6304,7 @@
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a182bc2e-4cd8-b648-44c5-3ff72ff67c24</v>
+        <v>c459af77-6b70-ca0c-5864-35022fb2b5ab</v>
       </c>
       <c r="B19" t="s">
         <v>336</v>
@@ -6432,7 +6439,7 @@
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>f21da402-9bed-d2f6-4704-777424e1e96b</v>
+        <v>86cb1002-f603-4dbb-0a02-96c2ce692210</v>
       </c>
       <c r="B20" t="s">
         <v>336</v>
@@ -6567,7 +6574,7 @@
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>97a12639-c865-eb04-19fa-d63a87eb709a</v>
+        <v>7b3ec990-dcda-57c2-d20e-5dddd01c02d4</v>
       </c>
       <c r="B21" t="s">
         <v>336</v>
@@ -6702,7 +6709,7 @@
     <row r="22" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>6c27b91e-9980-91a4-4e23-baa2bd936b50</v>
+        <v>8b18b0cc-fc0c-07c3-33b6-ae88cd14cf36</v>
       </c>
       <c r="B22" t="s">
         <v>336</v>
@@ -6837,7 +6844,7 @@
     <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2b0e8352-6361-df5e-016f-e2bb93a6118d</v>
+        <v>0d349a17-4bcd-b279-b664-9a1480fd27f0</v>
       </c>
       <c r="B23" t="s">
         <v>336</v>
@@ -6972,7 +6979,7 @@
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>cd1833ba-c3d3-d1f5-a631-4afb85cfa8d7</v>
+        <v>5eb64e6b-251c-a348-9752-11581e9979ca</v>
       </c>
       <c r="B24" t="s">
         <v>336</v>
@@ -7107,7 +7114,7 @@
     <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>e6916029-cdb5-cd59-4b20-390aa2a87f93</v>
+        <v>586f327e-6ca9-2834-eddd-bd59c853524c</v>
       </c>
       <c r="B25" t="s">
         <v>336</v>
@@ -7242,7 +7249,7 @@
     <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>83e8b48d-db63-bb69-c234-a227b8a96fa0</v>
+        <v>26b98f8c-c218-66ef-b687-cc778e03cbd6</v>
       </c>
       <c r="B26" t="s">
         <v>336</v>
@@ -7377,7 +7384,7 @@
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>43c80bde-02f9-9b0e-edbe-ec6b5e1c915b</v>
+        <v>5c0aef27-65fa-229f-f200-48e0031d476f</v>
       </c>
       <c r="B27" t="s">
         <v>336</v>
@@ -7512,7 +7519,7 @@
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>a2e3a295-eec6-720b-b0eb-8cfee6bb4b28</v>
+        <v>92ddd977-01f8-348d-968b-afe1daa57e8a</v>
       </c>
       <c r="B28" t="s">
         <v>336</v>
@@ -7647,7 +7654,7 @@
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>780e8608-f968-6000-02d3-7d1d87481560</v>
+        <v>203292a9-bdec-73bf-a648-69c336ba90d5</v>
       </c>
       <c r="B29" t="s">
         <v>336</v>
@@ -7782,7 +7789,7 @@
     <row r="30" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>f830a610-9454-fe2c-901f-11709b539b8c</v>
+        <v>0224b44b-1446-63e3-065d-02be4b1450c4</v>
       </c>
       <c r="B30" t="s">
         <v>336</v>
@@ -7917,7 +7924,7 @@
     <row r="31" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>317c814e-b77f-bbe1-0f2d-e455545e2a9f</v>
+        <v>162ee1cd-7899-14d2-6e2c-ef1933d21b9b</v>
       </c>
       <c r="B31" t="s">
         <v>336</v>
@@ -8052,7 +8059,7 @@
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2ef5ecb0-30af-1685-9168-edfba36923d8</v>
+        <v>c9a5abe8-7107-74db-ab9b-fccab9c1d216</v>
       </c>
       <c r="B32" t="s">
         <v>336</v>
@@ -8187,7 +8194,7 @@
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>c37d4681-8483-0fd3-26b0-4fe3f75ee4bc</v>
+        <v>eca81995-456b-2aef-5f58-1d9c539301f6</v>
       </c>
       <c r="B33" t="s">
         <v>336</v>
@@ -8322,7 +8329,7 @@
     <row r="34" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>7a7ecc3a-0b82-2256-33e7-a35128a6e1a2</v>
+        <v>0a579e1c-0cd6-03e3-1de7-71554ee4596c</v>
       </c>
       <c r="B34" t="s">
         <v>336</v>
@@ -8457,7 +8464,7 @@
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>f11bcac8-9e48-cb26-c14f-ece2135c459a</v>
+        <v>4b6de2de-0ab8-6ab5-1b2d-d144aeeaa5eb</v>
       </c>
       <c r="B35" t="s">
         <v>336</v>
@@ -8592,7 +8599,7 @@
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>242ca766-38b6-1643-1e1b-15ae54900817</v>
+        <v>4e598090-fb82-b662-f749-c816322e054a</v>
       </c>
       <c r="B36" t="s">
         <v>336</v>
@@ -8727,7 +8734,7 @@
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>5bbc67c3-b2dc-791b-a45d-c72d12911bb7</v>
+        <v>de90fc1a-3dbc-f22d-85f3-8859473bfd40</v>
       </c>
       <c r="B37" t="s">
         <v>336</v>
@@ -8862,7 +8869,7 @@
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>0ee0a54e-1915-d910-c59d-45948016a5b8</v>
+        <v>b8d5131a-0c5d-911c-c4d1-8dd248d37869</v>
       </c>
       <c r="B38" t="s">
         <v>336</v>
@@ -8997,7 +9004,7 @@
     <row r="39" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>0e219420-ca9c-4923-d984-0950f567046a</v>
+        <v>63b9d7a9-173b-44b7-58ae-b03bc91e5e50</v>
       </c>
       <c r="B39" t="s">
         <v>336</v>
@@ -9132,7 +9139,7 @@
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>57392130-639a-5f63-8e43-c588b51b54b4</v>
+        <v>17c13a46-4e8a-1f32-398f-0520aa32f2b4</v>
       </c>
       <c r="B40" t="s">
         <v>336</v>
@@ -9267,7 +9274,7 @@
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>6bd0118b-d74d-39b5-dfe1-834c7f004d90</v>
+        <v>6bb13c88-c5b0-571b-cdba-4ae2a5c445df</v>
       </c>
       <c r="B41" t="s">
         <v>336</v>
@@ -9402,7 +9409,7 @@
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>08461f0e-78e7-78c1-f20f-fcf01c12dadf</v>
+        <v>2dc07347-b6ae-c8d5-a454-39d5ded93f03</v>
       </c>
       <c r="B42" t="s">
         <v>336</v>
@@ -9537,7 +9544,7 @@
     <row r="43" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>69d49b98-0e8e-4a91-b128-3728532855d3</v>
+        <v>ea7f5ce3-4de6-c49a-1cd4-5b05230d05c9</v>
       </c>
       <c r="B43" t="s">
         <v>336</v>
@@ -9672,7 +9679,7 @@
     <row r="44" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>69f99a22-2d98-dd91-f4b9-4bef9dbc2ea8</v>
+        <v>d16ff3dc-c118-e0e7-205b-577ebb8de462</v>
       </c>
       <c r="B44" t="s">
         <v>336</v>
@@ -9807,7 +9814,7 @@
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>66501066-aa6d-6099-8ac0-2dd00c63174d</v>
+        <v>a1aa68c8-9396-149f-e02b-5caa4361b6ec</v>
       </c>
       <c r="B45" t="s">
         <v>336</v>
@@ -9942,7 +9949,7 @@
     <row r="46" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>02068c69-7e13-158f-fc8c-cb996e771feb</v>
+        <v>8e29cf11-a39a-a897-43d1-a456cb85e924</v>
       </c>
       <c r="B46" t="s">
         <v>111</v>
@@ -10038,7 +10045,7 @@
     <row r="47" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>d8993f6b-6fc5-478a-5469-e66167a83181</v>
+        <v>a48eb943-3251-d14e-9750-d631f71d0afb</v>
       </c>
       <c r="B47" t="s">
         <v>111</v>
@@ -10080,7 +10087,7 @@
     <row r="48" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>5ed721b3-06a2-4eca-6e89-f92e27ed4d7b</v>
+        <v>4eaa1a8f-960c-9134-ac9b-0b385be843ad</v>
       </c>
       <c r="B48" t="s">
         <v>111</v>
@@ -10122,7 +10129,7 @@
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2ec40969-6cdd-bfae-7918-eb25819c8761</v>
+        <v>7b9764c0-c848-2317-6690-f6c7c0352a96</v>
       </c>
       <c r="B49" t="s">
         <v>111</v>
@@ -10164,7 +10171,7 @@
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>6617e6e0-363d-9eae-52b7-1933098e8487</v>
+        <v>e3c17738-24b5-4556-057d-80fad52f2de0</v>
       </c>
       <c r="B50" t="s">
         <v>111</v>
@@ -10206,7 +10213,7 @@
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>829133c6-4ada-42d6-7fa1-2e0c62023e0d</v>
+        <v>f0fe7139-df6e-61f5-1e5c-be9244ab2faa</v>
       </c>
       <c r="B51" t="s">
         <v>111</v>
@@ -10218,10 +10225,10 @@
         <v>380</v>
       </c>
       <c r="E51" t="s">
-        <v>802</v>
+        <v>46</v>
       </c>
       <c r="F51" t="s">
-        <v>342</v>
+        <v>89</v>
       </c>
       <c r="G51" t="s">
         <v>381</v>
@@ -10230,13 +10237,13 @@
         <v>382</v>
       </c>
       <c r="I51" t="s">
-        <v>111</v>
+        <v>383</v>
       </c>
       <c r="K51" t="s">
         <v>74</v>
       </c>
       <c r="L51" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M51" t="s">
         <v>54</v>
@@ -10248,7 +10255,7 @@
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>f9b268c0-d296-0283-0601-41f3db93dfc5</v>
+        <v>66efb24f-4ec3-6e82-e3c8-9651301e8cad</v>
       </c>
       <c r="B52" t="s">
         <v>111</v>
@@ -10257,40 +10264,58 @@
         <v>112</v>
       </c>
       <c r="D52" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E52" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="F52" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="G52" t="s">
         <v>385</v>
       </c>
-      <c r="H52" t="s">
+      <c r="K52" t="s">
+        <v>52</v>
+      </c>
+      <c r="L52" t="s">
         <v>386</v>
-      </c>
-      <c r="I52" t="s">
-        <v>387</v>
-      </c>
-      <c r="K52" t="s">
-        <v>74</v>
-      </c>
-      <c r="L52" t="s">
-        <v>388</v>
       </c>
       <c r="M52" t="s">
         <v>54</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
+      </c>
+      <c r="O52" t="s">
+        <v>387</v>
+      </c>
+      <c r="P52" t="s">
+        <v>47</v>
+      </c>
+      <c r="R52" t="s">
+        <v>388</v>
+      </c>
+      <c r="S52" t="s">
+        <v>389</v>
+      </c>
+      <c r="T52" t="s">
+        <v>390</v>
+      </c>
+      <c r="U52" t="s">
+        <v>47</v>
+      </c>
+      <c r="W52" t="s">
+        <v>391</v>
+      </c>
+      <c r="X52" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>07d274ec-0798-c5f2-5672-6e6d9c5d7686</v>
+        <v>071ae078-b66a-c088-7035-e435a3510191</v>
       </c>
       <c r="B53" t="s">
         <v>111</v>
@@ -10299,58 +10324,40 @@
         <v>112</v>
       </c>
       <c r="D53" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E53" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F53" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G53" t="s">
-        <v>389</v>
+        <v>393</v>
+      </c>
+      <c r="H53" t="s">
+        <v>394</v>
+      </c>
+      <c r="I53" t="s">
+        <v>395</v>
       </c>
       <c r="K53" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L53" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="M53" t="s">
         <v>54</v>
       </c>
       <c r="N53" t="b">
         <v>1</v>
-      </c>
-      <c r="O53" t="s">
-        <v>391</v>
-      </c>
-      <c r="P53" t="s">
-        <v>47</v>
-      </c>
-      <c r="R53" t="s">
-        <v>392</v>
-      </c>
-      <c r="S53" t="s">
-        <v>393</v>
-      </c>
-      <c r="T53" t="s">
-        <v>394</v>
-      </c>
-      <c r="U53" t="s">
-        <v>47</v>
-      </c>
-      <c r="W53" t="s">
-        <v>395</v>
-      </c>
-      <c r="X53" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>56846715-7f13-327c-4736-913e17eeb8a8</v>
+        <v>6ffab4cf-d0f2-8b98-dd95-0e0230bc64c0</v>
       </c>
       <c r="B54" t="s">
         <v>111</v>
@@ -10359,13 +10366,13 @@
         <v>112</v>
       </c>
       <c r="D54" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E54" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="F54" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G54" t="s">
         <v>397</v>
@@ -10392,7 +10399,7 @@
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>cdadbd0f-381e-be71-2ede-119b30fd9872</v>
+        <v>eee73786-0ce7-558f-f530-be5e2bfea3d5</v>
       </c>
       <c r="B55" t="s">
         <v>111</v>
@@ -10401,31 +10408,31 @@
         <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E55" t="s">
-        <v>100</v>
+        <v>798</v>
       </c>
       <c r="F55" t="s">
-        <v>95</v>
+        <v>341</v>
       </c>
       <c r="G55" t="s">
         <v>401</v>
       </c>
-      <c r="H55" t="s">
+      <c r="I55">
+        <v>4</v>
+      </c>
+      <c r="J55" t="s">
         <v>402</v>
       </c>
-      <c r="I55" t="s">
+      <c r="K55" t="s">
+        <v>52</v>
+      </c>
+      <c r="L55" t="s">
         <v>403</v>
       </c>
-      <c r="K55" t="s">
-        <v>74</v>
-      </c>
-      <c r="L55" t="s">
-        <v>404</v>
-      </c>
       <c r="M55" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N55" t="b">
         <v>1</v>
@@ -10434,7 +10441,7 @@
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>9623777f-76dc-8da1-10af-0c00faeb3b8f</v>
+        <v>0f272426-4ace-4125-3f18-9b3f1dbda4e1</v>
       </c>
       <c r="B56" t="s">
         <v>111</v>
@@ -10443,25 +10450,25 @@
         <v>112</v>
       </c>
       <c r="D56" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E56" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="F56" t="s">
-        <v>341</v>
+        <v>95</v>
       </c>
       <c r="G56" t="s">
+        <v>404</v>
+      </c>
+      <c r="H56" t="s">
         <v>405</v>
       </c>
-      <c r="I56">
-        <v>4</v>
-      </c>
-      <c r="J56" t="s">
+      <c r="I56" t="s">
         <v>406</v>
       </c>
       <c r="K56" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L56" t="s">
         <v>407</v>
@@ -10476,7 +10483,7 @@
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ab5cdf84-7dc5-7016-bae6-780b2716de8a</v>
+        <v>733b9233-8991-e8bd-7e36-ef4759e7e1e1</v>
       </c>
       <c r="B57" t="s">
         <v>111</v>
@@ -10485,31 +10492,31 @@
         <v>112</v>
       </c>
       <c r="D57" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="E57" t="s">
-        <v>803</v>
+        <v>106</v>
       </c>
       <c r="F57" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="G57" t="s">
-        <v>408</v>
-      </c>
-      <c r="H57" t="s">
         <v>409</v>
       </c>
       <c r="I57" t="s">
         <v>410</v>
       </c>
+      <c r="J57" t="s">
+        <v>411</v>
+      </c>
       <c r="K57" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L57" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M57" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N57" t="b">
         <v>1</v>
@@ -10518,7 +10525,7 @@
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>192a8eb4-b21c-008d-ab39-3f10145bb67a</v>
+        <v>ef48a047-d7a1-da6d-5b45-818785f7e96a</v>
       </c>
       <c r="B58" t="s">
         <v>111</v>
@@ -10527,25 +10534,25 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E58" t="s">
         <v>106</v>
       </c>
       <c r="F58" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s">
         <v>413</v>
       </c>
+      <c r="H58" t="s">
+        <v>414</v>
+      </c>
       <c r="I58" t="s">
-        <v>414</v>
-      </c>
-      <c r="J58" t="s">
         <v>415</v>
       </c>
       <c r="K58" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L58" t="s">
         <v>416</v>
@@ -10560,7 +10567,7 @@
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>1a9fff3c-a017-41bc-f191-8b7d17711d23</v>
+        <v>d9afa3b0-76ef-2e3d-7ddd-30fd2c0fc634</v>
       </c>
       <c r="B59" t="s">
         <v>111</v>
@@ -10569,28 +10576,28 @@
         <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E59" t="s">
         <v>106</v>
       </c>
       <c r="F59" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G59" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H59" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I59" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K59" t="s">
         <v>74</v>
       </c>
       <c r="L59" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M59" t="s">
         <v>54</v>
@@ -10602,7 +10609,7 @@
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>0f39206e-7688-b946-3ae0-67da75110178</v>
+        <v>0be7628e-84b5-db7e-af21-fbd52c9d36c9</v>
       </c>
       <c r="B60" t="s">
         <v>111</v>
@@ -10611,40 +10618,58 @@
         <v>112</v>
       </c>
       <c r="D60" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E60" t="s">
         <v>106</v>
       </c>
       <c r="F60" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G60" t="s">
         <v>422</v>
       </c>
-      <c r="H60" t="s">
-        <v>423</v>
-      </c>
-      <c r="I60" t="s">
-        <v>424</v>
-      </c>
       <c r="K60" t="s">
         <v>74</v>
       </c>
       <c r="L60" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="M60" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N60" t="b">
         <v>1</v>
+      </c>
+      <c r="O60" t="s">
+        <v>424</v>
+      </c>
+      <c r="P60" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>425</v>
+      </c>
+      <c r="R60" t="s">
+        <v>426</v>
+      </c>
+      <c r="T60" t="s">
+        <v>427</v>
+      </c>
+      <c r="U60" t="s">
+        <v>61</v>
+      </c>
+      <c r="V60" t="s">
+        <v>425</v>
+      </c>
+      <c r="W60" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>52e13fbe-7a54-e580-1ffe-a4bf26942340</v>
+        <v>588062d6-cb36-8eb0-57bd-7e2b93b386bf</v>
       </c>
       <c r="B61" t="s">
         <v>111</v>
@@ -10653,58 +10678,40 @@
         <v>112</v>
       </c>
       <c r="D61" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E61" t="s">
         <v>106</v>
       </c>
       <c r="F61" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="G61" t="s">
-        <v>426</v>
+        <v>430</v>
+      </c>
+      <c r="H61" t="s">
+        <v>431</v>
+      </c>
+      <c r="I61" t="s">
+        <v>432</v>
       </c>
       <c r="K61" t="s">
         <v>74</v>
       </c>
       <c r="L61" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="M61" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
-      </c>
-      <c r="O61" t="s">
-        <v>428</v>
-      </c>
-      <c r="P61" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>429</v>
-      </c>
-      <c r="R61" t="s">
-        <v>430</v>
-      </c>
-      <c r="T61" t="s">
-        <v>431</v>
-      </c>
-      <c r="U61" t="s">
-        <v>61</v>
-      </c>
-      <c r="V61" t="s">
-        <v>429</v>
-      </c>
-      <c r="W61" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>29ce2a55-e336-8138-1162-4a901922364e</v>
+        <v>aa41c100-8d1d-4276-d627-61502f52bd92</v>
       </c>
       <c r="B62" t="s">
         <v>111</v>
@@ -10713,40 +10720,58 @@
         <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E62" t="s">
-        <v>106</v>
+        <v>344</v>
       </c>
       <c r="F62" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="G62" t="s">
         <v>434</v>
       </c>
-      <c r="H62" t="s">
+      <c r="K62" t="s">
+        <v>52</v>
+      </c>
+      <c r="L62" t="s">
         <v>435</v>
       </c>
-      <c r="I62" t="s">
-        <v>436</v>
-      </c>
-      <c r="K62" t="s">
-        <v>74</v>
-      </c>
-      <c r="L62" t="s">
-        <v>437</v>
-      </c>
       <c r="M62" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N62" t="b">
         <v>1</v>
+      </c>
+      <c r="O62" t="s">
+        <v>436</v>
+      </c>
+      <c r="P62" t="s">
+        <v>47</v>
+      </c>
+      <c r="R62" t="s">
+        <v>437</v>
+      </c>
+      <c r="S62" t="s">
+        <v>438</v>
+      </c>
+      <c r="T62" t="s">
+        <v>439</v>
+      </c>
+      <c r="U62" t="s">
+        <v>47</v>
+      </c>
+      <c r="W62" t="s">
+        <v>440</v>
+      </c>
+      <c r="X62" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>c30017f1-1799-6125-7d4b-9225d32e1118</v>
+        <v>cc5cf4be-cc01-07dc-1840-df8fc2486cd7</v>
       </c>
       <c r="B63" t="s">
         <v>111</v>
@@ -10755,58 +10780,40 @@
         <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E63" t="s">
-        <v>344</v>
+        <v>106</v>
       </c>
       <c r="F63" t="s">
-        <v>57</v>
+        <v>341</v>
       </c>
       <c r="G63" t="s">
-        <v>438</v>
+        <v>442</v>
+      </c>
+      <c r="I63" t="s">
+        <v>443</v>
+      </c>
+      <c r="J63" t="s">
+        <v>444</v>
       </c>
       <c r="K63" t="s">
         <v>52</v>
       </c>
       <c r="L63" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="M63" t="s">
         <v>197</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
-      </c>
-      <c r="O63" t="s">
-        <v>440</v>
-      </c>
-      <c r="P63" t="s">
-        <v>47</v>
-      </c>
-      <c r="R63" t="s">
-        <v>441</v>
-      </c>
-      <c r="S63" t="s">
-        <v>442</v>
-      </c>
-      <c r="T63" t="s">
-        <v>443</v>
-      </c>
-      <c r="U63" t="s">
-        <v>47</v>
-      </c>
-      <c r="W63" t="s">
-        <v>444</v>
-      </c>
-      <c r="X63" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>e2e4aab4-f2fd-eecb-83b1-bf381a276d35</v>
+        <v>f340dcee-f28e-adfc-4a62-1023537a3741</v>
       </c>
       <c r="B64" t="s">
         <v>111</v>
@@ -10815,40 +10822,58 @@
         <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="E64" t="s">
         <v>106</v>
       </c>
       <c r="F64" t="s">
-        <v>341</v>
+        <v>57</v>
       </c>
       <c r="G64" t="s">
-        <v>446</v>
-      </c>
-      <c r="I64" t="s">
         <v>447</v>
-      </c>
-      <c r="J64" t="s">
-        <v>448</v>
       </c>
       <c r="K64" t="s">
         <v>52</v>
       </c>
       <c r="L64" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M64" t="s">
         <v>197</v>
       </c>
       <c r="N64" t="b">
         <v>1</v>
+      </c>
+      <c r="O64" t="s">
+        <v>449</v>
+      </c>
+      <c r="P64" t="s">
+        <v>47</v>
+      </c>
+      <c r="R64" t="s">
+        <v>450</v>
+      </c>
+      <c r="S64" t="s">
+        <v>451</v>
+      </c>
+      <c r="T64" t="s">
+        <v>452</v>
+      </c>
+      <c r="U64" t="s">
+        <v>47</v>
+      </c>
+      <c r="W64" t="s">
+        <v>453</v>
+      </c>
+      <c r="X64" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>69bd5c39-1d97-95d8-098b-3c772db95f98</v>
+        <v>5a18fe3a-99df-8fa9-d516-f4dd210709bb</v>
       </c>
       <c r="B65" t="s">
         <v>111</v>
@@ -10857,7 +10882,7 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>450</v>
+        <v>417</v>
       </c>
       <c r="E65" t="s">
         <v>106</v>
@@ -10866,13 +10891,13 @@
         <v>57</v>
       </c>
       <c r="G65" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K65" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L65" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="M65" t="s">
         <v>197</v>
@@ -10881,34 +10906,34 @@
         <v>1</v>
       </c>
       <c r="O65" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="P65" t="s">
         <v>47</v>
       </c>
-      <c r="R65" t="s">
-        <v>454</v>
+      <c r="R65">
+        <v>90000</v>
       </c>
       <c r="S65" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="T65" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="U65" t="s">
         <v>47</v>
       </c>
-      <c r="W65" t="s">
-        <v>457</v>
+      <c r="W65">
+        <v>1500</v>
       </c>
       <c r="X65" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="66" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A66" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>bdd9dd41-dccf-0010-cb2e-dc99ef606170</v>
+        <f t="shared" ref="A66:A129" ca="1" si="1">IF(G66&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+        <v>98064354-62ed-4b6b-ade2-735aebab4217</v>
       </c>
       <c r="B66" t="s">
         <v>111</v>
@@ -10917,58 +10942,40 @@
         <v>112</v>
       </c>
       <c r="D66" t="s">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="E66" t="s">
         <v>106</v>
       </c>
       <c r="F66" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G66" t="s">
-        <v>459</v>
+        <v>462</v>
+      </c>
+      <c r="I66" t="s">
+        <v>463</v>
+      </c>
+      <c r="J66" t="s">
+        <v>464</v>
       </c>
       <c r="K66" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L66" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="M66" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N66" t="b">
         <v>1</v>
       </c>
-      <c r="O66" t="s">
-        <v>461</v>
-      </c>
-      <c r="P66" t="s">
-        <v>47</v>
-      </c>
-      <c r="R66">
-        <v>90000</v>
-      </c>
-      <c r="S66" t="s">
-        <v>462</v>
-      </c>
-      <c r="T66" t="s">
-        <v>463</v>
-      </c>
-      <c r="U66" t="s">
-        <v>47</v>
-      </c>
-      <c r="W66">
-        <v>1500</v>
-      </c>
-      <c r="X66" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="67" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A67" t="str">
-        <f t="shared" ref="A67:A130" ca="1" si="1">IF(G67&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>b90668bd-4e6a-8df9-6229-a46c74f5a789</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>92d54a44-8199-8064-8e66-95943e54b635</v>
       </c>
       <c r="B67" t="s">
         <v>111</v>
@@ -10977,40 +10984,58 @@
         <v>112</v>
       </c>
       <c r="D67" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E67" t="s">
         <v>106</v>
       </c>
       <c r="F67" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G67" t="s">
         <v>466</v>
       </c>
-      <c r="I67" t="s">
-        <v>467</v>
-      </c>
-      <c r="J67" t="s">
-        <v>468</v>
-      </c>
       <c r="K67" t="s">
         <v>52</v>
       </c>
       <c r="L67" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="M67" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N67" t="b">
         <v>1</v>
+      </c>
+      <c r="O67" t="s">
+        <v>468</v>
+      </c>
+      <c r="P67" t="s">
+        <v>47</v>
+      </c>
+      <c r="R67">
+        <v>19950</v>
+      </c>
+      <c r="S67" t="s">
+        <v>469</v>
+      </c>
+      <c r="T67" t="s">
+        <v>470</v>
+      </c>
+      <c r="U67" t="s">
+        <v>47</v>
+      </c>
+      <c r="W67">
+        <v>1050</v>
+      </c>
+      <c r="X67" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>39b8282d-df20-88eb-e87e-bd24080396de</v>
+        <v>4b08c604-bf02-8f83-d34b-dfa6d2260bb9</v>
       </c>
       <c r="B68" t="s">
         <v>111</v>
@@ -11019,58 +11044,37 @@
         <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="E68" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F68" t="s">
-        <v>57</v>
+        <v>312</v>
       </c>
       <c r="G68" t="s">
-        <v>470</v>
+        <v>473</v>
+      </c>
+      <c r="I68" t="s">
+        <v>474</v>
       </c>
       <c r="K68" t="s">
-        <v>52</v>
+        <v>312</v>
       </c>
       <c r="L68" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="M68" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N68" t="b">
         <v>1</v>
-      </c>
-      <c r="O68" t="s">
-        <v>472</v>
-      </c>
-      <c r="P68" t="s">
-        <v>47</v>
-      </c>
-      <c r="R68">
-        <v>19950</v>
-      </c>
-      <c r="S68" t="s">
-        <v>473</v>
-      </c>
-      <c r="T68" t="s">
-        <v>474</v>
-      </c>
-      <c r="U68" t="s">
-        <v>47</v>
-      </c>
-      <c r="W68">
-        <v>1050</v>
-      </c>
-      <c r="X68" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>3ed06f21-0e72-837d-289a-f271982ccb18</v>
+        <v>d2285ba9-dd88-8542-156f-18845f3b680b</v>
       </c>
       <c r="B69" t="s">
         <v>111</v>
@@ -11109,7 +11113,7 @@
     <row r="70" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>eb747caa-e933-7158-abc4-d4c1602dcb26</v>
+        <v>5ac0d0cc-25b7-3c46-ae91-a049f4fada51</v>
       </c>
       <c r="B70" t="s">
         <v>111</v>
@@ -11124,19 +11128,22 @@
         <v>100</v>
       </c>
       <c r="F70" t="s">
-        <v>312</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s">
         <v>481</v>
       </c>
+      <c r="H70" t="s">
+        <v>482</v>
+      </c>
       <c r="I70" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K70" t="s">
-        <v>312</v>
+        <v>74</v>
       </c>
       <c r="L70" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M70" t="s">
         <v>54</v>
@@ -11148,7 +11155,7 @@
     <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>7ed8040f-555e-2796-5e47-f975fb73c5a7</v>
+        <v>138054f4-0a0d-0da9-a183-aff9b5d1c103</v>
       </c>
       <c r="B71" t="s">
         <v>111</v>
@@ -11157,31 +11164,31 @@
         <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E71" t="s">
-        <v>100</v>
+        <v>798</v>
       </c>
       <c r="F71" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G71" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H71" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I71" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K71" t="s">
         <v>74</v>
       </c>
       <c r="L71" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M71" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="N71" t="b">
         <v>1</v>
@@ -11190,7 +11197,7 @@
     <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>384a4191-b886-9ad9-5959-553a9cb97c19</v>
+        <v>ea4c080b-adf9-5317-13ef-09751bc81383</v>
       </c>
       <c r="B72" t="s">
         <v>111</v>
@@ -11199,31 +11206,31 @@
         <v>112</v>
       </c>
       <c r="D72" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E72" t="s">
-        <v>803</v>
+        <v>100</v>
       </c>
       <c r="F72" t="s">
         <v>95</v>
       </c>
       <c r="G72" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H72" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I72" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K72" t="s">
         <v>74</v>
       </c>
       <c r="L72" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M72" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="N72" t="b">
         <v>1</v>
@@ -11232,7 +11239,7 @@
     <row r="73" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ff6a97d4-df73-c847-fa23-82f2c88995bd</v>
+        <v>32c4e27f-f28f-a527-8f3c-d35368aaf093</v>
       </c>
       <c r="B73" t="s">
         <v>111</v>
@@ -11241,13 +11248,13 @@
         <v>112</v>
       </c>
       <c r="D73" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E73" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F73" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G73" t="s">
         <v>495</v>
@@ -11274,7 +11281,7 @@
     <row r="74" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>69e3aa6a-251c-5604-3f58-94255dc95c00</v>
+        <v>1ff29409-7466-3c29-eba8-0bf7afb18214</v>
       </c>
       <c r="B74" t="s">
         <v>111</v>
@@ -11283,28 +11290,28 @@
         <v>112</v>
       </c>
       <c r="D74" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E74" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="F74" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G74" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H74" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I74" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K74" t="s">
         <v>74</v>
       </c>
       <c r="L74" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M74" t="s">
         <v>54</v>
@@ -11316,7 +11323,7 @@
     <row r="75" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>08411e9c-0a61-b490-8463-fc0938f3a320</v>
+        <v>470b7776-6bf9-90db-7547-271972167a46</v>
       </c>
       <c r="B75" t="s">
         <v>111</v>
@@ -11325,13 +11332,13 @@
         <v>112</v>
       </c>
       <c r="D75" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E75" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F75" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G75" t="s">
         <v>504</v>
@@ -11349,7 +11356,7 @@
         <v>507</v>
       </c>
       <c r="M75" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N75" t="b">
         <v>1</v>
@@ -11358,7 +11365,7 @@
     <row r="76" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>45a16661-7d94-43dd-84a5-1cbb142d53fb</v>
+        <v>232e8776-b118-f991-b74f-6cf8aae6ad8e</v>
       </c>
       <c r="B76" t="s">
         <v>111</v>
@@ -11367,31 +11374,31 @@
         <v>112</v>
       </c>
       <c r="D76" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E76" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="F76" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="G76" t="s">
-        <v>508</v>
-      </c>
-      <c r="H76" t="s">
         <v>509</v>
       </c>
       <c r="I76" t="s">
         <v>510</v>
       </c>
+      <c r="J76" t="s">
+        <v>511</v>
+      </c>
       <c r="K76" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L76" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M76" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
@@ -11400,7 +11407,7 @@
     <row r="77" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>a2fb110d-7ad6-8c41-b7c8-e87a32e40912</v>
+        <v>09d21bc3-1f3c-f12d-16e4-425e38a94c2d</v>
       </c>
       <c r="B77" t="s">
         <v>111</v>
@@ -11409,25 +11416,25 @@
         <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="E77" t="s">
         <v>106</v>
       </c>
       <c r="F77" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="G77" t="s">
         <v>513</v>
       </c>
+      <c r="H77" t="s">
+        <v>514</v>
+      </c>
       <c r="I77" t="s">
-        <v>514</v>
-      </c>
-      <c r="J77" t="s">
         <v>515</v>
       </c>
       <c r="K77" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L77" t="s">
         <v>516</v>
@@ -11442,7 +11449,7 @@
     <row r="78" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>219a848d-6c26-1ddf-51ec-a0ac46a2e0e0</v>
+        <v>9540ba0c-6cb1-5733-8017-3078ac66e1b3</v>
       </c>
       <c r="B78" t="s">
         <v>111</v>
@@ -11451,40 +11458,70 @@
         <v>112</v>
       </c>
       <c r="D78" t="s">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="E78" t="s">
         <v>106</v>
       </c>
       <c r="F78" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="G78" t="s">
-        <v>517</v>
-      </c>
-      <c r="H78" t="s">
         <v>518</v>
       </c>
-      <c r="I78" t="s">
+      <c r="K78" t="s">
+        <v>52</v>
+      </c>
+      <c r="L78" t="s">
         <v>519</v>
       </c>
-      <c r="K78" t="s">
-        <v>74</v>
-      </c>
-      <c r="L78" t="s">
-        <v>520</v>
-      </c>
       <c r="M78" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="N78" t="b">
         <v>1</v>
+      </c>
+      <c r="O78" t="s">
+        <v>520</v>
+      </c>
+      <c r="P78" t="s">
+        <v>47</v>
+      </c>
+      <c r="R78" t="s">
+        <v>521</v>
+      </c>
+      <c r="S78" t="s">
+        <v>522</v>
+      </c>
+      <c r="T78" t="s">
+        <v>523</v>
+      </c>
+      <c r="U78" t="s">
+        <v>47</v>
+      </c>
+      <c r="W78" t="s">
+        <v>524</v>
+      </c>
+      <c r="X78" t="s">
+        <v>525</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>526</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>527</v>
+      </c>
+      <c r="AB78" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="79" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>542e14e2-b43e-9877-8f40-395093b9ac65</v>
+        <v>0410ea99-b080-7871-4085-37b43955100b</v>
       </c>
       <c r="B79" t="s">
         <v>111</v>
@@ -11493,70 +11530,70 @@
         <v>112</v>
       </c>
       <c r="D79" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="E79" t="s">
-        <v>106</v>
+        <v>344</v>
       </c>
       <c r="F79" t="s">
         <v>57</v>
       </c>
       <c r="G79" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="K79" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L79" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="M79" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
       </c>
       <c r="O79" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="P79" t="s">
-        <v>47</v>
+        <v>61</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>533</v>
       </c>
       <c r="R79" t="s">
-        <v>525</v>
-      </c>
-      <c r="S79" t="s">
-        <v>526</v>
+        <v>122</v>
       </c>
       <c r="T79" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="U79" t="s">
-        <v>47</v>
+        <v>61</v>
+      </c>
+      <c r="V79" t="s">
+        <v>533</v>
       </c>
       <c r="W79" t="s">
-        <v>528</v>
-      </c>
-      <c r="X79" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="Y79" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="Z79" t="s">
         <v>61</v>
       </c>
       <c r="AA79" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AB79" t="s">
-        <v>532</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>8cde7031-8dd9-586e-a9b1-6cc080b3a756</v>
+        <v>ff86f897-08e2-4698-30c4-d2fd07ee6f5a</v>
       </c>
       <c r="B80" t="s">
         <v>111</v>
@@ -11565,70 +11602,40 @@
         <v>112</v>
       </c>
       <c r="D80" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="E80" t="s">
-        <v>344</v>
+        <v>100</v>
       </c>
       <c r="F80" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s">
-        <v>534</v>
+        <v>538</v>
+      </c>
+      <c r="H80" t="s">
+        <v>539</v>
+      </c>
+      <c r="I80" t="s">
+        <v>540</v>
       </c>
       <c r="K80" t="s">
         <v>74</v>
       </c>
       <c r="L80" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="M80" t="s">
         <v>54</v>
       </c>
       <c r="N80" t="b">
         <v>1</v>
-      </c>
-      <c r="O80" t="s">
-        <v>536</v>
-      </c>
-      <c r="P80" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>537</v>
-      </c>
-      <c r="R80" t="s">
-        <v>122</v>
-      </c>
-      <c r="T80" t="s">
-        <v>538</v>
-      </c>
-      <c r="U80" t="s">
-        <v>61</v>
-      </c>
-      <c r="V80" t="s">
-        <v>537</v>
-      </c>
-      <c r="W80" t="s">
-        <v>539</v>
-      </c>
-      <c r="Y80" t="s">
-        <v>540</v>
-      </c>
-      <c r="Z80" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA80" t="s">
-        <v>537</v>
-      </c>
-      <c r="AB80" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ff25a3f0-90dc-a1a3-bc6c-85950084faff</v>
+        <v>d11d7e64-fd12-24d6-35ce-300e1ba1d9f2</v>
       </c>
       <c r="B81" t="s">
         <v>111</v>
@@ -11637,13 +11644,13 @@
         <v>112</v>
       </c>
       <c r="D81" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E81" t="s">
         <v>100</v>
       </c>
       <c r="F81" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G81" t="s">
         <v>542</v>
@@ -11652,13 +11659,13 @@
         <v>543</v>
       </c>
       <c r="I81" t="s">
-        <v>544</v>
+        <v>420</v>
       </c>
       <c r="K81" t="s">
         <v>74</v>
       </c>
       <c r="L81" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="M81" t="s">
         <v>54</v>
@@ -11670,7 +11677,7 @@
     <row r="82" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>c4b12133-5121-08c8-ef11-6048cf7d6f76</v>
+        <v>17ba7d8f-63ce-b2b7-771f-6c5f1c2495c0</v>
       </c>
       <c r="B82" t="s">
         <v>111</v>
@@ -11679,22 +11686,22 @@
         <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E82" t="s">
-        <v>100</v>
+        <v>798</v>
       </c>
       <c r="F82" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G82" t="s">
+        <v>545</v>
+      </c>
+      <c r="H82" t="s">
         <v>546</v>
       </c>
-      <c r="H82" t="s">
+      <c r="I82" t="s">
         <v>547</v>
-      </c>
-      <c r="I82" t="s">
-        <v>424</v>
       </c>
       <c r="K82" t="s">
         <v>74</v>
@@ -11703,7 +11710,7 @@
         <v>548</v>
       </c>
       <c r="M82" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
@@ -11712,7 +11719,7 @@
     <row r="83" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>4458ab7a-40b7-765e-8338-76108d41545c</v>
+        <v>3dbb24bb-e232-1921-c7d4-32f4f9b37742</v>
       </c>
       <c r="B83" t="s">
         <v>111</v>
@@ -11721,40 +11728,58 @@
         <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E83" t="s">
-        <v>803</v>
+        <v>344</v>
       </c>
       <c r="F83" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="G83" t="s">
         <v>549</v>
       </c>
-      <c r="H83" t="s">
+      <c r="K83" t="s">
+        <v>52</v>
+      </c>
+      <c r="L83" t="s">
         <v>550</v>
-      </c>
-      <c r="I83" t="s">
-        <v>551</v>
-      </c>
-      <c r="K83" t="s">
-        <v>74</v>
-      </c>
-      <c r="L83" t="s">
-        <v>552</v>
       </c>
       <c r="M83" t="s">
         <v>197</v>
       </c>
       <c r="N83" t="b">
         <v>1</v>
+      </c>
+      <c r="O83" t="s">
+        <v>436</v>
+      </c>
+      <c r="P83" t="s">
+        <v>47</v>
+      </c>
+      <c r="R83" t="s">
+        <v>551</v>
+      </c>
+      <c r="S83" t="s">
+        <v>552</v>
+      </c>
+      <c r="T83" t="s">
+        <v>439</v>
+      </c>
+      <c r="U83" t="s">
+        <v>47</v>
+      </c>
+      <c r="W83" t="s">
+        <v>553</v>
+      </c>
+      <c r="X83" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="84" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ddde5c1b-6316-1061-77cd-3005e73b88a2</v>
+        <v>54251bd2-c469-f98f-da8f-9685a3e15d04</v>
       </c>
       <c r="B84" t="s">
         <v>111</v>
@@ -11763,7 +11788,7 @@
         <v>112</v>
       </c>
       <c r="D84" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E84" t="s">
         <v>344</v>
@@ -11772,13 +11797,13 @@
         <v>57</v>
       </c>
       <c r="G84" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K84" t="s">
         <v>52</v>
       </c>
       <c r="L84" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M84" t="s">
         <v>197</v>
@@ -11787,34 +11812,34 @@
         <v>1</v>
       </c>
       <c r="O84" t="s">
-        <v>440</v>
+        <v>557</v>
       </c>
       <c r="P84" t="s">
         <v>47</v>
       </c>
       <c r="R84" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="S84" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="T84" t="s">
-        <v>443</v>
+        <v>560</v>
       </c>
       <c r="U84" t="s">
         <v>47</v>
       </c>
       <c r="W84" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="X84" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="85" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>42b75a73-134d-e4ae-704b-53211749faa3</v>
+        <v>bf221a66-a326-5465-500e-7ae75a71b6fd</v>
       </c>
       <c r="B85" t="s">
         <v>111</v>
@@ -11823,58 +11848,40 @@
         <v>112</v>
       </c>
       <c r="D85" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E85" t="s">
-        <v>344</v>
+        <v>106</v>
       </c>
       <c r="F85" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="G85" t="s">
-        <v>559</v>
+        <v>563</v>
+      </c>
+      <c r="H85" t="s">
+        <v>564</v>
+      </c>
+      <c r="I85" t="s">
+        <v>565</v>
       </c>
       <c r="K85" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L85" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="M85" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="N85" t="b">
         <v>1</v>
-      </c>
-      <c r="O85" t="s">
-        <v>561</v>
-      </c>
-      <c r="P85" t="s">
-        <v>47</v>
-      </c>
-      <c r="R85" t="s">
-        <v>562</v>
-      </c>
-      <c r="S85" t="s">
-        <v>563</v>
-      </c>
-      <c r="T85" t="s">
-        <v>564</v>
-      </c>
-      <c r="U85" t="s">
-        <v>47</v>
-      </c>
-      <c r="W85" t="s">
-        <v>565</v>
-      </c>
-      <c r="X85" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="86" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>71f99644-369a-1cbd-4719-7cc1835c6782</v>
+        <v>ba6d8f30-d0f9-15aa-5b99-9aabb1a56f9b</v>
       </c>
       <c r="B86" t="s">
         <v>111</v>
@@ -11883,7 +11890,7 @@
         <v>112</v>
       </c>
       <c r="D86" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E86" t="s">
         <v>106</v>
@@ -11897,17 +11904,17 @@
       <c r="H86" t="s">
         <v>568</v>
       </c>
-      <c r="I86" t="s">
-        <v>569</v>
+      <c r="I86" s="2">
+        <v>10000</v>
       </c>
       <c r="K86" t="s">
         <v>74</v>
       </c>
       <c r="L86" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="M86" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="N86" t="b">
         <v>1</v>
@@ -11916,7 +11923,7 @@
     <row r="87" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>c1294a99-34c5-fdd7-1c52-3a56545f8a00</v>
+        <v>741c1231-49e1-4a54-0a6b-61764cb5e5ab</v>
       </c>
       <c r="B87" t="s">
         <v>111</v>
@@ -11925,13 +11932,13 @@
         <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>541</v>
+        <v>570</v>
       </c>
       <c r="E87" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F87" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G87" t="s">
         <v>571</v>
@@ -11939,17 +11946,17 @@
       <c r="H87" t="s">
         <v>572</v>
       </c>
-      <c r="I87" s="2">
-        <v>10000</v>
+      <c r="I87" t="s">
+        <v>573</v>
       </c>
       <c r="K87" t="s">
         <v>74</v>
       </c>
       <c r="L87" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M87" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N87" t="b">
         <v>1</v>
@@ -11958,7 +11965,7 @@
     <row r="88" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>58431291-fd2e-5d26-1f2c-5558b7d72e5a</v>
+        <v>0b2b037f-021d-497d-9f8f-48d5f6f7da6a</v>
       </c>
       <c r="B88" t="s">
         <v>111</v>
@@ -11967,13 +11974,13 @@
         <v>112</v>
       </c>
       <c r="D88" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E88" t="s">
         <v>119</v>
       </c>
       <c r="F88" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G88" t="s">
         <v>575</v>
@@ -12000,7 +12007,7 @@
     <row r="89" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>933083b2-52bc-b29e-885d-2e4d2c9cf392</v>
+        <v>51f05779-802e-0cd5-7863-9d79105f507e</v>
       </c>
       <c r="B89" t="s">
         <v>111</v>
@@ -12009,7 +12016,7 @@
         <v>112</v>
       </c>
       <c r="D89" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E89" t="s">
         <v>119</v>
@@ -12033,7 +12040,7 @@
         <v>582</v>
       </c>
       <c r="M89" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N89" t="b">
         <v>1</v>
@@ -12042,7 +12049,7 @@
     <row r="90" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>50ecc509-0f93-45e6-d466-c2bf36f8b479</v>
+        <v>366eab39-b0dc-64ae-cdea-c8a58008d1a0</v>
       </c>
       <c r="B90" t="s">
         <v>111</v>
@@ -12051,40 +12058,70 @@
         <v>112</v>
       </c>
       <c r="D90" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E90" t="s">
         <v>119</v>
       </c>
       <c r="F90" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="G90" t="s">
         <v>583</v>
       </c>
-      <c r="H90" t="s">
-        <v>584</v>
-      </c>
-      <c r="I90" t="s">
-        <v>585</v>
-      </c>
       <c r="K90" t="s">
         <v>74</v>
       </c>
       <c r="L90" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="M90" t="s">
         <v>197</v>
       </c>
       <c r="N90" t="b">
         <v>1</v>
+      </c>
+      <c r="O90" t="s">
+        <v>585</v>
+      </c>
+      <c r="P90" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>586</v>
+      </c>
+      <c r="R90" t="s">
+        <v>587</v>
+      </c>
+      <c r="T90" t="s">
+        <v>588</v>
+      </c>
+      <c r="U90" t="s">
+        <v>61</v>
+      </c>
+      <c r="V90" t="s">
+        <v>586</v>
+      </c>
+      <c r="W90" t="s">
+        <v>589</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>590</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>591</v>
+      </c>
+      <c r="AB90" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="91" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>f5a9bad7-baaa-645e-5cb7-db84b66bf489</v>
+        <v>d977e833-d042-143a-6284-4df6b4a125eb</v>
       </c>
       <c r="B91" t="s">
         <v>111</v>
@@ -12093,70 +12130,40 @@
         <v>112</v>
       </c>
       <c r="D91" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="E91" t="s">
-        <v>119</v>
+        <v>344</v>
       </c>
       <c r="F91" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G91" t="s">
-        <v>587</v>
+        <v>594</v>
+      </c>
+      <c r="H91" t="s">
+        <v>595</v>
+      </c>
+      <c r="I91" t="s">
+        <v>596</v>
       </c>
       <c r="K91" t="s">
         <v>74</v>
       </c>
       <c r="L91" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="M91" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N91" t="b">
         <v>1</v>
-      </c>
-      <c r="O91" t="s">
-        <v>589</v>
-      </c>
-      <c r="P91" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>590</v>
-      </c>
-      <c r="R91" t="s">
-        <v>591</v>
-      </c>
-      <c r="T91" t="s">
-        <v>592</v>
-      </c>
-      <c r="U91" t="s">
-        <v>61</v>
-      </c>
-      <c r="V91" t="s">
-        <v>590</v>
-      </c>
-      <c r="W91" t="s">
-        <v>593</v>
-      </c>
-      <c r="Y91" t="s">
-        <v>594</v>
-      </c>
-      <c r="Z91" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA91" t="s">
-        <v>595</v>
-      </c>
-      <c r="AB91" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="92" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>aeb2c0b2-bee5-926b-8b59-2a74172a1d56</v>
+        <v>10dbc739-085a-d54e-f456-133c76b2b03e</v>
       </c>
       <c r="B92" t="s">
         <v>111</v>
@@ -12165,13 +12172,13 @@
         <v>112</v>
       </c>
       <c r="D92" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E92" t="s">
         <v>344</v>
       </c>
       <c r="F92" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G92" t="s">
         <v>598</v>
@@ -12198,7 +12205,7 @@
     <row r="93" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>0c4e6b28-f929-3273-6959-6888c1635e71</v>
+        <v>bebd267b-b62a-41e2-513f-d99379f37a7e</v>
       </c>
       <c r="B93" t="s">
         <v>111</v>
@@ -12207,13 +12214,13 @@
         <v>112</v>
       </c>
       <c r="D93" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E93" t="s">
-        <v>344</v>
+        <v>119</v>
       </c>
       <c r="F93" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G93" t="s">
         <v>602</v>
@@ -12240,7 +12247,7 @@
     <row r="94" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>276a4b25-1992-8855-2192-3b146afdd0b5</v>
+        <v>300eb991-5f81-882b-382d-0c74fcc40b84</v>
       </c>
       <c r="B94" t="s">
         <v>111</v>
@@ -12249,13 +12256,13 @@
         <v>112</v>
       </c>
       <c r="D94" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E94" t="s">
-        <v>119</v>
+        <v>798</v>
       </c>
       <c r="F94" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G94" t="s">
         <v>606</v>
@@ -12273,7 +12280,7 @@
         <v>609</v>
       </c>
       <c r="M94" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N94" t="b">
         <v>1</v>
@@ -12282,7 +12289,7 @@
     <row r="95" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>da61c75b-0271-8cc8-1ca5-5a46c2fddf48</v>
+        <v>b97ec37e-4cfd-2d82-fc8b-ec98e486d053</v>
       </c>
       <c r="B95" t="s">
         <v>111</v>
@@ -12291,31 +12298,31 @@
         <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E95" t="s">
-        <v>803</v>
+        <v>100</v>
       </c>
       <c r="F95" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="G95" t="s">
         <v>610</v>
       </c>
-      <c r="H95" t="s">
+      <c r="I95" t="s">
         <v>611</v>
       </c>
-      <c r="I95" t="s">
+      <c r="J95" t="s">
         <v>612</v>
       </c>
       <c r="K95" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L95" t="s">
         <v>613</v>
       </c>
       <c r="M95" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N95" t="b">
         <v>1</v>
@@ -12324,7 +12331,7 @@
     <row r="96" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>0759baa6-eb80-0db8-97ae-19eadfdaa877</v>
+        <v>a5ffd76c-41a0-b276-3bd7-f237a5f75a7a</v>
       </c>
       <c r="B96" t="s">
         <v>111</v>
@@ -12333,31 +12340,31 @@
         <v>112</v>
       </c>
       <c r="D96" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="E96" t="s">
         <v>100</v>
       </c>
       <c r="F96" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="G96" t="s">
-        <v>614</v>
+        <v>615</v>
+      </c>
+      <c r="H96" t="s">
+        <v>616</v>
       </c>
       <c r="I96" t="s">
-        <v>615</v>
-      </c>
-      <c r="J96" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K96" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L96" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M96" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N96" t="b">
         <v>1</v>
@@ -12366,7 +12373,7 @@
     <row r="97" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>a411c358-cfcb-972f-aaa4-9ffa765c9b3c</v>
+        <v>51ca0c9b-5794-3f99-4958-dcb6a3e2fc2a</v>
       </c>
       <c r="B97" t="s">
         <v>111</v>
@@ -12375,40 +12382,58 @@
         <v>112</v>
       </c>
       <c r="D97" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="E97" t="s">
         <v>100</v>
       </c>
       <c r="F97" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="G97" t="s">
         <v>619</v>
       </c>
-      <c r="H97" t="s">
+      <c r="K97" t="s">
+        <v>52</v>
+      </c>
+      <c r="L97" t="s">
         <v>620</v>
       </c>
-      <c r="I97" t="s">
-        <v>621</v>
-      </c>
-      <c r="K97" t="s">
-        <v>74</v>
-      </c>
-      <c r="L97" t="s">
-        <v>622</v>
-      </c>
       <c r="M97" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N97" t="b">
         <v>1</v>
+      </c>
+      <c r="O97" t="s">
+        <v>621</v>
+      </c>
+      <c r="P97" t="s">
+        <v>47</v>
+      </c>
+      <c r="R97" t="s">
+        <v>622</v>
+      </c>
+      <c r="S97" t="s">
+        <v>623</v>
+      </c>
+      <c r="T97" t="s">
+        <v>624</v>
+      </c>
+      <c r="U97" t="s">
+        <v>47</v>
+      </c>
+      <c r="W97" t="s">
+        <v>625</v>
+      </c>
+      <c r="X97" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="98" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>4185e0a4-a02d-fb15-1b3e-e07a72f05513</v>
+        <v>304fdd8d-d755-7fbe-4ffb-a566c8a50c75</v>
       </c>
       <c r="B98" t="s">
         <v>111</v>
@@ -12417,58 +12442,40 @@
         <v>112</v>
       </c>
       <c r="D98" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="E98" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F98" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G98" t="s">
-        <v>623</v>
+        <v>627</v>
+      </c>
+      <c r="H98" t="s">
+        <v>628</v>
+      </c>
+      <c r="I98" t="s">
+        <v>629</v>
       </c>
       <c r="K98" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L98" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="M98" t="s">
         <v>54</v>
       </c>
       <c r="N98" t="b">
         <v>1</v>
-      </c>
-      <c r="O98" t="s">
-        <v>625</v>
-      </c>
-      <c r="P98" t="s">
-        <v>47</v>
-      </c>
-      <c r="R98" t="s">
-        <v>626</v>
-      </c>
-      <c r="S98" t="s">
-        <v>627</v>
-      </c>
-      <c r="T98" t="s">
-        <v>628</v>
-      </c>
-      <c r="U98" t="s">
-        <v>47</v>
-      </c>
-      <c r="W98" t="s">
-        <v>629</v>
-      </c>
-      <c r="X98" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="99" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>5c037389-564d-b386-9aea-9a5d51ca566b</v>
+        <v>fb8eff58-e354-891a-6087-79558ef95b91</v>
       </c>
       <c r="B99" t="s">
         <v>111</v>
@@ -12477,31 +12484,31 @@
         <v>112</v>
       </c>
       <c r="D99" t="s">
-        <v>618</v>
+        <v>631</v>
       </c>
       <c r="E99" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="F99" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G99" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H99" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="I99" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="K99" t="s">
         <v>74</v>
       </c>
       <c r="L99" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M99" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N99" t="b">
         <v>1</v>
@@ -12510,7 +12517,7 @@
     <row r="100" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>23df0869-5c1a-e973-08b0-72753fabc52e</v>
+        <v>516f0317-d5b5-7c7a-ec71-539705fc45af</v>
       </c>
       <c r="B100" t="s">
         <v>111</v>
@@ -12519,31 +12526,31 @@
         <v>112</v>
       </c>
       <c r="D100" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E100" t="s">
         <v>100</v>
       </c>
       <c r="F100" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="G100" t="s">
         <v>636</v>
       </c>
-      <c r="H100" t="s">
+      <c r="I100" t="s">
         <v>637</v>
       </c>
-      <c r="I100" t="s">
+      <c r="J100" t="s">
         <v>638</v>
       </c>
       <c r="K100" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L100" t="s">
         <v>639</v>
       </c>
       <c r="M100" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N100" t="b">
         <v>1</v>
@@ -12552,7 +12559,7 @@
     <row r="101" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A101" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>aeb47f64-60de-d264-7c21-9dcd0d85674b</v>
+        <v>89856b0e-2fca-8792-6b49-e629e77f0a3b</v>
       </c>
       <c r="B101" t="s">
         <v>111</v>
@@ -12561,40 +12568,58 @@
         <v>112</v>
       </c>
       <c r="D101" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="E101" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F101" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G101" t="s">
-        <v>640</v>
-      </c>
-      <c r="I101" t="s">
         <v>641</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
+        <v>74</v>
+      </c>
+      <c r="L101" t="s">
         <v>642</v>
       </c>
-      <c r="K101" t="s">
-        <v>52</v>
-      </c>
-      <c r="L101" t="s">
-        <v>643</v>
-      </c>
       <c r="M101" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N101" t="b">
         <v>1</v>
+      </c>
+      <c r="O101" t="s">
+        <v>643</v>
+      </c>
+      <c r="P101" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>644</v>
+      </c>
+      <c r="R101" t="s">
+        <v>228</v>
+      </c>
+      <c r="T101" t="s">
+        <v>645</v>
+      </c>
+      <c r="U101" t="s">
+        <v>61</v>
+      </c>
+      <c r="V101" t="s">
+        <v>644</v>
+      </c>
+      <c r="W101" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="102" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A102" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>5d7a215e-d8cf-7e36-29c9-e26ffbf5fcf7</v>
+        <v>b2efb979-6336-05cb-c8c9-823699856b9f</v>
       </c>
       <c r="B102" t="s">
         <v>111</v>
@@ -12603,58 +12628,40 @@
         <v>112</v>
       </c>
       <c r="D102" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E102" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="F102" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="G102" t="s">
-        <v>645</v>
+        <v>647</v>
+      </c>
+      <c r="H102" t="s">
+        <v>648</v>
+      </c>
+      <c r="I102" t="s">
+        <v>649</v>
       </c>
       <c r="K102" t="s">
         <v>74</v>
       </c>
       <c r="L102" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="M102" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N102" t="b">
         <v>1</v>
-      </c>
-      <c r="O102" t="s">
-        <v>647</v>
-      </c>
-      <c r="P102" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>648</v>
-      </c>
-      <c r="R102" t="s">
-        <v>228</v>
-      </c>
-      <c r="T102" t="s">
-        <v>649</v>
-      </c>
-      <c r="U102" t="s">
-        <v>61</v>
-      </c>
-      <c r="V102" t="s">
-        <v>648</v>
-      </c>
-      <c r="W102" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="103" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A103" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>9a3a2482-a54a-09c2-ad07-e4727199bca0</v>
+        <v>05eaa450-9223-b9c7-b4ca-50e74e938584</v>
       </c>
       <c r="B103" t="s">
         <v>111</v>
@@ -12663,10 +12670,10 @@
         <v>112</v>
       </c>
       <c r="D103" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E103" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F103" t="s">
         <v>95</v>
@@ -12687,7 +12694,7 @@
         <v>654</v>
       </c>
       <c r="M103" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N103" t="b">
         <v>1</v>
@@ -12696,7 +12703,7 @@
     <row r="104" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A104" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>6b77684c-7e6b-c5e0-b12b-e8c6dc83f328</v>
+        <v>83639d05-0560-1c1c-7f11-84efd87f5562</v>
       </c>
       <c r="B104" t="s">
         <v>111</v>
@@ -12705,7 +12712,7 @@
         <v>112</v>
       </c>
       <c r="D104" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E104" t="s">
         <v>119</v>
@@ -12720,13 +12727,13 @@
         <v>656</v>
       </c>
       <c r="I104" t="s">
-        <v>657</v>
+        <v>228</v>
       </c>
       <c r="K104" t="s">
         <v>74</v>
       </c>
       <c r="L104" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="M104" t="s">
         <v>197</v>
@@ -12738,7 +12745,7 @@
     <row r="105" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A105" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>49e226f8-a65a-a470-585f-960337e73489</v>
+        <v>57742392-6577-7c65-9955-0e1e2f1b764a</v>
       </c>
       <c r="B105" t="s">
         <v>111</v>
@@ -12747,22 +12754,22 @@
         <v>112</v>
       </c>
       <c r="D105" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E105" t="s">
         <v>119</v>
       </c>
       <c r="F105" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G105" t="s">
+        <v>658</v>
+      </c>
+      <c r="H105" t="s">
         <v>659</v>
       </c>
-      <c r="H105" t="s">
+      <c r="I105" t="s">
         <v>660</v>
-      </c>
-      <c r="I105" t="s">
-        <v>228</v>
       </c>
       <c r="K105" t="s">
         <v>74</v>
@@ -12771,7 +12778,7 @@
         <v>661</v>
       </c>
       <c r="M105" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="N105" t="b">
         <v>1</v>
@@ -12780,7 +12787,7 @@
     <row r="106" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A106" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>625b0a73-bc2c-2318-80e9-36df0f959a4a</v>
+        <v>6608cb58-423a-588c-3b30-cf43f796ff11</v>
       </c>
       <c r="B106" t="s">
         <v>111</v>
@@ -12789,40 +12796,94 @@
         <v>112</v>
       </c>
       <c r="D106" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E106" t="s">
         <v>119</v>
       </c>
       <c r="F106" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G106" t="s">
         <v>662</v>
       </c>
-      <c r="H106" t="s">
-        <v>663</v>
-      </c>
-      <c r="I106" t="s">
-        <v>664</v>
-      </c>
       <c r="K106" t="s">
         <v>74</v>
       </c>
       <c r="L106" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="M106" t="s">
         <v>124</v>
       </c>
       <c r="N106" t="b">
         <v>1</v>
+      </c>
+      <c r="O106" t="s">
+        <v>664</v>
+      </c>
+      <c r="P106" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>665</v>
+      </c>
+      <c r="R106" t="s">
+        <v>228</v>
+      </c>
+      <c r="T106" t="s">
+        <v>666</v>
+      </c>
+      <c r="U106" t="s">
+        <v>61</v>
+      </c>
+      <c r="V106" t="s">
+        <v>665</v>
+      </c>
+      <c r="W106" t="s">
+        <v>646</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>667</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>665</v>
+      </c>
+      <c r="AB106" t="s">
+        <v>668</v>
+      </c>
+      <c r="AD106" t="s">
+        <v>669</v>
+      </c>
+      <c r="AE106" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF106" t="s">
+        <v>665</v>
+      </c>
+      <c r="AG106" t="s">
+        <v>228</v>
+      </c>
+      <c r="AI106" t="s">
+        <v>670</v>
+      </c>
+      <c r="AJ106" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK106" t="s">
+        <v>665</v>
+      </c>
+      <c r="AL106" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="107" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A107" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>00bc516a-216f-f499-4daf-7129da3bbef0</v>
+        <v>d46548d1-ee96-0537-1760-57336b344978</v>
       </c>
       <c r="B107" t="s">
         <v>111</v>
@@ -12831,94 +12892,40 @@
         <v>112</v>
       </c>
       <c r="D107" t="s">
-        <v>644</v>
+        <v>671</v>
       </c>
       <c r="E107" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="F107" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="G107" t="s">
-        <v>666</v>
+        <v>672</v>
+      </c>
+      <c r="H107" t="s">
+        <v>673</v>
+      </c>
+      <c r="I107" t="s">
+        <v>674</v>
       </c>
       <c r="K107" t="s">
         <v>74</v>
       </c>
       <c r="L107" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="M107" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="N107" t="b">
         <v>1</v>
-      </c>
-      <c r="O107" t="s">
-        <v>668</v>
-      </c>
-      <c r="P107" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>669</v>
-      </c>
-      <c r="R107" t="s">
-        <v>228</v>
-      </c>
-      <c r="T107" t="s">
-        <v>670</v>
-      </c>
-      <c r="U107" t="s">
-        <v>61</v>
-      </c>
-      <c r="V107" t="s">
-        <v>669</v>
-      </c>
-      <c r="W107" t="s">
-        <v>650</v>
-      </c>
-      <c r="Y107" t="s">
-        <v>671</v>
-      </c>
-      <c r="Z107" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA107" t="s">
-        <v>669</v>
-      </c>
-      <c r="AB107" t="s">
-        <v>672</v>
-      </c>
-      <c r="AD107" t="s">
-        <v>673</v>
-      </c>
-      <c r="AE107" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF107" t="s">
-        <v>669</v>
-      </c>
-      <c r="AG107" t="s">
-        <v>228</v>
-      </c>
-      <c r="AI107" t="s">
-        <v>674</v>
-      </c>
-      <c r="AJ107" t="s">
-        <v>61</v>
-      </c>
-      <c r="AK107" t="s">
-        <v>669</v>
-      </c>
-      <c r="AL107" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="108" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A108" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>255ed068-5a0c-951a-0fdd-5c064bc731fe</v>
+        <v>94baf104-15b1-7e28-c755-0cd1336f3773</v>
       </c>
       <c r="B108" t="s">
         <v>111</v>
@@ -12927,7 +12934,7 @@
         <v>112</v>
       </c>
       <c r="D108" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="E108" t="s">
         <v>106</v>
@@ -12951,7 +12958,7 @@
         <v>679</v>
       </c>
       <c r="M108" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N108" t="b">
         <v>1</v>
@@ -12960,7 +12967,7 @@
     <row r="109" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A109" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>4eb6adec-7803-317b-1dea-a239091bd69c</v>
+        <v>b985ed1e-96b8-74d1-fb8d-21450b602bef</v>
       </c>
       <c r="B109" t="s">
         <v>111</v>
@@ -12969,13 +12976,13 @@
         <v>112</v>
       </c>
       <c r="D109" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="E109" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F109" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G109" t="s">
         <v>680</v>
@@ -12993,7 +13000,7 @@
         <v>683</v>
       </c>
       <c r="M109" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N109" t="b">
         <v>1</v>
@@ -13002,7 +13009,7 @@
     <row r="110" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A110" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>4143bd66-8ec9-8399-6202-5dbd4b8ec671</v>
+        <v>0d8a8c03-2cc8-1a68-6727-82f3677f5d6f</v>
       </c>
       <c r="B110" t="s">
         <v>111</v>
@@ -13011,13 +13018,13 @@
         <v>112</v>
       </c>
       <c r="D110" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="E110" t="s">
         <v>100</v>
       </c>
       <c r="F110" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G110" t="s">
         <v>684</v>
@@ -13044,7 +13051,7 @@
     <row r="111" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A111" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>7620f897-68df-788b-3e8b-b5c548a99752</v>
+        <v>47a18837-ba35-6a99-acbd-dd6aba42626f</v>
       </c>
       <c r="B111" t="s">
         <v>111</v>
@@ -13053,40 +13060,58 @@
         <v>112</v>
       </c>
       <c r="D111" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="E111" t="s">
         <v>100</v>
       </c>
       <c r="F111" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="G111" t="s">
         <v>688</v>
       </c>
-      <c r="H111" t="s">
+      <c r="K111" t="s">
+        <v>52</v>
+      </c>
+      <c r="L111" t="s">
         <v>689</v>
       </c>
-      <c r="I111" t="s">
-        <v>690</v>
-      </c>
-      <c r="K111" t="s">
-        <v>74</v>
-      </c>
-      <c r="L111" t="s">
-        <v>691</v>
-      </c>
       <c r="M111" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N111" t="b">
         <v>1</v>
+      </c>
+      <c r="O111" t="s">
+        <v>690</v>
+      </c>
+      <c r="P111" t="s">
+        <v>47</v>
+      </c>
+      <c r="R111" t="s">
+        <v>691</v>
+      </c>
+      <c r="S111" t="s">
+        <v>692</v>
+      </c>
+      <c r="T111" t="s">
+        <v>693</v>
+      </c>
+      <c r="U111" t="s">
+        <v>47</v>
+      </c>
+      <c r="W111" t="s">
+        <v>694</v>
+      </c>
+      <c r="X111" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="112" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A112" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>d8d50406-3d4d-7ced-f198-af58909092d2</v>
+        <v>3704f11e-03a0-b671-9116-550ed448b0d3</v>
       </c>
       <c r="B112" t="s">
         <v>111</v>
@@ -13095,58 +13120,40 @@
         <v>112</v>
       </c>
       <c r="D112" t="s">
-        <v>675</v>
+        <v>696</v>
       </c>
       <c r="E112" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F112" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G112" t="s">
-        <v>692</v>
+        <v>697</v>
+      </c>
+      <c r="H112" t="s">
+        <v>698</v>
+      </c>
+      <c r="I112" t="s">
+        <v>699</v>
       </c>
       <c r="K112" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L112" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="M112" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N112" t="b">
         <v>1</v>
-      </c>
-      <c r="O112" t="s">
-        <v>694</v>
-      </c>
-      <c r="P112" t="s">
-        <v>47</v>
-      </c>
-      <c r="R112" t="s">
-        <v>695</v>
-      </c>
-      <c r="S112" t="s">
-        <v>696</v>
-      </c>
-      <c r="T112" t="s">
-        <v>697</v>
-      </c>
-      <c r="U112" t="s">
-        <v>47</v>
-      </c>
-      <c r="W112" t="s">
-        <v>698</v>
-      </c>
-      <c r="X112" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="113" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A113" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>f9b7352d-8cc0-409d-04d3-fc1e90bc2fc9</v>
+        <v>cfcd68d7-39be-5693-dabd-69d163795f1e</v>
       </c>
       <c r="B113" t="s">
         <v>111</v>
@@ -13155,13 +13162,13 @@
         <v>112</v>
       </c>
       <c r="D113" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E113" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="F113" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G113" t="s">
         <v>701</v>
@@ -13188,7 +13195,7 @@
     <row r="114" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A114" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>7b3b4d06-2a3f-85d7-4d94-b9da5aad9cfd</v>
+        <v>b0183f3c-aad0-f8f0-4804-dfd734595702</v>
       </c>
       <c r="B114" t="s">
         <v>111</v>
@@ -13197,40 +13204,58 @@
         <v>112</v>
       </c>
       <c r="D114" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E114" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F114" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="G114" t="s">
         <v>705</v>
       </c>
-      <c r="H114" t="s">
+      <c r="K114" t="s">
+        <v>52</v>
+      </c>
+      <c r="L114" t="s">
         <v>706</v>
-      </c>
-      <c r="I114" t="s">
-        <v>707</v>
-      </c>
-      <c r="K114" t="s">
-        <v>74</v>
-      </c>
-      <c r="L114" t="s">
-        <v>708</v>
       </c>
       <c r="M114" t="s">
         <v>54</v>
       </c>
       <c r="N114" t="b">
         <v>1</v>
+      </c>
+      <c r="O114" t="s">
+        <v>707</v>
+      </c>
+      <c r="P114" t="s">
+        <v>47</v>
+      </c>
+      <c r="R114" t="s">
+        <v>708</v>
+      </c>
+      <c r="S114" t="s">
+        <v>709</v>
+      </c>
+      <c r="T114" t="s">
+        <v>710</v>
+      </c>
+      <c r="U114" t="s">
+        <v>47</v>
+      </c>
+      <c r="W114" t="s">
+        <v>711</v>
+      </c>
+      <c r="X114" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="115" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A115" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>9a11d46e-edb5-e8c1-327e-df76b777d1e4</v>
+        <v>b9ec287d-1a1a-a80e-e1da-399404577940</v>
       </c>
       <c r="B115" t="s">
         <v>111</v>
@@ -13239,58 +13264,40 @@
         <v>112</v>
       </c>
       <c r="D115" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E115" t="s">
         <v>119</v>
       </c>
       <c r="F115" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="G115" t="s">
-        <v>709</v>
+        <v>713</v>
+      </c>
+      <c r="H115" t="s">
+        <v>714</v>
+      </c>
+      <c r="I115" t="s">
+        <v>715</v>
       </c>
       <c r="K115" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L115" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="M115" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N115" t="b">
         <v>1</v>
-      </c>
-      <c r="O115" t="s">
-        <v>711</v>
-      </c>
-      <c r="P115" t="s">
-        <v>47</v>
-      </c>
-      <c r="R115" t="s">
-        <v>712</v>
-      </c>
-      <c r="S115" t="s">
-        <v>713</v>
-      </c>
-      <c r="T115" t="s">
-        <v>714</v>
-      </c>
-      <c r="U115" t="s">
-        <v>47</v>
-      </c>
-      <c r="W115" t="s">
-        <v>715</v>
-      </c>
-      <c r="X115" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="116" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A116" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>373bd050-4e6e-b470-509a-59e79f9a76e0</v>
+        <v>821e235e-218e-0435-96a5-a9197467f4d0</v>
       </c>
       <c r="B116" t="s">
         <v>111</v>
@@ -13299,13 +13306,13 @@
         <v>112</v>
       </c>
       <c r="D116" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E116" t="s">
         <v>119</v>
       </c>
       <c r="F116" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G116" t="s">
         <v>717</v>
@@ -13323,7 +13330,7 @@
         <v>720</v>
       </c>
       <c r="M116" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N116" t="b">
         <v>1</v>
@@ -13332,7 +13339,7 @@
     <row r="117" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A117" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>352f73db-6653-db79-fdd6-e9aa4b5227df</v>
+        <v>ae5acf0c-38e7-98e3-8c90-0b549487c9ca</v>
       </c>
       <c r="B117" t="s">
         <v>111</v>
@@ -13341,13 +13348,13 @@
         <v>112</v>
       </c>
       <c r="D117" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E117" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="F117" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="G117" t="s">
         <v>721</v>
@@ -13374,7 +13381,7 @@
     <row r="118" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A118" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>789a3a9e-164a-427a-c560-499938705531</v>
+        <v>d86f33fc-6b12-5a9f-7619-e0f7a4c54487</v>
       </c>
       <c r="B118" t="s">
         <v>111</v>
@@ -13383,13 +13390,13 @@
         <v>112</v>
       </c>
       <c r="D118" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E118" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F118" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G118" t="s">
         <v>725</v>
@@ -13416,7 +13423,7 @@
     <row r="119" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A119" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>8e122ce3-2448-5e98-2123-6e3321b585f2</v>
+        <v>5345b9cc-4aae-cf34-d1fb-1c5b34db9634</v>
       </c>
       <c r="B119" t="s">
         <v>111</v>
@@ -13425,31 +13432,31 @@
         <v>112</v>
       </c>
       <c r="D119" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E119" t="s">
         <v>119</v>
       </c>
       <c r="F119" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="G119" t="s">
         <v>729</v>
       </c>
-      <c r="H119" t="s">
+      <c r="I119" t="s">
         <v>730</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J119" t="s">
         <v>731</v>
       </c>
       <c r="K119" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L119" t="s">
         <v>732</v>
       </c>
       <c r="M119" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="N119" t="b">
         <v>1</v>
@@ -13458,7 +13465,7 @@
     <row r="120" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A120" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>49970bad-87a0-e4ae-4d27-dc026baaf21e</v>
+        <v>6a643a33-7271-d231-6655-3963c148a2f3</v>
       </c>
       <c r="B120" t="s">
         <v>111</v>
@@ -13467,31 +13474,31 @@
         <v>112</v>
       </c>
       <c r="D120" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E120" t="s">
-        <v>119</v>
+        <v>798</v>
       </c>
       <c r="F120" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="G120" t="s">
         <v>733</v>
       </c>
+      <c r="H120" t="s">
+        <v>734</v>
+      </c>
       <c r="I120" t="s">
-        <v>734</v>
-      </c>
-      <c r="J120" t="s">
         <v>735</v>
       </c>
       <c r="K120" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L120" t="s">
         <v>736</v>
       </c>
       <c r="M120" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="N120" t="b">
         <v>1</v>
@@ -13500,7 +13507,7 @@
     <row r="121" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A121" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>c2480c83-f6f4-ad88-b416-6573e6ef9f8b</v>
+        <v>6311e392-330a-d5c1-24ce-f5c5a2cf7f18</v>
       </c>
       <c r="B121" t="s">
         <v>111</v>
@@ -13509,10 +13516,10 @@
         <v>112</v>
       </c>
       <c r="D121" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E121" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="F121" t="s">
         <v>95</v>
@@ -13542,7 +13549,7 @@
     <row r="122" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A122" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>7b83c1db-ecce-d106-c728-af82128d1372</v>
+        <v>ef364c43-d1f3-c835-7fd4-f0e2704c943d</v>
       </c>
       <c r="B122" t="s">
         <v>111</v>
@@ -13551,28 +13558,28 @@
         <v>112</v>
       </c>
       <c r="D122" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E122" t="s">
-        <v>803</v>
+        <v>106</v>
       </c>
       <c r="F122" t="s">
-        <v>95</v>
+        <v>341</v>
       </c>
       <c r="G122" t="s">
         <v>741</v>
       </c>
-      <c r="H122" t="s">
+      <c r="I122">
+        <v>46667</v>
+      </c>
+      <c r="J122" t="s">
         <v>742</v>
       </c>
-      <c r="I122" t="s">
+      <c r="K122" t="s">
+        <v>52</v>
+      </c>
+      <c r="L122" t="s">
         <v>743</v>
-      </c>
-      <c r="K122" t="s">
-        <v>74</v>
-      </c>
-      <c r="L122" t="s">
-        <v>744</v>
       </c>
       <c r="M122" t="s">
         <v>197</v>
@@ -13584,7 +13591,7 @@
     <row r="123" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A123" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2b1af7fa-6be7-4e34-fb04-c2a436f47df2</v>
+        <v>eaff9b6e-537b-4e71-6000-b489491aa8ce</v>
       </c>
       <c r="B123" t="s">
         <v>111</v>
@@ -13593,25 +13600,25 @@
         <v>112</v>
       </c>
       <c r="D123" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E123" t="s">
-        <v>106</v>
+        <v>798</v>
       </c>
       <c r="F123" t="s">
-        <v>341</v>
+        <v>95</v>
       </c>
       <c r="G123" t="s">
+        <v>744</v>
+      </c>
+      <c r="H123" t="s">
         <v>745</v>
       </c>
-      <c r="I123">
-        <v>46667</v>
-      </c>
-      <c r="J123" t="s">
+      <c r="I123" t="s">
         <v>746</v>
       </c>
       <c r="K123" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L123" t="s">
         <v>747</v>
@@ -13626,7 +13633,7 @@
     <row r="124" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A124" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>5d054db7-2115-894b-6287-4b87ba8cb6c2</v>
+        <v>253ee4dc-c184-77c1-030e-6bffeea99d50</v>
       </c>
       <c r="B124" t="s">
         <v>111</v>
@@ -13635,40 +13642,70 @@
         <v>112</v>
       </c>
       <c r="D124" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E124" t="s">
-        <v>803</v>
+        <v>106</v>
       </c>
       <c r="F124" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="G124" t="s">
         <v>748</v>
       </c>
-      <c r="H124" t="s">
+      <c r="K124" t="s">
+        <v>52</v>
+      </c>
+      <c r="L124" t="s">
         <v>749</v>
-      </c>
-      <c r="I124" t="s">
-        <v>750</v>
-      </c>
-      <c r="K124" t="s">
-        <v>74</v>
-      </c>
-      <c r="L124" t="s">
-        <v>751</v>
       </c>
       <c r="M124" t="s">
         <v>197</v>
       </c>
       <c r="N124" t="b">
         <v>1</v>
+      </c>
+      <c r="O124" t="s">
+        <v>750</v>
+      </c>
+      <c r="P124" t="s">
+        <v>47</v>
+      </c>
+      <c r="R124">
+        <v>4900000</v>
+      </c>
+      <c r="S124" t="s">
+        <v>751</v>
+      </c>
+      <c r="T124" t="s">
+        <v>752</v>
+      </c>
+      <c r="U124" t="s">
+        <v>47</v>
+      </c>
+      <c r="W124">
+        <v>900000</v>
+      </c>
+      <c r="X124" t="s">
+        <v>753</v>
+      </c>
+      <c r="Y124" t="s">
+        <v>754</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB124">
+        <v>9100000</v>
+      </c>
+      <c r="AC124" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="125" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A125" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>cbe478e0-2c09-9fce-94f9-98544c2054ab</v>
+        <v>a8334272-f1e9-43a6-d3a2-75f60a351c43</v>
       </c>
       <c r="B125" t="s">
         <v>111</v>
@@ -13677,70 +13714,40 @@
         <v>112</v>
       </c>
       <c r="D125" t="s">
-        <v>700</v>
+        <v>756</v>
       </c>
       <c r="E125" t="s">
         <v>106</v>
       </c>
       <c r="F125" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="G125" t="s">
-        <v>752</v>
+        <v>757</v>
+      </c>
+      <c r="H125" t="s">
+        <v>758</v>
+      </c>
+      <c r="I125" t="s">
+        <v>759</v>
       </c>
       <c r="K125" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L125" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="M125" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="N125" t="b">
         <v>1</v>
-      </c>
-      <c r="O125" t="s">
-        <v>754</v>
-      </c>
-      <c r="P125" t="s">
-        <v>47</v>
-      </c>
-      <c r="R125">
-        <v>4900000</v>
-      </c>
-      <c r="S125" t="s">
-        <v>755</v>
-      </c>
-      <c r="T125" t="s">
-        <v>756</v>
-      </c>
-      <c r="U125" t="s">
-        <v>47</v>
-      </c>
-      <c r="W125">
-        <v>900000</v>
-      </c>
-      <c r="X125" t="s">
-        <v>757</v>
-      </c>
-      <c r="Y125" t="s">
-        <v>758</v>
-      </c>
-      <c r="Z125" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB125">
-        <v>9100000</v>
-      </c>
-      <c r="AC125" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="126" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A126" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>0f6e67c9-66e8-dab1-99c2-de75bbc3c590</v>
+        <v>1c8013aa-e42f-8714-6c11-2046f6057dc2</v>
       </c>
       <c r="B126" t="s">
         <v>111</v>
@@ -13749,13 +13756,13 @@
         <v>112</v>
       </c>
       <c r="D126" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="E126" t="s">
         <v>106</v>
       </c>
       <c r="F126" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G126" t="s">
         <v>761</v>
@@ -13782,7 +13789,7 @@
     <row r="127" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A127" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>61476452-8c3e-2263-8d9c-4b084a24519c</v>
+        <v>e285e872-8d6a-4ecd-57e5-9426bb0c460d</v>
       </c>
       <c r="B127" t="s">
         <v>111</v>
@@ -13791,31 +13798,31 @@
         <v>112</v>
       </c>
       <c r="D127" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="E127" t="s">
         <v>106</v>
       </c>
       <c r="F127" t="s">
-        <v>61</v>
+        <v>341</v>
       </c>
       <c r="G127" t="s">
         <v>765</v>
       </c>
-      <c r="H127" t="s">
+      <c r="I127">
+        <v>700</v>
+      </c>
+      <c r="J127" t="s">
         <v>766</v>
       </c>
-      <c r="I127" t="s">
+      <c r="K127" t="s">
+        <v>52</v>
+      </c>
+      <c r="L127" t="s">
         <v>767</v>
       </c>
-      <c r="K127" t="s">
-        <v>74</v>
-      </c>
-      <c r="L127" t="s">
-        <v>768</v>
-      </c>
       <c r="M127" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="N127" t="b">
         <v>1</v>
@@ -13824,7 +13831,7 @@
     <row r="128" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A128" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>2ed74f60-678e-18a5-e545-bbcd43cd4554</v>
+        <v>6e0f7f8b-96fb-f100-258b-61f838179e74</v>
       </c>
       <c r="B128" t="s">
         <v>111</v>
@@ -13833,25 +13840,25 @@
         <v>112</v>
       </c>
       <c r="D128" t="s">
-        <v>760</v>
+        <v>696</v>
       </c>
       <c r="E128" t="s">
-        <v>106</v>
+        <v>798</v>
       </c>
       <c r="F128" t="s">
-        <v>341</v>
+        <v>95</v>
       </c>
       <c r="G128" t="s">
+        <v>768</v>
+      </c>
+      <c r="H128" t="s">
         <v>769</v>
       </c>
-      <c r="I128">
-        <v>700</v>
-      </c>
-      <c r="J128" t="s">
+      <c r="I128" t="s">
         <v>770</v>
       </c>
       <c r="K128" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L128" t="s">
         <v>771</v>
@@ -13866,7 +13873,7 @@
     <row r="129" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A129" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ab868501-7331-ba39-af22-7d3e17891cce</v>
+        <v>66def53f-b980-b907-75d8-01d2f7b4a8d0</v>
       </c>
       <c r="B129" t="s">
         <v>111</v>
@@ -13875,28 +13882,28 @@
         <v>112</v>
       </c>
       <c r="D129" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E129" t="s">
-        <v>803</v>
+        <v>106</v>
       </c>
       <c r="F129" t="s">
-        <v>95</v>
+        <v>341</v>
       </c>
       <c r="G129" t="s">
         <v>772</v>
       </c>
-      <c r="H129" t="s">
+      <c r="I129">
+        <v>1100</v>
+      </c>
+      <c r="J129" t="s">
         <v>773</v>
       </c>
-      <c r="I129" t="s">
+      <c r="K129" t="s">
+        <v>52</v>
+      </c>
+      <c r="L129" t="s">
         <v>774</v>
-      </c>
-      <c r="K129" t="s">
-        <v>74</v>
-      </c>
-      <c r="L129" t="s">
-        <v>775</v>
       </c>
       <c r="M129" t="s">
         <v>197</v>
@@ -13907,8 +13914,8 @@
     </row>
     <row r="130" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A130" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>ae0183de-ce37-7ccc-182d-20e4b3c7c3bd</v>
+        <f t="shared" ref="A130:A132" ca="1" si="2">IF(G130&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+        <v>2f1ffb51-cac5-8984-278c-60ff9559ed3e</v>
       </c>
       <c r="B130" t="s">
         <v>111</v>
@@ -13917,40 +13924,82 @@
         <v>112</v>
       </c>
       <c r="D130" t="s">
-        <v>700</v>
+        <v>756</v>
       </c>
       <c r="E130" t="s">
         <v>106</v>
       </c>
       <c r="F130" t="s">
-        <v>341</v>
+        <v>57</v>
       </c>
       <c r="G130" t="s">
-        <v>776</v>
-      </c>
-      <c r="I130">
-        <v>1100</v>
-      </c>
-      <c r="J130" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="K130" t="s">
         <v>52</v>
       </c>
       <c r="L130" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="M130" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="N130" t="b">
         <v>1</v>
       </c>
+      <c r="O130" t="s">
+        <v>777</v>
+      </c>
+      <c r="P130" t="s">
+        <v>47</v>
+      </c>
+      <c r="R130">
+        <v>50</v>
+      </c>
+      <c r="S130" t="s">
+        <v>778</v>
+      </c>
+      <c r="T130" t="s">
+        <v>779</v>
+      </c>
+      <c r="U130" t="s">
+        <v>47</v>
+      </c>
+      <c r="W130" t="s">
+        <v>780</v>
+      </c>
+      <c r="X130" t="s">
+        <v>781</v>
+      </c>
+      <c r="Y130" t="s">
+        <v>782</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB130">
+        <v>50</v>
+      </c>
+      <c r="AC130" t="s">
+        <v>778</v>
+      </c>
+      <c r="AD130" t="s">
+        <v>783</v>
+      </c>
+      <c r="AE130" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG130" t="s">
+        <v>784</v>
+      </c>
+      <c r="AH130" t="s">
+        <v>785</v>
+      </c>
     </row>
     <row r="131" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A131" t="str">
-        <f t="shared" ref="A131:A133" ca="1" si="2">IF(G131&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>17f6141e-2ff2-be99-900b-fc121e43249b</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>09100904-5b94-757f-5deb-5339a014f26b</v>
       </c>
       <c r="B131" t="s">
         <v>111</v>
@@ -13959,82 +14008,40 @@
         <v>112</v>
       </c>
       <c r="D131" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="E131" t="s">
         <v>106</v>
       </c>
       <c r="F131" t="s">
-        <v>57</v>
+        <v>341</v>
       </c>
       <c r="G131" t="s">
-        <v>779</v>
+        <v>786</v>
+      </c>
+      <c r="I131">
+        <v>575</v>
+      </c>
+      <c r="J131" t="s">
+        <v>787</v>
       </c>
       <c r="K131" t="s">
         <v>52</v>
       </c>
       <c r="L131" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="M131" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="N131" t="b">
         <v>1</v>
-      </c>
-      <c r="O131" t="s">
-        <v>781</v>
-      </c>
-      <c r="P131" t="s">
-        <v>47</v>
-      </c>
-      <c r="R131">
-        <v>50</v>
-      </c>
-      <c r="S131" t="s">
-        <v>782</v>
-      </c>
-      <c r="T131" t="s">
-        <v>783</v>
-      </c>
-      <c r="U131" t="s">
-        <v>47</v>
-      </c>
-      <c r="W131" t="s">
-        <v>784</v>
-      </c>
-      <c r="X131" t="s">
-        <v>785</v>
-      </c>
-      <c r="Y131" t="s">
-        <v>786</v>
-      </c>
-      <c r="Z131" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB131">
-        <v>50</v>
-      </c>
-      <c r="AC131" t="s">
-        <v>782</v>
-      </c>
-      <c r="AD131" t="s">
-        <v>787</v>
-      </c>
-      <c r="AE131" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG131" t="s">
-        <v>788</v>
-      </c>
-      <c r="AH131" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="132" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A132" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>fbbdcad4-0329-5173-9151-cb4756b8dc69</v>
+        <v>ad2f1d1d-673b-afcd-9aa7-56899725c129</v>
       </c>
       <c r="B132" t="s">
         <v>111</v>
@@ -14043,139 +14050,136 @@
         <v>112</v>
       </c>
       <c r="D132" t="s">
-        <v>760</v>
+        <v>696</v>
       </c>
       <c r="E132" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="F132" t="s">
-        <v>341</v>
+        <v>57</v>
       </c>
       <c r="G132" t="s">
+        <v>789</v>
+      </c>
+      <c r="K132" t="s">
+        <v>74</v>
+      </c>
+      <c r="L132" t="s">
         <v>790</v>
       </c>
-      <c r="I132">
-        <v>575</v>
-      </c>
-      <c r="J132" t="s">
-        <v>791</v>
-      </c>
-      <c r="K132" t="s">
-        <v>52</v>
-      </c>
-      <c r="L132" t="s">
-        <v>792</v>
-      </c>
       <c r="M132" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="N132" t="b">
         <v>1</v>
       </c>
+      <c r="O132" t="s">
+        <v>791</v>
+      </c>
+      <c r="P132" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>792</v>
+      </c>
+      <c r="R132" t="s">
+        <v>793</v>
+      </c>
+      <c r="T132" t="s">
+        <v>794</v>
+      </c>
+      <c r="U132" t="s">
+        <v>61</v>
+      </c>
+      <c r="V132" t="s">
+        <v>792</v>
+      </c>
+      <c r="W132" t="s">
+        <v>795</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>796</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA132" t="s">
+        <v>792</v>
+      </c>
+      <c r="AB132" t="s">
+        <v>797</v>
+      </c>
     </row>
     <row r="133" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A133" t="str">
-        <f t="shared" ca="1" si="2"/>
-        <v>c127a8c2-c924-f40e-400c-ea582af72f31</v>
+        <f t="shared" ref="A133:A187" ca="1" si="3">IF(G133&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
+        <v>dcf00aa0-194d-1875-1be6-a5caeed1f55f</v>
       </c>
       <c r="B133" t="s">
-        <v>111</v>
+        <v>921</v>
       </c>
       <c r="C133" t="s">
-        <v>112</v>
+        <v>799</v>
       </c>
       <c r="D133" t="s">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E133" t="s">
-        <v>119</v>
+        <v>801</v>
       </c>
       <c r="F133" t="s">
-        <v>57</v>
+        <v>342</v>
       </c>
       <c r="G133" t="s">
-        <v>793</v>
+        <v>506</v>
+      </c>
+      <c r="I133" t="s">
+        <v>802</v>
       </c>
       <c r="K133" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L133" t="s">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="M133" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="N133" t="b">
         <v>1</v>
       </c>
-      <c r="O133" t="s">
-        <v>795</v>
-      </c>
-      <c r="P133" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q133" t="s">
-        <v>796</v>
-      </c>
-      <c r="R133" t="s">
-        <v>797</v>
-      </c>
-      <c r="T133" t="s">
-        <v>798</v>
-      </c>
-      <c r="U133" t="s">
-        <v>61</v>
-      </c>
-      <c r="V133" t="s">
-        <v>796</v>
-      </c>
-      <c r="W133" t="s">
-        <v>799</v>
-      </c>
-      <c r="Y133" t="s">
-        <v>800</v>
-      </c>
-      <c r="Z133" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA133" t="s">
-        <v>796</v>
-      </c>
-      <c r="AB133" t="s">
-        <v>801</v>
-      </c>
     </row>
     <row r="134" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A134" t="str">
-        <f t="shared" ref="A134:A188" ca="1" si="3">IF(G134&lt;&gt;"",LOWER(CONCATENATE(DEC2HEX(RANDBETWEEN(0,4294967295),8),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,65535),4),"-",DEC2HEX(RANDBETWEEN(0,4294967295),8),DEC2HEX(RANDBETWEEN(0,65535),4))),"")</f>
-        <v>1e400829-9ece-2aa3-4421-f2143e3bbc9f</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>7977dfe3-3839-07de-470d-4e7a6ac66ada</v>
       </c>
       <c r="B134" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C134" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D134" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E134" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F134" t="s">
         <v>342</v>
       </c>
       <c r="G134" t="s">
-        <v>510</v>
+        <v>804</v>
       </c>
       <c r="I134" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="K134" t="s">
         <v>52</v>
       </c>
       <c r="L134" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="M134" t="s">
         <v>54</v>
@@ -14187,34 +14191,34 @@
     <row r="135" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A135" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>16ab1862-0d14-34e2-b0bb-c4f00173b256</v>
+        <v>3d78d2b9-f4eb-8a82-8539-0a1c8052239e</v>
       </c>
       <c r="B135" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C135" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D135" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E135" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F135" t="s">
         <v>342</v>
       </c>
       <c r="G135" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="I135" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="K135" t="s">
         <v>52</v>
       </c>
       <c r="L135" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="M135" t="s">
         <v>54</v>
@@ -14226,34 +14230,34 @@
     <row r="136" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A136" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>202a1f39-e437-db02-802d-e0e5eaea2d3c</v>
+        <v>c68dab5a-c620-d547-1f2c-8202e85df278</v>
       </c>
       <c r="B136" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C136" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D136" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E136" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F136" t="s">
         <v>342</v>
       </c>
       <c r="G136" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="I136" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="K136" t="s">
         <v>52</v>
       </c>
       <c r="L136" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="M136" t="s">
         <v>54</v>
@@ -14265,34 +14269,34 @@
     <row r="137" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A137" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>f8fcbfff-1688-1d43-9a83-cddf85c19b3f</v>
+        <v>4611124d-9203-f1d6-e11a-d4698efc0478</v>
       </c>
       <c r="B137" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C137" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D137" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E137" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F137" t="s">
         <v>342</v>
       </c>
       <c r="G137" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="I137" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="K137" t="s">
         <v>52</v>
       </c>
       <c r="L137" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="M137" t="s">
         <v>54</v>
@@ -14304,34 +14308,34 @@
     <row r="138" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A138" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>ba7eaf9c-b7e6-21ba-ea5a-fcb58fc2d7ef</v>
+        <v>8f28ed1e-26a9-1512-a3fe-d7ddae62a88a</v>
       </c>
       <c r="B138" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C138" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D138" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E138" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F138" t="s">
         <v>342</v>
       </c>
       <c r="G138" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="I138" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="K138" t="s">
         <v>52</v>
       </c>
       <c r="L138" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="M138" t="s">
         <v>54</v>
@@ -14343,34 +14347,34 @@
     <row r="139" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A139" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>28d65c23-44df-9fd6-df53-cec91267f5ad</v>
+        <v>a0464192-635f-d60d-6a3c-678aa7eeb17c</v>
       </c>
       <c r="B139" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C139" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D139" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E139" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F139" t="s">
         <v>342</v>
       </c>
       <c r="G139" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="I139" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="K139" t="s">
         <v>52</v>
       </c>
       <c r="L139" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="M139" t="s">
         <v>54</v>
@@ -14382,34 +14386,34 @@
     <row r="140" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A140" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>730526a7-7b76-c91f-ea11-d036c6f11e68</v>
+        <v>fd90e0ca-f9ac-df79-9cf2-06ce64842db5</v>
       </c>
       <c r="B140" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C140" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D140" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E140" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F140" t="s">
         <v>342</v>
       </c>
       <c r="G140" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="I140" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="K140" t="s">
         <v>52</v>
       </c>
       <c r="L140" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="M140" t="s">
         <v>54</v>
@@ -14421,34 +14425,34 @@
     <row r="141" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A141" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>65a6020b-9347-e296-d626-13e010ae151b</v>
+        <v>0221cc55-199b-4009-c0b9-3fe664a2de1c</v>
       </c>
       <c r="B141" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C141" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D141" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E141" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F141" t="s">
         <v>342</v>
       </c>
       <c r="G141" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="I141" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="K141" t="s">
         <v>52</v>
       </c>
       <c r="L141" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="M141" t="s">
         <v>54</v>
@@ -14460,34 +14464,34 @@
     <row r="142" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A142" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>311f22f7-7ac3-9e83-a089-dda187757e30</v>
+        <v>31922ac0-9372-1f69-e841-fb3dfd7e33b3</v>
       </c>
       <c r="B142" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C142" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D142" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E142" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F142" t="s">
         <v>342</v>
       </c>
       <c r="G142" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="I142" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="K142" t="s">
         <v>52</v>
       </c>
       <c r="L142" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="M142" t="s">
         <v>54</v>
@@ -14499,34 +14503,34 @@
     <row r="143" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A143" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>5110920e-12ae-384f-f604-fea9e132837b</v>
+        <v>fe253c0f-a70b-c304-f669-de518e46cee5</v>
       </c>
       <c r="B143" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C143" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D143" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E143" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F143" t="s">
         <v>342</v>
       </c>
       <c r="G143" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="I143" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="K143" t="s">
         <v>52</v>
       </c>
       <c r="L143" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="M143" t="s">
         <v>54</v>
@@ -14538,34 +14542,34 @@
     <row r="144" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A144" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>135b0a03-28b3-78cd-5c90-4277158d4e33</v>
+        <v>1698a5a4-c8a9-d847-4ee1-dff935310b01</v>
       </c>
       <c r="B144" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C144" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D144" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E144" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F144" t="s">
         <v>342</v>
       </c>
       <c r="G144" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="I144" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="K144" t="s">
         <v>52</v>
       </c>
       <c r="L144" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="M144" t="s">
         <v>54</v>
@@ -14577,34 +14581,34 @@
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>069acb01-235e-7be9-1d34-e2172703ac9b</v>
+        <v>3e5fd833-616f-b582-4c19-498287667498</v>
       </c>
       <c r="B145" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C145" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D145" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E145" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F145" t="s">
         <v>342</v>
       </c>
       <c r="G145" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="I145" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="K145" t="s">
         <v>52</v>
       </c>
       <c r="L145" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="M145" t="s">
         <v>54</v>
@@ -14616,34 +14620,34 @@
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>433db9b6-fe7a-1e5d-63d4-794d736a5b32</v>
+        <v>fbea1a26-05c5-2ae1-931b-7e213d9d1e85</v>
       </c>
       <c r="B146" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C146" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D146" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E146" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F146" t="s">
         <v>342</v>
       </c>
       <c r="G146" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="I146" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="K146" t="s">
         <v>52</v>
       </c>
       <c r="L146" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="M146" t="s">
         <v>54</v>
@@ -14655,34 +14659,35 @@
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>a0b8ef01-f34d-4db3-d348-79aa2cb2790e</v>
+        <v>3631ce58-15c4-2a6a-7298-097c7e627506</v>
       </c>
       <c r="B147" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C147" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D147" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E147" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F147" t="s">
         <v>342</v>
       </c>
       <c r="G147" t="s">
-        <v>845</v>
-      </c>
+        <v>843</v>
+      </c>
+      <c r="H147" s="2"/>
       <c r="I147" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="K147" t="s">
         <v>52</v>
       </c>
       <c r="L147" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="M147" t="s">
         <v>54</v>
@@ -14694,35 +14699,34 @@
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>74a76c21-4299-128d-87f6-d7a9b3881590</v>
+        <v>4506766b-f1ba-b18c-3ccf-c586bee26617</v>
       </c>
       <c r="B148" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C148" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D148" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E148" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F148" t="s">
         <v>342</v>
       </c>
       <c r="G148" t="s">
-        <v>848</v>
-      </c>
-      <c r="H148" s="2"/>
+        <v>846</v>
+      </c>
       <c r="I148" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="K148" t="s">
         <v>52</v>
       </c>
       <c r="L148" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="M148" t="s">
         <v>54</v>
@@ -14734,34 +14738,34 @@
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>943dd6a5-d27f-19d5-93b1-2a3a8c90651c</v>
+        <v>71566d59-19e7-d748-a1f3-e017bce85d5e</v>
       </c>
       <c r="B149" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C149" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D149" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E149" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F149" t="s">
         <v>342</v>
       </c>
       <c r="G149" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="I149" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="K149" t="s">
         <v>52</v>
       </c>
       <c r="L149" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="M149" t="s">
         <v>54</v>
@@ -14773,34 +14777,34 @@
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>f4f8a294-38c1-254c-bdc5-6d170684832a</v>
+        <v>aeeac83b-64f7-b6e8-1d70-bc1191b93d38</v>
       </c>
       <c r="B150" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C150" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D150" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E150" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F150" t="s">
         <v>342</v>
       </c>
       <c r="G150" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="I150" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="K150" t="s">
         <v>52</v>
       </c>
       <c r="L150" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="M150" t="s">
         <v>54</v>
@@ -14812,34 +14816,34 @@
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>2bb21c19-5402-626c-508b-6bbbb0588a83</v>
+        <v>5c103017-ca67-d5c1-4406-e629c2c1d44a</v>
       </c>
       <c r="B151" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C151" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D151" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E151" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F151" t="s">
         <v>342</v>
       </c>
       <c r="G151" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="I151" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="K151" t="s">
         <v>52</v>
       </c>
       <c r="L151" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="M151" t="s">
         <v>54</v>
@@ -14851,34 +14855,34 @@
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>0afa29bd-035a-6b16-c779-747e8f22dc37</v>
+        <v>e1ab1308-917f-4030-9338-67f5e461fc10</v>
       </c>
       <c r="B152" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C152" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D152" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E152" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F152" t="s">
         <v>342</v>
       </c>
       <c r="G152" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="I152" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="K152" t="s">
         <v>52</v>
       </c>
       <c r="L152" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="M152" t="s">
         <v>54</v>
@@ -14890,34 +14894,34 @@
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>06bc1cde-fc04-1ffc-39a8-165ba5b1d046</v>
+        <v>330cbbfd-98ee-115e-2279-db1de42a8353</v>
       </c>
       <c r="B153" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C153" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D153" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E153" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F153" t="s">
         <v>342</v>
       </c>
       <c r="G153" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="I153" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="K153" t="s">
         <v>52</v>
       </c>
       <c r="L153" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="M153" t="s">
         <v>54</v>
@@ -14929,34 +14933,34 @@
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>8607067c-41b2-7335-afe1-f3e4c8d5d2c3</v>
+        <v>4ed54978-3a0c-a6ef-5021-bf6657f8a522</v>
       </c>
       <c r="B154" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C154" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D154" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E154" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F154" t="s">
         <v>342</v>
       </c>
       <c r="G154" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="I154" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="K154" t="s">
         <v>52</v>
       </c>
       <c r="L154" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="M154" t="s">
         <v>54</v>
@@ -14968,34 +14972,34 @@
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>c2597366-de77-3855-b7a9-60c4cff26fdf</v>
+        <v>ad1f165d-bb15-f1a5-6b31-976a07cbb925</v>
       </c>
       <c r="B155" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C155" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D155" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E155" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F155" t="s">
         <v>342</v>
       </c>
       <c r="G155" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="I155" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="K155" t="s">
         <v>52</v>
       </c>
       <c r="L155" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="M155" t="s">
         <v>54</v>
@@ -15007,34 +15011,34 @@
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>1e24047c-4f8b-a228-a4f9-8e1dabba1c68</v>
+        <v>ff3f76cd-725c-64e1-5fbe-a634b5ab0964</v>
       </c>
       <c r="B156" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C156" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D156" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E156" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F156" t="s">
         <v>342</v>
       </c>
       <c r="G156" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="I156" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="K156" t="s">
         <v>52</v>
       </c>
       <c r="L156" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="M156" t="s">
         <v>54</v>
@@ -15046,34 +15050,34 @@
     <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>62754cf0-213c-200d-36ba-19bf98edce84</v>
+        <v>a391d8b6-ad4e-ab66-ed77-de2b30b6d751</v>
       </c>
       <c r="B157" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C157" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D157" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E157" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F157" t="s">
         <v>342</v>
       </c>
       <c r="G157" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="I157" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="K157" t="s">
         <v>52</v>
       </c>
       <c r="L157" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="M157" t="s">
         <v>54</v>
@@ -15085,34 +15089,34 @@
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>8cb00df7-6a32-4487-6983-1b0175cc039e</v>
+        <v>16a1a999-e818-50c9-0577-120bdf5b40d7</v>
       </c>
       <c r="B158" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C158" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D158" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E158" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F158" t="s">
         <v>342</v>
       </c>
       <c r="G158" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="I158" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="K158" t="s">
         <v>52</v>
       </c>
       <c r="L158" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="M158" t="s">
         <v>54</v>
@@ -15124,34 +15128,34 @@
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>2cbc17f3-21a9-c240-368b-dc960eb637fa</v>
+        <v>3a9f095e-fdf3-774b-502c-890f8845cc17</v>
       </c>
       <c r="B159" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C159" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D159" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E159" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F159" t="s">
         <v>342</v>
       </c>
       <c r="G159" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="I159" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="K159" t="s">
         <v>52</v>
       </c>
       <c r="L159" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="M159" t="s">
         <v>54</v>
@@ -15163,34 +15167,34 @@
     <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>80c0fc12-c93a-f00b-7098-dc1fe3c54756</v>
+        <v>22583986-b69b-69a2-b54c-1550d6f55e87</v>
       </c>
       <c r="B160" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C160" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D160" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E160" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F160" t="s">
         <v>342</v>
       </c>
       <c r="G160" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="I160" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="K160" t="s">
         <v>52</v>
       </c>
       <c r="L160" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="M160" t="s">
         <v>54</v>
@@ -15202,34 +15206,34 @@
     <row r="161" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A161" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>0172d2e3-dd25-2f66-afd2-6ff99da2a32f</v>
+        <v>dcc8680f-0230-30b0-7772-c9f4ac722e82</v>
       </c>
       <c r="B161" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C161" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D161" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E161" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F161" t="s">
         <v>342</v>
       </c>
       <c r="G161" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="I161" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="K161" t="s">
         <v>52</v>
       </c>
       <c r="L161" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="M161" t="s">
         <v>54</v>
@@ -15241,34 +15245,34 @@
     <row r="162" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A162" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>405657c8-8fe9-4959-7c32-41f2448306ba</v>
+        <v>43f8363f-a3c6-1d05-f7db-58b8fa1d0986</v>
       </c>
       <c r="B162" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C162" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D162" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E162" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F162" t="s">
         <v>342</v>
       </c>
       <c r="G162" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="I162" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="K162" t="s">
         <v>52</v>
       </c>
       <c r="L162" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="M162" t="s">
         <v>54</v>
@@ -15280,34 +15284,34 @@
     <row r="163" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A163" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>f583fc24-b5c3-e269-eb2c-91360251974d</v>
+        <v>bce9c3c5-f16e-51b6-f063-7f2c2b0073b2</v>
       </c>
       <c r="B163" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C163" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D163" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E163" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F163" t="s">
         <v>342</v>
       </c>
       <c r="G163" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="I163" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="K163" t="s">
         <v>52</v>
       </c>
       <c r="L163" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="M163" t="s">
         <v>54</v>
@@ -15319,34 +15323,34 @@
     <row r="164" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A164" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>33dd57a6-e087-8055-834b-8dfe2412a5a0</v>
+        <v>4a212abd-172a-567e-03f5-0e6f587ee6a9</v>
       </c>
       <c r="B164" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C164" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D164" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E164" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F164" t="s">
         <v>342</v>
       </c>
       <c r="G164" t="s">
-        <v>896</v>
+        <v>111</v>
       </c>
       <c r="I164" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="K164" t="s">
         <v>52</v>
       </c>
       <c r="L164" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="M164" t="s">
         <v>54</v>
@@ -15358,34 +15362,34 @@
     <row r="165" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A165" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>1fdde85e-cce5-12f4-5da5-f60c0af1d258</v>
+        <v>20b4d168-cddf-d477-c1e2-9643e6378386</v>
       </c>
       <c r="B165" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C165" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D165" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E165" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F165" t="s">
         <v>342</v>
       </c>
       <c r="G165" t="s">
-        <v>111</v>
+        <v>896</v>
       </c>
       <c r="I165" t="s">
-        <v>899</v>
+        <v>227</v>
       </c>
       <c r="K165" t="s">
         <v>52</v>
       </c>
       <c r="L165" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="M165" t="s">
         <v>54</v>
@@ -15397,34 +15401,34 @@
     <row r="166" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A166" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>9ae5b9c4-8ad3-ff12-07c4-24f3a3a74ecd</v>
+        <v>c15446c5-df56-7d06-622b-df06bb747f45</v>
       </c>
       <c r="B166" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C166" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D166" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E166" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F166" t="s">
         <v>342</v>
       </c>
       <c r="G166" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="I166" t="s">
-        <v>227</v>
+        <v>899</v>
       </c>
       <c r="K166" t="s">
         <v>52</v>
       </c>
       <c r="L166" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="M166" t="s">
         <v>54</v>
@@ -15436,34 +15440,34 @@
     <row r="167" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A167" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>0e2261f3-e5ce-c9ef-9f0a-8c041094a84f</v>
+        <v>38b84380-4eb0-1c36-7ba2-b5afcfb80077</v>
       </c>
       <c r="B167" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C167" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D167" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E167" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F167" t="s">
         <v>342</v>
       </c>
       <c r="G167" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="I167" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="K167" t="s">
         <v>52</v>
       </c>
       <c r="L167" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="M167" t="s">
         <v>54</v>
@@ -15475,34 +15479,34 @@
     <row r="168" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A168" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>9f14911c-ad7d-f78e-f5fe-6fe61fbfdb4e</v>
+        <v>ce6ebde7-5f59-c212-1d27-0ce665cd3ca5</v>
       </c>
       <c r="B168" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C168" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D168" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E168" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F168" t="s">
         <v>342</v>
       </c>
       <c r="G168" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="I168" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="K168" t="s">
         <v>52</v>
       </c>
       <c r="L168" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="M168" t="s">
         <v>54</v>
@@ -15514,34 +15518,34 @@
     <row r="169" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A169" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>484ef302-1824-0a94-c7ef-7aa2a7dab656</v>
+        <v>6a3758b0-56b2-a1c7-e3c7-0d2c0ed7f2d3</v>
       </c>
       <c r="B169" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C169" t="s">
-        <v>804</v>
+        <v>908</v>
       </c>
       <c r="D169" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E169" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F169" t="s">
         <v>342</v>
       </c>
       <c r="G169" t="s">
+        <v>907</v>
+      </c>
+      <c r="I169" t="s">
         <v>909</v>
-      </c>
-      <c r="I169" t="s">
-        <v>910</v>
       </c>
       <c r="K169" t="s">
         <v>52</v>
       </c>
       <c r="L169" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="M169" t="s">
         <v>54</v>
@@ -15553,34 +15557,34 @@
     <row r="170" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A170" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>0898e398-fdeb-f9e1-8367-a0a4f4d1885e</v>
+        <v>3fbc0c96-ce53-701b-4de8-7a18e1ff4eab</v>
       </c>
       <c r="B170" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C170" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="D170" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E170" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F170" t="s">
         <v>342</v>
       </c>
       <c r="G170" t="s">
+        <v>911</v>
+      </c>
+      <c r="I170" t="s">
         <v>912</v>
-      </c>
-      <c r="I170" t="s">
-        <v>914</v>
       </c>
       <c r="K170" t="s">
         <v>52</v>
       </c>
       <c r="L170" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="M170" t="s">
         <v>54</v>
@@ -15592,34 +15596,34 @@
     <row r="171" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A171" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>e9e6c547-54ef-7cbf-26a9-1b2a7722da44</v>
+        <v>fa26b643-917a-842d-501c-a9599b69bed3</v>
       </c>
       <c r="B171" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C171" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D171" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E171" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F171" t="s">
         <v>342</v>
       </c>
       <c r="G171" t="s">
+        <v>914</v>
+      </c>
+      <c r="I171" t="s">
         <v>916</v>
-      </c>
-      <c r="I171" t="s">
-        <v>917</v>
       </c>
       <c r="K171" t="s">
         <v>52</v>
       </c>
       <c r="L171" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="M171" t="s">
         <v>54</v>
@@ -15631,34 +15635,34 @@
     <row r="172" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A172" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>6a7e8cfe-2a0d-9ce5-db65-99f7248b088e</v>
+        <v>12465add-67a8-d17b-8eac-c69be514aa03</v>
       </c>
       <c r="B172" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C172" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="D172" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E172" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F172" t="s">
         <v>342</v>
       </c>
       <c r="G172" t="s">
+        <v>918</v>
+      </c>
+      <c r="I172" t="s">
         <v>919</v>
-      </c>
-      <c r="I172" t="s">
-        <v>921</v>
       </c>
       <c r="K172" t="s">
         <v>52</v>
       </c>
       <c r="L172" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="M172" t="s">
         <v>54</v>
@@ -15670,46 +15674,59 @@
     <row r="173" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A173" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>bf624815-aaa2-1ead-fcb0-ccef0edbdbd7</v>
-      </c>
-      <c r="B173" t="s">
+        <v>63b3876d-0500-df17-4936-fd72816137cd</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="H173" s="3"/>
+      <c r="I173" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="J173" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="K173" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L173" s="3" t="s">
         <v>926</v>
       </c>
-      <c r="C173" t="s">
-        <v>920</v>
-      </c>
-      <c r="D173" t="s">
-        <v>805</v>
-      </c>
-      <c r="E173" t="s">
-        <v>806</v>
-      </c>
-      <c r="F173" t="s">
-        <v>342</v>
-      </c>
-      <c r="G173" t="s">
-        <v>923</v>
-      </c>
-      <c r="I173" t="s">
-        <v>924</v>
-      </c>
-      <c r="K173" t="s">
-        <v>52</v>
-      </c>
-      <c r="L173" t="s">
-        <v>925</v>
-      </c>
-      <c r="M173" t="s">
-        <v>54</v>
-      </c>
-      <c r="N173" t="b">
+      <c r="M173" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="N173" s="3" t="b">
         <v>1</v>
       </c>
+      <c r="O173" s="3"/>
+      <c r="P173" s="3"/>
+      <c r="Q173" s="3"/>
+      <c r="R173" s="3"/>
+      <c r="S173" s="3"/>
+      <c r="T173" s="3"/>
+      <c r="U173" s="3"/>
+      <c r="V173" s="3"/>
+      <c r="W173" s="3"/>
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A174" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>28957050-801f-fd71-2778-551f5745a005</v>
+        <v>868d9d60-8cfe-38a0-b904-c4b7c06dfb1d</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>111</v>
@@ -15718,32 +15735,32 @@
         <v>112</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>433</v>
+        <v>927</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>928</v>
       </c>
-      <c r="H174" s="3"/>
+      <c r="H174" s="3" t="s">
+        <v>929</v>
+      </c>
       <c r="I174" s="3" t="s">
-        <v>929</v>
-      </c>
-      <c r="J174" s="3" t="s">
         <v>930</v>
       </c>
+      <c r="J174" s="3"/>
       <c r="K174" s="3" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L174" s="3" t="s">
         <v>931</v>
       </c>
       <c r="M174" s="3" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N174" s="3" t="b">
         <v>1</v>
@@ -15761,7 +15778,7 @@
     <row r="175" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A175" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>814d77ca-e073-3f17-2daf-3a71ef797b44</v>
+        <v>94a4eb10-1c6d-66c6-0378-8e5c79c6d06f</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>111</v>
@@ -15776,7 +15793,7 @@
         <v>100</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>933</v>
@@ -15785,14 +15802,14 @@
         <v>934</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="J175" s="3"/>
       <c r="K175" s="3" t="s">
         <v>74</v>
       </c>
       <c r="L175" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="M175" s="3" t="s">
         <v>54</v>
@@ -15813,7 +15830,7 @@
     <row r="176" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A176" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>a04dafc4-6f41-2d8d-9f26-f3eeb9b83d8a</v>
+        <v>02a0f0bd-ded9-f320-7ee5-c5c593f683f4</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>111</v>
@@ -15822,22 +15839,22 @@
         <v>112</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>100</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="G176" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="H176" s="3" t="s">
         <v>938</v>
       </c>
-      <c r="H176" s="3" t="s">
+      <c r="I176" s="3" t="s">
         <v>939</v>
-      </c>
-      <c r="I176" s="3" t="s">
-        <v>927</v>
       </c>
       <c r="J176" s="3"/>
       <c r="K176" s="3" t="s">
@@ -15847,7 +15864,7 @@
         <v>940</v>
       </c>
       <c r="M176" s="3" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="N176" s="3" t="b">
         <v>1</v>
@@ -15865,7 +15882,7 @@
     <row r="177" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A177" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>12e855d6-4e0e-5132-df10-ae656e9013b5</v>
+        <v>7bb4f398-4d42-01a3-e644-bbf144f125ed</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>111</v>
@@ -15880,26 +15897,26 @@
         <v>100</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>942</v>
       </c>
-      <c r="H177" s="3" t="s">
+      <c r="H177" s="3"/>
+      <c r="I177" s="3" t="s">
         <v>943</v>
       </c>
-      <c r="I177" s="3" t="s">
+      <c r="J177" s="3" t="s">
         <v>944</v>
       </c>
-      <c r="J177" s="3"/>
       <c r="K177" s="3" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L177" s="3" t="s">
         <v>945</v>
       </c>
       <c r="M177" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="N177" s="3" t="b">
         <v>1</v>
@@ -15917,7 +15934,7 @@
     <row r="178" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A178" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>49729094-5732-717a-84c3-88e4f336db06</v>
+        <v>284b9adb-4009-07d5-5053-1872bd93e34b</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>111</v>
@@ -15932,18 +15949,14 @@
         <v>100</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>947</v>
       </c>
       <c r="H178" s="3"/>
-      <c r="I178" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="J178" s="3" t="s">
-        <v>949</v>
-      </c>
+      <c r="I178" s="3"/>
+      <c r="J178" s="3"/>
       <c r="K178" s="3" t="s">
         <v>52</v>
       </c>
@@ -15951,25 +15964,37 @@
         <v>950</v>
       </c>
       <c r="M178" s="3" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N178" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="O178" s="3"/>
-      <c r="P178" s="3"/>
+      <c r="O178" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="P178" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="Q178" s="3"/>
-      <c r="R178" s="3"/>
+      <c r="R178" s="3" t="s">
+        <v>948</v>
+      </c>
       <c r="S178" s="3"/>
-      <c r="T178" s="3"/>
-      <c r="U178" s="3"/>
+      <c r="T178" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U178" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="V178" s="3"/>
-      <c r="W178" s="3"/>
+      <c r="W178" s="3" t="s">
+        <v>949</v>
+      </c>
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A179" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>64f5ec06-bfcc-bbf6-1373-3ff9a75b660b</v>
+        <v>22d7c25f-579a-2577-12cc-416533c0bbaa</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>111</v>
@@ -15978,25 +16003,29 @@
         <v>112</v>
       </c>
       <c r="D179" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G179" s="3" t="s">
         <v>951</v>
       </c>
-      <c r="E179" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G179" s="3" t="s">
+      <c r="H179" s="3" t="s">
         <v>952</v>
       </c>
-      <c r="H179" s="3"/>
-      <c r="I179" s="3"/>
+      <c r="I179" s="3" t="s">
+        <v>953</v>
+      </c>
       <c r="J179" s="3"/>
       <c r="K179" s="3" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="L179" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="M179" s="3" t="s">
         <v>197</v>
@@ -16004,32 +16033,20 @@
       <c r="N179" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="O179" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P179" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="O179" s="3"/>
+      <c r="P179" s="3"/>
       <c r="Q179" s="3"/>
-      <c r="R179" s="3" t="s">
-        <v>953</v>
-      </c>
+      <c r="R179" s="3"/>
       <c r="S179" s="3"/>
-      <c r="T179" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="U179" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="T179" s="3"/>
+      <c r="U179" s="3"/>
       <c r="V179" s="3"/>
-      <c r="W179" s="3" t="s">
-        <v>954</v>
-      </c>
+      <c r="W179" s="3"/>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A180" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>8047082d-a1b5-51da-62e7-586d6cc4e15f</v>
+        <v>4985cfff-ee6e-1be3-c12e-d42029b537a4</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>111</v>
@@ -16038,13 +16055,13 @@
         <v>112</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>635</v>
+        <v>955</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>119</v>
+        <v>344</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G180" s="3" t="s">
         <v>956</v>
@@ -16063,7 +16080,7 @@
         <v>959</v>
       </c>
       <c r="M180" s="3" t="s">
-        <v>197</v>
+        <v>54</v>
       </c>
       <c r="N180" s="3" t="b">
         <v>1</v>
@@ -16081,7 +16098,7 @@
     <row r="181" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A181" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>de881fd7-7160-84bf-c54d-7389ae80201c</v>
+        <v>778c5053-af40-1737-f2b4-f3dde801c611</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>111</v>
@@ -16090,32 +16107,32 @@
         <v>112</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>344</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G181" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="H181" s="3"/>
+      <c r="I181" s="3" t="s">
         <v>961</v>
       </c>
-      <c r="H181" s="3" t="s">
+      <c r="J181" s="3" t="s">
         <v>962</v>
       </c>
-      <c r="I181" s="3" t="s">
+      <c r="K181" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L181" s="3" t="s">
         <v>963</v>
       </c>
-      <c r="J181" s="3"/>
-      <c r="K181" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="L181" s="3" t="s">
-        <v>964</v>
-      </c>
       <c r="M181" s="3" t="s">
-        <v>54</v>
+        <v>197</v>
       </c>
       <c r="N181" s="3" t="b">
         <v>1</v>
@@ -16133,54 +16150,8 @@
     <row r="182" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A182" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>7a8c1ea9-b37b-9607-8e6e-e3968e12be15</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C182" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>960</v>
-      </c>
-      <c r="E182" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="F182" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>965</v>
-      </c>
-      <c r="H182" s="3"/>
-      <c r="I182" s="3" t="s">
-        <v>966</v>
-      </c>
-      <c r="J182" s="3" t="s">
-        <v>967</v>
-      </c>
-      <c r="K182" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="L182" s="3" t="s">
-        <v>968</v>
-      </c>
-      <c r="M182" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="N182" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O182" s="3"/>
-      <c r="P182" s="3"/>
-      <c r="Q182" s="3"/>
-      <c r="R182" s="3"/>
-      <c r="S182" s="3"/>
-      <c r="T182" s="3"/>
-      <c r="U182" s="3"/>
-      <c r="V182" s="3"/>
-      <c r="W182" s="3"/>
+        <v/>
+      </c>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A183" t="str">
@@ -16193,31 +16164,53 @@
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
+      <c r="E184" t="str" cm="1">
+        <f t="array" ref="E184:E190">_xlfn.UNIQUE(E2:E181)</f>
+        <v>Definition</v>
+      </c>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A185" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
+      <c r="E185" t="str">
+        <v>Recognition</v>
+      </c>
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A186" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
+      <c r="E186" t="str">
+        <v>Measurement</v>
+      </c>
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A187" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
+      <c r="E187" t="str">
+        <v>Classification</v>
+      </c>
+      <c r="H187" s="2"/>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A188" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v/>
-      </c>
-      <c r="H188" s="2"/>
+      <c r="E188" t="str">
+        <v>Application</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="E189" t="str">
+        <v>Presentation</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="E190" t="str">
+        <v>Standards recall</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16231,19 +16224,19 @@
           <x14:formula1>
             <xm:f>Sheet1!$C$7:$C$13</xm:f>
           </x14:formula1>
-          <xm:sqref>F73:F133 E2:E72 E134:E173 E183:E1048576</xm:sqref>
+          <xm:sqref>F72:F132 E133:E172 E182:E1048576 E2:E71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F82C379E-17BC-45F0-BE92-97BE1BFDF793}">
           <x14:formula1>
             <xm:f>Sheet1!$A$7:$A$14</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F72 G73:G133 F134:F173 F183:F1048576</xm:sqref>
+          <xm:sqref>G72:G132 F133:F172 F182:F1048576 F2:F71</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6469E828-7DAC-4E27-A0AC-825DA2AE9210}">
           <x14:formula1>
             <xm:f>Sheet1!$B$7:$B$9</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K72 L73:L133 K134:K173 K183:K1048576</xm:sqref>
+          <xm:sqref>L72:L132 K133:K172 K182:K1048576 K2:K71</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
